--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G6">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G19">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G42">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G62">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G70">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G82">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.8</v>
+        <v>3.64</v>
       </c>
       <c r="O87">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="P87">
-        <v>4.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB87">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,49 +14816,49 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.64</v>
+        <v>1.8</v>
       </c>
       <c r="O89">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="P89">
+        <v>4.08</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>1.87</v>
+      </c>
+      <c r="AB89">
         <v>1.93</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
-      <c r="T89">
-        <v>0</v>
-      </c>
-      <c r="U89">
-        <v>0</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-      <c r="X89">
-        <v>0</v>
-      </c>
-      <c r="Y89">
-        <v>0</v>
-      </c>
-      <c r="Z89">
-        <v>0</v>
-      </c>
-      <c r="AA89">
-        <v>1.9</v>
-      </c>
-      <c r="AB89">
-        <v>1.9</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G111">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="O114">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="P114">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AB114">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="O115">
-        <v>3.72</v>
+        <v>3.36</v>
       </c>
       <c r="P115">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AB115">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N116">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.24</v>
+        <v>2.79</v>
       </c>
       <c r="O123">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P123">
-        <v>3.19</v>
+        <v>2.47</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,16 +20397,16 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.79</v>
+        <v>1.39</v>
       </c>
       <c r="O124">
-        <v>3.99</v>
+        <v>5.57</v>
       </c>
       <c r="P124">
-        <v>2.47</v>
+        <v>8.75</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20566,10 +20566,10 @@
         <v>0</v>
       </c>
       <c r="AC124">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD124">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AE124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.39</v>
+        <v>10.9</v>
       </c>
       <c r="O125">
-        <v>5.57</v>
+        <v>8.4</v>
       </c>
       <c r="P125">
-        <v>8.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20729,13 +20729,13 @@
         <v>0</v>
       </c>
       <c r="AC125">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD125">
+        <v>0</v>
+      </c>
+      <c r="AE125">
         <v>1.77</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
       </c>
       <c r="AF125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>10.9</v>
+        <v>2.24</v>
       </c>
       <c r="O126">
-        <v>8.4</v>
+        <v>3.93</v>
       </c>
       <c r="P126">
-        <v>1.24</v>
+        <v>3.19</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20898,7 +20898,7 @@
         <v>0</v>
       </c>
       <c r="AE126">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF126">
         <v>0</v>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N127">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="O130">
-        <v>3.66</v>
+        <v>4.22</v>
       </c>
       <c r="P130">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21538,16 +21538,16 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB130">
+        <v>0</v>
+      </c>
+      <c r="AC130">
         <v>2</v>
       </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.86</v>
+        <v>2.92</v>
       </c>
       <c r="O131">
-        <v>4.22</v>
+        <v>3.66</v>
       </c>
       <c r="P131">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21701,16 +21701,16 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD131">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE131">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O143">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="P143">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O145">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P145">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G157">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G164">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O167">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P167">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB167">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O168">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="P168">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AB168">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O169">
-        <v>3.32</v>
+        <v>3.62</v>
       </c>
       <c r="P169">
-        <v>2.48</v>
+        <v>3.27</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB169">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="O170">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P170">
-        <v>2.71</v>
+        <v>3.93</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB170">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O171">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="P171">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB171">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="O172">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="P172">
-        <v>3.93</v>
+        <v>2.71</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB172">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.2</v>
+        <v>2.78</v>
       </c>
       <c r="O176">
-        <v>6.6</v>
+        <v>3.48</v>
       </c>
       <c r="P176">
-        <v>11.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,16 +29036,16 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC176">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD176">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.78</v>
+        <v>1.55</v>
       </c>
       <c r="O177">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="P177">
-        <v>2.36</v>
+        <v>5.35</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,16 +29199,16 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="O178">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
-        <v>5.35</v>
+        <v>3.52</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,16 +29362,16 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC178">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD178">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="P179">
-        <v>3.52</v>
+        <v>11.7</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,16 +29525,16 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O182">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P182">
-        <v>4.24</v>
+        <v>4.08</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="O183">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="P183">
-        <v>4.08</v>
+        <v>4.69</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="O184">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="P184">
-        <v>4.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="O185">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P185">
-        <v>3.31</v>
+        <v>4.31</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O187">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>6.75</v>
+        <v>3.35</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="O188">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P188">
-        <v>3.35</v>
+        <v>4.24</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="O189">
-        <v>3.58</v>
+        <v>4.95</v>
       </c>
       <c r="P189">
-        <v>4.31</v>
+        <v>6.75</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB189">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G191">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G210">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G219">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G222">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G229">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G237">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G238">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G243">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G246">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G247">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G253">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G254">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G256">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G260">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G261">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="O301">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="P301">
-        <v>3.6</v>
+        <v>23</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
       <c r="O302">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="P302">
-        <v>23</v>
+        <v>4.2</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="O303">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P303">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49737,10 +49737,10 @@
         <v>0</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="O304">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P304">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49900,10 +49900,10 @@
         <v>0</v>
       </c>
       <c r="AA304">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB304">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC304">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G307">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G322">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G331">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,55 +54751,55 @@
         </is>
       </c>
       <c r="N334">
+        <v>2.12</v>
+      </c>
+      <c r="O334">
+        <v>3.97</v>
+      </c>
+      <c r="P334">
+        <v>3.26</v>
+      </c>
+      <c r="Q334">
+        <v>0</v>
+      </c>
+      <c r="R334">
+        <v>0</v>
+      </c>
+      <c r="S334">
+        <v>0</v>
+      </c>
+      <c r="T334">
+        <v>0</v>
+      </c>
+      <c r="U334">
+        <v>0</v>
+      </c>
+      <c r="V334">
+        <v>0</v>
+      </c>
+      <c r="W334">
+        <v>0</v>
+      </c>
+      <c r="X334">
+        <v>0</v>
+      </c>
+      <c r="Y334">
+        <v>0</v>
+      </c>
+      <c r="Z334">
+        <v>0</v>
+      </c>
+      <c r="AA334">
+        <v>0</v>
+      </c>
+      <c r="AB334">
+        <v>0</v>
+      </c>
+      <c r="AC334">
         <v>1.98</v>
       </c>
-      <c r="O334">
-        <v>3.94</v>
-      </c>
-      <c r="P334">
-        <v>3.67</v>
-      </c>
-      <c r="Q334">
-        <v>0</v>
-      </c>
-      <c r="R334">
-        <v>0</v>
-      </c>
-      <c r="S334">
-        <v>0</v>
-      </c>
-      <c r="T334">
-        <v>0</v>
-      </c>
-      <c r="U334">
-        <v>0</v>
-      </c>
-      <c r="V334">
-        <v>0</v>
-      </c>
-      <c r="W334">
-        <v>0</v>
-      </c>
-      <c r="X334">
-        <v>0</v>
-      </c>
-      <c r="Y334">
-        <v>0</v>
-      </c>
-      <c r="Z334">
-        <v>0</v>
-      </c>
-      <c r="AA334">
-        <v>0</v>
-      </c>
-      <c r="AB334">
-        <v>0</v>
-      </c>
-      <c r="AC334">
-        <v>2.15</v>
-      </c>
       <c r="AD334">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE334">
         <v>0</v>
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.31</v>
+        <v>2.17</v>
       </c>
       <c r="O335">
-        <v>6.46</v>
+        <v>4.03</v>
       </c>
       <c r="P335">
-        <v>8.949999999999999</v>
+        <v>3.11</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -54959,10 +54959,10 @@
         <v>0</v>
       </c>
       <c r="AC335">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AD335">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AE335">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="O337">
-        <v>3.97</v>
+        <v>5.76</v>
       </c>
       <c r="P337">
-        <v>3.26</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55285,10 +55285,10 @@
         <v>0</v>
       </c>
       <c r="AC337">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AD337">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="O338">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="P338">
-        <v>2.74</v>
+        <v>3.67</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55448,10 +55448,10 @@
         <v>0</v>
       </c>
       <c r="AC338">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD338">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="O339">
-        <v>5.76</v>
+        <v>6.46</v>
       </c>
       <c r="P339">
-        <v>8.449999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AD339">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="O340">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="P340">
-        <v>3.11</v>
+        <v>2.74</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD340">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE340">
         <v>0</v>
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G343">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G344">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G345">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G346">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G347">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G348">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G350">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G359">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G111">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>10.9</v>
+        <v>2.24</v>
       </c>
       <c r="O125">
-        <v>8.4</v>
+        <v>3.93</v>
       </c>
       <c r="P125">
-        <v>1.24</v>
+        <v>3.19</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -20735,7 +20735,7 @@
         <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.24</v>
+        <v>10.9</v>
       </c>
       <c r="O126">
-        <v>3.93</v>
+        <v>8.4</v>
       </c>
       <c r="P126">
-        <v>3.19</v>
+        <v>1.24</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20898,7 +20898,7 @@
         <v>0</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF126">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O145">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="P145">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O171">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P171">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB171">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="O172">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P172">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB172">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O173">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P173">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="O178">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="P178">
-        <v>3.52</v>
+        <v>11.7</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,16 +29362,16 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="O179">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="P179">
-        <v>11.7</v>
+        <v>3.52</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,16 +29525,16 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC179">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD179">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="O181">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="P181">
-        <v>3.21</v>
+        <v>4.08</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="O182">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="P182">
-        <v>4.08</v>
+        <v>4.69</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="O183">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="P183">
-        <v>4.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="O184">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="P184">
-        <v>3.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="O185">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>4.31</v>
+        <v>3.35</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB185">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="O186">
-        <v>3.48</v>
+        <v>4.95</v>
       </c>
       <c r="P186">
-        <v>2.37</v>
+        <v>6.75</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P187">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="O188">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="P188">
-        <v>4.24</v>
+        <v>3.21</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="O189">
-        <v>4.95</v>
+        <v>3.55</v>
       </c>
       <c r="P189">
-        <v>6.75</v>
+        <v>4.24</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G191">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G218">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39800,10 +39800,10 @@
         <v>0</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40126,10 +40126,10 @@
         <v>0</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE244">
         <v>0</v>
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G251">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G252">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43060,10 +43060,10 @@
         <v>0</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE262">
         <v>0</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>0</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50389,10 +50389,10 @@
         <v>0</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC307">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="O337">
-        <v>5.76</v>
+        <v>3.94</v>
       </c>
       <c r="P337">
-        <v>8.449999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55285,10 +55285,10 @@
         <v>0</v>
       </c>
       <c r="AC337">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD337">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="O338">
-        <v>3.94</v>
+        <v>6.46</v>
       </c>
       <c r="P338">
-        <v>3.67</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55448,10 +55448,10 @@
         <v>0</v>
       </c>
       <c r="AC338">
+        <v>1.61</v>
+      </c>
+      <c r="AD338">
         <v>2.15</v>
-      </c>
-      <c r="AD338">
-        <v>1.62</v>
       </c>
       <c r="AE338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.31</v>
+        <v>2.42</v>
       </c>
       <c r="O339">
-        <v>6.46</v>
+        <v>3.96</v>
       </c>
       <c r="P339">
-        <v>8.949999999999999</v>
+        <v>2.74</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AD339">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="O340">
-        <v>3.96</v>
+        <v>5.76</v>
       </c>
       <c r="P340">
-        <v>2.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD340">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE340">
         <v>0</v>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G350">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G11">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G19">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="O53">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="P53">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="O54">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P54">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB54">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.23</v>
+        <v>2.24</v>
       </c>
       <c r="O55">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P55">
-        <v>2.18</v>
+        <v>3.14</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="O75">
-        <v>4.41</v>
+        <v>11.6</v>
       </c>
       <c r="P75">
-        <v>2.11</v>
+        <v>33</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="O76">
-        <v>11.6</v>
+        <v>4.41</v>
       </c>
       <c r="P76">
-        <v>33</v>
+        <v>2.11</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="O86">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="P86">
-        <v>3.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB86">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,49 +14490,49 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.64</v>
+        <v>1.8</v>
       </c>
       <c r="O87">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="P87">
+        <v>4.08</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87">
+        <v>1.87</v>
+      </c>
+      <c r="AB87">
         <v>1.93</v>
-      </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>0</v>
-      </c>
-      <c r="Y87">
-        <v>0</v>
-      </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <v>1.9</v>
-      </c>
-      <c r="AB87">
-        <v>1.9</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P88">
-        <v>2.87</v>
+        <v>3.69</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>4.08</v>
+        <v>2.87</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G93">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G101">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G111">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="O114">
-        <v>3.72</v>
+        <v>3.36</v>
       </c>
       <c r="P114">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AB114">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="O115">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="P115">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AB115">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.83</v>
+        <v>1.39</v>
       </c>
       <c r="O122">
-        <v>4.73</v>
+        <v>5.57</v>
       </c>
       <c r="P122">
-        <v>1.68</v>
+        <v>8.75</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20240,10 +20240,10 @@
         <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AD122">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="O123">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="P123">
-        <v>2.47</v>
+        <v>3.19</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,16 +20397,16 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC123">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.39</v>
+        <v>4.83</v>
       </c>
       <c r="O124">
-        <v>5.57</v>
+        <v>4.73</v>
       </c>
       <c r="P124">
-        <v>8.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20566,10 +20566,10 @@
         <v>0</v>
       </c>
       <c r="AC124">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD124">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.24</v>
+        <v>2.79</v>
       </c>
       <c r="O125">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P125">
-        <v>3.19</v>
+        <v>2.47</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,16 +20723,16 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE125">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G142">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O144">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="P144">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O145">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P145">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G157">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="O178">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
-        <v>11.7</v>
+        <v>3.52</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,16 +29362,16 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC178">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD178">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="P179">
-        <v>3.52</v>
+        <v>11.7</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,16 +29525,16 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="O187">
-        <v>3.58</v>
+        <v>3.24</v>
       </c>
       <c r="P187">
-        <v>4.31</v>
+        <v>3.21</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB187">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="O188">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="P188">
-        <v>3.21</v>
+        <v>4.24</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="O189">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P189">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G218">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G246">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G247">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G322">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O334">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="P334">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54796,10 +54796,10 @@
         <v>0</v>
       </c>
       <c r="AC334">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD334">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE334">
         <v>0</v>
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="O335">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="P335">
-        <v>3.11</v>
+        <v>3.67</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -54959,10 +54959,10 @@
         <v>0</v>
       </c>
       <c r="AC335">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD335">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE335">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="O336">
-        <v>4.22</v>
+        <v>6.46</v>
       </c>
       <c r="P336">
-        <v>4.12</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55122,10 +55122,10 @@
         <v>0</v>
       </c>
       <c r="AC336">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AD336">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AE336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="O337">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P337">
-        <v>3.67</v>
+        <v>2.74</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55285,10 +55285,10 @@
         <v>0</v>
       </c>
       <c r="AC337">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD337">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O338">
-        <v>6.46</v>
+        <v>5.76</v>
       </c>
       <c r="P338">
-        <v>8.949999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55448,10 +55448,10 @@
         <v>0</v>
       </c>
       <c r="AC338">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD338">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="O339">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="P339">
-        <v>2.74</v>
+        <v>3.26</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD339">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="O340">
-        <v>5.76</v>
+        <v>4.22</v>
       </c>
       <c r="P340">
-        <v>8.449999999999999</v>
+        <v>4.12</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD340">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AE340">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G344">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G345">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G346">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G347">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G348">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G350">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O7">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G42">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.23</v>
+        <v>2.24</v>
       </c>
       <c r="O53">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P53">
-        <v>2.18</v>
+        <v>3.14</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.24</v>
+        <v>3.23</v>
       </c>
       <c r="O55">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P55">
-        <v>3.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AB55">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G111">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O144">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P144">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="O171">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P171">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB171">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O172">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P172">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O173">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P173">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB173">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="O337">
-        <v>3.96</v>
+        <v>5.76</v>
       </c>
       <c r="P337">
-        <v>2.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55285,10 +55285,10 @@
         <v>0</v>
       </c>
       <c r="AC337">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD337">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="O338">
-        <v>5.76</v>
+        <v>3.97</v>
       </c>
       <c r="P338">
-        <v>8.449999999999999</v>
+        <v>3.26</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55448,10 +55448,10 @@
         <v>0</v>
       </c>
       <c r="AC338">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD338">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="O339">
-        <v>3.97</v>
+        <v>4.22</v>
       </c>
       <c r="P339">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD339">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="O340">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="P340">
-        <v>4.12</v>
+        <v>2.74</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD340">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE340">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G101">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O143">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P143">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O144">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="P144">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.6</v>
+        <v>6.96</v>
       </c>
       <c r="O211">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P211">
-        <v>2.52</v>
+        <v>1.41</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,16 +34741,16 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB211">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>6.96</v>
+        <v>2.6</v>
       </c>
       <c r="O212">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P212">
-        <v>1.41</v>
+        <v>2.52</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34904,16 +34904,16 @@
         <v>0</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC212">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD212">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE212">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q261">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G160">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU365"/>
+  <dimension ref="A1:AU364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G145">
@@ -56828,22 +56828,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G347">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G348">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G350">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G352">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G353">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G354">
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,13 +58174,13 @@
         </is>
       </c>
       <c r="N355">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O355">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P355">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q355">
         <v>0</v>
@@ -58213,10 +58213,10 @@
         <v>0</v>
       </c>
       <c r="AA355">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB355">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC355">
         <v>0</v>
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,13 +58337,13 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.11</v>
+        <v>3.69</v>
       </c>
       <c r="O356">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="P356">
-        <v>3.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q356">
         <v>0</v>
@@ -58376,10 +58376,10 @@
         <v>0</v>
       </c>
       <c r="AA356">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AB356">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC356">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,13 +58500,13 @@
         </is>
       </c>
       <c r="N357">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="O357">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="P357">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="Q357">
         <v>0</v>
@@ -58539,16 +58539,16 @@
         <v>0</v>
       </c>
       <c r="AA357">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB357">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC357">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD357">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE357">
         <v>0</v>
@@ -58616,12 +58616,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,13 +58663,13 @@
         </is>
       </c>
       <c r="N358">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O358">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P358">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q358">
         <v>0</v>
@@ -58708,10 +58708,10 @@
         <v>0</v>
       </c>
       <c r="AC358">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD358">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE358">
         <v>0</v>
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-10 21:30:00</t>
+          <t>2026-10-10 22:00:00</t>
         </is>
       </c>
     </row>
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G359">
@@ -58942,12 +58942,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G360">
@@ -58989,13 +58989,13 @@
         </is>
       </c>
       <c r="N360">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O360">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P360">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q360">
         <v>0</v>
@@ -59034,10 +59034,10 @@
         <v>0</v>
       </c>
       <c r="AC360">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD360">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE360">
         <v>0</v>
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-10-10 22:00:00</t>
+          <t>2026-10-10 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59105,12 +59105,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G361">
@@ -59152,13 +59152,13 @@
         </is>
       </c>
       <c r="N361">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O361">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P361">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q361">
         <v>0</v>
@@ -59197,10 +59197,10 @@
         <v>0</v>
       </c>
       <c r="AC361">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD361">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE361">
         <v>0</v>
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-10-10 22:30:00</t>
+          <t>2026-10-10 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G363">
@@ -59594,12 +59594,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O364">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P364">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59680,10 +59680,10 @@
         <v>0</v>
       </c>
       <c r="AA364">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB364">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC364">
         <v>0</v>
@@ -59744,169 +59744,6 @@
         <v>0</v>
       </c>
       <c r="AU364" t="inlineStr">
-        <is>
-          <t>2026-10-10 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="G365">
-        <v>0</v>
-      </c>
-      <c r="H365">
-        <v>0</v>
-      </c>
-      <c r="I365">
-        <v>0</v>
-      </c>
-      <c r="J365">
-        <v>0</v>
-      </c>
-      <c r="K365">
-        <v>0</v>
-      </c>
-      <c r="L365">
-        <v>0</v>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N365">
-        <v>2.73</v>
-      </c>
-      <c r="O365">
-        <v>3.84</v>
-      </c>
-      <c r="P365">
-        <v>2.48</v>
-      </c>
-      <c r="Q365">
-        <v>0</v>
-      </c>
-      <c r="R365">
-        <v>0</v>
-      </c>
-      <c r="S365">
-        <v>0</v>
-      </c>
-      <c r="T365">
-        <v>0</v>
-      </c>
-      <c r="U365">
-        <v>0</v>
-      </c>
-      <c r="V365">
-        <v>0</v>
-      </c>
-      <c r="W365">
-        <v>0</v>
-      </c>
-      <c r="X365">
-        <v>0</v>
-      </c>
-      <c r="Y365">
-        <v>0</v>
-      </c>
-      <c r="Z365">
-        <v>0</v>
-      </c>
-      <c r="AA365">
-        <v>1.55</v>
-      </c>
-      <c r="AB365">
-        <v>2.3</v>
-      </c>
-      <c r="AC365">
-        <v>0</v>
-      </c>
-      <c r="AD365">
-        <v>0</v>
-      </c>
-      <c r="AE365">
-        <v>0</v>
-      </c>
-      <c r="AF365">
-        <v>0</v>
-      </c>
-      <c r="AG365">
-        <v>0</v>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ365">
-        <v>0</v>
-      </c>
-      <c r="AK365">
-        <v>0</v>
-      </c>
-      <c r="AL365">
-        <v>0</v>
-      </c>
-      <c r="AM365">
-        <v>-1</v>
-      </c>
-      <c r="AN365">
-        <v>-1</v>
-      </c>
-      <c r="AO365">
-        <v>-1</v>
-      </c>
-      <c r="AP365">
-        <v>-1</v>
-      </c>
-      <c r="AQ365">
-        <v>0</v>
-      </c>
-      <c r="AR365">
-        <v>0</v>
-      </c>
-      <c r="AS365">
-        <v>0</v>
-      </c>
-      <c r="AT365">
-        <v>0</v>
-      </c>
-      <c r="AU365" t="inlineStr">
         <is>
           <t>2026-10-10 23:30:00</t>
         </is>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G83">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N119">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G145">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="O342">
-        <v>5.76</v>
+        <v>3.97</v>
       </c>
       <c r="P342">
-        <v>8.449999999999999</v>
+        <v>3.26</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56100,10 +56100,10 @@
         <v>0</v>
       </c>
       <c r="AC342">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD342">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE342">
         <v>0</v>
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="O343">
-        <v>3.97</v>
+        <v>4.22</v>
       </c>
       <c r="P343">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56263,10 +56263,10 @@
         <v>0</v>
       </c>
       <c r="AC343">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD343">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE343">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="O344">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="P344">
-        <v>4.12</v>
+        <v>2.74</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56426,10 +56426,10 @@
         <v>0</v>
       </c>
       <c r="AC344">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD344">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE344">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="O345">
-        <v>3.96</v>
+        <v>5.76</v>
       </c>
       <c r="P345">
-        <v>2.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56589,10 +56589,10 @@
         <v>0</v>
       </c>
       <c r="AC345">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD345">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE345">
         <v>0</v>
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G352">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G354">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G363">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU364"/>
+  <dimension ref="A1:AU359"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>3.47</v>
       </c>
       <c r="O66">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="P66">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.47</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="P67">
-        <v>2.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G227">
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45505,10 +45505,10 @@
         <v>0</v>
       </c>
       <c r="AC277">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD277">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE277">
         <v>0</v>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45668,10 +45668,10 @@
         <v>0</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE278">
         <v>0</v>
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-10-10 13:45:00</t>
+          <t>2026-10-10 13:30:00</t>
         </is>
       </c>
     </row>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="O281">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="P281">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB281">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-10-10 14:00:00</t>
+          <t>2026-10-10 13:45:00</t>
         </is>
       </c>
     </row>
@@ -46233,22 +46233,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.85</v>
+        <v>6.93</v>
       </c>
       <c r="O282">
-        <v>4.09</v>
+        <v>5.29</v>
       </c>
       <c r="P282">
-        <v>4.09</v>
+        <v>1.39</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,16 +46314,16 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC282">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD282">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE282">
         <v>0</v>
@@ -46396,22 +46396,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>11</v>
+        <v>1.85</v>
       </c>
       <c r="O283">
-        <v>5.68</v>
+        <v>4.09</v>
       </c>
       <c r="P283">
-        <v>1.31</v>
+        <v>4.09</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,16 +46477,16 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB283">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE283">
         <v>0</v>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,49 +46601,49 @@
         </is>
       </c>
       <c r="N284">
+        <v>11</v>
+      </c>
+      <c r="O284">
+        <v>5.68</v>
+      </c>
+      <c r="P284">
+        <v>1.31</v>
+      </c>
+      <c r="Q284">
+        <v>0</v>
+      </c>
+      <c r="R284">
+        <v>0</v>
+      </c>
+      <c r="S284">
+        <v>0</v>
+      </c>
+      <c r="T284">
+        <v>0</v>
+      </c>
+      <c r="U284">
+        <v>0</v>
+      </c>
+      <c r="V284">
+        <v>0</v>
+      </c>
+      <c r="W284">
+        <v>0</v>
+      </c>
+      <c r="X284">
+        <v>0</v>
+      </c>
+      <c r="Y284">
+        <v>0</v>
+      </c>
+      <c r="Z284">
+        <v>0</v>
+      </c>
+      <c r="AA284">
         <v>1.78</v>
       </c>
-      <c r="O284">
-        <v>3.44</v>
-      </c>
-      <c r="P284">
-        <v>4.41</v>
-      </c>
-      <c r="Q284">
-        <v>0</v>
-      </c>
-      <c r="R284">
-        <v>0</v>
-      </c>
-      <c r="S284">
-        <v>0</v>
-      </c>
-      <c r="T284">
-        <v>0</v>
-      </c>
-      <c r="U284">
-        <v>0</v>
-      </c>
-      <c r="V284">
-        <v>0</v>
-      </c>
-      <c r="W284">
-        <v>0</v>
-      </c>
-      <c r="X284">
-        <v>0</v>
-      </c>
-      <c r="Y284">
-        <v>0</v>
-      </c>
-      <c r="Z284">
-        <v>0</v>
-      </c>
-      <c r="AA284">
-        <v>1.95</v>
-      </c>
       <c r="AB284">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC284">
         <v>0</v>
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46803,10 +46803,10 @@
         <v>0</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC285">
         <v>0</v>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O286">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P286">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30:00</t>
+          <t>2026-10-10 14:00:00</t>
         </is>
       </c>
     </row>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O288">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P288">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB288">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47374,22 +47374,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-10-10 15:00:00</t>
+          <t>2026-10-10 14:30:00</t>
         </is>
       </c>
     </row>
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O295">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P295">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB299">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-10 15:15:00</t>
+          <t>2026-10-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.51</v>
+        <v>1.49</v>
       </c>
       <c r="O300">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P300">
-        <v>2.49</v>
+        <v>5.81</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30:00</t>
+          <t>2026-10-10 15:15:00</t>
         </is>
       </c>
     </row>
@@ -49493,22 +49493,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,22 +49656,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,22 +49819,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O304">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="P304">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49906,10 +49906,10 @@
         <v>0</v>
       </c>
       <c r="AC304">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD304">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE304">
         <v>0</v>
@@ -49982,22 +49982,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="O305">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="P305">
-        <v>5.87</v>
+        <v>4.12</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50069,10 +50069,10 @@
         <v>0</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE305">
         <v>0</v>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="O306">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="P306">
-        <v>23</v>
+        <v>5.87</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-10-10 15:45:00</t>
+          <t>2026-10-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="O307">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="P307">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="O308">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P308">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50552,10 +50552,10 @@
         <v>0</v>
       </c>
       <c r="AA308">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB308">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,49 +50676,49 @@
         </is>
       </c>
       <c r="N309">
+        <v>2.63</v>
+      </c>
+      <c r="O309">
+        <v>3.4</v>
+      </c>
+      <c r="P309">
+        <v>2.5</v>
+      </c>
+      <c r="Q309">
+        <v>0</v>
+      </c>
+      <c r="R309">
+        <v>0</v>
+      </c>
+      <c r="S309">
+        <v>0</v>
+      </c>
+      <c r="T309">
+        <v>0</v>
+      </c>
+      <c r="U309">
+        <v>0</v>
+      </c>
+      <c r="V309">
+        <v>0</v>
+      </c>
+      <c r="W309">
+        <v>0</v>
+      </c>
+      <c r="X309">
+        <v>0</v>
+      </c>
+      <c r="Y309">
+        <v>0</v>
+      </c>
+      <c r="Z309">
+        <v>0</v>
+      </c>
+      <c r="AA309">
+        <v>1.85</v>
+      </c>
+      <c r="AB309">
         <v>2</v>
-      </c>
-      <c r="O309">
-        <v>3.5</v>
-      </c>
-      <c r="P309">
-        <v>3.6</v>
-      </c>
-      <c r="Q309">
-        <v>0</v>
-      </c>
-      <c r="R309">
-        <v>0</v>
-      </c>
-      <c r="S309">
-        <v>0</v>
-      </c>
-      <c r="T309">
-        <v>0</v>
-      </c>
-      <c r="U309">
-        <v>0</v>
-      </c>
-      <c r="V309">
-        <v>0</v>
-      </c>
-      <c r="W309">
-        <v>0</v>
-      </c>
-      <c r="X309">
-        <v>0</v>
-      </c>
-      <c r="Y309">
-        <v>0</v>
-      </c>
-      <c r="Z309">
-        <v>0</v>
-      </c>
-      <c r="AA309">
-        <v>0</v>
-      </c>
-      <c r="AB309">
-        <v>0</v>
       </c>
       <c r="AC309">
         <v>0</v>
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="O310">
-        <v>4.94</v>
+        <v>3.5</v>
       </c>
       <c r="P310">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -50878,10 +50878,10 @@
         <v>0</v>
       </c>
       <c r="AA310">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB310">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC310">
         <v>0</v>
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="O311">
-        <v>4.62</v>
+        <v>4.94</v>
       </c>
       <c r="P311">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51041,10 +51041,10 @@
         <v>0</v>
       </c>
       <c r="AA311">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB311">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="O312">
-        <v>3.53</v>
+        <v>4.62</v>
       </c>
       <c r="P312">
-        <v>2.6</v>
+        <v>6.67</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -51204,10 +51204,10 @@
         <v>0</v>
       </c>
       <c r="AA312">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB312">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC312">
         <v>0</v>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51367,10 +51367,10 @@
         <v>0</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC313">
         <v>0</v>
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00:00</t>
+          <t>2026-10-10 15:45:00</t>
         </is>
       </c>
     </row>
@@ -51449,22 +51449,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,22 +51775,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G316">
@@ -51938,7 +51938,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G317">
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O318">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P318">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q318">
         <v>0</v>
@@ -52182,10 +52182,10 @@
         <v>0</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC318">
         <v>0</v>
@@ -52259,27 +52259,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-10-10 16:15:00</t>
+          <t>2026-10-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30:00</t>
+          <t>2026-10-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30:00</t>
+          <t>2026-10-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -52753,7 +52753,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G322">
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00:00</t>
+          <t>2026-10-10 16:30:00</t>
         </is>
       </c>
     </row>
@@ -53074,27 +53074,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G324">
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00:00</t>
+          <t>2026-10-10 16:30:00</t>
         </is>
       </c>
     </row>
@@ -53242,7 +53242,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G327">
@@ -53731,7 +53731,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G328">
@@ -53889,12 +53889,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-10-10 17:30:00</t>
+          <t>2026-10-10 17:00:00</t>
         </is>
       </c>
     </row>
@@ -54052,12 +54052,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-10-10 17:30:00</t>
+          <t>2026-10-10 17:00:00</t>
         </is>
       </c>
     </row>
@@ -54215,12 +54215,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-10-10 18:00:00</t>
+          <t>2026-10-10 17:30:00</t>
         </is>
       </c>
     </row>
@@ -54378,12 +54378,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-10-10 19:00:00</t>
+          <t>2026-10-10 17:30:00</t>
         </is>
       </c>
     </row>
@@ -54541,7 +54541,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-10-10 20:00:00</t>
+          <t>2026-10-10 18:00:00</t>
         </is>
       </c>
     </row>
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O334">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54790,10 +54790,10 @@
         <v>0</v>
       </c>
       <c r="AA334">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB334">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC334">
         <v>0</v>
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-10-10 20:00:00</t>
+          <t>2026-10-10 18:30:00</t>
         </is>
       </c>
     </row>
@@ -54867,7 +54867,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-10-10 20:00:00</t>
+          <t>2026-10-10 19:00:00</t>
         </is>
       </c>
     </row>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G336">
@@ -55198,7 +55198,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G337">
@@ -55356,12 +55356,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G338">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>2026-10-10 20:30:00</t>
+          <t>2026-10-10 20:00:00</t>
         </is>
       </c>
     </row>
@@ -55519,12 +55519,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O339">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="P339">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD339">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55670,7 +55670,7 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>2026-10-10 20:30:00</t>
+          <t>2026-10-10 20:00:00</t>
         </is>
       </c>
     </row>
@@ -55682,12 +55682,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O340">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P340">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD340">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE340">
         <v>0</v>
@@ -55833,7 +55833,7 @@
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>2026-10-10 20:30:00</t>
+          <t>2026-10-10 20:00:00</t>
         </is>
       </c>
     </row>
@@ -55850,7 +55850,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O341">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="P341">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -55937,10 +55937,10 @@
         <v>0</v>
       </c>
       <c r="AC341">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD341">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O342">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="P342">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56100,10 +56100,10 @@
         <v>0</v>
       </c>
       <c r="AC342">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD342">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE342">
         <v>0</v>
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="O343">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="P343">
-        <v>4.12</v>
+        <v>3.67</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56263,10 +56263,10 @@
         <v>0</v>
       </c>
       <c r="AC343">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD343">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE343">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.42</v>
+        <v>1.31</v>
       </c>
       <c r="O344">
-        <v>3.96</v>
+        <v>6.46</v>
       </c>
       <c r="P344">
-        <v>2.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56426,10 +56426,10 @@
         <v>0</v>
       </c>
       <c r="AC344">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AD344">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE344">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="O345">
-        <v>5.76</v>
+        <v>3.97</v>
       </c>
       <c r="P345">
-        <v>8.449999999999999</v>
+        <v>3.26</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56589,10 +56589,10 @@
         <v>0</v>
       </c>
       <c r="AC345">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD345">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE345">
         <v>0</v>
@@ -56660,12 +56660,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O346">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P346">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56752,10 +56752,10 @@
         <v>0</v>
       </c>
       <c r="AC346">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD346">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE346">
         <v>0</v>
@@ -56811,7 +56811,7 @@
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56823,12 +56823,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O347">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P347">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -56915,10 +56915,10 @@
         <v>0</v>
       </c>
       <c r="AC347">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD347">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE347">
         <v>0</v>
@@ -56974,7 +56974,7 @@
       </c>
       <c r="AU347" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56986,12 +56986,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O348">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="P348">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57078,10 +57078,10 @@
         <v>0</v>
       </c>
       <c r="AC348">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD348">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE348">
         <v>0</v>
@@ -57137,7 +57137,7 @@
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 20:30:00</t>
         </is>
       </c>
     </row>
@@ -57154,7 +57154,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G349">
@@ -57312,12 +57312,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G350">
@@ -57359,13 +57359,13 @@
         </is>
       </c>
       <c r="N350">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O350">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P350">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q350">
         <v>0</v>
@@ -57398,10 +57398,10 @@
         <v>0</v>
       </c>
       <c r="AA350">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB350">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC350">
         <v>0</v>
@@ -57463,7 +57463,7 @@
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 21:30:00</t>
         </is>
       </c>
     </row>
@@ -57475,12 +57475,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -57561,10 +57561,10 @@
         <v>0</v>
       </c>
       <c r="AA351">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB351">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC351">
         <v>0</v>
@@ -57626,7 +57626,7 @@
       </c>
       <c r="AU351" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 21:30:00</t>
         </is>
       </c>
     </row>
@@ -57638,12 +57638,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O352">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P352">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q352">
         <v>0</v>
@@ -57730,10 +57730,10 @@
         <v>0</v>
       </c>
       <c r="AC352">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD352">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE352">
         <v>0</v>
@@ -57789,7 +57789,7 @@
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 21:30:00</t>
         </is>
       </c>
     </row>
@@ -57801,12 +57801,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G353">
@@ -57952,7 +57952,7 @@
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 22:00:00</t>
         </is>
       </c>
     </row>
@@ -57964,12 +57964,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G354">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>2026-10-10 21:00:00</t>
+          <t>2026-10-10 22:00:00</t>
         </is>
       </c>
     </row>
@@ -58127,7 +58127,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,13 +58174,13 @@
         </is>
       </c>
       <c r="N355">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="O355">
-        <v>3.74</v>
+        <v>4.07</v>
       </c>
       <c r="P355">
-        <v>3.46</v>
+        <v>4.17</v>
       </c>
       <c r="Q355">
         <v>0</v>
@@ -58213,16 +58213,16 @@
         <v>0</v>
       </c>
       <c r="AA355">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB355">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC355">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD355">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE355">
         <v>0</v>
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-10 21:30:00</t>
+          <t>2026-10-10 22:30:00</t>
         </is>
       </c>
     </row>
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,13 +58337,13 @@
         </is>
       </c>
       <c r="N356">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O356">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P356">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q356">
         <v>0</v>
@@ -58376,10 +58376,10 @@
         <v>0</v>
       </c>
       <c r="AA356">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB356">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC356">
         <v>0</v>
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-10 21:30:00</t>
+          <t>2026-10-10 23:00:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,13 +58500,13 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O357">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P357">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q357">
         <v>0</v>
@@ -58545,10 +58545,10 @@
         <v>0</v>
       </c>
       <c r="AC357">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD357">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE357">
         <v>0</v>
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-10-10 21:30:00</t>
+          <t>2026-10-10 23:00:00</t>
         </is>
       </c>
     </row>
@@ -58616,7 +58616,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G358">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-10 22:00:00</t>
+          <t>2026-10-10 23:00:00</t>
         </is>
       </c>
     </row>
@@ -58779,12 +58779,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G359">
@@ -58826,13 +58826,13 @@
         </is>
       </c>
       <c r="N359">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O359">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P359">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q359">
         <v>0</v>
@@ -58865,10 +58865,10 @@
         <v>0</v>
       </c>
       <c r="AA359">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB359">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC359">
         <v>0</v>
@@ -58929,821 +58929,6 @@
         <v>0</v>
       </c>
       <c r="AU359" t="inlineStr">
-        <is>
-          <t>2026-10-10 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="G360">
-        <v>0</v>
-      </c>
-      <c r="H360">
-        <v>0</v>
-      </c>
-      <c r="I360">
-        <v>0</v>
-      </c>
-      <c r="J360">
-        <v>0</v>
-      </c>
-      <c r="K360">
-        <v>0</v>
-      </c>
-      <c r="L360">
-        <v>0</v>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N360">
-        <v>1.83</v>
-      </c>
-      <c r="O360">
-        <v>4.07</v>
-      </c>
-      <c r="P360">
-        <v>4.17</v>
-      </c>
-      <c r="Q360">
-        <v>0</v>
-      </c>
-      <c r="R360">
-        <v>0</v>
-      </c>
-      <c r="S360">
-        <v>0</v>
-      </c>
-      <c r="T360">
-        <v>0</v>
-      </c>
-      <c r="U360">
-        <v>0</v>
-      </c>
-      <c r="V360">
-        <v>0</v>
-      </c>
-      <c r="W360">
-        <v>0</v>
-      </c>
-      <c r="X360">
-        <v>0</v>
-      </c>
-      <c r="Y360">
-        <v>0</v>
-      </c>
-      <c r="Z360">
-        <v>0</v>
-      </c>
-      <c r="AA360">
-        <v>0</v>
-      </c>
-      <c r="AB360">
-        <v>0</v>
-      </c>
-      <c r="AC360">
-        <v>2.15</v>
-      </c>
-      <c r="AD360">
-        <v>1.6</v>
-      </c>
-      <c r="AE360">
-        <v>0</v>
-      </c>
-      <c r="AF360">
-        <v>0</v>
-      </c>
-      <c r="AG360">
-        <v>0</v>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI360" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ360">
-        <v>0</v>
-      </c>
-      <c r="AK360">
-        <v>0</v>
-      </c>
-      <c r="AL360">
-        <v>0</v>
-      </c>
-      <c r="AM360">
-        <v>-1</v>
-      </c>
-      <c r="AN360">
-        <v>-1</v>
-      </c>
-      <c r="AO360">
-        <v>-1</v>
-      </c>
-      <c r="AP360">
-        <v>-1</v>
-      </c>
-      <c r="AQ360">
-        <v>0</v>
-      </c>
-      <c r="AR360">
-        <v>0</v>
-      </c>
-      <c r="AS360">
-        <v>0</v>
-      </c>
-      <c r="AT360">
-        <v>0</v>
-      </c>
-      <c r="AU360" t="inlineStr">
-        <is>
-          <t>2026-10-10 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>Colorado Springs</t>
-        </is>
-      </c>
-      <c r="G361">
-        <v>0</v>
-      </c>
-      <c r="H361">
-        <v>0</v>
-      </c>
-      <c r="I361">
-        <v>0</v>
-      </c>
-      <c r="J361">
-        <v>0</v>
-      </c>
-      <c r="K361">
-        <v>0</v>
-      </c>
-      <c r="L361">
-        <v>0</v>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N361">
-        <v>0</v>
-      </c>
-      <c r="O361">
-        <v>0</v>
-      </c>
-      <c r="P361">
-        <v>0</v>
-      </c>
-      <c r="Q361">
-        <v>0</v>
-      </c>
-      <c r="R361">
-        <v>0</v>
-      </c>
-      <c r="S361">
-        <v>0</v>
-      </c>
-      <c r="T361">
-        <v>0</v>
-      </c>
-      <c r="U361">
-        <v>0</v>
-      </c>
-      <c r="V361">
-        <v>0</v>
-      </c>
-      <c r="W361">
-        <v>0</v>
-      </c>
-      <c r="X361">
-        <v>0</v>
-      </c>
-      <c r="Y361">
-        <v>0</v>
-      </c>
-      <c r="Z361">
-        <v>0</v>
-      </c>
-      <c r="AA361">
-        <v>0</v>
-      </c>
-      <c r="AB361">
-        <v>0</v>
-      </c>
-      <c r="AC361">
-        <v>0</v>
-      </c>
-      <c r="AD361">
-        <v>0</v>
-      </c>
-      <c r="AE361">
-        <v>0</v>
-      </c>
-      <c r="AF361">
-        <v>0</v>
-      </c>
-      <c r="AG361">
-        <v>0</v>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ361">
-        <v>0</v>
-      </c>
-      <c r="AK361">
-        <v>0</v>
-      </c>
-      <c r="AL361">
-        <v>0</v>
-      </c>
-      <c r="AM361">
-        <v>-1</v>
-      </c>
-      <c r="AN361">
-        <v>-1</v>
-      </c>
-      <c r="AO361">
-        <v>-1</v>
-      </c>
-      <c r="AP361">
-        <v>-1</v>
-      </c>
-      <c r="AQ361">
-        <v>0</v>
-      </c>
-      <c r="AR361">
-        <v>0</v>
-      </c>
-      <c r="AS361">
-        <v>0</v>
-      </c>
-      <c r="AT361">
-        <v>0</v>
-      </c>
-      <c r="AU361" t="inlineStr">
-        <is>
-          <t>2026-10-10 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="G362">
-        <v>0</v>
-      </c>
-      <c r="H362">
-        <v>0</v>
-      </c>
-      <c r="I362">
-        <v>0</v>
-      </c>
-      <c r="J362">
-        <v>0</v>
-      </c>
-      <c r="K362">
-        <v>0</v>
-      </c>
-      <c r="L362">
-        <v>0</v>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N362">
-        <v>0</v>
-      </c>
-      <c r="O362">
-        <v>0</v>
-      </c>
-      <c r="P362">
-        <v>0</v>
-      </c>
-      <c r="Q362">
-        <v>0</v>
-      </c>
-      <c r="R362">
-        <v>0</v>
-      </c>
-      <c r="S362">
-        <v>0</v>
-      </c>
-      <c r="T362">
-        <v>0</v>
-      </c>
-      <c r="U362">
-        <v>0</v>
-      </c>
-      <c r="V362">
-        <v>0</v>
-      </c>
-      <c r="W362">
-        <v>0</v>
-      </c>
-      <c r="X362">
-        <v>0</v>
-      </c>
-      <c r="Y362">
-        <v>0</v>
-      </c>
-      <c r="Z362">
-        <v>0</v>
-      </c>
-      <c r="AA362">
-        <v>0</v>
-      </c>
-      <c r="AB362">
-        <v>0</v>
-      </c>
-      <c r="AC362">
-        <v>0</v>
-      </c>
-      <c r="AD362">
-        <v>0</v>
-      </c>
-      <c r="AE362">
-        <v>0</v>
-      </c>
-      <c r="AF362">
-        <v>0</v>
-      </c>
-      <c r="AG362">
-        <v>0</v>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI362" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ362">
-        <v>0</v>
-      </c>
-      <c r="AK362">
-        <v>0</v>
-      </c>
-      <c r="AL362">
-        <v>0</v>
-      </c>
-      <c r="AM362">
-        <v>-1</v>
-      </c>
-      <c r="AN362">
-        <v>-1</v>
-      </c>
-      <c r="AO362">
-        <v>-1</v>
-      </c>
-      <c r="AP362">
-        <v>-1</v>
-      </c>
-      <c r="AQ362">
-        <v>0</v>
-      </c>
-      <c r="AR362">
-        <v>0</v>
-      </c>
-      <c r="AS362">
-        <v>0</v>
-      </c>
-      <c r="AT362">
-        <v>0</v>
-      </c>
-      <c r="AU362" t="inlineStr">
-        <is>
-          <t>2026-10-10 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G363">
-        <v>0</v>
-      </c>
-      <c r="H363">
-        <v>0</v>
-      </c>
-      <c r="I363">
-        <v>0</v>
-      </c>
-      <c r="J363">
-        <v>0</v>
-      </c>
-      <c r="K363">
-        <v>0</v>
-      </c>
-      <c r="L363">
-        <v>0</v>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N363">
-        <v>0</v>
-      </c>
-      <c r="O363">
-        <v>0</v>
-      </c>
-      <c r="P363">
-        <v>0</v>
-      </c>
-      <c r="Q363">
-        <v>0</v>
-      </c>
-      <c r="R363">
-        <v>0</v>
-      </c>
-      <c r="S363">
-        <v>0</v>
-      </c>
-      <c r="T363">
-        <v>0</v>
-      </c>
-      <c r="U363">
-        <v>0</v>
-      </c>
-      <c r="V363">
-        <v>0</v>
-      </c>
-      <c r="W363">
-        <v>0</v>
-      </c>
-      <c r="X363">
-        <v>0</v>
-      </c>
-      <c r="Y363">
-        <v>0</v>
-      </c>
-      <c r="Z363">
-        <v>0</v>
-      </c>
-      <c r="AA363">
-        <v>0</v>
-      </c>
-      <c r="AB363">
-        <v>0</v>
-      </c>
-      <c r="AC363">
-        <v>0</v>
-      </c>
-      <c r="AD363">
-        <v>0</v>
-      </c>
-      <c r="AE363">
-        <v>0</v>
-      </c>
-      <c r="AF363">
-        <v>0</v>
-      </c>
-      <c r="AG363">
-        <v>0</v>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI363" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ363">
-        <v>0</v>
-      </c>
-      <c r="AK363">
-        <v>0</v>
-      </c>
-      <c r="AL363">
-        <v>0</v>
-      </c>
-      <c r="AM363">
-        <v>-1</v>
-      </c>
-      <c r="AN363">
-        <v>-1</v>
-      </c>
-      <c r="AO363">
-        <v>-1</v>
-      </c>
-      <c r="AP363">
-        <v>-1</v>
-      </c>
-      <c r="AQ363">
-        <v>0</v>
-      </c>
-      <c r="AR363">
-        <v>0</v>
-      </c>
-      <c r="AS363">
-        <v>0</v>
-      </c>
-      <c r="AT363">
-        <v>0</v>
-      </c>
-      <c r="AU363" t="inlineStr">
-        <is>
-          <t>2026-10-10 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="G364">
-        <v>0</v>
-      </c>
-      <c r="H364">
-        <v>0</v>
-      </c>
-      <c r="I364">
-        <v>0</v>
-      </c>
-      <c r="J364">
-        <v>0</v>
-      </c>
-      <c r="K364">
-        <v>0</v>
-      </c>
-      <c r="L364">
-        <v>0</v>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N364">
-        <v>2.73</v>
-      </c>
-      <c r="O364">
-        <v>3.84</v>
-      </c>
-      <c r="P364">
-        <v>2.48</v>
-      </c>
-      <c r="Q364">
-        <v>0</v>
-      </c>
-      <c r="R364">
-        <v>0</v>
-      </c>
-      <c r="S364">
-        <v>0</v>
-      </c>
-      <c r="T364">
-        <v>0</v>
-      </c>
-      <c r="U364">
-        <v>0</v>
-      </c>
-      <c r="V364">
-        <v>0</v>
-      </c>
-      <c r="W364">
-        <v>0</v>
-      </c>
-      <c r="X364">
-        <v>0</v>
-      </c>
-      <c r="Y364">
-        <v>0</v>
-      </c>
-      <c r="Z364">
-        <v>0</v>
-      </c>
-      <c r="AA364">
-        <v>1.55</v>
-      </c>
-      <c r="AB364">
-        <v>2.3</v>
-      </c>
-      <c r="AC364">
-        <v>0</v>
-      </c>
-      <c r="AD364">
-        <v>0</v>
-      </c>
-      <c r="AE364">
-        <v>0</v>
-      </c>
-      <c r="AF364">
-        <v>0</v>
-      </c>
-      <c r="AG364">
-        <v>0</v>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ364">
-        <v>0</v>
-      </c>
-      <c r="AK364">
-        <v>0</v>
-      </c>
-      <c r="AL364">
-        <v>0</v>
-      </c>
-      <c r="AM364">
-        <v>-1</v>
-      </c>
-      <c r="AN364">
-        <v>-1</v>
-      </c>
-      <c r="AO364">
-        <v>-1</v>
-      </c>
-      <c r="AP364">
-        <v>-1</v>
-      </c>
-      <c r="AQ364">
-        <v>0</v>
-      </c>
-      <c r="AR364">
-        <v>0</v>
-      </c>
-      <c r="AS364">
-        <v>0</v>
-      </c>
-      <c r="AT364">
-        <v>0</v>
-      </c>
-      <c r="AU364" t="inlineStr">
         <is>
           <t>2026-10-10 23:30:00</t>
         </is>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G145">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33111,10 +33111,10 @@
         <v>0</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC201">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G227">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46972,10 +46972,10 @@
         <v>0</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE286">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23494,10 +23494,10 @@
         <v>0</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC142">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49906,10 +49906,10 @@
         <v>0</v>
       </c>
       <c r="AC304">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD304">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE304">
         <v>0</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O317">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P317">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q317">
         <v>0</v>
@@ -52019,10 +52019,10 @@
         <v>0</v>
       </c>
       <c r="AA317">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB317">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC317">
         <v>0</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53323,10 +53323,10 @@
         <v>0</v>
       </c>
       <c r="AA325">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB325">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC325">
         <v>0</v>
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57235,10 +57235,10 @@
         <v>0</v>
       </c>
       <c r="AA349">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB349">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC349">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G329">

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26102,10 +26102,10 @@
         <v>0</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC158">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34095,10 +34095,10 @@
         <v>0</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE207">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,10 +34741,10 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB211">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC211">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G225">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G227">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46157,10 +46157,10 @@
         <v>0</v>
       </c>
       <c r="AC281">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD281">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE281">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47298,10 +47298,10 @@
         <v>0</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE288">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49091,10 +49091,10 @@
         <v>0</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE299">
         <v>0</v>
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52514,10 +52514,10 @@
         <v>0</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE320">
         <v>0</v>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53160,10 +53160,10 @@
         <v>0</v>
       </c>
       <c r="AA324">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB324">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC324">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -644,34 +644,34 @@
         <v>5.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA2">
         <v>1.81</v>
@@ -680,19 +680,19 @@
         <v>2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>4.27</v>
+        <v>4.07</v>
       </c>
       <c r="P4">
-        <v>5.2</v>
+        <v>4.97</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AB4">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="O5">
-        <v>4.07</v>
+        <v>3.67</v>
       </c>
       <c r="P5">
-        <v>4.97</v>
+        <v>4.2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="O6">
-        <v>3.67</v>
+        <v>4.27</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AA7">
         <v>1.85</v>
@@ -1495,19 +1495,19 @@
         <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,34 +1622,34 @@
         <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA8">
         <v>1.95</v>
@@ -1658,19 +1658,19 @@
         <v>1.83</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>3.07</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="O10">
-        <v>3.08</v>
+        <v>4.21</v>
       </c>
       <c r="P10">
-        <v>2.45</v>
+        <v>4.45</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="O11">
-        <v>4.21</v>
+        <v>3.08</v>
       </c>
       <c r="P11">
-        <v>4.45</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G44">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G101">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="O153">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="P153">
-        <v>2.78</v>
+        <v>4.03</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB153">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="O154">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="P154">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB154">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.16</v>
+        <v>3.9</v>
       </c>
       <c r="O155">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="P155">
-        <v>2.98</v>
+        <v>1.81</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="O156">
-        <v>4.29</v>
+        <v>3.72</v>
       </c>
       <c r="P156">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>3.9</v>
+        <v>2.49</v>
       </c>
       <c r="O157">
-        <v>4.17</v>
+        <v>3.83</v>
       </c>
       <c r="P157">
-        <v>1.81</v>
+        <v>2.57</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.49</v>
+        <v>3.85</v>
       </c>
       <c r="O158">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="P158">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26102,10 +26102,10 @@
         <v>0</v>
       </c>
       <c r="AA158">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB158">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC158">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48427,10 +48427,10 @@
         <v>0</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA295">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49731,10 +49731,10 @@
         <v>0</v>
       </c>
       <c r="Y303">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z303">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA303">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51856,10 +51856,10 @@
         <v>0</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC316">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -52991,10 +52991,10 @@
         <v>0</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O335">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P335">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O336">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O337">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P337">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O338">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P338">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O353">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P353">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q353">
         <v>0</v>
@@ -58011,13 +58011,13 @@
         </is>
       </c>
       <c r="N354">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O354">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P354">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q354">
         <v>0</v>
@@ -58337,13 +58337,13 @@
         </is>
       </c>
       <c r="N356">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O356">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P356">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q356">
         <v>0</v>
@@ -58376,10 +58376,10 @@
         <v>0</v>
       </c>
       <c r="AA356">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB356">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC356">
         <v>0</v>
@@ -58500,13 +58500,13 @@
         </is>
       </c>
       <c r="N357">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O357">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P357">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q357">
         <v>0</v>
@@ -58663,13 +58663,13 @@
         </is>
       </c>
       <c r="N358">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O358">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P358">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q358">
         <v>0</v>
@@ -58702,10 +58702,10 @@
         <v>0</v>
       </c>
       <c r="AA358">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB358">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC358">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="O149">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="P149">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O150">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P150">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB150">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="O151">
-        <v>3.89</v>
+        <v>4.16</v>
       </c>
       <c r="P151">
-        <v>3.24</v>
+        <v>4.26</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AB151">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O152">
-        <v>4.16</v>
+        <v>3.85</v>
       </c>
       <c r="P152">
-        <v>4.26</v>
+        <v>4.03</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB152">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="O153">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="P153">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.16</v>
+        <v>3.9</v>
       </c>
       <c r="O154">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="P154">
-        <v>2.98</v>
+        <v>1.81</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="O155">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="P155">
-        <v>1.81</v>
+        <v>2.78</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="O156">
-        <v>3.72</v>
+        <v>3.83</v>
       </c>
       <c r="P156">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB156">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.49</v>
+        <v>3.85</v>
       </c>
       <c r="O157">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="P157">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB157">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.85</v>
+        <v>2.26</v>
       </c>
       <c r="O158">
-        <v>4.29</v>
+        <v>3.62</v>
       </c>
       <c r="P158">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O337">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="P337">
-        <v>3.09</v>
+        <v>3.61</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="O338">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="P338">
-        <v>3.61</v>
+        <v>3.05</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="O339">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="P339">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>1.31</v>
+        <v>2.12</v>
       </c>
       <c r="O344">
-        <v>6.46</v>
+        <v>3.97</v>
       </c>
       <c r="P344">
-        <v>8.949999999999999</v>
+        <v>3.26</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56426,10 +56426,10 @@
         <v>0</v>
       </c>
       <c r="AC344">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AD344">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AE344">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="O345">
-        <v>3.97</v>
+        <v>4.22</v>
       </c>
       <c r="P345">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56589,10 +56589,10 @@
         <v>0</v>
       </c>
       <c r="AC345">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD345">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="O346">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="P346">
-        <v>4.12</v>
+        <v>2.74</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56752,10 +56752,10 @@
         <v>0</v>
       </c>
       <c r="AC346">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD346">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="O347">
-        <v>3.96</v>
+        <v>5.76</v>
       </c>
       <c r="P347">
-        <v>2.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -56915,10 +56915,10 @@
         <v>0</v>
       </c>
       <c r="AC347">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD347">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="O348">
-        <v>5.76</v>
+        <v>6.46</v>
       </c>
       <c r="P348">
-        <v>8.449999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57078,10 +57078,10 @@
         <v>0</v>
       </c>
       <c r="AC348">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AD348">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AE348">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="O353">
-        <v>4.39</v>
+        <v>4.69</v>
       </c>
       <c r="P353">
-        <v>4.23</v>
+        <v>5.35</v>
       </c>
       <c r="Q353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,13 +58011,13 @@
         </is>
       </c>
       <c r="N354">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O354">
-        <v>4.69</v>
+        <v>4.39</v>
       </c>
       <c r="P354">
-        <v>5.35</v>
+        <v>4.23</v>
       </c>
       <c r="Q354">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O7">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>4.12</v>
+        <v>3.44</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.39</v>
+        <v>3.69</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>3.44</v>
+        <v>4.12</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>3.69</v>
+        <v>3.39</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC8">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
       </c>
       <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.64</v>
       </c>
-      <c r="AG8">
-        <v>2.07</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>1.3</v>
-      </c>
-      <c r="AK8">
-        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.09</v>
+        <v>2.67</v>
       </c>
       <c r="O39">
-        <v>3.95</v>
+        <v>3.76</v>
       </c>
       <c r="P39">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q39">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
+        <v>3.75</v>
+      </c>
+      <c r="U39">
+        <v>2.25</v>
+      </c>
+      <c r="V39">
+        <v>1.6</v>
+      </c>
+      <c r="W39">
+        <v>1.11</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.12</v>
+      </c>
+      <c r="Z39">
+        <v>4.75</v>
+      </c>
+      <c r="AA39">
+        <v>1.53</v>
+      </c>
+      <c r="AB39">
+        <v>2.3</v>
+      </c>
+      <c r="AC39">
+        <v>2.25</v>
+      </c>
+      <c r="AD39">
+        <v>1.55</v>
+      </c>
+      <c r="AE39">
         <v>1.18</v>
       </c>
-      <c r="T39">
-        <v>3.92</v>
-      </c>
-      <c r="U39">
-        <v>2</v>
-      </c>
-      <c r="V39">
-        <v>1.73</v>
-      </c>
-      <c r="W39">
-        <v>1.2</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.11</v>
-      </c>
-      <c r="Z39">
-        <v>6.79</v>
-      </c>
-      <c r="AA39">
-        <v>1.4</v>
-      </c>
-      <c r="AB39">
-        <v>2.99</v>
-      </c>
-      <c r="AC39">
-        <v>1.95</v>
-      </c>
-      <c r="AD39">
-        <v>1.73</v>
-      </c>
-      <c r="AE39">
-        <v>1.3</v>
-      </c>
       <c r="AF39">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,65 +6829,65 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="O40">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="P40">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="Q40">
+        <v>2.98</v>
+      </c>
+      <c r="R40">
+        <v>2.49</v>
+      </c>
+      <c r="S40">
+        <v>1.2</v>
+      </c>
+      <c r="T40">
+        <v>4.2</v>
+      </c>
+      <c r="U40">
+        <v>2.06</v>
+      </c>
+      <c r="V40">
+        <v>1.74</v>
+      </c>
+      <c r="W40">
+        <v>1.18</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.07</v>
+      </c>
+      <c r="Z40">
+        <v>6.96</v>
+      </c>
+      <c r="AA40">
+        <v>1.39</v>
+      </c>
+      <c r="AB40">
+        <v>2.78</v>
+      </c>
+      <c r="AC40">
+        <v>2</v>
+      </c>
+      <c r="AD40">
+        <v>1.7</v>
+      </c>
+      <c r="AE40">
+        <v>1.3</v>
+      </c>
+      <c r="AF40">
+        <v>1.34</v>
+      </c>
+      <c r="AG40">
         <v>3.1</v>
       </c>
-      <c r="R40">
-        <v>2.38</v>
-      </c>
-      <c r="S40">
-        <v>1.25</v>
-      </c>
-      <c r="T40">
-        <v>3.75</v>
-      </c>
-      <c r="U40">
-        <v>2.25</v>
-      </c>
-      <c r="V40">
-        <v>1.6</v>
-      </c>
-      <c r="W40">
-        <v>1.11</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.12</v>
-      </c>
-      <c r="Z40">
-        <v>4.75</v>
-      </c>
-      <c r="AA40">
-        <v>1.53</v>
-      </c>
-      <c r="AB40">
-        <v>2.3</v>
-      </c>
-      <c r="AC40">
-        <v>2.25</v>
-      </c>
-      <c r="AD40">
-        <v>1.55</v>
-      </c>
-      <c r="AE40">
-        <v>1.18</v>
-      </c>
-      <c r="AF40">
-        <v>1.44</v>
-      </c>
-      <c r="AG40">
-        <v>2.5</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AK40">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="O41">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="P41">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="Q41">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="R41">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
+        <v>1.18</v>
+      </c>
+      <c r="T41">
+        <v>3.92</v>
+      </c>
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41">
+        <v>1.73</v>
+      </c>
+      <c r="W41">
         <v>1.2</v>
-      </c>
-      <c r="T41">
-        <v>4.2</v>
-      </c>
-      <c r="U41">
-        <v>2.06</v>
-      </c>
-      <c r="V41">
-        <v>1.74</v>
-      </c>
-      <c r="W41">
-        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>6.96</v>
+        <v>6.79</v>
       </c>
       <c r="AA41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="AC41">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE41">
         <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AG41">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>4.24</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>4.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q51">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="R51">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="P52">
-        <v>2.65</v>
+        <v>4.49</v>
       </c>
       <c r="Q52">
-        <v>2.98</v>
+        <v>2.08</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA52">
+        <v>1.83</v>
+      </c>
+      <c r="AB52">
+        <v>1.94</v>
+      </c>
+      <c r="AC52">
+        <v>2.59</v>
+      </c>
+      <c r="AD52">
+        <v>1.42</v>
+      </c>
+      <c r="AE52">
+        <v>1.13</v>
+      </c>
+      <c r="AF52">
         <v>1.71</v>
       </c>
-      <c r="AB52">
-        <v>2.05</v>
-      </c>
-      <c r="AC52">
-        <v>2.77</v>
-      </c>
-      <c r="AD52">
-        <v>1.4</v>
-      </c>
-      <c r="AE52">
-        <v>1.11</v>
-      </c>
-      <c r="AF52">
-        <v>1.57</v>
-      </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="O53">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="Q53">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="R53">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="U53">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="V53">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="AA53">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AB53">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="AC53">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="AD53">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE53">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF53">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG53">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="Q54">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T54">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="U54">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="V54">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA54">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AB54">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AC54">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AD54">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG54">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK54">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="O77">
-        <v>4.41</v>
+        <v>11.6</v>
       </c>
       <c r="P77">
-        <v>2.11</v>
+        <v>33</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>1.49</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="T77">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="U77">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="V77">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="W77">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AA77">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AB77">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AC77">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AD77">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE77">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AF77">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG77">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="AK77">
-        <v>1.41</v>
+        <v>6</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="O78">
-        <v>11.6</v>
+        <v>4.41</v>
       </c>
       <c r="P78">
-        <v>33</v>
+        <v>2.11</v>
       </c>
       <c r="Q78">
-        <v>1.49</v>
+        <v>3.4</v>
       </c>
       <c r="R78">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="V78">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z78">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AA78">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AB78">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC78">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AD78">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE78">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AF78">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AK78">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G84">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="O112">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="P112">
-        <v>3.06</v>
+        <v>2.59</v>
       </c>
       <c r="Q112">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R112">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
         <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="U112">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
         <v>1.44</v>
       </c>
       <c r="W112">
+        <v>1.07</v>
+      </c>
+      <c r="X112">
+        <v>1.01</v>
+      </c>
+      <c r="Y112">
+        <v>1.22</v>
+      </c>
+      <c r="Z112">
+        <v>3.5</v>
+      </c>
+      <c r="AA112">
+        <v>1.77</v>
+      </c>
+      <c r="AB112">
+        <v>1.91</v>
+      </c>
+      <c r="AC112">
+        <v>2.83</v>
+      </c>
+      <c r="AD112">
+        <v>1.33</v>
+      </c>
+      <c r="AE112">
         <v>1.1</v>
       </c>
-      <c r="X112">
-        <v>1.04</v>
-      </c>
-      <c r="Y112">
-        <v>1.2</v>
-      </c>
-      <c r="Z112">
-        <v>3.68</v>
-      </c>
-      <c r="AA112">
-        <v>1.79</v>
-      </c>
-      <c r="AB112">
-        <v>1.97</v>
-      </c>
-      <c r="AC112">
-        <v>2.88</v>
-      </c>
-      <c r="AD112">
-        <v>1.4</v>
-      </c>
-      <c r="AE112">
-        <v>1.08</v>
-      </c>
       <c r="AF112">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="O113">
-        <v>3.85</v>
+        <v>4.09</v>
       </c>
       <c r="P113">
         <v>2.59</v>
@@ -18740,52 +18740,52 @@
         <v>2.88</v>
       </c>
       <c r="R113">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T113">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="U113">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W113">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z113">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA113">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB113">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="AC113">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="AD113">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF113">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="O114">
-        <v>4.09</v>
+        <v>3.82</v>
       </c>
       <c r="P114">
-        <v>2.59</v>
+        <v>3.06</v>
       </c>
       <c r="Q114">
+        <v>2.63</v>
+      </c>
+      <c r="R114">
+        <v>2.12</v>
+      </c>
+      <c r="S114">
+        <v>1.28</v>
+      </c>
+      <c r="T114">
+        <v>3.08</v>
+      </c>
+      <c r="U114">
+        <v>2.63</v>
+      </c>
+      <c r="V114">
+        <v>1.44</v>
+      </c>
+      <c r="W114">
+        <v>1.1</v>
+      </c>
+      <c r="X114">
+        <v>1.04</v>
+      </c>
+      <c r="Y114">
+        <v>1.2</v>
+      </c>
+      <c r="Z114">
+        <v>3.68</v>
+      </c>
+      <c r="AA114">
+        <v>1.79</v>
+      </c>
+      <c r="AB114">
+        <v>1.97</v>
+      </c>
+      <c r="AC114">
         <v>2.88</v>
       </c>
-      <c r="R114">
-        <v>2.3</v>
-      </c>
-      <c r="S114">
-        <v>1.24</v>
-      </c>
-      <c r="T114">
-        <v>3.6</v>
-      </c>
-      <c r="U114">
-        <v>2.12</v>
-      </c>
-      <c r="V114">
-        <v>1.62</v>
-      </c>
-      <c r="W114">
-        <v>1.14</v>
-      </c>
-      <c r="X114">
-        <v>1.01</v>
-      </c>
-      <c r="Y114">
-        <v>1.15</v>
-      </c>
-      <c r="Z114">
-        <v>4.75</v>
-      </c>
-      <c r="AA114">
-        <v>1.55</v>
-      </c>
-      <c r="AB114">
-        <v>2.39</v>
-      </c>
-      <c r="AC114">
-        <v>2.41</v>
-      </c>
       <c r="AD114">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG114">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.42</v>
+        <v>2.09</v>
       </c>
       <c r="O117">
-        <v>3.72</v>
+        <v>3.98</v>
       </c>
       <c r="P117">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="Q117">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="R117">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="S117">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T117">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z117">
-        <v>4.45</v>
+        <v>6.75</v>
       </c>
       <c r="AA117">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AB117">
-        <v>2.3</v>
+        <v>3.08</v>
       </c>
       <c r="AC117">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD117">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AF117">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AG117">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK117">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.09</v>
+        <v>3.42</v>
       </c>
       <c r="O118">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="P118">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="Q118">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="R118">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="S118">
+        <v>1.22</v>
+      </c>
+      <c r="T118">
+        <v>3.75</v>
+      </c>
+      <c r="U118">
+        <v>2.25</v>
+      </c>
+      <c r="V118">
+        <v>1.57</v>
+      </c>
+      <c r="W118">
+        <v>1.11</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
         <v>1.14</v>
       </c>
-      <c r="T118">
-        <v>5</v>
-      </c>
-      <c r="U118">
-        <v>1.8</v>
-      </c>
-      <c r="V118">
-        <v>1.84</v>
-      </c>
-      <c r="W118">
-        <v>1.23</v>
-      </c>
-      <c r="X118">
-        <v>1.01</v>
-      </c>
-      <c r="Y118">
-        <v>1.04</v>
-      </c>
       <c r="Z118">
-        <v>6.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA118">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AB118">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="AC118">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD118">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AE118">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AF118">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AG118">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.79</v>
+        <v>10.9</v>
       </c>
       <c r="O127">
-        <v>3.99</v>
+        <v>8.4</v>
       </c>
       <c r="P127">
-        <v>2.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q127">
-        <v>3.06</v>
+        <v>7.6</v>
       </c>
       <c r="R127">
-        <v>2.43</v>
+        <v>3.64</v>
       </c>
       <c r="S127">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U127">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="V127">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="W127">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z127">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AA127">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AB127">
-        <v>2.64</v>
+        <v>5.75</v>
       </c>
       <c r="AC127">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AD127">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="AE127">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="AF127">
         <v>1.4</v>
       </c>
       <c r="AG127">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AK127">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>10.9</v>
+        <v>2.79</v>
       </c>
       <c r="O129">
-        <v>8.4</v>
+        <v>3.99</v>
       </c>
       <c r="P129">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="Q129">
-        <v>7.6</v>
+        <v>3.06</v>
       </c>
       <c r="R129">
-        <v>3.64</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
+        <v>4</v>
+      </c>
+      <c r="U129">
+        <v>2.1</v>
+      </c>
+      <c r="V129">
+        <v>1.67</v>
+      </c>
+      <c r="W129">
+        <v>1.18</v>
+      </c>
+      <c r="X129">
+        <v>1.02</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
         <v>6</v>
       </c>
-      <c r="U129">
-        <v>1.57</v>
-      </c>
-      <c r="V129">
-        <v>2.25</v>
-      </c>
-      <c r="W129">
-        <v>1.41</v>
-      </c>
-      <c r="X129">
-        <v>1</v>
-      </c>
-      <c r="Y129">
-        <v>1.04</v>
-      </c>
-      <c r="Z129">
-        <v>13</v>
-      </c>
       <c r="AA129">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="AD129">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE129">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
         <v>1.4</v>
       </c>
       <c r="AG129">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK129">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="O143">
-        <v>3.8</v>
+        <v>4.32</v>
       </c>
       <c r="P143">
-        <v>4.39</v>
+        <v>6.15</v>
       </c>
       <c r="Q143">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="R143">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S143">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T143">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="U143">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="V143">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W143">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X143">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z143">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA143">
+        <v>1.93</v>
+      </c>
+      <c r="AB143">
         <v>1.83</v>
       </c>
-      <c r="AB143">
-        <v>1.93</v>
-      </c>
       <c r="AC143">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD143">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE143">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF143">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG143">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK143">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="O145">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="P145">
-        <v>6.15</v>
+        <v>4.39</v>
       </c>
       <c r="Q145">
+        <v>2.36</v>
+      </c>
+      <c r="R145">
         <v>2.06</v>
       </c>
-      <c r="R145">
-        <v>2.19</v>
-      </c>
       <c r="S145">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T145">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="U145">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="V145">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W145">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA145">
+        <v>1.83</v>
+      </c>
+      <c r="AB145">
         <v>1.93</v>
       </c>
-      <c r="AB145">
-        <v>1.83</v>
-      </c>
       <c r="AC145">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD145">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF145">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG145">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK145">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O146">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P146">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q146">
-        <v>2.66</v>
+        <v>2.01</v>
       </c>
       <c r="R146">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="S146">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="T146">
+        <v>3.26</v>
+      </c>
+      <c r="U146">
+        <v>2.5</v>
+      </c>
+      <c r="V146">
+        <v>1.51</v>
+      </c>
+      <c r="W146">
+        <v>1.09</v>
+      </c>
+      <c r="X146">
+        <v>1.01</v>
+      </c>
+      <c r="Y146">
+        <v>1.16</v>
+      </c>
+      <c r="Z146">
+        <v>4.1</v>
+      </c>
+      <c r="AA146">
+        <v>1.71</v>
+      </c>
+      <c r="AB146">
+        <v>2.18</v>
+      </c>
+      <c r="AC146">
+        <v>2.59</v>
+      </c>
+      <c r="AD146">
+        <v>1.44</v>
+      </c>
+      <c r="AE146">
+        <v>1.16</v>
+      </c>
+      <c r="AF146">
+        <v>1.75</v>
+      </c>
+      <c r="AG146">
+        <v>1.97</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
+        <v>1.22</v>
+      </c>
+      <c r="AK146">
         <v>2.47</v>
-      </c>
-      <c r="U146">
-        <v>3.12</v>
-      </c>
-      <c r="V146">
-        <v>1.3</v>
-      </c>
-      <c r="W146">
-        <v>1.02</v>
-      </c>
-      <c r="X146">
-        <v>1.03</v>
-      </c>
-      <c r="Y146">
-        <v>1.34</v>
-      </c>
-      <c r="Z146">
-        <v>2.78</v>
-      </c>
-      <c r="AA146">
-        <v>2.23</v>
-      </c>
-      <c r="AB146">
-        <v>1.67</v>
-      </c>
-      <c r="AC146">
-        <v>3.82</v>
-      </c>
-      <c r="AD146">
-        <v>1.18</v>
-      </c>
-      <c r="AE146">
-        <v>1.03</v>
-      </c>
-      <c r="AF146">
-        <v>1.9</v>
-      </c>
-      <c r="AG146">
-        <v>1.8</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.34</v>
-      </c>
-      <c r="AK146">
-        <v>1.75</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O147">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="P147">
-        <v>5.54</v>
+        <v>5.96</v>
       </c>
       <c r="Q147">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="R147">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="S147">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T147">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U147">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V147">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W147">
         <v>1.02</v>
       </c>
       <c r="X147">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z147">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AA147">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB147">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC147">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD147">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE147">
         <v>1.03</v>
       </c>
       <c r="AF147">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AG147">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK147">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O148">
-        <v>3.98</v>
+        <v>3.66</v>
       </c>
       <c r="P148">
-        <v>6.01</v>
+        <v>5.54</v>
       </c>
       <c r="Q148">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="R148">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S148">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="T148">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="U148">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="V148">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="W148">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X148">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z148">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA148">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="AB148">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="AC148">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="AD148">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AE148">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF148">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AG148">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK148">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,80 +24596,80 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="O149">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="P149">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="Q149">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="R149">
+        <v>2.18</v>
+      </c>
+      <c r="S149">
+        <v>1.28</v>
+      </c>
+      <c r="T149">
+        <v>3.22</v>
+      </c>
+      <c r="U149">
+        <v>2.34</v>
+      </c>
+      <c r="V149">
+        <v>1.51</v>
+      </c>
+      <c r="W149">
+        <v>1.1</v>
+      </c>
+      <c r="X149">
+        <v>1.02</v>
+      </c>
+      <c r="Y149">
+        <v>1.17</v>
+      </c>
+      <c r="Z149">
+        <v>4.1</v>
+      </c>
+      <c r="AA149">
+        <v>1.65</v>
+      </c>
+      <c r="AB149">
         <v>2.14</v>
       </c>
-      <c r="S149">
-        <v>1.31</v>
-      </c>
-      <c r="T149">
-        <v>3.17</v>
-      </c>
-      <c r="U149">
-        <v>2.67</v>
-      </c>
-      <c r="V149">
-        <v>1.48</v>
-      </c>
-      <c r="W149">
-        <v>1.07</v>
-      </c>
-      <c r="X149">
-        <v>1</v>
-      </c>
-      <c r="Y149">
-        <v>1.22</v>
-      </c>
-      <c r="Z149">
-        <v>3.5</v>
-      </c>
-      <c r="AA149">
-        <v>1.93</v>
-      </c>
-      <c r="AB149">
-        <v>1.93</v>
-      </c>
       <c r="AC149">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="AD149">
+        <v>1.43</v>
+      </c>
+      <c r="AE149">
+        <v>1.14</v>
+      </c>
+      <c r="AF149">
+        <v>1.54</v>
+      </c>
+      <c r="AG149">
+        <v>2.32</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ149">
         <v>1.33</v>
       </c>
-      <c r="AE149">
-        <v>1.1</v>
-      </c>
-      <c r="AF149">
-        <v>1.65</v>
-      </c>
-      <c r="AG149">
-        <v>2.15</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>1.27</v>
-      </c>
       <c r="AK149">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="O150">
-        <v>3.99</v>
+        <v>3.72</v>
       </c>
       <c r="P150">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="Q150">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="R150">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S150">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T150">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U150">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V150">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W150">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X150">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z150">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA150">
+        <v>1.9</v>
+      </c>
+      <c r="AB150">
+        <v>1.87</v>
+      </c>
+      <c r="AC150">
+        <v>2.92</v>
+      </c>
+      <c r="AD150">
+        <v>1.31</v>
+      </c>
+      <c r="AE150">
+        <v>1.09</v>
+      </c>
+      <c r="AF150">
         <v>1.65</v>
       </c>
-      <c r="AB150">
-        <v>2.14</v>
-      </c>
-      <c r="AC150">
-        <v>2.49</v>
-      </c>
-      <c r="AD150">
-        <v>1.43</v>
-      </c>
-      <c r="AE150">
-        <v>1.14</v>
-      </c>
-      <c r="AF150">
-        <v>1.54</v>
-      </c>
       <c r="AG150">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
+        <v>3.85</v>
+      </c>
+      <c r="O151">
+        <v>4.29</v>
+      </c>
+      <c r="P151">
+        <v>1.8</v>
+      </c>
+      <c r="Q151">
+        <v>4.43</v>
+      </c>
+      <c r="R151">
         <v>2.38</v>
       </c>
-      <c r="O151">
-        <v>3.72</v>
-      </c>
-      <c r="P151">
-        <v>2.78</v>
-      </c>
-      <c r="Q151">
-        <v>2.97</v>
-      </c>
-      <c r="R151">
-        <v>2.11</v>
-      </c>
       <c r="S151">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="U151">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V151">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W151">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z151">
-        <v>3.42</v>
+        <v>4.35</v>
       </c>
       <c r="AA151">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB151">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AC151">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="AD151">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AE151">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF151">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG151">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.85</v>
+        <v>2.26</v>
       </c>
       <c r="O152">
-        <v>4.29</v>
+        <v>3.62</v>
       </c>
       <c r="P152">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="Q152">
-        <v>4.43</v>
+        <v>2.69</v>
       </c>
       <c r="R152">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T152">
-        <v>3.32</v>
+        <v>2.67</v>
       </c>
       <c r="U152">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="V152">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W152">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z152">
-        <v>4.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA152">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB152">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="AC152">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="AD152">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AE152">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF152">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AG152">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK152">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="O153">
-        <v>3.62</v>
+        <v>3.83</v>
       </c>
       <c r="P153">
-        <v>3.03</v>
+        <v>2.57</v>
       </c>
       <c r="Q153">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="R153">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="S153">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T153">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="U153">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="V153">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W153">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z153">
-        <v>2.92</v>
+        <v>3.68</v>
       </c>
       <c r="AA153">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB153">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AC153">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="AD153">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE153">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF153">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AG153">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.9</v>
+        <v>2.02</v>
       </c>
       <c r="O154">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P154">
-        <v>1.81</v>
+        <v>3.45</v>
       </c>
       <c r="Q154">
-        <v>4.2</v>
+        <v>2.53</v>
       </c>
       <c r="R154">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S154">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T154">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U154">
-        <v>2.32</v>
+        <v>2.67</v>
       </c>
       <c r="V154">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z154">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA154">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AB154">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AC154">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD154">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF154">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG154">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="O155">
-        <v>3.85</v>
+        <v>4.17</v>
       </c>
       <c r="P155">
-        <v>4.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q155">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R155">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="S155">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T155">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U155">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="V155">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z155">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA155">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AB155">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="AC155">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD155">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AE155">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG155">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK155">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.49</v>
+        <v>1.85</v>
       </c>
       <c r="O156">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="P156">
-        <v>2.57</v>
+        <v>4.03</v>
       </c>
       <c r="Q156">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R156">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S156">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T156">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U156">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="V156">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z156">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB156">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC156">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AD156">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE156">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF156">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG156">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O158">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P158">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="Q158">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="R158">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S158">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T158">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="U158">
         <v>2.67</v>
       </c>
       <c r="V158">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W158">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y158">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z158">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA158">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB158">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC158">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AD158">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE158">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF158">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG158">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK158">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O171">
-        <v>3.32</v>
+        <v>3.62</v>
       </c>
       <c r="P171">
-        <v>2.48</v>
+        <v>3.27</v>
       </c>
       <c r="Q171">
+        <v>2.73</v>
+      </c>
+      <c r="R171">
+        <v>2.25</v>
+      </c>
+      <c r="S171">
+        <v>1.29</v>
+      </c>
+      <c r="T171">
         <v>3.24</v>
       </c>
-      <c r="R171">
-        <v>2.14</v>
-      </c>
-      <c r="S171">
-        <v>1.33</v>
-      </c>
-      <c r="T171">
-        <v>3.22</v>
-      </c>
       <c r="U171">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V171">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="W171">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X171">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z171">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="AA171">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB171">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC171">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD171">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE171">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF171">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG171">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK171">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="O172">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P172">
-        <v>3.27</v>
+        <v>2.56</v>
       </c>
       <c r="Q172">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="R172">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S172">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T172">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="U172">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V172">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W172">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X172">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z172">
-        <v>4.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA172">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB172">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC172">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD172">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE172">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF172">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AG172">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK172">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.87</v>
+        <v>2.94</v>
       </c>
       <c r="O173">
-        <v>3.56</v>
+        <v>3.26</v>
       </c>
       <c r="P173">
-        <v>3.93</v>
+        <v>2.36</v>
       </c>
       <c r="Q173">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="R173">
         <v>2.1</v>
       </c>
       <c r="S173">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T173">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U173">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V173">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W173">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z173">
-        <v>3.43</v>
+        <v>3.04</v>
       </c>
       <c r="AA173">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB173">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC173">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD173">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE173">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF173">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AG173">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O175">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P175">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q175">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S175">
         <v>1.33</v>
       </c>
       <c r="T175">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U175">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V175">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W175">
         <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z175">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA175">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB175">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC175">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD175">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE175">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF175">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG175">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.94</v>
+        <v>1.87</v>
       </c>
       <c r="O176">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="P176">
-        <v>2.36</v>
+        <v>3.93</v>
       </c>
       <c r="Q176">
-        <v>3.34</v>
+        <v>2.66</v>
       </c>
       <c r="R176">
         <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T176">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U176">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V176">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z176">
-        <v>3.04</v>
+        <v>3.43</v>
       </c>
       <c r="AA176">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB176">
+        <v>1.83</v>
+      </c>
+      <c r="AC176">
+        <v>3.42</v>
+      </c>
+      <c r="AD176">
+        <v>1.28</v>
+      </c>
+      <c r="AE176">
+        <v>1.07</v>
+      </c>
+      <c r="AF176">
         <v>1.71</v>
       </c>
-      <c r="AC176">
-        <v>3.2</v>
-      </c>
-      <c r="AD176">
-        <v>1.29</v>
-      </c>
-      <c r="AE176">
-        <v>1.06</v>
-      </c>
-      <c r="AF176">
-        <v>1.76</v>
-      </c>
       <c r="AG176">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.28</v>
       </c>
       <c r="AK176">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="O183">
-        <v>3.64</v>
+        <v>3.24</v>
       </c>
       <c r="P183">
-        <v>4.08</v>
+        <v>3.21</v>
       </c>
       <c r="Q183">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="R183">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S183">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T183">
-        <v>3.12</v>
+        <v>2.53</v>
       </c>
       <c r="U183">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="V183">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W183">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X183">
         <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="Z183">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA183">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB183">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AC183">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AD183">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE183">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF183">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG183">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK183">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,80 +30301,80 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="O184">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="P184">
-        <v>3.21</v>
+        <v>4.24</v>
       </c>
       <c r="Q184">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="R184">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S184">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T184">
-        <v>2.53</v>
+        <v>3.12</v>
       </c>
       <c r="U184">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="V184">
+        <v>1.46</v>
+      </c>
+      <c r="W184">
+        <v>1.06</v>
+      </c>
+      <c r="X184">
+        <v>1.02</v>
+      </c>
+      <c r="Y184">
+        <v>1.26</v>
+      </c>
+      <c r="Z184">
+        <v>3.8</v>
+      </c>
+      <c r="AA184">
+        <v>1.85</v>
+      </c>
+      <c r="AB184">
+        <v>2.02</v>
+      </c>
+      <c r="AC184">
+        <v>2.83</v>
+      </c>
+      <c r="AD184">
         <v>1.33</v>
       </c>
-      <c r="W184">
-        <v>1.03</v>
-      </c>
-      <c r="X184">
-        <v>1.03</v>
-      </c>
-      <c r="Y184">
-        <v>1.32</v>
-      </c>
-      <c r="Z184">
-        <v>2.88</v>
-      </c>
-      <c r="AA184">
+      <c r="AE184">
+        <v>1.13</v>
+      </c>
+      <c r="AF184">
+        <v>1.8</v>
+      </c>
+      <c r="AG184">
+        <v>1.98</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ184">
+        <v>1.2</v>
+      </c>
+      <c r="AK184">
         <v>2.1</v>
-      </c>
-      <c r="AB184">
-        <v>1.7</v>
-      </c>
-      <c r="AC184">
-        <v>3.5</v>
-      </c>
-      <c r="AD184">
-        <v>1.22</v>
-      </c>
-      <c r="AE184">
-        <v>1.05</v>
-      </c>
-      <c r="AF184">
-        <v>1.82</v>
-      </c>
-      <c r="AG184">
-        <v>1.88</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ184">
-        <v>1.25</v>
-      </c>
-      <c r="AK184">
-        <v>1.62</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="O185">
-        <v>3.55</v>
+        <v>4.95</v>
       </c>
       <c r="P185">
-        <v>4.24</v>
+        <v>6.75</v>
       </c>
       <c r="Q185">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="R185">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="S185">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T185">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="U185">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="V185">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W185">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X185">
         <v>1.02</v>
       </c>
       <c r="Y185">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="Z185">
-        <v>3.8</v>
+        <v>5.45</v>
       </c>
       <c r="AA185">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AB185">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AC185">
-        <v>2.83</v>
+        <v>1.98</v>
       </c>
       <c r="AD185">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AE185">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF185">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG185">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK185">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="O186">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P186">
-        <v>4.31</v>
+        <v>3.31</v>
       </c>
       <c r="Q186">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="R186">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S186">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T186">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U186">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V186">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W186">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X186">
         <v>1.03</v>
       </c>
       <c r="Y186">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z186">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA186">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB186">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AC186">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AD186">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE186">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AG186">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="O187">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="Q187">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R187">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="S187">
         <v>1.29</v>
       </c>
       <c r="T187">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U187">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V187">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W187">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z187">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AA187">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB187">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC187">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AD187">
         <v>1.46</v>
       </c>
       <c r="AE187">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF187">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG187">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AK187">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="O188">
-        <v>4.95</v>
+        <v>3.64</v>
       </c>
       <c r="P188">
-        <v>6.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q188">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="R188">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S188">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T188">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="U188">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V188">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="W188">
+        <v>1.07</v>
+      </c>
+      <c r="X188">
+        <v>1.03</v>
+      </c>
+      <c r="Y188">
         <v>1.16</v>
       </c>
-      <c r="X188">
-        <v>1.02</v>
-      </c>
-      <c r="Y188">
-        <v>1.08</v>
-      </c>
       <c r="Z188">
-        <v>5.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA188">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AB188">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="AC188">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AD188">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AE188">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF188">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AG188">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK188">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,28 +31116,28 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="O189">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="P189">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q189">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R189">
         <v>2.18</v>
       </c>
       <c r="S189">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T189">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U189">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V189">
         <v>1.5</v>
@@ -31146,34 +31146,34 @@
         <v>1.09</v>
       </c>
       <c r="X189">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z189">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AA189">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB189">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AC189">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AD189">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE189">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF189">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG189">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK189">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="O192">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P192">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="Q192">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R192">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U192">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="V192">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W192">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X192">
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z192">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA192">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB192">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC192">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="AD192">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE192">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF192">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AG192">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK192">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>6.05</v>
+        <v>2.24</v>
       </c>
       <c r="O252">
-        <v>5</v>
+        <v>4.07</v>
       </c>
       <c r="P252">
-        <v>1.46</v>
+        <v>2.79</v>
       </c>
       <c r="Q252">
-        <v>6.66</v>
+        <v>2.5</v>
       </c>
       <c r="R252">
+        <v>2.17</v>
+      </c>
+      <c r="S252">
+        <v>1.29</v>
+      </c>
+      <c r="T252">
+        <v>3.25</v>
+      </c>
+      <c r="U252">
         <v>2.55</v>
       </c>
-      <c r="S252">
-        <v>1.22</v>
-      </c>
-      <c r="T252">
-        <v>3.55</v>
-      </c>
-      <c r="U252">
-        <v>2.23</v>
-      </c>
       <c r="V252">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W252">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X252">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z252">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="AA252">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="AB252">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC252">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AD252">
+        <v>1.42</v>
+      </c>
+      <c r="AE252">
+        <v>1.15</v>
+      </c>
+      <c r="AF252">
         <v>1.57</v>
       </c>
-      <c r="AE252">
-        <v>1.18</v>
-      </c>
-      <c r="AF252">
-        <v>1.7</v>
-      </c>
       <c r="AG252">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK252">
-        <v>1.05</v>
+        <v>1.76</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,80 +41548,80 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.24</v>
+        <v>6.05</v>
       </c>
       <c r="O253">
-        <v>4.07</v>
+        <v>5</v>
       </c>
       <c r="P253">
-        <v>2.79</v>
+        <v>1.46</v>
       </c>
       <c r="Q253">
-        <v>2.5</v>
+        <v>6.66</v>
       </c>
       <c r="R253">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="S253">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T253">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U253">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="V253">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W253">
+        <v>1.11</v>
+      </c>
+      <c r="X253">
+        <v>1.02</v>
+      </c>
+      <c r="Y253">
+        <v>1.1</v>
+      </c>
+      <c r="Z253">
+        <v>5</v>
+      </c>
+      <c r="AA253">
+        <v>1.46</v>
+      </c>
+      <c r="AB253">
+        <v>2.4</v>
+      </c>
+      <c r="AC253">
+        <v>2.29</v>
+      </c>
+      <c r="AD253">
+        <v>1.57</v>
+      </c>
+      <c r="AE253">
+        <v>1.18</v>
+      </c>
+      <c r="AF253">
+        <v>1.7</v>
+      </c>
+      <c r="AG253">
+        <v>2.05</v>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ253">
         <v>1.13</v>
       </c>
-      <c r="X253">
-        <v>1.01</v>
-      </c>
-      <c r="Y253">
-        <v>1.21</v>
-      </c>
-      <c r="Z253">
-        <v>3.96</v>
-      </c>
-      <c r="AA253">
-        <v>1.81</v>
-      </c>
-      <c r="AB253">
-        <v>1.95</v>
-      </c>
-      <c r="AC253">
-        <v>2.49</v>
-      </c>
-      <c r="AD253">
-        <v>1.42</v>
-      </c>
-      <c r="AE253">
-        <v>1.15</v>
-      </c>
-      <c r="AF253">
-        <v>1.57</v>
-      </c>
-      <c r="AG253">
-        <v>2.26</v>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ253">
-        <v>1.26</v>
-      </c>
       <c r="AK253">
-        <v>1.76</v>
+        <v>1.05</v>
       </c>
       <c r="AL253">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>3.44</v>
+        <v>4.12</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.69</v>
+        <v>3.39</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AD7">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
+        <v>1.73</v>
+      </c>
+      <c r="AG7">
+        <v>1.98</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.64</v>
       </c>
-      <c r="AG7">
-        <v>2.07</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>1.3</v>
-      </c>
-      <c r="AK7">
-        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>4.12</v>
+        <v>3.44</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.39</v>
+        <v>3.69</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC8">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G34">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="O40">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="P40">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="Q40">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S40">
+        <v>1.18</v>
+      </c>
+      <c r="T40">
+        <v>3.92</v>
+      </c>
+      <c r="U40">
+        <v>2</v>
+      </c>
+      <c r="V40">
+        <v>1.73</v>
+      </c>
+      <c r="W40">
         <v>1.2</v>
-      </c>
-      <c r="T40">
-        <v>4.2</v>
-      </c>
-      <c r="U40">
-        <v>2.06</v>
-      </c>
-      <c r="V40">
-        <v>1.74</v>
-      </c>
-      <c r="W40">
-        <v>1.18</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>6.96</v>
+        <v>6.79</v>
       </c>
       <c r="AA40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD40">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
         <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AG40">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="O41">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="P41">
-        <v>2.96</v>
+        <v>2.51</v>
       </c>
       <c r="Q41">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S41">
+        <v>1.2</v>
+      </c>
+      <c r="T41">
+        <v>4.2</v>
+      </c>
+      <c r="U41">
+        <v>2.06</v>
+      </c>
+      <c r="V41">
+        <v>1.74</v>
+      </c>
+      <c r="W41">
         <v>1.18</v>
-      </c>
-      <c r="T41">
-        <v>3.92</v>
-      </c>
-      <c r="U41">
-        <v>2</v>
-      </c>
-      <c r="V41">
-        <v>1.73</v>
-      </c>
-      <c r="W41">
-        <v>1.2</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>6.79</v>
+        <v>6.96</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB41">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="AC41">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD41">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE41">
         <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AG41">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK41">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="P51">
-        <v>2.65</v>
+        <v>4.49</v>
       </c>
       <c r="Q51">
-        <v>2.98</v>
+        <v>2.08</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA51">
+        <v>1.83</v>
+      </c>
+      <c r="AB51">
+        <v>1.94</v>
+      </c>
+      <c r="AC51">
+        <v>2.59</v>
+      </c>
+      <c r="AD51">
+        <v>1.42</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
         <v>1.71</v>
       </c>
-      <c r="AB51">
-        <v>2.05</v>
-      </c>
-      <c r="AC51">
-        <v>2.77</v>
-      </c>
-      <c r="AD51">
-        <v>1.4</v>
-      </c>
-      <c r="AE51">
-        <v>1.11</v>
-      </c>
-      <c r="AF51">
-        <v>1.57</v>
-      </c>
       <c r="AG51">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>4.24</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>4.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="R52">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AD52">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>3.69</v>
+        <v>2.87</v>
       </c>
       <c r="Q90">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S90">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T90">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="V90">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W90">
+        <v>1.05</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
+        <v>1.25</v>
+      </c>
+      <c r="Z90">
+        <v>3.28</v>
+      </c>
+      <c r="AA90">
+        <v>2</v>
+      </c>
+      <c r="AB90">
+        <v>1.83</v>
+      </c>
+      <c r="AC90">
+        <v>3.04</v>
+      </c>
+      <c r="AD90">
+        <v>1.29</v>
+      </c>
+      <c r="AE90">
         <v>1.07</v>
       </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.28</v>
-      </c>
-      <c r="Z90">
-        <v>3.08</v>
-      </c>
-      <c r="AA90">
-        <v>2.01</v>
-      </c>
-      <c r="AB90">
-        <v>1.8</v>
-      </c>
-      <c r="AC90">
-        <v>3.08</v>
-      </c>
-      <c r="AD90">
-        <v>1.28</v>
-      </c>
-      <c r="AE90">
-        <v>1.08</v>
-      </c>
       <c r="AF90">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG90">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK90">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P91">
-        <v>2.87</v>
+        <v>3.69</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R91">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T91">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="U91">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W91">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB91">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD91">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="O125">
-        <v>5.57</v>
+        <v>3.93</v>
       </c>
       <c r="P125">
-        <v>8.75</v>
+        <v>3.19</v>
       </c>
       <c r="Q125">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="R125">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S125">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T125">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="U125">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="V125">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="W125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z125">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="AA125">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AB125">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="AC125">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AD125">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE125">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF125">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG125">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>2.78</v>
+        <v>1.62</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.24</v>
+        <v>10.9</v>
       </c>
       <c r="O126">
-        <v>3.93</v>
+        <v>8.4</v>
       </c>
       <c r="P126">
-        <v>3.19</v>
+        <v>1.24</v>
       </c>
       <c r="Q126">
-        <v>2.68</v>
+        <v>7.6</v>
       </c>
       <c r="R126">
-        <v>2.38</v>
+        <v>3.64</v>
       </c>
       <c r="S126">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="T126">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="U126">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="V126">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="W126">
+        <v>1.41</v>
+      </c>
+      <c r="X126">
+        <v>1</v>
+      </c>
+      <c r="Y126">
+        <v>1.04</v>
+      </c>
+      <c r="Z126">
+        <v>13</v>
+      </c>
+      <c r="AA126">
         <v>1.14</v>
       </c>
-      <c r="X126">
-        <v>1.01</v>
-      </c>
-      <c r="Y126">
-        <v>1.14</v>
-      </c>
-      <c r="Z126">
-        <v>4.75</v>
-      </c>
-      <c r="AA126">
-        <v>1.63</v>
-      </c>
       <c r="AB126">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="AC126">
-        <v>2.35</v>
+        <v>1.37</v>
       </c>
       <c r="AD126">
-        <v>1.51</v>
+        <v>2.9</v>
       </c>
       <c r="AE126">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="AF126">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG126">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AK126">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>10.9</v>
+        <v>2.79</v>
       </c>
       <c r="O127">
-        <v>8.4</v>
+        <v>3.99</v>
       </c>
       <c r="P127">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="Q127">
-        <v>7.6</v>
+        <v>3.06</v>
       </c>
       <c r="R127">
-        <v>3.64</v>
+        <v>2.43</v>
       </c>
       <c r="S127">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
+        <v>4</v>
+      </c>
+      <c r="U127">
+        <v>2.1</v>
+      </c>
+      <c r="V127">
+        <v>1.67</v>
+      </c>
+      <c r="W127">
+        <v>1.18</v>
+      </c>
+      <c r="X127">
+        <v>1.02</v>
+      </c>
+      <c r="Y127">
+        <v>1.08</v>
+      </c>
+      <c r="Z127">
         <v>6</v>
       </c>
-      <c r="U127">
-        <v>1.57</v>
-      </c>
-      <c r="V127">
-        <v>2.25</v>
-      </c>
-      <c r="W127">
-        <v>1.41</v>
-      </c>
-      <c r="X127">
-        <v>1</v>
-      </c>
-      <c r="Y127">
-        <v>1.04</v>
-      </c>
-      <c r="Z127">
-        <v>13</v>
-      </c>
       <c r="AA127">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AB127">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC127">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="AD127">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE127">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="AF127">
         <v>1.4</v>
       </c>
       <c r="AG127">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,34 +21336,34 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.79</v>
+        <v>1.39</v>
       </c>
       <c r="O129">
-        <v>3.99</v>
+        <v>5.57</v>
       </c>
       <c r="P129">
-        <v>2.47</v>
+        <v>8.75</v>
       </c>
       <c r="Q129">
-        <v>3.06</v>
+        <v>1.75</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T129">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
         <v>1.02</v>
@@ -21372,28 +21372,28 @@
         <v>1.08</v>
       </c>
       <c r="Z129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA129">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB129">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AC129">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD129">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AE129">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF129">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK129">
-        <v>1.36</v>
+        <v>2.78</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="O132">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="P132">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q132">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="R132">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S132">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T132">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U132">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V132">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="AA132">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB132">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC132">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="AD132">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE132">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF132">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG132">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AK132">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="O133">
-        <v>3.66</v>
+        <v>4.22</v>
       </c>
       <c r="P133">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="Q133">
-        <v>2.87</v>
+        <v>2.24</v>
       </c>
       <c r="R133">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="S133">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T133">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U133">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="V133">
+        <v>1.67</v>
+      </c>
+      <c r="W133">
+        <v>1.17</v>
+      </c>
+      <c r="X133">
+        <v>1.02</v>
+      </c>
+      <c r="Y133">
+        <v>1.1</v>
+      </c>
+      <c r="Z133">
+        <v>6.5</v>
+      </c>
+      <c r="AA133">
         <v>1.5</v>
       </c>
-      <c r="W133">
-        <v>1.12</v>
-      </c>
-      <c r="X133">
-        <v>1.01</v>
-      </c>
-      <c r="Y133">
-        <v>1.18</v>
-      </c>
-      <c r="Z133">
-        <v>4.4</v>
-      </c>
-      <c r="AA133">
-        <v>1.7</v>
-      </c>
       <c r="AB133">
+        <v>2.66</v>
+      </c>
+      <c r="AC133">
         <v>2</v>
       </c>
-      <c r="AC133">
-        <v>2.5</v>
-      </c>
       <c r="AD133">
+        <v>1.72</v>
+      </c>
+      <c r="AE133">
+        <v>1.26</v>
+      </c>
+      <c r="AF133">
         <v>1.44</v>
       </c>
-      <c r="AE133">
-        <v>1.13</v>
-      </c>
-      <c r="AF133">
-        <v>1.53</v>
-      </c>
       <c r="AG133">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AK133">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
       <c r="O134">
-        <v>4.22</v>
+        <v>3.54</v>
       </c>
       <c r="P134">
-        <v>4.17</v>
+        <v>2.44</v>
       </c>
       <c r="Q134">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="R134">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S134">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T134">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="V134">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
+        <v>1.22</v>
+      </c>
+      <c r="Z134">
+        <v>3.74</v>
+      </c>
+      <c r="AA134">
+        <v>1.85</v>
+      </c>
+      <c r="AB134">
+        <v>1.85</v>
+      </c>
+      <c r="AC134">
+        <v>2.84</v>
+      </c>
+      <c r="AD134">
+        <v>1.36</v>
+      </c>
+      <c r="AE134">
         <v>1.1</v>
       </c>
-      <c r="Z134">
-        <v>6.5</v>
-      </c>
-      <c r="AA134">
-        <v>1.5</v>
-      </c>
-      <c r="AB134">
-        <v>2.66</v>
-      </c>
-      <c r="AC134">
-        <v>2</v>
-      </c>
-      <c r="AD134">
-        <v>1.72</v>
-      </c>
-      <c r="AE134">
-        <v>1.26</v>
-      </c>
       <c r="AF134">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG134">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK134">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="O143">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="P143">
-        <v>6.15</v>
+        <v>4.39</v>
       </c>
       <c r="Q143">
+        <v>2.36</v>
+      </c>
+      <c r="R143">
         <v>2.06</v>
       </c>
-      <c r="R143">
-        <v>2.19</v>
-      </c>
       <c r="S143">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T143">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="U143">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="V143">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W143">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y143">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z143">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA143">
+        <v>1.83</v>
+      </c>
+      <c r="AB143">
         <v>1.93</v>
       </c>
-      <c r="AB143">
-        <v>1.83</v>
-      </c>
       <c r="AC143">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD143">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE143">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF143">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG143">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK143">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="O144">
-        <v>3.74</v>
+        <v>4.32</v>
       </c>
       <c r="P144">
-        <v>2.79</v>
+        <v>6.15</v>
       </c>
       <c r="Q144">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="R144">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="S144">
+        <v>1.36</v>
+      </c>
+      <c r="T144">
+        <v>2.72</v>
+      </c>
+      <c r="U144">
+        <v>2.72</v>
+      </c>
+      <c r="V144">
+        <v>1.36</v>
+      </c>
+      <c r="W144">
+        <v>1.05</v>
+      </c>
+      <c r="X144">
+        <v>1.01</v>
+      </c>
+      <c r="Y144">
+        <v>1.27</v>
+      </c>
+      <c r="Z144">
+        <v>3.14</v>
+      </c>
+      <c r="AA144">
+        <v>1.93</v>
+      </c>
+      <c r="AB144">
+        <v>1.83</v>
+      </c>
+      <c r="AC144">
+        <v>3.14</v>
+      </c>
+      <c r="AD144">
         <v>1.3</v>
       </c>
-      <c r="T144">
-        <v>3.14</v>
-      </c>
-      <c r="U144">
-        <v>2.61</v>
-      </c>
-      <c r="V144">
-        <v>1.39</v>
-      </c>
-      <c r="W144">
+      <c r="AE144">
         <v>1.07</v>
       </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="Y144">
-        <v>1.21</v>
-      </c>
-      <c r="Z144">
-        <v>3.58</v>
-      </c>
-      <c r="AA144">
-        <v>1.88</v>
-      </c>
-      <c r="AB144">
-        <v>1.96</v>
-      </c>
-      <c r="AC144">
-        <v>2.92</v>
-      </c>
-      <c r="AD144">
-        <v>1.31</v>
-      </c>
-      <c r="AE144">
-        <v>1.08</v>
-      </c>
       <c r="AF144">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AG144">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK144">
-        <v>1.49</v>
+        <v>2.29</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P145">
-        <v>4.39</v>
+        <v>2.79</v>
       </c>
       <c r="Q145">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S145">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="U145">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="V145">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W145">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z145">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA145">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB145">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC145">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE145">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF145">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O146">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="P146">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="Q146">
-        <v>2.01</v>
+        <v>2.66</v>
       </c>
       <c r="R146">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="S146">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="T146">
-        <v>3.26</v>
+        <v>2.47</v>
       </c>
       <c r="U146">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="V146">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W146">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Z146">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="AA146">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="AB146">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="AC146">
-        <v>2.59</v>
+        <v>3.82</v>
       </c>
       <c r="AD146">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE146">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF146">
+        <v>1.9</v>
+      </c>
+      <c r="AG146">
+        <v>1.8</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
+        <v>1.34</v>
+      </c>
+      <c r="AK146">
         <v>1.75</v>
-      </c>
-      <c r="AG146">
-        <v>1.97</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.22</v>
-      </c>
-      <c r="AK146">
-        <v>2.47</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,80 +24270,80 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O147">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="P147">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="Q147">
-        <v>2.66</v>
+        <v>2.01</v>
       </c>
       <c r="R147">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="S147">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="T147">
+        <v>3.26</v>
+      </c>
+      <c r="U147">
+        <v>2.5</v>
+      </c>
+      <c r="V147">
+        <v>1.51</v>
+      </c>
+      <c r="W147">
+        <v>1.09</v>
+      </c>
+      <c r="X147">
+        <v>1.01</v>
+      </c>
+      <c r="Y147">
+        <v>1.16</v>
+      </c>
+      <c r="Z147">
+        <v>4.1</v>
+      </c>
+      <c r="AA147">
+        <v>1.71</v>
+      </c>
+      <c r="AB147">
+        <v>2.18</v>
+      </c>
+      <c r="AC147">
+        <v>2.59</v>
+      </c>
+      <c r="AD147">
+        <v>1.44</v>
+      </c>
+      <c r="AE147">
+        <v>1.16</v>
+      </c>
+      <c r="AF147">
+        <v>1.75</v>
+      </c>
+      <c r="AG147">
+        <v>1.97</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.22</v>
+      </c>
+      <c r="AK147">
         <v>2.47</v>
-      </c>
-      <c r="U147">
-        <v>3.12</v>
-      </c>
-      <c r="V147">
-        <v>1.3</v>
-      </c>
-      <c r="W147">
-        <v>1.02</v>
-      </c>
-      <c r="X147">
-        <v>1.03</v>
-      </c>
-      <c r="Y147">
-        <v>1.34</v>
-      </c>
-      <c r="Z147">
-        <v>2.78</v>
-      </c>
-      <c r="AA147">
-        <v>2.23</v>
-      </c>
-      <c r="AB147">
-        <v>1.67</v>
-      </c>
-      <c r="AC147">
-        <v>3.82</v>
-      </c>
-      <c r="AD147">
-        <v>1.18</v>
-      </c>
-      <c r="AE147">
-        <v>1.03</v>
-      </c>
-      <c r="AF147">
-        <v>1.9</v>
-      </c>
-      <c r="AG147">
-        <v>1.8</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.34</v>
-      </c>
-      <c r="AK147">
-        <v>1.75</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,61 +25085,61 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="O152">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="P152">
-        <v>3.03</v>
+        <v>4.03</v>
       </c>
       <c r="Q152">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="R152">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S152">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T152">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="U152">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="V152">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W152">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X152">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z152">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA152">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB152">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AC152">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD152">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE152">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF152">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG152">
         <v>1.9</v>
@@ -25158,7 +25158,7 @@
         <v>1.26</v>
       </c>
       <c r="AK152">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="O153">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
       <c r="P153">
-        <v>2.57</v>
+        <v>3.03</v>
       </c>
       <c r="Q153">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R153">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="S153">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T153">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="U153">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="V153">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X153">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z153">
-        <v>3.68</v>
+        <v>2.92</v>
       </c>
       <c r="AA153">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB153">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AC153">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD153">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE153">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF153">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AG153">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK153">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="O154">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="P154">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="Q154">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="R154">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S154">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T154">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U154">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AA154">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB154">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC154">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AD154">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF154">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG154">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O155">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="P155">
-        <v>1.81</v>
+        <v>4.26</v>
       </c>
       <c r="Q155">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="R155">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S155">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T155">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U155">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V155">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W155">
+        <v>1.07</v>
+      </c>
+      <c r="X155">
+        <v>1.01</v>
+      </c>
+      <c r="Y155">
+        <v>1.2</v>
+      </c>
+      <c r="Z155">
+        <v>3.72</v>
+      </c>
+      <c r="AA155">
+        <v>1.86</v>
+      </c>
+      <c r="AB155">
+        <v>1.9</v>
+      </c>
+      <c r="AC155">
+        <v>2.78</v>
+      </c>
+      <c r="AD155">
+        <v>1.34</v>
+      </c>
+      <c r="AE155">
         <v>1.1</v>
       </c>
-      <c r="X155">
-        <v>1.02</v>
-      </c>
-      <c r="Y155">
-        <v>1.16</v>
-      </c>
-      <c r="Z155">
-        <v>4.1</v>
-      </c>
-      <c r="AA155">
-        <v>1.67</v>
-      </c>
-      <c r="AB155">
-        <v>2.11</v>
-      </c>
-      <c r="AC155">
-        <v>2.75</v>
-      </c>
-      <c r="AD155">
-        <v>1.43</v>
-      </c>
-      <c r="AE155">
-        <v>1.11</v>
-      </c>
       <c r="AF155">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG155">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.25</v>
+        <v>2.09</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="O156">
-        <v>3.85</v>
+        <v>4.17</v>
       </c>
       <c r="P156">
-        <v>4.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q156">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R156">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="S156">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T156">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U156">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z156">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA156">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AB156">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="AC156">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD156">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AE156">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG156">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK156">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="O157">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="P157">
-        <v>4.26</v>
+        <v>3.45</v>
       </c>
       <c r="Q157">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="R157">
         <v>2.15</v>
       </c>
       <c r="S157">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T157">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U157">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="V157">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
         <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z157">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="AA157">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB157">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC157">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD157">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE157">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG157">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="O171">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.27</v>
+        <v>2.56</v>
       </c>
       <c r="Q171">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="R171">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S171">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T171">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="U171">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V171">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W171">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z171">
-        <v>4.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA171">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB171">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC171">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD171">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE171">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF171">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AG171">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK171">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O172">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P172">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q172">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R172">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S172">
         <v>1.33</v>
       </c>
       <c r="T172">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U172">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V172">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W172">
         <v>1.07</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y172">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z172">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA172">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB172">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC172">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD172">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE172">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF172">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG172">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK172">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O173">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P173">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q173">
         <v>3.34</v>
       </c>
       <c r="R173">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S173">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T173">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U173">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V173">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z173">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AA173">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB173">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AC173">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD173">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE173">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF173">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG173">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O174">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P174">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q174">
         <v>3.34</v>
       </c>
       <c r="R174">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S174">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T174">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U174">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V174">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z174">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AA174">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB174">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AC174">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD174">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE174">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF174">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG174">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK174">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O175">
-        <v>3.32</v>
+        <v>3.62</v>
       </c>
       <c r="P175">
-        <v>2.48</v>
+        <v>3.27</v>
       </c>
       <c r="Q175">
+        <v>2.73</v>
+      </c>
+      <c r="R175">
+        <v>2.25</v>
+      </c>
+      <c r="S175">
+        <v>1.29</v>
+      </c>
+      <c r="T175">
         <v>3.24</v>
       </c>
-      <c r="R175">
-        <v>2.14</v>
-      </c>
-      <c r="S175">
-        <v>1.33</v>
-      </c>
-      <c r="T175">
-        <v>3.22</v>
-      </c>
       <c r="U175">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V175">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z175">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="AA175">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB175">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC175">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD175">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE175">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF175">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG175">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK175">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,80 +30464,80 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="O185">
-        <v>4.95</v>
+        <v>3.52</v>
       </c>
       <c r="P185">
-        <v>6.75</v>
+        <v>3.31</v>
       </c>
       <c r="Q185">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="R185">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="S185">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="U185">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V185">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W185">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X185">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z185">
-        <v>5.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA185">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AB185">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="AC185">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AD185">
+        <v>1.43</v>
+      </c>
+      <c r="AE185">
+        <v>1.13</v>
+      </c>
+      <c r="AF185">
+        <v>1.56</v>
+      </c>
+      <c r="AG185">
+        <v>2.28</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>1.22</v>
+      </c>
+      <c r="AK185">
         <v>1.73</v>
-      </c>
-      <c r="AE185">
-        <v>1.31</v>
-      </c>
-      <c r="AF185">
-        <v>1.55</v>
-      </c>
-      <c r="AG185">
-        <v>2.3</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ185">
-        <v>1.1</v>
-      </c>
-      <c r="AK185">
-        <v>2.75</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,28 +30627,28 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="O186">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="P186">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q186">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R186">
         <v>2.18</v>
       </c>
       <c r="S186">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T186">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U186">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V186">
         <v>1.5</v>
@@ -30657,34 +30657,34 @@
         <v>1.09</v>
       </c>
       <c r="X186">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z186">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AA186">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB186">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AC186">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AD186">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE186">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF186">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG186">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK186">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,65 +30790,65 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="P187">
-        <v>3.35</v>
+        <v>6.75</v>
       </c>
       <c r="Q187">
+        <v>1.83</v>
+      </c>
+      <c r="R187">
+        <v>2.63</v>
+      </c>
+      <c r="S187">
+        <v>1.2</v>
+      </c>
+      <c r="T187">
+        <v>4.2</v>
+      </c>
+      <c r="U187">
+        <v>2</v>
+      </c>
+      <c r="V187">
+        <v>1.69</v>
+      </c>
+      <c r="W187">
+        <v>1.16</v>
+      </c>
+      <c r="X187">
+        <v>1.02</v>
+      </c>
+      <c r="Y187">
+        <v>1.08</v>
+      </c>
+      <c r="Z187">
+        <v>5.45</v>
+      </c>
+      <c r="AA187">
+        <v>1.41</v>
+      </c>
+      <c r="AB187">
+        <v>2.66</v>
+      </c>
+      <c r="AC187">
+        <v>1.98</v>
+      </c>
+      <c r="AD187">
+        <v>1.73</v>
+      </c>
+      <c r="AE187">
+        <v>1.31</v>
+      </c>
+      <c r="AF187">
+        <v>1.55</v>
+      </c>
+      <c r="AG187">
         <v>2.3</v>
       </c>
-      <c r="R187">
-        <v>2.48</v>
-      </c>
-      <c r="S187">
-        <v>1.29</v>
-      </c>
-      <c r="T187">
-        <v>3.4</v>
-      </c>
-      <c r="U187">
-        <v>2.26</v>
-      </c>
-      <c r="V187">
-        <v>1.56</v>
-      </c>
-      <c r="W187">
-        <v>1.11</v>
-      </c>
-      <c r="X187">
-        <v>1.03</v>
-      </c>
-      <c r="Y187">
-        <v>1.15</v>
-      </c>
-      <c r="Z187">
-        <v>4.25</v>
-      </c>
-      <c r="AA187">
-        <v>1.6</v>
-      </c>
-      <c r="AB187">
-        <v>2.25</v>
-      </c>
-      <c r="AC187">
-        <v>2.39</v>
-      </c>
-      <c r="AD187">
-        <v>1.46</v>
-      </c>
-      <c r="AE187">
-        <v>1.17</v>
-      </c>
-      <c r="AF187">
-        <v>1.56</v>
-      </c>
-      <c r="AG187">
-        <v>2.28</v>
-      </c>
       <c r="AH187" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK187">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="O188">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="Q188">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R188">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S188">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U188">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="V188">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W188">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
         <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z188">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA188">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB188">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC188">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AD188">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE188">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF188">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AG188">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,61 +31116,61 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="O189">
         <v>3.48</v>
       </c>
       <c r="P189">
+        <v>2.37</v>
+      </c>
+      <c r="Q189">
+        <v>3.2</v>
+      </c>
+      <c r="R189">
+        <v>2.19</v>
+      </c>
+      <c r="S189">
+        <v>1.3</v>
+      </c>
+      <c r="T189">
+        <v>3.14</v>
+      </c>
+      <c r="U189">
+        <v>2.35</v>
+      </c>
+      <c r="V189">
+        <v>1.51</v>
+      </c>
+      <c r="W189">
+        <v>1.12</v>
+      </c>
+      <c r="X189">
+        <v>1</v>
+      </c>
+      <c r="Y189">
+        <v>1.18</v>
+      </c>
+      <c r="Z189">
+        <v>3.88</v>
+      </c>
+      <c r="AA189">
+        <v>1.69</v>
+      </c>
+      <c r="AB189">
+        <v>2.09</v>
+      </c>
+      <c r="AC189">
         <v>2.56</v>
       </c>
-      <c r="Q189">
-        <v>3.4</v>
-      </c>
-      <c r="R189">
-        <v>2.18</v>
-      </c>
-      <c r="S189">
-        <v>1.29</v>
-      </c>
-      <c r="T189">
-        <v>3.3</v>
-      </c>
-      <c r="U189">
-        <v>2.32</v>
-      </c>
-      <c r="V189">
-        <v>1.5</v>
-      </c>
-      <c r="W189">
-        <v>1.09</v>
-      </c>
-      <c r="X189">
-        <v>1.01</v>
-      </c>
-      <c r="Y189">
-        <v>1.2</v>
-      </c>
-      <c r="Z189">
-        <v>4.15</v>
-      </c>
-      <c r="AA189">
-        <v>1.66</v>
-      </c>
-      <c r="AB189">
-        <v>2.07</v>
-      </c>
-      <c r="AC189">
-        <v>2.53</v>
-      </c>
       <c r="AD189">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE189">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF189">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG189">
         <v>2.3</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AK189">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,49 +31279,49 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.77</v>
+        <v>1.82</v>
       </c>
       <c r="O190">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="P190">
-        <v>2.37</v>
+        <v>4.08</v>
       </c>
       <c r="Q190">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="R190">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S190">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T190">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U190">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V190">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W190">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X190">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z190">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AA190">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB190">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AC190">
         <v>2.56</v>
@@ -31330,13 +31330,13 @@
         <v>1.4</v>
       </c>
       <c r="AE190">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF190">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AG190">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>1.23</v>
       </c>
       <c r="AK190">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="AL190">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G18">
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G19">
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="O113">
-        <v>4.09</v>
+        <v>3.82</v>
       </c>
       <c r="P113">
-        <v>2.59</v>
+        <v>3.06</v>
       </c>
       <c r="Q113">
+        <v>2.63</v>
+      </c>
+      <c r="R113">
+        <v>2.12</v>
+      </c>
+      <c r="S113">
+        <v>1.28</v>
+      </c>
+      <c r="T113">
+        <v>3.08</v>
+      </c>
+      <c r="U113">
+        <v>2.63</v>
+      </c>
+      <c r="V113">
+        <v>1.44</v>
+      </c>
+      <c r="W113">
+        <v>1.1</v>
+      </c>
+      <c r="X113">
+        <v>1.04</v>
+      </c>
+      <c r="Y113">
+        <v>1.2</v>
+      </c>
+      <c r="Z113">
+        <v>3.68</v>
+      </c>
+      <c r="AA113">
+        <v>1.79</v>
+      </c>
+      <c r="AB113">
+        <v>1.97</v>
+      </c>
+      <c r="AC113">
         <v>2.88</v>
       </c>
-      <c r="R113">
-        <v>2.3</v>
-      </c>
-      <c r="S113">
-        <v>1.24</v>
-      </c>
-      <c r="T113">
-        <v>3.6</v>
-      </c>
-      <c r="U113">
-        <v>2.12</v>
-      </c>
-      <c r="V113">
-        <v>1.62</v>
-      </c>
-      <c r="W113">
-        <v>1.14</v>
-      </c>
-      <c r="X113">
-        <v>1.01</v>
-      </c>
-      <c r="Y113">
-        <v>1.15</v>
-      </c>
-      <c r="Z113">
-        <v>4.75</v>
-      </c>
-      <c r="AA113">
-        <v>1.55</v>
-      </c>
-      <c r="AB113">
-        <v>2.39</v>
-      </c>
-      <c r="AC113">
-        <v>2.41</v>
-      </c>
       <c r="AD113">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE113">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF113">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG113">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="O114">
-        <v>3.82</v>
+        <v>4.09</v>
       </c>
       <c r="P114">
-        <v>3.06</v>
+        <v>2.59</v>
       </c>
       <c r="Q114">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R114">
+        <v>2.3</v>
+      </c>
+      <c r="S114">
+        <v>1.24</v>
+      </c>
+      <c r="T114">
+        <v>3.6</v>
+      </c>
+      <c r="U114">
         <v>2.12</v>
       </c>
-      <c r="S114">
-        <v>1.28</v>
-      </c>
-      <c r="T114">
-        <v>3.08</v>
-      </c>
-      <c r="U114">
-        <v>2.63</v>
-      </c>
       <c r="V114">
+        <v>1.62</v>
+      </c>
+      <c r="W114">
+        <v>1.14</v>
+      </c>
+      <c r="X114">
+        <v>1.01</v>
+      </c>
+      <c r="Y114">
+        <v>1.15</v>
+      </c>
+      <c r="Z114">
+        <v>4.75</v>
+      </c>
+      <c r="AA114">
+        <v>1.55</v>
+      </c>
+      <c r="AB114">
+        <v>2.39</v>
+      </c>
+      <c r="AC114">
+        <v>2.41</v>
+      </c>
+      <c r="AD114">
+        <v>1.53</v>
+      </c>
+      <c r="AE114">
+        <v>1.18</v>
+      </c>
+      <c r="AF114">
         <v>1.44</v>
       </c>
-      <c r="W114">
-        <v>1.1</v>
-      </c>
-      <c r="X114">
-        <v>1.04</v>
-      </c>
-      <c r="Y114">
+      <c r="AG114">
+        <v>2.56</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.2</v>
       </c>
-      <c r="Z114">
-        <v>3.68</v>
-      </c>
-      <c r="AA114">
-        <v>1.79</v>
-      </c>
-      <c r="AB114">
-        <v>1.97</v>
-      </c>
-      <c r="AC114">
-        <v>2.88</v>
-      </c>
-      <c r="AD114">
-        <v>1.4</v>
-      </c>
-      <c r="AE114">
-        <v>1.08</v>
-      </c>
-      <c r="AF114">
-        <v>1.65</v>
-      </c>
-      <c r="AG114">
-        <v>2.1</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.3</v>
-      </c>
       <c r="AK114">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.79</v>
+        <v>4.83</v>
       </c>
       <c r="O127">
-        <v>3.99</v>
+        <v>4.73</v>
       </c>
       <c r="P127">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="Q127">
-        <v>3.06</v>
+        <v>4.7</v>
       </c>
       <c r="R127">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="S127">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U127">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V127">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W127">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA127">
+        <v>1.34</v>
+      </c>
+      <c r="AB127">
+        <v>2.93</v>
+      </c>
+      <c r="AC127">
+        <v>1.98</v>
+      </c>
+      <c r="AD127">
+        <v>1.73</v>
+      </c>
+      <c r="AE127">
+        <v>1.36</v>
+      </c>
+      <c r="AF127">
         <v>1.44</v>
       </c>
-      <c r="AB127">
-        <v>2.64</v>
-      </c>
-      <c r="AC127">
-        <v>2.1</v>
-      </c>
-      <c r="AD127">
-        <v>1.65</v>
-      </c>
-      <c r="AE127">
-        <v>1.27</v>
-      </c>
-      <c r="AF127">
-        <v>1.4</v>
-      </c>
       <c r="AG127">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.29</v>
+        <v>2.27</v>
       </c>
       <c r="AK127">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.83</v>
+        <v>2.79</v>
       </c>
       <c r="O128">
-        <v>4.73</v>
+        <v>3.99</v>
       </c>
       <c r="P128">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="Q128">
-        <v>4.7</v>
+        <v>3.06</v>
       </c>
       <c r="R128">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T128">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U128">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V128">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA128">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB128">
-        <v>2.93</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD128">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE128">
+        <v>1.27</v>
+      </c>
+      <c r="AF128">
+        <v>1.4</v>
+      </c>
+      <c r="AG128">
+        <v>2.81</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>1.29</v>
+      </c>
+      <c r="AK128">
         <v>1.36</v>
-      </c>
-      <c r="AF128">
-        <v>1.44</v>
-      </c>
-      <c r="AG128">
-        <v>2.66</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>2.27</v>
-      </c>
-      <c r="AK128">
-        <v>1.21</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.33</v>
+        <v>1.36</v>
       </c>
       <c r="O137">
-        <v>4.02</v>
+        <v>5.37</v>
       </c>
       <c r="P137">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="Q137">
-        <v>3.75</v>
+        <v>1.81</v>
       </c>
       <c r="R137">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S137">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T137">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U137">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V137">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W137">
+        <v>1.15</v>
+      </c>
+      <c r="X137">
+        <v>1.01</v>
+      </c>
+      <c r="Y137">
+        <v>1.14</v>
+      </c>
+      <c r="Z137">
+        <v>4.58</v>
+      </c>
+      <c r="AA137">
+        <v>1.52</v>
+      </c>
+      <c r="AB137">
+        <v>2.24</v>
+      </c>
+      <c r="AC137">
+        <v>2.33</v>
+      </c>
+      <c r="AD137">
+        <v>1.51</v>
+      </c>
+      <c r="AE137">
+        <v>1.17</v>
+      </c>
+      <c r="AF137">
+        <v>1.8</v>
+      </c>
+      <c r="AG137">
+        <v>1.91</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>1.11</v>
       </c>
-      <c r="X137">
-        <v>1.02</v>
-      </c>
-      <c r="Y137">
-        <v>1.16</v>
-      </c>
-      <c r="Z137">
-        <v>4.2</v>
-      </c>
-      <c r="AA137">
-        <v>1.61</v>
-      </c>
-      <c r="AB137">
-        <v>2.13</v>
-      </c>
-      <c r="AC137">
-        <v>2.49</v>
-      </c>
-      <c r="AD137">
-        <v>1.42</v>
-      </c>
-      <c r="AE137">
-        <v>1.13</v>
-      </c>
-      <c r="AF137">
-        <v>1.54</v>
-      </c>
-      <c r="AG137">
-        <v>2.29</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.2</v>
-      </c>
       <c r="AK137">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.36</v>
+        <v>3.33</v>
       </c>
       <c r="O138">
-        <v>5.37</v>
+        <v>4.02</v>
       </c>
       <c r="P138">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="Q138">
-        <v>1.81</v>
+        <v>3.75</v>
       </c>
       <c r="R138">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T138">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U138">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V138">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W138">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z138">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA138">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AB138">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AC138">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="AD138">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AE138">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF138">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AG138">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK138">
-        <v>2.78</v>
+        <v>1.24</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O147">
-        <v>3.98</v>
+        <v>3.66</v>
       </c>
       <c r="P147">
-        <v>6.01</v>
+        <v>5.54</v>
       </c>
       <c r="Q147">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="R147">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S147">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="T147">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="U147">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="V147">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="W147">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X147">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z147">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA147">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="AB147">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="AC147">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="AD147">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AE147">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF147">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AG147">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK147">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="O148">
-        <v>3.66</v>
+        <v>3.98</v>
       </c>
       <c r="P148">
-        <v>5.54</v>
+        <v>6.01</v>
       </c>
       <c r="Q148">
+        <v>2.01</v>
+      </c>
+      <c r="R148">
+        <v>2.29</v>
+      </c>
+      <c r="S148">
+        <v>1.28</v>
+      </c>
+      <c r="T148">
+        <v>3.26</v>
+      </c>
+      <c r="U148">
+        <v>2.5</v>
+      </c>
+      <c r="V148">
+        <v>1.51</v>
+      </c>
+      <c r="W148">
+        <v>1.09</v>
+      </c>
+      <c r="X148">
+        <v>1.01</v>
+      </c>
+      <c r="Y148">
+        <v>1.16</v>
+      </c>
+      <c r="Z148">
+        <v>4.1</v>
+      </c>
+      <c r="AA148">
+        <v>1.71</v>
+      </c>
+      <c r="AB148">
         <v>2.18</v>
       </c>
-      <c r="R148">
-        <v>2.19</v>
-      </c>
-      <c r="S148">
-        <v>1.43</v>
-      </c>
-      <c r="T148">
-        <v>2.7</v>
-      </c>
-      <c r="U148">
-        <v>3.08</v>
-      </c>
-      <c r="V148">
-        <v>1.31</v>
-      </c>
-      <c r="W148">
-        <v>1.02</v>
-      </c>
-      <c r="X148">
-        <v>1.02</v>
-      </c>
-      <c r="Y148">
-        <v>1.33</v>
-      </c>
-      <c r="Z148">
-        <v>2.94</v>
-      </c>
-      <c r="AA148">
-        <v>2.19</v>
-      </c>
-      <c r="AB148">
-        <v>1.69</v>
-      </c>
       <c r="AC148">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD148">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AE148">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF148">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AG148">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O152">
-        <v>3.85</v>
+        <v>4.16</v>
       </c>
       <c r="P152">
-        <v>4.03</v>
+        <v>4.26</v>
       </c>
       <c r="Q152">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R152">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S152">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T152">
+        <v>3.22</v>
+      </c>
+      <c r="U152">
+        <v>2.44</v>
+      </c>
+      <c r="V152">
+        <v>1.47</v>
+      </c>
+      <c r="W152">
+        <v>1.07</v>
+      </c>
+      <c r="X152">
+        <v>1.01</v>
+      </c>
+      <c r="Y152">
+        <v>1.2</v>
+      </c>
+      <c r="Z152">
+        <v>3.72</v>
+      </c>
+      <c r="AA152">
+        <v>1.86</v>
+      </c>
+      <c r="AB152">
+        <v>1.9</v>
+      </c>
+      <c r="AC152">
         <v>2.78</v>
       </c>
-      <c r="U152">
-        <v>2.7</v>
-      </c>
-      <c r="V152">
-        <v>1.39</v>
-      </c>
-      <c r="W152">
-        <v>1.05</v>
-      </c>
-      <c r="X152">
-        <v>1.03</v>
-      </c>
-      <c r="Y152">
-        <v>1.26</v>
-      </c>
-      <c r="Z152">
-        <v>3.2</v>
-      </c>
-      <c r="AA152">
-        <v>1.92</v>
-      </c>
-      <c r="AB152">
-        <v>1.92</v>
-      </c>
-      <c r="AC152">
-        <v>3.14</v>
-      </c>
       <c r="AD152">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE152">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF152">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG152">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK152">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,61 +25248,61 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="O153">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="P153">
-        <v>3.03</v>
+        <v>4.03</v>
       </c>
       <c r="Q153">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="R153">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S153">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T153">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="U153">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="V153">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W153">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z153">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA153">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB153">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AC153">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD153">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE153">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF153">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG153">
         <v>1.9</v>
@@ -25321,7 +25321,7 @@
         <v>1.26</v>
       </c>
       <c r="AK153">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="O155">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="P155">
-        <v>4.26</v>
+        <v>3.45</v>
       </c>
       <c r="Q155">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="R155">
         <v>2.15</v>
       </c>
       <c r="S155">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T155">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U155">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="V155">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z155">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="AA155">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB155">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC155">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD155">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE155">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF155">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG155">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK155">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="O156">
-        <v>4.17</v>
+        <v>3.62</v>
       </c>
       <c r="P156">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q156">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="R156">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="S156">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="U156">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="V156">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="W156">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X156">
         <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z156">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA156">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB156">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="AC156">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD156">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF156">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AG156">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="O157">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P157">
-        <v>3.45</v>
+        <v>1.81</v>
       </c>
       <c r="Q157">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="R157">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S157">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="T157">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
-        <v>2.67</v>
+        <v>2.32</v>
       </c>
       <c r="V157">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z157">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA157">
+        <v>1.67</v>
+      </c>
+      <c r="AB157">
+        <v>2.11</v>
+      </c>
+      <c r="AC157">
+        <v>2.75</v>
+      </c>
+      <c r="AD157">
+        <v>1.43</v>
+      </c>
+      <c r="AE157">
+        <v>1.11</v>
+      </c>
+      <c r="AF157">
+        <v>1.6</v>
+      </c>
+      <c r="AG157">
+        <v>2.19</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.88</v>
       </c>
-      <c r="AB157">
-        <v>1.88</v>
-      </c>
-      <c r="AC157">
-        <v>3.05</v>
-      </c>
-      <c r="AD157">
-        <v>1.28</v>
-      </c>
-      <c r="AE157">
-        <v>1.07</v>
-      </c>
-      <c r="AF157">
-        <v>1.71</v>
-      </c>
-      <c r="AG157">
-        <v>2.02</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.29</v>
-      </c>
       <c r="AK157">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O171">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P171">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q171">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R171">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S171">
         <v>1.33</v>
       </c>
       <c r="T171">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U171">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V171">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W171">
         <v>1.07</v>
       </c>
       <c r="X171">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y171">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z171">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA171">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB171">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC171">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD171">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE171">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF171">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG171">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK171">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O172">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="P172">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q172">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="R172">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S172">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T172">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="U172">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V172">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W172">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X172">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y172">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z172">
-        <v>3.74</v>
+        <v>3.04</v>
       </c>
       <c r="AA172">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AB172">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC172">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD172">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE172">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF172">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG172">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK172">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
+        <v>1.87</v>
+      </c>
+      <c r="O173">
+        <v>3.56</v>
+      </c>
+      <c r="P173">
+        <v>3.93</v>
+      </c>
+      <c r="Q173">
+        <v>2.66</v>
+      </c>
+      <c r="R173">
+        <v>2.1</v>
+      </c>
+      <c r="S173">
+        <v>1.36</v>
+      </c>
+      <c r="T173">
+        <v>2.82</v>
+      </c>
+      <c r="U173">
         <v>2.7</v>
       </c>
-      <c r="O173">
-        <v>3.28</v>
-      </c>
-      <c r="P173">
-        <v>2.5</v>
-      </c>
-      <c r="Q173">
-        <v>3.34</v>
-      </c>
-      <c r="R173">
-        <v>2.08</v>
-      </c>
-      <c r="S173">
-        <v>1.37</v>
-      </c>
-      <c r="T173">
-        <v>2.78</v>
-      </c>
-      <c r="U173">
-        <v>2.6</v>
-      </c>
       <c r="V173">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X173">
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z173">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="AA173">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB173">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC173">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="AD173">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE173">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG173">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O174">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P174">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q174">
         <v>3.34</v>
       </c>
       <c r="R174">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S174">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T174">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U174">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V174">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W174">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X174">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z174">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AA174">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB174">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AC174">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD174">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE174">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF174">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG174">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="O176">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P176">
-        <v>3.93</v>
+        <v>2.56</v>
       </c>
       <c r="Q176">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="R176">
         <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T176">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U176">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V176">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W176">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z176">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA176">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB176">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC176">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AD176">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE176">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF176">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AG176">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.07</v>
+        <v>1.39</v>
       </c>
       <c r="O185">
-        <v>3.52</v>
+        <v>4.95</v>
       </c>
       <c r="P185">
-        <v>3.31</v>
+        <v>6.75</v>
       </c>
       <c r="Q185">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="R185">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="S185">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T185">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="U185">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V185">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W185">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X185">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y185">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z185">
-        <v>3.6</v>
+        <v>5.45</v>
       </c>
       <c r="AA185">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AB185">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="AC185">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="AD185">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AE185">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF185">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG185">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK185">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,61 +30627,61 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="O186">
         <v>3.48</v>
       </c>
       <c r="P186">
+        <v>2.37</v>
+      </c>
+      <c r="Q186">
+        <v>3.2</v>
+      </c>
+      <c r="R186">
+        <v>2.19</v>
+      </c>
+      <c r="S186">
+        <v>1.3</v>
+      </c>
+      <c r="T186">
+        <v>3.14</v>
+      </c>
+      <c r="U186">
+        <v>2.35</v>
+      </c>
+      <c r="V186">
+        <v>1.51</v>
+      </c>
+      <c r="W186">
+        <v>1.12</v>
+      </c>
+      <c r="X186">
+        <v>1</v>
+      </c>
+      <c r="Y186">
+        <v>1.18</v>
+      </c>
+      <c r="Z186">
+        <v>3.88</v>
+      </c>
+      <c r="AA186">
+        <v>1.69</v>
+      </c>
+      <c r="AB186">
+        <v>2.09</v>
+      </c>
+      <c r="AC186">
         <v>2.56</v>
       </c>
-      <c r="Q186">
-        <v>3.4</v>
-      </c>
-      <c r="R186">
-        <v>2.18</v>
-      </c>
-      <c r="S186">
-        <v>1.29</v>
-      </c>
-      <c r="T186">
-        <v>3.3</v>
-      </c>
-      <c r="U186">
-        <v>2.32</v>
-      </c>
-      <c r="V186">
-        <v>1.5</v>
-      </c>
-      <c r="W186">
-        <v>1.09</v>
-      </c>
-      <c r="X186">
-        <v>1.01</v>
-      </c>
-      <c r="Y186">
-        <v>1.2</v>
-      </c>
-      <c r="Z186">
-        <v>4.15</v>
-      </c>
-      <c r="AA186">
-        <v>1.66</v>
-      </c>
-      <c r="AB186">
-        <v>2.07</v>
-      </c>
-      <c r="AC186">
-        <v>2.53</v>
-      </c>
       <c r="AD186">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE186">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG186">
         <v>2.3</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AK186">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="O187">
-        <v>4.95</v>
+        <v>3.64</v>
       </c>
       <c r="P187">
-        <v>6.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q187">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="R187">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S187">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T187">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="U187">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V187">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="W187">
+        <v>1.07</v>
+      </c>
+      <c r="X187">
+        <v>1.03</v>
+      </c>
+      <c r="Y187">
         <v>1.16</v>
       </c>
-      <c r="X187">
-        <v>1.02</v>
-      </c>
-      <c r="Y187">
-        <v>1.08</v>
-      </c>
       <c r="Z187">
-        <v>5.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA187">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AB187">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="AC187">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AD187">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AE187">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF187">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AG187">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK187">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="O188">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P188">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="Q188">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R188">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="S188">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T188">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U188">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="V188">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X188">
         <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z188">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA188">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB188">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC188">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="AD188">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE188">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF188">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AG188">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,61 +31116,61 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="O189">
         <v>3.48</v>
       </c>
       <c r="P189">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="Q189">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R189">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S189">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T189">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U189">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="V189">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W189">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X189">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
+        <v>1.2</v>
+      </c>
+      <c r="Z189">
+        <v>4.15</v>
+      </c>
+      <c r="AA189">
+        <v>1.66</v>
+      </c>
+      <c r="AB189">
+        <v>2.07</v>
+      </c>
+      <c r="AC189">
+        <v>2.53</v>
+      </c>
+      <c r="AD189">
+        <v>1.46</v>
+      </c>
+      <c r="AE189">
         <v>1.18</v>
       </c>
-      <c r="Z189">
-        <v>3.88</v>
-      </c>
-      <c r="AA189">
-        <v>1.69</v>
-      </c>
-      <c r="AB189">
-        <v>2.09</v>
-      </c>
-      <c r="AC189">
-        <v>2.56</v>
-      </c>
-      <c r="AD189">
-        <v>1.4</v>
-      </c>
-      <c r="AE189">
-        <v>1.13</v>
-      </c>
       <c r="AF189">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG189">
         <v>2.3</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AK189">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,80 +31279,80 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="O190">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="P190">
-        <v>4.08</v>
+        <v>4.69</v>
       </c>
       <c r="Q190">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R190">
+        <v>2.47</v>
+      </c>
+      <c r="S190">
+        <v>1.18</v>
+      </c>
+      <c r="T190">
+        <v>3.92</v>
+      </c>
+      <c r="U190">
+        <v>2.1</v>
+      </c>
+      <c r="V190">
+        <v>1.69</v>
+      </c>
+      <c r="W190">
+        <v>1.17</v>
+      </c>
+      <c r="X190">
+        <v>1.02</v>
+      </c>
+      <c r="Y190">
+        <v>1.08</v>
+      </c>
+      <c r="Z190">
+        <v>5.45</v>
+      </c>
+      <c r="AA190">
+        <v>1.39</v>
+      </c>
+      <c r="AB190">
+        <v>2.75</v>
+      </c>
+      <c r="AC190">
+        <v>2.13</v>
+      </c>
+      <c r="AD190">
+        <v>1.71</v>
+      </c>
+      <c r="AE190">
+        <v>1.25</v>
+      </c>
+      <c r="AF190">
+        <v>1.47</v>
+      </c>
+      <c r="AG190">
+        <v>2.63</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
+        <v>1.13</v>
+      </c>
+      <c r="AK190">
         <v>2.3</v>
-      </c>
-      <c r="S190">
-        <v>1.25</v>
-      </c>
-      <c r="T190">
-        <v>3.12</v>
-      </c>
-      <c r="U190">
-        <v>2.45</v>
-      </c>
-      <c r="V190">
-        <v>1.47</v>
-      </c>
-      <c r="W190">
-        <v>1.07</v>
-      </c>
-      <c r="X190">
-        <v>1.03</v>
-      </c>
-      <c r="Y190">
-        <v>1.16</v>
-      </c>
-      <c r="Z190">
-        <v>3.7</v>
-      </c>
-      <c r="AA190">
-        <v>1.65</v>
-      </c>
-      <c r="AB190">
-        <v>2.14</v>
-      </c>
-      <c r="AC190">
-        <v>2.56</v>
-      </c>
-      <c r="AD190">
-        <v>1.4</v>
-      </c>
-      <c r="AE190">
-        <v>1.12</v>
-      </c>
-      <c r="AF190">
-        <v>1.63</v>
-      </c>
-      <c r="AG190">
-        <v>2.14</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ190">
-        <v>1.23</v>
-      </c>
-      <c r="AK190">
-        <v>2.06</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="O191">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="P191">
-        <v>4.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q191">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="R191">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="S191">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T191">
-        <v>3.92</v>
+        <v>3.12</v>
       </c>
       <c r="U191">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V191">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W191">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z191">
-        <v>5.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA191">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AB191">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="AC191">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="AD191">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AE191">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF191">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AG191">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK191">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="O192">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P192">
-        <v>4.31</v>
+        <v>3.35</v>
       </c>
       <c r="Q192">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R192">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="S192">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U192">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="V192">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W192">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X192">
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z192">
-        <v>3.28</v>
+        <v>4.25</v>
       </c>
       <c r="AA192">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AB192">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AC192">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="AD192">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AE192">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF192">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AG192">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK192">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="O193">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="P193">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="Q193">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="R193">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S193">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T193">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U193">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V193">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W193">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z193">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="AA193">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB193">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC193">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="AD193">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE193">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF193">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG193">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK193">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="O194">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="P194">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="Q194">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="R194">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S194">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T194">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U194">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V194">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W194">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z194">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="AA194">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AB194">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC194">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="AD194">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE194">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF194">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG194">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK194">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O259">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P259">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="Q259">
-        <v>6.07</v>
+        <v>4.25</v>
       </c>
       <c r="R259">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="S259">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T259">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U259">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V259">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W259">
         <v>1.08</v>
       </c>
       <c r="X259">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z259">
-        <v>3.73</v>
+        <v>4.14</v>
       </c>
       <c r="AA259">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AB259">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AC259">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD259">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE259">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF259">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG259">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK259">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="O260">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P260">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="Q260">
-        <v>4.25</v>
+        <v>6.07</v>
       </c>
       <c r="R260">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S260">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T260">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U260">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V260">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W260">
         <v>1.08</v>
       </c>
       <c r="X260">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y260">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z260">
-        <v>4.14</v>
+        <v>3.73</v>
       </c>
       <c r="AA260">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AB260">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AC260">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD260">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE260">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF260">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG260">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK260">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,80 +43504,80 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="O265">
-        <v>3.16</v>
+        <v>6.1</v>
       </c>
       <c r="P265">
-        <v>2.89</v>
+        <v>13.2</v>
       </c>
       <c r="Q265">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="R265">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="S265">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="T265">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="U265">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="V265">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="W265">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X265">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y265">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="Z265">
-        <v>2.69</v>
+        <v>5.12</v>
       </c>
       <c r="AA265">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AB265">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC265">
+        <v>2.2</v>
+      </c>
+      <c r="AD265">
+        <v>1.58</v>
+      </c>
+      <c r="AE265">
+        <v>1.23</v>
+      </c>
+      <c r="AF265">
+        <v>1.95</v>
+      </c>
+      <c r="AG265">
+        <v>1.72</v>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ265">
+        <v>1.1</v>
+      </c>
+      <c r="AK265">
         <v>4</v>
-      </c>
-      <c r="AD265">
-        <v>1.17</v>
-      </c>
-      <c r="AE265">
-        <v>1.02</v>
-      </c>
-      <c r="AF265">
-        <v>1.9</v>
-      </c>
-      <c r="AG265">
-        <v>1.8</v>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ265">
-        <v>1.29</v>
-      </c>
-      <c r="AK265">
-        <v>1.48</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="O266">
-        <v>6.1</v>
+        <v>3.16</v>
       </c>
       <c r="P266">
-        <v>13.2</v>
+        <v>2.89</v>
       </c>
       <c r="Q266">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="R266">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="S266">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="T266">
-        <v>3.8</v>
+        <v>2.64</v>
       </c>
       <c r="U266">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="V266">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="W266">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X266">
+        <v>1.04</v>
+      </c>
+      <c r="Y266">
+        <v>1.39</v>
+      </c>
+      <c r="Z266">
+        <v>2.69</v>
+      </c>
+      <c r="AA266">
+        <v>2.25</v>
+      </c>
+      <c r="AB266">
+        <v>1.57</v>
+      </c>
+      <c r="AC266">
+        <v>4</v>
+      </c>
+      <c r="AD266">
+        <v>1.17</v>
+      </c>
+      <c r="AE266">
         <v>1.02</v>
       </c>
-      <c r="Y266">
-        <v>1.11</v>
-      </c>
-      <c r="Z266">
-        <v>5.12</v>
-      </c>
-      <c r="AA266">
-        <v>1.45</v>
-      </c>
-      <c r="AB266">
-        <v>2.7</v>
-      </c>
-      <c r="AC266">
-        <v>2.2</v>
-      </c>
-      <c r="AD266">
-        <v>1.58</v>
-      </c>
-      <c r="AE266">
-        <v>1.23</v>
-      </c>
       <c r="AF266">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG266">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK266">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -46447,55 +46447,55 @@
         <v>2.45</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48566,34 +48566,34 @@
         <v>5.81</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X296">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA296">
         <v>1.95</v>
@@ -48602,19 +48602,19 @@
         <v>1.85</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -49218,40 +49218,40 @@
         <v>2.74</v>
       </c>
       <c r="Q300">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R300">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T300">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U300">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V300">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W300">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X300">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y300">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z300">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC300">
         <v>2</v>
@@ -49260,13 +49260,13 @@
         <v>1.7</v>
       </c>
       <c r="AE300">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG300">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK300">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49544,55 +49544,55 @@
         <v>5.87</v>
       </c>
       <c r="Q302">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R302">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S302">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T302">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U302">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V302">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W302">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X302">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y302">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z302">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA302">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB302">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE302">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF302">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG302">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK302">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50359,34 +50359,34 @@
         <v>7.1</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA307">
         <v>1.6</v>
@@ -50395,19 +50395,19 @@
         <v>2.2</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50522,34 +50522,34 @@
         <v>6.67</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X308">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA308">
         <v>1.62</v>
@@ -50558,19 +50558,19 @@
         <v>2.15</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50685,34 +50685,34 @@
         <v>2.6</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA309">
         <v>1.75</v>
@@ -50721,19 +50721,19 @@
         <v>1.95</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51337,34 +51337,34 @@
         <v>3.05</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA313">
         <v>1.9</v>
@@ -51373,19 +51373,19 @@
         <v>1.9</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q315">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R315">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S315">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T315">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U315">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V315">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W315">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X315">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y315">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z315">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA315">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB315">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC315">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD315">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE315">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF315">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG315">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK315">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51826,40 +51826,40 @@
         <v>5.62</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R316">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S316">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T316">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U316">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V316">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W316">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X316">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y316">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z316">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC316">
         <v>1.77</v>
@@ -51868,13 +51868,13 @@
         <v>1.93</v>
       </c>
       <c r="AE316">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF316">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG316">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK316">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -52152,55 +52152,55 @@
         <v>3.04</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T318">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W318">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X318">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52478,34 +52478,34 @@
         <v>3.08</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA320">
         <v>1.85</v>
@@ -52514,19 +52514,19 @@
         <v>1.83</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,55 +55566,55 @@
         </is>
       </c>
       <c r="N339">
+        <v>2.12</v>
+      </c>
+      <c r="O339">
+        <v>3.97</v>
+      </c>
+      <c r="P339">
+        <v>3.26</v>
+      </c>
+      <c r="Q339">
+        <v>0</v>
+      </c>
+      <c r="R339">
+        <v>0</v>
+      </c>
+      <c r="S339">
+        <v>0</v>
+      </c>
+      <c r="T339">
+        <v>0</v>
+      </c>
+      <c r="U339">
+        <v>0</v>
+      </c>
+      <c r="V339">
+        <v>0</v>
+      </c>
+      <c r="W339">
+        <v>0</v>
+      </c>
+      <c r="X339">
+        <v>0</v>
+      </c>
+      <c r="Y339">
+        <v>0</v>
+      </c>
+      <c r="Z339">
+        <v>0</v>
+      </c>
+      <c r="AA339">
+        <v>0</v>
+      </c>
+      <c r="AB339">
+        <v>0</v>
+      </c>
+      <c r="AC339">
         <v>1.98</v>
       </c>
-      <c r="O339">
-        <v>3.94</v>
-      </c>
-      <c r="P339">
-        <v>3.67</v>
-      </c>
-      <c r="Q339">
-        <v>0</v>
-      </c>
-      <c r="R339">
-        <v>0</v>
-      </c>
-      <c r="S339">
-        <v>0</v>
-      </c>
-      <c r="T339">
-        <v>0</v>
-      </c>
-      <c r="U339">
-        <v>0</v>
-      </c>
-      <c r="V339">
-        <v>0</v>
-      </c>
-      <c r="W339">
-        <v>0</v>
-      </c>
-      <c r="X339">
-        <v>0</v>
-      </c>
-      <c r="Y339">
-        <v>0</v>
-      </c>
-      <c r="Z339">
-        <v>0</v>
-      </c>
-      <c r="AA339">
-        <v>0</v>
-      </c>
-      <c r="AB339">
-        <v>0</v>
-      </c>
-      <c r="AC339">
-        <v>2.15</v>
-      </c>
       <c r="AD339">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="O340">
-        <v>3.97</v>
+        <v>4.22</v>
       </c>
       <c r="P340">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55774,10 +55774,10 @@
         <v>0</v>
       </c>
       <c r="AC340">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD340">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE340">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="O341">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="P341">
-        <v>4.12</v>
+        <v>2.74</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -55937,10 +55937,10 @@
         <v>0</v>
       </c>
       <c r="AC341">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD341">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.42</v>
+        <v>1.31</v>
       </c>
       <c r="O342">
-        <v>3.96</v>
+        <v>6.46</v>
       </c>
       <c r="P342">
-        <v>2.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56100,10 +56100,10 @@
         <v>0</v>
       </c>
       <c r="AC342">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AD342">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE342">
         <v>0</v>
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="O343">
-        <v>5.76</v>
+        <v>3.94</v>
       </c>
       <c r="P343">
-        <v>8.449999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56263,10 +56263,10 @@
         <v>0</v>
       </c>
       <c r="AC343">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD343">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE343">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O344">
-        <v>6.46</v>
+        <v>5.76</v>
       </c>
       <c r="P344">
-        <v>8.949999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56426,10 +56426,10 @@
         <v>0</v>
       </c>
       <c r="AC344">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD344">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE344">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="P40">
-        <v>2.96</v>
+        <v>2.51</v>
       </c>
       <c r="Q40">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="R40">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
+        <v>1.2</v>
+      </c>
+      <c r="T40">
+        <v>4.2</v>
+      </c>
+      <c r="U40">
+        <v>2.06</v>
+      </c>
+      <c r="V40">
+        <v>1.74</v>
+      </c>
+      <c r="W40">
         <v>1.18</v>
-      </c>
-      <c r="T40">
-        <v>3.92</v>
-      </c>
-      <c r="U40">
-        <v>2</v>
-      </c>
-      <c r="V40">
-        <v>1.73</v>
-      </c>
-      <c r="W40">
-        <v>1.2</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
-        <v>6.79</v>
+        <v>6.96</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB40">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="AC40">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE40">
         <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AG40">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK40">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="O41">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="P41">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="Q41">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="R41">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
+        <v>1.18</v>
+      </c>
+      <c r="T41">
+        <v>3.92</v>
+      </c>
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41">
+        <v>1.73</v>
+      </c>
+      <c r="W41">
         <v>1.2</v>
-      </c>
-      <c r="T41">
-        <v>4.2</v>
-      </c>
-      <c r="U41">
-        <v>2.06</v>
-      </c>
-      <c r="V41">
-        <v>1.74</v>
-      </c>
-      <c r="W41">
-        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>6.96</v>
+        <v>6.79</v>
       </c>
       <c r="AA41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="AC41">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE41">
         <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AG41">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>10.9</v>
+        <v>4.83</v>
       </c>
       <c r="O127">
-        <v>8.4</v>
+        <v>4.73</v>
       </c>
       <c r="P127">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q127">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="R127">
-        <v>3.64</v>
+        <v>2.67</v>
       </c>
       <c r="S127">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T127">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="U127">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="V127">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="W127">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z127">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AB127">
-        <v>5.75</v>
+        <v>2.93</v>
       </c>
       <c r="AC127">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="AD127">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="AE127">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AF127">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG127">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.07</v>
+        <v>2.27</v>
       </c>
       <c r="AK127">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.39</v>
+        <v>2.79</v>
       </c>
       <c r="O128">
-        <v>5.57</v>
+        <v>3.99</v>
       </c>
       <c r="P128">
-        <v>8.75</v>
+        <v>2.47</v>
       </c>
       <c r="Q128">
-        <v>1.75</v>
+        <v>3.06</v>
       </c>
       <c r="R128">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S128">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T128">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U128">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V128">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X128">
         <v>1.02</v>
@@ -21209,28 +21209,28 @@
         <v>1.08</v>
       </c>
       <c r="Z128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA128">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB128">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD128">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AE128">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF128">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG128">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK128">
-        <v>2.78</v>
+        <v>1.36</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.83</v>
+        <v>1.39</v>
       </c>
       <c r="O129">
-        <v>4.73</v>
+        <v>5.57</v>
       </c>
       <c r="P129">
-        <v>1.68</v>
+        <v>8.75</v>
       </c>
       <c r="Q129">
-        <v>4.7</v>
+        <v>1.75</v>
       </c>
       <c r="R129">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="S129">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T129">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="U129">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V129">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W129">
         <v>1.2</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z129">
         <v>7</v>
       </c>
       <c r="AA129">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AB129">
-        <v>2.93</v>
+        <v>2.72</v>
       </c>
       <c r="AC129">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AD129">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE129">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF129">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK129">
-        <v>1.21</v>
+        <v>2.78</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.79</v>
+        <v>10.9</v>
       </c>
       <c r="O130">
-        <v>3.99</v>
+        <v>8.4</v>
       </c>
       <c r="P130">
-        <v>2.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q130">
-        <v>3.06</v>
+        <v>7.6</v>
       </c>
       <c r="R130">
-        <v>2.43</v>
+        <v>3.64</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U130">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="V130">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="W130">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y130">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z130">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AA130">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AB130">
-        <v>2.64</v>
+        <v>5.75</v>
       </c>
       <c r="AC130">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AD130">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="AE130">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="AF130">
         <v>1.4</v>
       </c>
       <c r="AG130">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P145">
-        <v>4.39</v>
+        <v>2.79</v>
       </c>
       <c r="Q145">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S145">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="U145">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="V145">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W145">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z145">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA145">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB145">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC145">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE145">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF145">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="O146">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P146">
-        <v>2.79</v>
+        <v>4.39</v>
       </c>
       <c r="Q146">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="R146">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T146">
-        <v>3.14</v>
+        <v>2.64</v>
       </c>
       <c r="U146">
-        <v>2.61</v>
+        <v>2.94</v>
       </c>
       <c r="V146">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z146">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA146">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB146">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC146">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD146">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF146">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="O154">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="P154">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="Q154">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="R154">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S154">
+        <v>1.4</v>
+      </c>
+      <c r="T154">
+        <v>2.67</v>
+      </c>
+      <c r="U154">
+        <v>2.92</v>
+      </c>
+      <c r="V154">
         <v>1.34</v>
       </c>
-      <c r="T154">
-        <v>2.7</v>
-      </c>
-      <c r="U154">
-        <v>2.67</v>
-      </c>
-      <c r="V154">
-        <v>1.4</v>
-      </c>
       <c r="W154">
+        <v>1.04</v>
+      </c>
+      <c r="X154">
+        <v>1.02</v>
+      </c>
+      <c r="Y154">
+        <v>1.31</v>
+      </c>
+      <c r="Z154">
+        <v>2.92</v>
+      </c>
+      <c r="AA154">
+        <v>2.05</v>
+      </c>
+      <c r="AB154">
+        <v>1.71</v>
+      </c>
+      <c r="AC154">
+        <v>3.5</v>
+      </c>
+      <c r="AD154">
+        <v>1.22</v>
+      </c>
+      <c r="AE154">
         <v>1.05</v>
       </c>
-      <c r="X154">
-        <v>1.01</v>
-      </c>
-      <c r="Y154">
-        <v>1.24</v>
-      </c>
-      <c r="Z154">
-        <v>3.34</v>
-      </c>
-      <c r="AA154">
-        <v>1.88</v>
-      </c>
-      <c r="AB154">
-        <v>1.88</v>
-      </c>
-      <c r="AC154">
-        <v>3.05</v>
-      </c>
-      <c r="AD154">
-        <v>1.28</v>
-      </c>
-      <c r="AE154">
-        <v>1.07</v>
-      </c>
       <c r="AF154">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG154">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK154">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="O155">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="P155">
-        <v>2.57</v>
+        <v>3.24</v>
       </c>
       <c r="Q155">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="R155">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S155">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T155">
-        <v>2.85</v>
+        <v>3.17</v>
       </c>
       <c r="U155">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="V155">
         <v>1.48</v>
       </c>
       <c r="W155">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z155">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA155">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB155">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC155">
         <v>2.81</v>
       </c>
       <c r="AD155">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE155">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG155">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK155">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,61 +25737,61 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="O156">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="P156">
-        <v>3.03</v>
+        <v>4.03</v>
       </c>
       <c r="Q156">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="R156">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T156">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="U156">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="V156">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W156">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z156">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB156">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AC156">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD156">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE156">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF156">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG156">
         <v>1.9</v>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
+        <v>2.49</v>
+      </c>
+      <c r="O157">
+        <v>3.83</v>
+      </c>
+      <c r="P157">
+        <v>2.57</v>
+      </c>
+      <c r="Q157">
+        <v>3.1</v>
+      </c>
+      <c r="R157">
+        <v>2.18</v>
+      </c>
+      <c r="S157">
+        <v>1.35</v>
+      </c>
+      <c r="T157">
+        <v>2.85</v>
+      </c>
+      <c r="U157">
+        <v>2.42</v>
+      </c>
+      <c r="V157">
+        <v>1.48</v>
+      </c>
+      <c r="W157">
+        <v>1.09</v>
+      </c>
+      <c r="X157">
+        <v>1.01</v>
+      </c>
+      <c r="Y157">
+        <v>1.2</v>
+      </c>
+      <c r="Z157">
+        <v>3.68</v>
+      </c>
+      <c r="AA157">
         <v>1.85</v>
       </c>
-      <c r="O157">
-        <v>3.85</v>
-      </c>
-      <c r="P157">
-        <v>4.03</v>
-      </c>
-      <c r="Q157">
-        <v>2.4</v>
-      </c>
-      <c r="R157">
-        <v>2.12</v>
-      </c>
-      <c r="S157">
-        <v>1.37</v>
-      </c>
-      <c r="T157">
-        <v>2.78</v>
-      </c>
-      <c r="U157">
-        <v>2.7</v>
-      </c>
-      <c r="V157">
-        <v>1.39</v>
-      </c>
-      <c r="W157">
-        <v>1.05</v>
-      </c>
-      <c r="X157">
-        <v>1.03</v>
-      </c>
-      <c r="Y157">
-        <v>1.26</v>
-      </c>
-      <c r="Z157">
-        <v>3.2</v>
-      </c>
-      <c r="AA157">
-        <v>1.92</v>
-      </c>
       <c r="AB157">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC157">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="AD157">
+        <v>1.38</v>
+      </c>
+      <c r="AE157">
+        <v>1.14</v>
+      </c>
+      <c r="AF157">
+        <v>1.61</v>
+      </c>
+      <c r="AG157">
+        <v>2.2</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.29</v>
       </c>
-      <c r="AE157">
-        <v>1.06</v>
-      </c>
-      <c r="AF157">
-        <v>1.9</v>
-      </c>
-      <c r="AG157">
-        <v>1.9</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.26</v>
-      </c>
       <c r="AK157">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.07</v>
+        <v>3.9</v>
       </c>
       <c r="O158">
-        <v>3.89</v>
+        <v>4.17</v>
       </c>
       <c r="P158">
-        <v>3.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q158">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="R158">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S158">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T158">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="U158">
-        <v>2.67</v>
+        <v>2.32</v>
       </c>
       <c r="V158">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W158">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z158">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA158">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AB158">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AC158">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AD158">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE158">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF158">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG158">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AK158">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.9</v>
+        <v>2.02</v>
       </c>
       <c r="O159">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P159">
-        <v>1.81</v>
+        <v>3.45</v>
       </c>
       <c r="Q159">
-        <v>4.2</v>
+        <v>2.53</v>
       </c>
       <c r="R159">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S159">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T159">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U159">
-        <v>2.32</v>
+        <v>2.67</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z159">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA159">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AB159">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AC159">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD159">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF159">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG159">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK159">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="O172">
-        <v>3.56</v>
+        <v>3.28</v>
       </c>
       <c r="P172">
-        <v>3.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q172">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="R172">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S172">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T172">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U172">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V172">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W172">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X172">
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z172">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="AA172">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB172">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC172">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="AD172">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE172">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF172">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG172">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK172">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="O173">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P173">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q173">
         <v>3.34</v>
@@ -28523,49 +28523,49 @@
         <v>2.1</v>
       </c>
       <c r="S173">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T173">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U173">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="V173">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
+        <v>1.23</v>
+      </c>
+      <c r="Z173">
+        <v>3.42</v>
+      </c>
+      <c r="AA173">
+        <v>1.8</v>
+      </c>
+      <c r="AB173">
+        <v>1.88</v>
+      </c>
+      <c r="AC173">
+        <v>2.88</v>
+      </c>
+      <c r="AD173">
         <v>1.32</v>
       </c>
-      <c r="Z173">
-        <v>3.04</v>
-      </c>
-      <c r="AA173">
-        <v>1.98</v>
-      </c>
-      <c r="AB173">
-        <v>1.71</v>
-      </c>
-      <c r="AC173">
-        <v>3.2</v>
-      </c>
-      <c r="AD173">
-        <v>1.29</v>
-      </c>
       <c r="AE173">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF173">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG173">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O174">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P174">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="Q174">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R174">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S174">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="U174">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V174">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z174">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
       <c r="AA174">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB174">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC174">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="AD174">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE174">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF174">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AG174">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK174">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="O176">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="P176">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="Q176">
         <v>3.34</v>
@@ -29012,65 +29012,65 @@
         <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T176">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U176">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="V176">
+        <v>1.38</v>
+      </c>
+      <c r="W176">
+        <v>1.06</v>
+      </c>
+      <c r="X176">
+        <v>1.03</v>
+      </c>
+      <c r="Y176">
+        <v>1.32</v>
+      </c>
+      <c r="Z176">
+        <v>3.04</v>
+      </c>
+      <c r="AA176">
+        <v>1.98</v>
+      </c>
+      <c r="AB176">
+        <v>1.71</v>
+      </c>
+      <c r="AC176">
+        <v>3.2</v>
+      </c>
+      <c r="AD176">
+        <v>1.29</v>
+      </c>
+      <c r="AE176">
+        <v>1.06</v>
+      </c>
+      <c r="AF176">
+        <v>1.76</v>
+      </c>
+      <c r="AG176">
+        <v>1.96</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
+        <v>1.28</v>
+      </c>
+      <c r="AK176">
         <v>1.44</v>
-      </c>
-      <c r="W176">
-        <v>1.07</v>
-      </c>
-      <c r="X176">
-        <v>1.01</v>
-      </c>
-      <c r="Y176">
-        <v>1.23</v>
-      </c>
-      <c r="Z176">
-        <v>3.42</v>
-      </c>
-      <c r="AA176">
-        <v>1.8</v>
-      </c>
-      <c r="AB176">
-        <v>1.88</v>
-      </c>
-      <c r="AC176">
-        <v>2.88</v>
-      </c>
-      <c r="AD176">
-        <v>1.32</v>
-      </c>
-      <c r="AE176">
-        <v>1.09</v>
-      </c>
-      <c r="AF176">
-        <v>1.64</v>
-      </c>
-      <c r="AG176">
-        <v>2.13</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.3</v>
-      </c>
-      <c r="AK176">
-        <v>1.42</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="O177">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P177">
-        <v>2.71</v>
+        <v>3.93</v>
       </c>
       <c r="Q177">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="R177">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S177">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T177">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X177">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z177">
-        <v>4.25</v>
+        <v>3.43</v>
       </c>
       <c r="AA177">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB177">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC177">
-        <v>2.38</v>
+        <v>3.42</v>
       </c>
       <c r="AD177">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE177">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF177">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="AG177">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,80 +30627,80 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.79</v>
+        <v>2.52</v>
       </c>
       <c r="O186">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P186">
-        <v>4.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q186">
+        <v>3.4</v>
+      </c>
+      <c r="R186">
+        <v>2.18</v>
+      </c>
+      <c r="S186">
+        <v>1.29</v>
+      </c>
+      <c r="T186">
+        <v>3.3</v>
+      </c>
+      <c r="U186">
         <v>2.32</v>
       </c>
-      <c r="R186">
-        <v>2.12</v>
-      </c>
-      <c r="S186">
-        <v>1.36</v>
-      </c>
-      <c r="T186">
-        <v>3</v>
-      </c>
-      <c r="U186">
-        <v>2.75</v>
-      </c>
       <c r="V186">
+        <v>1.5</v>
+      </c>
+      <c r="W186">
+        <v>1.09</v>
+      </c>
+      <c r="X186">
+        <v>1.01</v>
+      </c>
+      <c r="Y186">
+        <v>1.2</v>
+      </c>
+      <c r="Z186">
+        <v>4.15</v>
+      </c>
+      <c r="AA186">
+        <v>1.66</v>
+      </c>
+      <c r="AB186">
+        <v>2.07</v>
+      </c>
+      <c r="AC186">
+        <v>2.53</v>
+      </c>
+      <c r="AD186">
+        <v>1.46</v>
+      </c>
+      <c r="AE186">
+        <v>1.18</v>
+      </c>
+      <c r="AF186">
+        <v>1.57</v>
+      </c>
+      <c r="AG186">
+        <v>2.3</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ186">
+        <v>1.49</v>
+      </c>
+      <c r="AK186">
         <v>1.4</v>
-      </c>
-      <c r="W186">
-        <v>1.07</v>
-      </c>
-      <c r="X186">
-        <v>1.03</v>
-      </c>
-      <c r="Y186">
-        <v>1.25</v>
-      </c>
-      <c r="Z186">
-        <v>3.28</v>
-      </c>
-      <c r="AA186">
-        <v>1.98</v>
-      </c>
-      <c r="AB186">
-        <v>1.88</v>
-      </c>
-      <c r="AC186">
-        <v>3</v>
-      </c>
-      <c r="AD186">
-        <v>1.32</v>
-      </c>
-      <c r="AE186">
-        <v>1.07</v>
-      </c>
-      <c r="AF186">
-        <v>1.82</v>
-      </c>
-      <c r="AG186">
-        <v>1.88</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ186">
-        <v>1.22</v>
-      </c>
-      <c r="AK186">
-        <v>2</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="O187">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="Q187">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R187">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="S187">
         <v>1.29</v>
       </c>
       <c r="T187">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U187">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V187">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W187">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z187">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AA187">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB187">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC187">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AD187">
         <v>1.46</v>
       </c>
       <c r="AE187">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF187">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG187">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AK187">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,65 +31116,65 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="O189">
-        <v>3.64</v>
+        <v>4.95</v>
       </c>
       <c r="P189">
-        <v>4.08</v>
+        <v>6.75</v>
       </c>
       <c r="Q189">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="R189">
+        <v>2.63</v>
+      </c>
+      <c r="S189">
+        <v>1.2</v>
+      </c>
+      <c r="T189">
+        <v>4.2</v>
+      </c>
+      <c r="U189">
+        <v>2</v>
+      </c>
+      <c r="V189">
+        <v>1.69</v>
+      </c>
+      <c r="W189">
+        <v>1.16</v>
+      </c>
+      <c r="X189">
+        <v>1.02</v>
+      </c>
+      <c r="Y189">
+        <v>1.08</v>
+      </c>
+      <c r="Z189">
+        <v>5.45</v>
+      </c>
+      <c r="AA189">
+        <v>1.41</v>
+      </c>
+      <c r="AB189">
+        <v>2.66</v>
+      </c>
+      <c r="AC189">
+        <v>1.98</v>
+      </c>
+      <c r="AD189">
+        <v>1.73</v>
+      </c>
+      <c r="AE189">
+        <v>1.31</v>
+      </c>
+      <c r="AF189">
+        <v>1.55</v>
+      </c>
+      <c r="AG189">
         <v>2.3</v>
       </c>
-      <c r="S189">
-        <v>1.25</v>
-      </c>
-      <c r="T189">
-        <v>3.12</v>
-      </c>
-      <c r="U189">
-        <v>2.45</v>
-      </c>
-      <c r="V189">
-        <v>1.47</v>
-      </c>
-      <c r="W189">
-        <v>1.07</v>
-      </c>
-      <c r="X189">
-        <v>1.03</v>
-      </c>
-      <c r="Y189">
-        <v>1.16</v>
-      </c>
-      <c r="Z189">
-        <v>3.7</v>
-      </c>
-      <c r="AA189">
-        <v>1.65</v>
-      </c>
-      <c r="AB189">
-        <v>2.14</v>
-      </c>
-      <c r="AC189">
-        <v>2.56</v>
-      </c>
-      <c r="AD189">
-        <v>1.4</v>
-      </c>
-      <c r="AE189">
-        <v>1.12</v>
-      </c>
-      <c r="AF189">
-        <v>1.63</v>
-      </c>
-      <c r="AG189">
-        <v>2.14</v>
-      </c>
       <c r="AH189" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK189">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,80 +31442,80 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="O191">
-        <v>4.95</v>
+        <v>3.58</v>
       </c>
       <c r="P191">
-        <v>6.75</v>
+        <v>4.31</v>
       </c>
       <c r="Q191">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="R191">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="S191">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T191">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="U191">
+        <v>2.75</v>
+      </c>
+      <c r="V191">
+        <v>1.4</v>
+      </c>
+      <c r="W191">
+        <v>1.07</v>
+      </c>
+      <c r="X191">
+        <v>1.03</v>
+      </c>
+      <c r="Y191">
+        <v>1.25</v>
+      </c>
+      <c r="Z191">
+        <v>3.28</v>
+      </c>
+      <c r="AA191">
+        <v>1.98</v>
+      </c>
+      <c r="AB191">
+        <v>1.88</v>
+      </c>
+      <c r="AC191">
+        <v>3</v>
+      </c>
+      <c r="AD191">
+        <v>1.32</v>
+      </c>
+      <c r="AE191">
+        <v>1.07</v>
+      </c>
+      <c r="AF191">
+        <v>1.82</v>
+      </c>
+      <c r="AG191">
+        <v>1.88</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ191">
+        <v>1.22</v>
+      </c>
+      <c r="AK191">
         <v>2</v>
-      </c>
-      <c r="V191">
-        <v>1.69</v>
-      </c>
-      <c r="W191">
-        <v>1.16</v>
-      </c>
-      <c r="X191">
-        <v>1.02</v>
-      </c>
-      <c r="Y191">
-        <v>1.08</v>
-      </c>
-      <c r="Z191">
-        <v>5.45</v>
-      </c>
-      <c r="AA191">
-        <v>1.41</v>
-      </c>
-      <c r="AB191">
-        <v>2.66</v>
-      </c>
-      <c r="AC191">
-        <v>1.98</v>
-      </c>
-      <c r="AD191">
-        <v>1.73</v>
-      </c>
-      <c r="AE191">
-        <v>1.31</v>
-      </c>
-      <c r="AF191">
-        <v>1.55</v>
-      </c>
-      <c r="AG191">
-        <v>2.3</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ191">
-        <v>1.1</v>
-      </c>
-      <c r="AK191">
-        <v>2.75</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="O192">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P192">
-        <v>3.35</v>
+        <v>4.08</v>
       </c>
       <c r="Q192">
+        <v>2.25</v>
+      </c>
+      <c r="R192">
         <v>2.3</v>
       </c>
-      <c r="R192">
-        <v>2.48</v>
-      </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U192">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="V192">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="W192">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X192">
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z192">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA192">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB192">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC192">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="AD192">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE192">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF192">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AG192">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK192">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="O194">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="P194">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="Q194">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="R194">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S194">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T194">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U194">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V194">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W194">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z194">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="AA194">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AB194">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC194">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="AD194">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE194">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF194">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG194">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK194">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="O195">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="P195">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="Q195">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="R195">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S195">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T195">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U195">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V195">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W195">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X195">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z195">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="AA195">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB195">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC195">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="AD195">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE195">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF195">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG195">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK195">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="O306">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="P306">
-        <v>23</v>
+        <v>3.6</v>
       </c>
       <c r="Q306">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="R306">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="S306">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="T306">
-        <v>5</v>
+        <v>3.16</v>
       </c>
       <c r="U306">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="V306">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="W306">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="X306">
         <v>1.01</v>
       </c>
       <c r="Y306">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="Z306">
-        <v>9</v>
+        <v>3.84</v>
       </c>
       <c r="AA306">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AB306">
-        <v>4.15</v>
+        <v>2</v>
       </c>
       <c r="AC306">
-        <v>1.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD306">
-        <v>2.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE306">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="AF306">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AG306">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AK306">
-        <v>10</v>
+        <v>1.87</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O307">
+        <v>3.75</v>
+      </c>
+      <c r="P307">
+        <v>4.2</v>
+      </c>
+      <c r="Q307">
+        <v>2.06</v>
+      </c>
+      <c r="R307">
+        <v>2.38</v>
+      </c>
+      <c r="S307">
+        <v>1.3</v>
+      </c>
+      <c r="T307">
         <v>3.5</v>
       </c>
-      <c r="P307">
-        <v>3.6</v>
-      </c>
-      <c r="Q307">
-        <v>2.5</v>
-      </c>
-      <c r="R307">
-        <v>2.26</v>
-      </c>
-      <c r="S307">
-        <v>1.34</v>
-      </c>
-      <c r="T307">
-        <v>3.16</v>
-      </c>
       <c r="U307">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V307">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W307">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X307">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z307">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AA307">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AB307">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC307">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AD307">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE307">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF307">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG307">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK307">
-        <v>1.87</v>
+        <v>2.31</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="O308">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P308">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q308">
-        <v>2.06</v>
+        <v>3.72</v>
       </c>
       <c r="R308">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S308">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T308">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U308">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V308">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W308">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X308">
         <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z308">
-        <v>4.55</v>
+        <v>3.56</v>
       </c>
       <c r="AA308">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB308">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC308">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="AD308">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE308">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF308">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG308">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK308">
-        <v>2.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.63</v>
+        <v>1.07</v>
       </c>
       <c r="O309">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="P309">
-        <v>2.5</v>
+        <v>23</v>
       </c>
       <c r="Q309">
-        <v>3.72</v>
+        <v>1.3</v>
       </c>
       <c r="R309">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="S309">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="T309">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="U309">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="V309">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="W309">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="X309">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="Z309">
-        <v>3.56</v>
+        <v>9</v>
       </c>
       <c r="AA309">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AB309">
-        <v>2</v>
+        <v>4.15</v>
       </c>
       <c r="AC309">
-        <v>3.08</v>
+        <v>1.59</v>
       </c>
       <c r="AD309">
-        <v>1.31</v>
+        <v>2.39</v>
       </c>
       <c r="AE309">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="AF309">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AG309">
-        <v>2.11</v>
+        <v>1.69</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AK309">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="O338">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="P338">
-        <v>3.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q338">
+        <v>4.27</v>
+      </c>
+      <c r="R338">
+        <v>2.25</v>
+      </c>
+      <c r="S338">
+        <v>1.33</v>
+      </c>
+      <c r="T338">
+        <v>2.94</v>
+      </c>
+      <c r="U338">
         <v>2.6</v>
       </c>
-      <c r="R338">
-        <v>2.3</v>
-      </c>
-      <c r="S338">
-        <v>1.24</v>
-      </c>
-      <c r="T338">
-        <v>3.25</v>
-      </c>
-      <c r="U338">
-        <v>2.38</v>
-      </c>
       <c r="V338">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W338">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X338">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y338">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z338">
-        <v>4.35</v>
+        <v>3.59</v>
       </c>
       <c r="AA338">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AB338">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC338">
-        <v>2.38</v>
+        <v>3.07</v>
       </c>
       <c r="AD338">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE338">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF338">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG338">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK338">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,80 +55566,80 @@
         </is>
       </c>
       <c r="N339">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="O339">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P339">
-        <v>1.92</v>
+        <v>3.09</v>
       </c>
       <c r="Q339">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="R339">
+        <v>2.3</v>
+      </c>
+      <c r="S339">
+        <v>1.24</v>
+      </c>
+      <c r="T339">
+        <v>3.25</v>
+      </c>
+      <c r="U339">
+        <v>2.38</v>
+      </c>
+      <c r="V339">
+        <v>1.53</v>
+      </c>
+      <c r="W339">
+        <v>1.12</v>
+      </c>
+      <c r="X339">
+        <v>1.02</v>
+      </c>
+      <c r="Y339">
+        <v>1.14</v>
+      </c>
+      <c r="Z339">
+        <v>4.35</v>
+      </c>
+      <c r="AA339">
+        <v>1.61</v>
+      </c>
+      <c r="AB339">
         <v>2.25</v>
       </c>
-      <c r="S339">
-        <v>1.33</v>
-      </c>
-      <c r="T339">
-        <v>2.94</v>
-      </c>
-      <c r="U339">
-        <v>2.6</v>
-      </c>
-      <c r="V339">
-        <v>1.43</v>
-      </c>
-      <c r="W339">
-        <v>1.1</v>
-      </c>
-      <c r="X339">
-        <v>1.01</v>
-      </c>
-      <c r="Y339">
+      <c r="AC339">
+        <v>2.38</v>
+      </c>
+      <c r="AD339">
+        <v>1.46</v>
+      </c>
+      <c r="AE339">
+        <v>1.15</v>
+      </c>
+      <c r="AF339">
+        <v>1.5</v>
+      </c>
+      <c r="AG339">
+        <v>2.38</v>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ339">
         <v>1.27</v>
       </c>
-      <c r="Z339">
-        <v>3.59</v>
-      </c>
-      <c r="AA339">
-        <v>1.87</v>
-      </c>
-      <c r="AB339">
-        <v>2.07</v>
-      </c>
-      <c r="AC339">
-        <v>3.07</v>
-      </c>
-      <c r="AD339">
-        <v>1.34</v>
-      </c>
-      <c r="AE339">
-        <v>1.1</v>
-      </c>
-      <c r="AF339">
-        <v>1.65</v>
-      </c>
-      <c r="AG339">
-        <v>2.08</v>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ339">
-        <v>1.25</v>
-      </c>
       <c r="AK339">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O353">
-        <v>4.69</v>
+        <v>4.39</v>
       </c>
       <c r="P353">
-        <v>5.35</v>
+        <v>4.23</v>
       </c>
       <c r="Q353">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R353">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S353">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T353">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U353">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V353">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W353">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X353">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y353">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z353">
-        <v>3.86</v>
+        <v>4.65</v>
       </c>
       <c r="AA353">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AB353">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AC353">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD353">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE353">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF353">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AG353">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>1.17</v>
       </c>
       <c r="AK353">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
+        <v>1.54</v>
+      </c>
+      <c r="O354">
+        <v>4.69</v>
+      </c>
+      <c r="P354">
+        <v>5.35</v>
+      </c>
+      <c r="Q354">
+        <v>2.07</v>
+      </c>
+      <c r="R354">
+        <v>2.38</v>
+      </c>
+      <c r="S354">
+        <v>1.25</v>
+      </c>
+      <c r="T354">
+        <v>3.5</v>
+      </c>
+      <c r="U354">
+        <v>2.27</v>
+      </c>
+      <c r="V354">
+        <v>1.51</v>
+      </c>
+      <c r="W354">
+        <v>1.11</v>
+      </c>
+      <c r="X354">
+        <v>1.02</v>
+      </c>
+      <c r="Y354">
+        <v>1.18</v>
+      </c>
+      <c r="Z354">
+        <v>3.86</v>
+      </c>
+      <c r="AA354">
+        <v>1.66</v>
+      </c>
+      <c r="AB354">
+        <v>2.02</v>
+      </c>
+      <c r="AC354">
+        <v>2.62</v>
+      </c>
+      <c r="AD354">
+        <v>1.38</v>
+      </c>
+      <c r="AE354">
+        <v>1.12</v>
+      </c>
+      <c r="AF354">
         <v>1.71</v>
       </c>
-      <c r="O354">
-        <v>4.39</v>
-      </c>
-      <c r="P354">
-        <v>4.23</v>
-      </c>
-      <c r="Q354">
-        <v>2.1</v>
-      </c>
-      <c r="R354">
-        <v>2.43</v>
-      </c>
-      <c r="S354">
-        <v>1.19</v>
-      </c>
-      <c r="T354">
-        <v>3.7</v>
-      </c>
-      <c r="U354">
-        <v>2.2</v>
-      </c>
-      <c r="V354">
-        <v>1.62</v>
-      </c>
-      <c r="W354">
-        <v>1.15</v>
-      </c>
-      <c r="X354">
-        <v>1.01</v>
-      </c>
-      <c r="Y354">
-        <v>1.16</v>
-      </c>
-      <c r="Z354">
-        <v>4.65</v>
-      </c>
-      <c r="AA354">
-        <v>1.48</v>
-      </c>
-      <c r="AB354">
-        <v>2.35</v>
-      </c>
-      <c r="AC354">
-        <v>2.3</v>
-      </c>
-      <c r="AD354">
-        <v>1.59</v>
-      </c>
-      <c r="AE354">
-        <v>1.19</v>
-      </c>
-      <c r="AF354">
-        <v>1.52</v>
-      </c>
       <c r="AG354">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>1.17</v>
       </c>
       <c r="AK354">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,80 +58337,80 @@
         </is>
       </c>
       <c r="N356">
-        <v>1.87</v>
+        <v>2.54</v>
       </c>
       <c r="O356">
-        <v>4.14</v>
+        <v>3.72</v>
       </c>
       <c r="P356">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="Q356">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R356">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S356">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T356">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U356">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="V356">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W356">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X356">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y356">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z356">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA356">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB356">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC356">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD356">
+        <v>1.27</v>
+      </c>
+      <c r="AE356">
+        <v>1.06</v>
+      </c>
+      <c r="AF356">
+        <v>1.67</v>
+      </c>
+      <c r="AG356">
+        <v>2.02</v>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ356">
+        <v>1.22</v>
+      </c>
+      <c r="AK356">
         <v>1.44</v>
-      </c>
-      <c r="AE356">
-        <v>1.14</v>
-      </c>
-      <c r="AF356">
-        <v>1.57</v>
-      </c>
-      <c r="AG356">
-        <v>2.25</v>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI356" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ356">
-        <v>1.25</v>
-      </c>
-      <c r="AK356">
-        <v>1.82</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,80 +58500,80 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="O357">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="P357">
-        <v>2.56</v>
+        <v>3.92</v>
       </c>
       <c r="Q357">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R357">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S357">
+        <v>1.36</v>
+      </c>
+      <c r="T357">
+        <v>2.72</v>
+      </c>
+      <c r="U357">
+        <v>2.85</v>
+      </c>
+      <c r="V357">
+        <v>1.33</v>
+      </c>
+      <c r="W357">
+        <v>1.03</v>
+      </c>
+      <c r="X357">
+        <v>1.02</v>
+      </c>
+      <c r="Y357">
         <v>1.28</v>
       </c>
-      <c r="T357">
+      <c r="Z357">
         <v>3.08</v>
       </c>
-      <c r="U357">
-        <v>2.75</v>
-      </c>
-      <c r="V357">
-        <v>1.4</v>
-      </c>
-      <c r="W357">
-        <v>1.06</v>
-      </c>
-      <c r="X357">
-        <v>1</v>
-      </c>
-      <c r="Y357">
-        <v>1.23</v>
-      </c>
-      <c r="Z357">
-        <v>3.42</v>
-      </c>
       <c r="AA357">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB357">
+        <v>1.78</v>
+      </c>
+      <c r="AC357">
+        <v>3.5</v>
+      </c>
+      <c r="AD357">
+        <v>1.22</v>
+      </c>
+      <c r="AE357">
+        <v>1.04</v>
+      </c>
+      <c r="AF357">
+        <v>1.8</v>
+      </c>
+      <c r="AG357">
+        <v>1.91</v>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ357">
+        <v>1.29</v>
+      </c>
+      <c r="AK357">
         <v>1.85</v>
-      </c>
-      <c r="AC357">
-        <v>3.14</v>
-      </c>
-      <c r="AD357">
-        <v>1.27</v>
-      </c>
-      <c r="AE357">
-        <v>1.06</v>
-      </c>
-      <c r="AF357">
-        <v>1.67</v>
-      </c>
-      <c r="AG357">
-        <v>2.02</v>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI357" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ357">
-        <v>1.22</v>
-      </c>
-      <c r="AK357">
-        <v>1.44</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,64 +58663,64 @@
         </is>
       </c>
       <c r="N358">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O358">
-        <v>3.73</v>
+        <v>4.14</v>
       </c>
       <c r="P358">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="Q358">
+        <v>2.25</v>
+      </c>
+      <c r="R358">
         <v>2.4</v>
       </c>
-      <c r="R358">
-        <v>2.15</v>
-      </c>
       <c r="S358">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T358">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="U358">
-        <v>2.85</v>
+        <v>2.27</v>
       </c>
       <c r="V358">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W358">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X358">
         <v>1.02</v>
       </c>
       <c r="Y358">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z358">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA358">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AB358">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AC358">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD358">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE358">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF358">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG358">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK358">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL358">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -3083,7 +3083,7 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
         <v>1.7</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
         <v>3.2</v>
@@ -3433,7 +3433,7 @@
         <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3448,7 +3448,7 @@
         <v>1.78</v>
       </c>
       <c r="AB19">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
         <v>2.85</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
         <v>1.62</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O60">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P60">
-        <v>5.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="R60">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T60">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U60">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W60">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA60">
+        <v>1.93</v>
+      </c>
+      <c r="AB60">
+        <v>1.93</v>
+      </c>
+      <c r="AC60">
+        <v>3.16</v>
+      </c>
+      <c r="AD60">
+        <v>1.35</v>
+      </c>
+      <c r="AE60">
+        <v>1.06</v>
+      </c>
+      <c r="AF60">
         <v>1.66</v>
       </c>
-      <c r="AB60">
-        <v>2.15</v>
-      </c>
-      <c r="AC60">
-        <v>2.5</v>
-      </c>
-      <c r="AD60">
-        <v>1.42</v>
-      </c>
-      <c r="AE60">
-        <v>1.14</v>
-      </c>
-      <c r="AF60">
-        <v>1.74</v>
-      </c>
       <c r="AG60">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="O61">
+        <v>4.3</v>
+      </c>
+      <c r="P61">
+        <v>5.95</v>
+      </c>
+      <c r="Q61">
+        <v>2</v>
+      </c>
+      <c r="R61">
+        <v>2.38</v>
+      </c>
+      <c r="S61">
+        <v>1.26</v>
+      </c>
+      <c r="T61">
         <v>3.3</v>
       </c>
-      <c r="P61">
-        <v>2.4</v>
-      </c>
-      <c r="Q61">
-        <v>3.1</v>
-      </c>
-      <c r="R61">
-        <v>2.1</v>
-      </c>
-      <c r="S61">
-        <v>1.31</v>
-      </c>
-      <c r="T61">
-        <v>3.08</v>
-      </c>
       <c r="U61">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="V61">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA61">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB61">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC61">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="AD61">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AG61">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O68">
-        <v>5.05</v>
+        <v>4.62</v>
       </c>
       <c r="P68">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q68">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="R68">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="S68">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="U68">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V68">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="W68">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>6.01</v>
+        <v>4.3</v>
       </c>
       <c r="AA68">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB68">
-        <v>2.83</v>
+        <v>2.18</v>
       </c>
       <c r="AC68">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AD68">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AE68">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG68">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O69">
-        <v>4.62</v>
+        <v>3.75</v>
       </c>
       <c r="P69">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q69">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S69">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T69">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="U69">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V69">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
         <v>1.12</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
+        <v>1.18</v>
+      </c>
+      <c r="Z69">
+        <v>4.45</v>
+      </c>
+      <c r="AA69">
+        <v>1.61</v>
+      </c>
+      <c r="AB69">
+        <v>2.19</v>
+      </c>
+      <c r="AC69">
+        <v>2.41</v>
+      </c>
+      <c r="AD69">
+        <v>1.48</v>
+      </c>
+      <c r="AE69">
         <v>1.15</v>
       </c>
-      <c r="Z69">
-        <v>4.3</v>
-      </c>
-      <c r="AA69">
-        <v>1.58</v>
-      </c>
-      <c r="AB69">
-        <v>2.18</v>
-      </c>
-      <c r="AC69">
-        <v>2.43</v>
-      </c>
-      <c r="AD69">
-        <v>1.44</v>
-      </c>
-      <c r="AE69">
-        <v>1.14</v>
-      </c>
       <c r="AF69">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>5.05</v>
       </c>
       <c r="P70">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q70">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="R70">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U70">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="V70">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
         <v>1.11</v>
       </c>
       <c r="Z70">
-        <v>4.85</v>
+        <v>6.01</v>
       </c>
       <c r="AA70">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB70">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AC70">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="AD70">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AE70">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF70">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="O71">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="Q71">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S71">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="AA71">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AB71">
-        <v>2.19</v>
+        <v>2.66</v>
       </c>
       <c r="AC71">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AD71">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AG71">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O72">
+        <v>3.6</v>
+      </c>
+      <c r="P72">
+        <v>2.7</v>
+      </c>
+      <c r="Q72">
+        <v>2.62</v>
+      </c>
+      <c r="R72">
+        <v>2.33</v>
+      </c>
+      <c r="S72">
+        <v>1.22</v>
+      </c>
+      <c r="T72">
         <v>3.7</v>
       </c>
-      <c r="P72">
-        <v>2.75</v>
-      </c>
-      <c r="Q72">
-        <v>2.5</v>
-      </c>
-      <c r="R72">
-        <v>2.42</v>
-      </c>
-      <c r="S72">
-        <v>1.18</v>
-      </c>
-      <c r="T72">
-        <v>3.9</v>
-      </c>
       <c r="U72">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="V72">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="W72">
         <v>1.14</v>
@@ -12078,31 +12078,31 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>5.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA72">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="AC72">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AD72">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AE72">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF72">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AG72">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="O145">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P145">
-        <v>2.79</v>
+        <v>4.39</v>
       </c>
       <c r="Q145">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="R145">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T145">
-        <v>3.14</v>
+        <v>2.64</v>
       </c>
       <c r="U145">
-        <v>2.61</v>
+        <v>2.94</v>
       </c>
       <c r="V145">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA145">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB145">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC145">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD145">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF145">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG145">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK145">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="O146">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P146">
-        <v>4.39</v>
+        <v>2.79</v>
       </c>
       <c r="Q146">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="R146">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S146">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T146">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="U146">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="V146">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W146">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z146">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA146">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB146">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC146">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD146">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE146">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF146">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG146">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK146">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="O154">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="P154">
-        <v>3.03</v>
+        <v>3.24</v>
       </c>
       <c r="Q154">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="R154">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="S154">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T154">
+        <v>3.17</v>
+      </c>
+      <c r="U154">
         <v>2.67</v>
       </c>
-      <c r="U154">
-        <v>2.92</v>
-      </c>
       <c r="V154">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W154">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X154">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y154">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z154">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AA154">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB154">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC154">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="AD154">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE154">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF154">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG154">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK154">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.07</v>
+        <v>3.9</v>
       </c>
       <c r="O155">
-        <v>3.89</v>
+        <v>4.17</v>
       </c>
       <c r="P155">
-        <v>3.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q155">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="R155">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S155">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T155">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="U155">
-        <v>2.67</v>
+        <v>2.32</v>
       </c>
       <c r="V155">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W155">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z155">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA155">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AB155">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AC155">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AD155">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE155">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG155">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AK155">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,61 +25737,61 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="O156">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="P156">
-        <v>4.03</v>
+        <v>3.03</v>
       </c>
       <c r="Q156">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="R156">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="S156">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="U156">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W156">
+        <v>1.04</v>
+      </c>
+      <c r="X156">
+        <v>1.02</v>
+      </c>
+      <c r="Y156">
+        <v>1.31</v>
+      </c>
+      <c r="Z156">
+        <v>2.92</v>
+      </c>
+      <c r="AA156">
+        <v>2.05</v>
+      </c>
+      <c r="AB156">
+        <v>1.71</v>
+      </c>
+      <c r="AC156">
+        <v>3.5</v>
+      </c>
+      <c r="AD156">
+        <v>1.22</v>
+      </c>
+      <c r="AE156">
         <v>1.05</v>
       </c>
-      <c r="X156">
-        <v>1.03</v>
-      </c>
-      <c r="Y156">
-        <v>1.26</v>
-      </c>
-      <c r="Z156">
-        <v>3.2</v>
-      </c>
-      <c r="AA156">
-        <v>1.92</v>
-      </c>
-      <c r="AB156">
-        <v>1.92</v>
-      </c>
-      <c r="AC156">
-        <v>3.14</v>
-      </c>
-      <c r="AD156">
-        <v>1.29</v>
-      </c>
-      <c r="AE156">
-        <v>1.06</v>
-      </c>
       <c r="AF156">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG156">
         <v>1.9</v>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.49</v>
+        <v>1.85</v>
       </c>
       <c r="O157">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="P157">
-        <v>2.57</v>
+        <v>4.03</v>
       </c>
       <c r="Q157">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R157">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S157">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T157">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U157">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="V157">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W157">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z157">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="AA157">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB157">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC157">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AD157">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE157">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF157">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG157">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.9</v>
+        <v>2.49</v>
       </c>
       <c r="O158">
-        <v>4.17</v>
+        <v>3.83</v>
       </c>
       <c r="P158">
-        <v>1.81</v>
+        <v>2.57</v>
       </c>
       <c r="Q158">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S158">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T158">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U158">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V158">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z158">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="AA158">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB158">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AC158">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AD158">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE158">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF158">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK158">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O172">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P172">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="Q172">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R172">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S172">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T172">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="U172">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V172">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W172">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y172">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z172">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
       <c r="AA172">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB172">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC172">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="AD172">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE172">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF172">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AG172">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK172">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="O173">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P173">
-        <v>2.56</v>
+        <v>3.27</v>
       </c>
       <c r="Q173">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="R173">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T173">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="U173">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V173">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>4.45</v>
       </c>
       <c r="AA173">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB173">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC173">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD173">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE173">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF173">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG173">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK173">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="O174">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P174">
-        <v>2.71</v>
+        <v>3.93</v>
       </c>
       <c r="Q174">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="R174">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S174">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T174">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="U174">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V174">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W174">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X174">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z174">
-        <v>4.25</v>
+        <v>3.43</v>
       </c>
       <c r="AA174">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB174">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC174">
-        <v>2.38</v>
+        <v>3.42</v>
       </c>
       <c r="AD174">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE174">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF174">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="AG174">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK174">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O175">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="P175">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q175">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="R175">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T175">
-        <v>3.24</v>
+        <v>2.78</v>
       </c>
       <c r="U175">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V175">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W175">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z175">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB175">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC175">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AD175">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE175">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF175">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AG175">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK175">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="O177">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
-        <v>3.93</v>
+        <v>2.56</v>
       </c>
       <c r="Q177">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="R177">
         <v>2.1</v>
       </c>
       <c r="S177">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T177">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U177">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V177">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z177">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA177">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB177">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC177">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AD177">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE177">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF177">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AG177">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK177">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,28 +30627,28 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="O186">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="P186">
-        <v>2.56</v>
+        <v>3.31</v>
       </c>
       <c r="Q186">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="R186">
         <v>2.18</v>
       </c>
       <c r="S186">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T186">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U186">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V186">
         <v>1.5</v>
@@ -30657,34 +30657,34 @@
         <v>1.09</v>
       </c>
       <c r="X186">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y186">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z186">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA186">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB186">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AC186">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AD186">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE186">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG186">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P187">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="Q187">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R187">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="S187">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U187">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="V187">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W187">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X187">
         <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z187">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA187">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB187">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC187">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="AD187">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE187">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF187">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AG187">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,58 +30953,58 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O188">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="Q188">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="R188">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="S188">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U188">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="V188">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W188">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
         <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z188">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA188">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB188">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC188">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AD188">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE188">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF188">
         <v>1.56</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,80 +31279,80 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.77</v>
+        <v>1.61</v>
       </c>
       <c r="O190">
-        <v>3.48</v>
+        <v>4.25</v>
       </c>
       <c r="P190">
-        <v>2.37</v>
+        <v>4.69</v>
       </c>
       <c r="Q190">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="R190">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="S190">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T190">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="U190">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="V190">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="W190">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X190">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z190">
-        <v>3.88</v>
+        <v>5.45</v>
       </c>
       <c r="AA190">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="AB190">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="AC190">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="AD190">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AE190">
+        <v>1.25</v>
+      </c>
+      <c r="AF190">
+        <v>1.47</v>
+      </c>
+      <c r="AG190">
+        <v>2.63</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
         <v>1.13</v>
       </c>
-      <c r="AF190">
-        <v>1.55</v>
-      </c>
-      <c r="AG190">
+      <c r="AK190">
         <v>2.3</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ190">
-        <v>1.23</v>
-      </c>
-      <c r="AK190">
-        <v>1.44</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.79</v>
+        <v>2.77</v>
       </c>
       <c r="O191">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P191">
-        <v>4.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q191">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="R191">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="S191">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T191">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="U191">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="V191">
+        <v>1.51</v>
+      </c>
+      <c r="W191">
+        <v>1.12</v>
+      </c>
+      <c r="X191">
+        <v>1</v>
+      </c>
+      <c r="Y191">
+        <v>1.18</v>
+      </c>
+      <c r="Z191">
+        <v>3.88</v>
+      </c>
+      <c r="AA191">
+        <v>1.69</v>
+      </c>
+      <c r="AB191">
+        <v>2.09</v>
+      </c>
+      <c r="AC191">
+        <v>2.56</v>
+      </c>
+      <c r="AD191">
         <v>1.4</v>
       </c>
-      <c r="W191">
-        <v>1.07</v>
-      </c>
-      <c r="X191">
-        <v>1.03</v>
-      </c>
-      <c r="Y191">
-        <v>1.25</v>
-      </c>
-      <c r="Z191">
-        <v>3.28</v>
-      </c>
-      <c r="AA191">
-        <v>1.98</v>
-      </c>
-      <c r="AB191">
-        <v>1.88</v>
-      </c>
-      <c r="AC191">
-        <v>3</v>
-      </c>
-      <c r="AD191">
-        <v>1.32</v>
-      </c>
       <c r="AE191">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF191">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AG191">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK191">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.61</v>
+        <v>2.52</v>
       </c>
       <c r="O193">
-        <v>4.25</v>
+        <v>3.48</v>
       </c>
       <c r="P193">
-        <v>4.69</v>
+        <v>2.56</v>
       </c>
       <c r="Q193">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="R193">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="S193">
+        <v>1.29</v>
+      </c>
+      <c r="T193">
+        <v>3.3</v>
+      </c>
+      <c r="U193">
+        <v>2.32</v>
+      </c>
+      <c r="V193">
+        <v>1.5</v>
+      </c>
+      <c r="W193">
+        <v>1.09</v>
+      </c>
+      <c r="X193">
+        <v>1.01</v>
+      </c>
+      <c r="Y193">
+        <v>1.2</v>
+      </c>
+      <c r="Z193">
+        <v>4.15</v>
+      </c>
+      <c r="AA193">
+        <v>1.66</v>
+      </c>
+      <c r="AB193">
+        <v>2.07</v>
+      </c>
+      <c r="AC193">
+        <v>2.53</v>
+      </c>
+      <c r="AD193">
+        <v>1.46</v>
+      </c>
+      <c r="AE193">
         <v>1.18</v>
       </c>
-      <c r="T193">
-        <v>3.92</v>
-      </c>
-      <c r="U193">
-        <v>2.1</v>
-      </c>
-      <c r="V193">
-        <v>1.69</v>
-      </c>
-      <c r="W193">
-        <v>1.17</v>
-      </c>
-      <c r="X193">
-        <v>1.02</v>
-      </c>
-      <c r="Y193">
-        <v>1.08</v>
-      </c>
-      <c r="Z193">
-        <v>5.45</v>
-      </c>
-      <c r="AA193">
-        <v>1.39</v>
-      </c>
-      <c r="AB193">
-        <v>2.75</v>
-      </c>
-      <c r="AC193">
-        <v>2.13</v>
-      </c>
-      <c r="AD193">
-        <v>1.71</v>
-      </c>
-      <c r="AE193">
-        <v>1.25</v>
-      </c>
       <c r="AF193">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG193">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="AK193">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48596,10 +48596,10 @@
         <v>0</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC296">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="Q51">
-        <v>2.05</v>
+        <v>3.12</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U51">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF51">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="Q52">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="R52">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AD52">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="O128">
-        <v>8</v>
+        <v>4.66</v>
       </c>
       <c r="P128">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="Q128">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="R128">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="S128">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T128">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="U128">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="V128">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="W128">
+        <v>1.2</v>
+      </c>
+      <c r="X128">
+        <v>1.01</v>
+      </c>
+      <c r="Y128">
+        <v>1.05</v>
+      </c>
+      <c r="Z128">
+        <v>7</v>
+      </c>
+      <c r="AA128">
+        <v>1.39</v>
+      </c>
+      <c r="AB128">
+        <v>3.05</v>
+      </c>
+      <c r="AC128">
+        <v>2.02</v>
+      </c>
+      <c r="AD128">
+        <v>1.84</v>
+      </c>
+      <c r="AE128">
+        <v>1.36</v>
+      </c>
+      <c r="AF128">
         <v>1.44</v>
       </c>
-      <c r="X128">
-        <v>1</v>
-      </c>
-      <c r="Y128">
-        <v>1.04</v>
-      </c>
-      <c r="Z128">
-        <v>15</v>
-      </c>
-      <c r="AA128">
-        <v>1.14</v>
-      </c>
-      <c r="AB128">
-        <v>5.75</v>
-      </c>
-      <c r="AC128">
-        <v>1.38</v>
-      </c>
-      <c r="AD128">
-        <v>2.8</v>
-      </c>
-      <c r="AE128">
-        <v>1.87</v>
-      </c>
-      <c r="AF128">
-        <v>1.4</v>
-      </c>
       <c r="AG128">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.07</v>
+        <v>2.27</v>
       </c>
       <c r="AK128">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O129">
-        <v>4.66</v>
+        <v>3.8</v>
       </c>
       <c r="P129">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="Q129">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="R129">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U129">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AA129">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AD129">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
+        <v>1.27</v>
+      </c>
+      <c r="AF129">
         <v>1.36</v>
       </c>
-      <c r="AF129">
-        <v>1.44</v>
-      </c>
       <c r="AG129">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>2.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK129">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.9</v>
+        <v>9</v>
       </c>
       <c r="O130">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="P130">
-        <v>2.16</v>
+        <v>1.22</v>
       </c>
       <c r="Q130">
-        <v>3.32</v>
+        <v>7.5</v>
       </c>
       <c r="R130">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U130">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="V130">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="W130">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y130">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z130">
-        <v>5.45</v>
+        <v>15</v>
       </c>
       <c r="AA130">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AB130">
-        <v>2.64</v>
+        <v>5.75</v>
       </c>
       <c r="AC130">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="AD130">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="AE130">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AF130">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG130">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
+        <v>3.8</v>
+      </c>
+      <c r="O154">
+        <v>3.75</v>
+      </c>
+      <c r="P154">
         <v>1.85</v>
       </c>
-      <c r="O154">
-        <v>3.5</v>
-      </c>
-      <c r="P154">
+      <c r="Q154">
         <v>4.2</v>
       </c>
-      <c r="Q154">
-        <v>2.3</v>
-      </c>
       <c r="R154">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="S154">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="V154">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z154">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA154">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AB154">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="AC154">
-        <v>3.14</v>
+        <v>2.72</v>
       </c>
       <c r="AD154">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG154">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK154">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="O155">
         <v>3.5</v>
       </c>
       <c r="P155">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q155">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="R155">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S155">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T155">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U155">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V155">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z155">
-        <v>3.74</v>
+        <v>3.51</v>
       </c>
       <c r="AA155">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB155">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC155">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AD155">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE155">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG155">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK155">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
+        <v>3.1</v>
+      </c>
+      <c r="Q156">
+        <v>2.69</v>
+      </c>
+      <c r="R156">
+        <v>1.98</v>
+      </c>
+      <c r="S156">
+        <v>1.45</v>
+      </c>
+      <c r="T156">
+        <v>2.5</v>
+      </c>
+      <c r="U156">
+        <v>3</v>
+      </c>
+      <c r="V156">
+        <v>1.32</v>
+      </c>
+      <c r="W156">
+        <v>1.04</v>
+      </c>
+      <c r="X156">
+        <v>1.04</v>
+      </c>
+      <c r="Y156">
+        <v>1.34</v>
+      </c>
+      <c r="Z156">
+        <v>2.78</v>
+      </c>
+      <c r="AA156">
+        <v>2.22</v>
+      </c>
+      <c r="AB156">
         <v>1.7</v>
       </c>
-      <c r="Q156">
-        <v>3.72</v>
-      </c>
-      <c r="R156">
-        <v>2.27</v>
-      </c>
-      <c r="S156">
-        <v>1.25</v>
-      </c>
-      <c r="T156">
-        <v>3.5</v>
-      </c>
-      <c r="U156">
-        <v>2.27</v>
-      </c>
-      <c r="V156">
-        <v>1.57</v>
-      </c>
-      <c r="W156">
-        <v>1.14</v>
-      </c>
-      <c r="X156">
-        <v>1.01</v>
-      </c>
-      <c r="Y156">
-        <v>1.14</v>
-      </c>
-      <c r="Z156">
-        <v>4.35</v>
-      </c>
-      <c r="AA156">
-        <v>1.57</v>
-      </c>
-      <c r="AB156">
-        <v>2.29</v>
-      </c>
       <c r="AC156">
-        <v>2.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD156">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AE156">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF156">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
+        <v>1.85</v>
+      </c>
+      <c r="O157">
+        <v>3.5</v>
+      </c>
+      <c r="P157">
+        <v>4.2</v>
+      </c>
+      <c r="Q157">
         <v>2.3</v>
       </c>
-      <c r="O157">
-        <v>3.3</v>
-      </c>
-      <c r="P157">
-        <v>3.1</v>
-      </c>
-      <c r="Q157">
-        <v>2.69</v>
-      </c>
       <c r="R157">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S157">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V157">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W157">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X157">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z157">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AA157">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AB157">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC157">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AD157">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE157">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG157">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="O158">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q158">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S158">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U158">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V158">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z158">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA158">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB158">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC158">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="AD158">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE158">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF158">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="O159">
+        <v>4.2</v>
+      </c>
+      <c r="P159">
+        <v>1.7</v>
+      </c>
+      <c r="Q159">
+        <v>3.72</v>
+      </c>
+      <c r="R159">
+        <v>2.27</v>
+      </c>
+      <c r="S159">
+        <v>1.25</v>
+      </c>
+      <c r="T159">
         <v>3.5</v>
       </c>
-      <c r="P159">
-        <v>3.6</v>
-      </c>
-      <c r="Q159">
-        <v>2.55</v>
-      </c>
-      <c r="R159">
-        <v>2.25</v>
-      </c>
-      <c r="S159">
-        <v>1.34</v>
-      </c>
-      <c r="T159">
-        <v>2.7</v>
-      </c>
       <c r="U159">
-        <v>2.67</v>
+        <v>2.27</v>
       </c>
       <c r="V159">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z159">
-        <v>3.51</v>
+        <v>4.35</v>
       </c>
       <c r="AA159">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AB159">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="AC159">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="AD159">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF159">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG159">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK159">
-        <v>1.74</v>
+        <v>1.14</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O173">
+        <v>3.35</v>
+      </c>
+      <c r="P173">
+        <v>2.3</v>
+      </c>
+      <c r="Q173">
         <v>3.3</v>
       </c>
-      <c r="P173">
-        <v>2.6</v>
-      </c>
-      <c r="Q173">
-        <v>3.34</v>
-      </c>
       <c r="R173">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S173">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T173">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="U173">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V173">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z173">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA173">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB173">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC173">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD173">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE173">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF173">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG173">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="O175">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q175">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="R175">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S175">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T175">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U175">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V175">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z175">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB175">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC175">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD175">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE175">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF175">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG175">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
+        <v>2.65</v>
+      </c>
+      <c r="O176">
+        <v>3.3</v>
+      </c>
+      <c r="P176">
+        <v>2.6</v>
+      </c>
+      <c r="Q176">
+        <v>3.34</v>
+      </c>
+      <c r="R176">
         <v>2.05</v>
       </c>
-      <c r="O176">
-        <v>3.4</v>
-      </c>
-      <c r="P176">
-        <v>3.5</v>
-      </c>
-      <c r="Q176">
-        <v>2.6</v>
-      </c>
-      <c r="R176">
-        <v>2.12</v>
-      </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T176">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="U176">
         <v>2.7</v>
       </c>
       <c r="V176">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W176">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z176">
+        <v>3.04</v>
+      </c>
+      <c r="AA176">
+        <v>1.99</v>
+      </c>
+      <c r="AB176">
+        <v>1.8</v>
+      </c>
+      <c r="AC176">
         <v>3.34</v>
       </c>
-      <c r="AA176">
-        <v>2</v>
-      </c>
-      <c r="AB176">
-        <v>1.75</v>
-      </c>
-      <c r="AC176">
-        <v>3.05</v>
-      </c>
       <c r="AD176">
+        <v>1.24</v>
+      </c>
+      <c r="AE176">
+        <v>1.1</v>
+      </c>
+      <c r="AF176">
+        <v>1.76</v>
+      </c>
+      <c r="AG176">
+        <v>1.93</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
         <v>1.28</v>
       </c>
-      <c r="AE176">
-        <v>1.11</v>
-      </c>
-      <c r="AF176">
-        <v>1.75</v>
-      </c>
-      <c r="AG176">
-        <v>2</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.25</v>
-      </c>
       <c r="AK176">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,80 +30790,80 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="O187">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P187">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q187">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R187">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S187">
+        <v>1.25</v>
+      </c>
+      <c r="T187">
+        <v>3.4</v>
+      </c>
+      <c r="U187">
+        <v>2.3</v>
+      </c>
+      <c r="V187">
+        <v>1.47</v>
+      </c>
+      <c r="W187">
+        <v>1.12</v>
+      </c>
+      <c r="X187">
+        <v>1.03</v>
+      </c>
+      <c r="Y187">
+        <v>1.16</v>
+      </c>
+      <c r="Z187">
+        <v>4.15</v>
+      </c>
+      <c r="AA187">
+        <v>1.65</v>
+      </c>
+      <c r="AB187">
+        <v>2.2</v>
+      </c>
+      <c r="AC187">
+        <v>2.56</v>
+      </c>
+      <c r="AD187">
+        <v>1.4</v>
+      </c>
+      <c r="AE187">
+        <v>1.12</v>
+      </c>
+      <c r="AF187">
+        <v>1.62</v>
+      </c>
+      <c r="AG187">
+        <v>2.2</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ187">
         <v>1.2</v>
       </c>
-      <c r="T187">
-        <v>4.2</v>
-      </c>
-      <c r="U187">
+      <c r="AK187">
         <v>2</v>
-      </c>
-      <c r="V187">
-        <v>1.69</v>
-      </c>
-      <c r="W187">
-        <v>1.17</v>
-      </c>
-      <c r="X187">
-        <v>1.02</v>
-      </c>
-      <c r="Y187">
-        <v>1.08</v>
-      </c>
-      <c r="Z187">
-        <v>5.45</v>
-      </c>
-      <c r="AA187">
-        <v>1.41</v>
-      </c>
-      <c r="AB187">
-        <v>2.87</v>
-      </c>
-      <c r="AC187">
-        <v>2.03</v>
-      </c>
-      <c r="AD187">
-        <v>1.76</v>
-      </c>
-      <c r="AE187">
-        <v>1.31</v>
-      </c>
-      <c r="AF187">
-        <v>1.57</v>
-      </c>
-      <c r="AG187">
-        <v>2.25</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ187">
-        <v>1.18</v>
-      </c>
-      <c r="AK187">
-        <v>2.8</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,49 +30953,49 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="O188">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P188">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q188">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R188">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S188">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U188">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V188">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
         <v>1.16</v>
       </c>
       <c r="Z188">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA188">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB188">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC188">
         <v>2.56</v>
@@ -31004,13 +31004,13 @@
         <v>1.4</v>
       </c>
       <c r="AE188">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF188">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG188">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,19 +31116,19 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O189">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P189">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q189">
-        <v>2.41</v>
+        <v>3.13</v>
       </c>
       <c r="R189">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S189">
         <v>1.29</v>
@@ -31143,37 +31143,37 @@
         <v>1.5</v>
       </c>
       <c r="W189">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y189">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z189">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA189">
         <v>1.7</v>
       </c>
       <c r="AB189">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC189">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AD189">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE189">
         <v>1.13</v>
       </c>
       <c r="AF189">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG189">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK189">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O190">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P190">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Q190">
         <v>2.2</v>
       </c>
       <c r="R190">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="S190">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T190">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U190">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="V190">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W190">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X190">
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z190">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA190">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AB190">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC190">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="AD190">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AE190">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF190">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG190">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK190">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,80 +31442,80 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.62</v>
+        <v>1.41</v>
       </c>
       <c r="O191">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P191">
-        <v>2.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q191">
-        <v>3.13</v>
+        <v>1.83</v>
       </c>
       <c r="R191">
+        <v>2.63</v>
+      </c>
+      <c r="S191">
+        <v>1.2</v>
+      </c>
+      <c r="T191">
+        <v>4.2</v>
+      </c>
+      <c r="U191">
+        <v>2</v>
+      </c>
+      <c r="V191">
+        <v>1.69</v>
+      </c>
+      <c r="W191">
+        <v>1.17</v>
+      </c>
+      <c r="X191">
+        <v>1.02</v>
+      </c>
+      <c r="Y191">
+        <v>1.08</v>
+      </c>
+      <c r="Z191">
+        <v>5.45</v>
+      </c>
+      <c r="AA191">
+        <v>1.41</v>
+      </c>
+      <c r="AB191">
+        <v>2.87</v>
+      </c>
+      <c r="AC191">
+        <v>2.03</v>
+      </c>
+      <c r="AD191">
+        <v>1.76</v>
+      </c>
+      <c r="AE191">
+        <v>1.31</v>
+      </c>
+      <c r="AF191">
+        <v>1.57</v>
+      </c>
+      <c r="AG191">
         <v>2.25</v>
       </c>
-      <c r="S191">
-        <v>1.29</v>
-      </c>
-      <c r="T191">
-        <v>3.3</v>
-      </c>
-      <c r="U191">
-        <v>2.4</v>
-      </c>
-      <c r="V191">
-        <v>1.5</v>
-      </c>
-      <c r="W191">
-        <v>1.11</v>
-      </c>
-      <c r="X191">
-        <v>1</v>
-      </c>
-      <c r="Y191">
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ191">
         <v>1.18</v>
       </c>
-      <c r="Z191">
-        <v>3.88</v>
-      </c>
-      <c r="AA191">
-        <v>1.7</v>
-      </c>
-      <c r="AB191">
-        <v>2.09</v>
-      </c>
-      <c r="AC191">
-        <v>2.53</v>
-      </c>
-      <c r="AD191">
-        <v>1.44</v>
-      </c>
-      <c r="AE191">
-        <v>1.13</v>
-      </c>
-      <c r="AF191">
-        <v>1.55</v>
-      </c>
-      <c r="AG191">
-        <v>2.38</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ191">
-        <v>1.28</v>
-      </c>
       <c r="AK191">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O192">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P192">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q192">
         <v>2.2</v>
       </c>
       <c r="R192">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="S192">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U192">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="V192">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W192">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X192">
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z192">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA192">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AB192">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC192">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="AD192">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE192">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF192">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG192">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK192">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
+        <v>1.54</v>
+      </c>
+      <c r="O354">
+        <v>4.69</v>
+      </c>
+      <c r="P354">
+        <v>5.35</v>
+      </c>
+      <c r="Q354">
+        <v>2.07</v>
+      </c>
+      <c r="R354">
+        <v>2.38</v>
+      </c>
+      <c r="S354">
+        <v>1.25</v>
+      </c>
+      <c r="T354">
+        <v>3.5</v>
+      </c>
+      <c r="U354">
+        <v>2.27</v>
+      </c>
+      <c r="V354">
+        <v>1.51</v>
+      </c>
+      <c r="W354">
+        <v>1.11</v>
+      </c>
+      <c r="X354">
+        <v>1.02</v>
+      </c>
+      <c r="Y354">
+        <v>1.18</v>
+      </c>
+      <c r="Z354">
+        <v>3.86</v>
+      </c>
+      <c r="AA354">
+        <v>1.66</v>
+      </c>
+      <c r="AB354">
+        <v>2.02</v>
+      </c>
+      <c r="AC354">
+        <v>2.62</v>
+      </c>
+      <c r="AD354">
+        <v>1.38</v>
+      </c>
+      <c r="AE354">
+        <v>1.12</v>
+      </c>
+      <c r="AF354">
         <v>1.71</v>
       </c>
-      <c r="O354">
-        <v>4.39</v>
-      </c>
-      <c r="P354">
-        <v>4.23</v>
-      </c>
-      <c r="Q354">
-        <v>2.1</v>
-      </c>
-      <c r="R354">
-        <v>2.43</v>
-      </c>
-      <c r="S354">
-        <v>1.19</v>
-      </c>
-      <c r="T354">
-        <v>3.7</v>
-      </c>
-      <c r="U354">
-        <v>2.2</v>
-      </c>
-      <c r="V354">
-        <v>1.62</v>
-      </c>
-      <c r="W354">
-        <v>1.15</v>
-      </c>
-      <c r="X354">
-        <v>1.01</v>
-      </c>
-      <c r="Y354">
-        <v>1.16</v>
-      </c>
-      <c r="Z354">
-        <v>4.65</v>
-      </c>
-      <c r="AA354">
-        <v>1.48</v>
-      </c>
-      <c r="AB354">
-        <v>2.35</v>
-      </c>
-      <c r="AC354">
-        <v>2.3</v>
-      </c>
-      <c r="AD354">
-        <v>1.59</v>
-      </c>
-      <c r="AE354">
-        <v>1.19</v>
-      </c>
-      <c r="AF354">
-        <v>1.52</v>
-      </c>
       <c r="AG354">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>1.17</v>
       </c>
       <c r="AK354">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,64 +58174,64 @@
         </is>
       </c>
       <c r="N355">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O355">
-        <v>4.69</v>
+        <v>4.39</v>
       </c>
       <c r="P355">
-        <v>5.35</v>
+        <v>4.23</v>
       </c>
       <c r="Q355">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R355">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S355">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T355">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U355">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V355">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W355">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X355">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y355">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z355">
-        <v>3.86</v>
+        <v>4.65</v>
       </c>
       <c r="AA355">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AB355">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AC355">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD355">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE355">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF355">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AG355">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AH355" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>1.17</v>
       </c>
       <c r="AK355">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL355">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
         <v>2.68</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
+        <v>1.73</v>
+      </c>
+      <c r="AK15">
         <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="R16">
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
         <v>2.68</v>
       </c>
       <c r="U16">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
+        <v>1.22</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
         <v>1.11</v>
       </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.12</v>
-      </c>
       <c r="Z40">
-        <v>4.75</v>
+        <v>6.78</v>
       </c>
       <c r="AA40">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="AC40">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AD40">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG40">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="Q41">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z41">
-        <v>6.78</v>
+        <v>4.75</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="AD41">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AE41">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK41">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P51">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="R51">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG51">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="Q52">
-        <v>2.05</v>
+        <v>3.12</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AD52">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P69">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q69">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="R69">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="S69">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U69">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V69">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W69">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X69">
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="AA69">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB69">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC69">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AD69">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE69">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF69">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AG69">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P70">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q70">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R70">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T70">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="U70">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>5.15</v>
+        <v>4.45</v>
       </c>
       <c r="AA70">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB70">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="AC70">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="AD70">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="O71">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="Q71">
-        <v>3.4</v>
+        <v>2.47</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S71">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="AA71">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AB71">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AC71">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AD71">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AG71">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="O100">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>5.36</v>
+        <v>2.8</v>
       </c>
       <c r="Q100">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R100">
-        <v>2.76</v>
+        <v>2.24</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U100">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="V100">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W100">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y100">
+        <v>1.27</v>
+      </c>
+      <c r="Z100">
+        <v>3.61</v>
+      </c>
+      <c r="AA100">
+        <v>1.83</v>
+      </c>
+      <c r="AB100">
+        <v>1.95</v>
+      </c>
+      <c r="AC100">
+        <v>3.17</v>
+      </c>
+      <c r="AD100">
+        <v>1.34</v>
+      </c>
+      <c r="AE100">
         <v>1.12</v>
       </c>
-      <c r="Z100">
-        <v>6</v>
-      </c>
-      <c r="AA100">
-        <v>1.38</v>
-      </c>
-      <c r="AB100">
-        <v>2.62</v>
-      </c>
-      <c r="AC100">
-        <v>2.05</v>
-      </c>
-      <c r="AD100">
-        <v>1.75</v>
-      </c>
-      <c r="AE100">
-        <v>1.29</v>
-      </c>
       <c r="AF100">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>1.93</v>
+      </c>
+      <c r="R101">
         <v>2.5</v>
       </c>
-      <c r="O101">
-        <v>3.4</v>
-      </c>
-      <c r="P101">
-        <v>2.8</v>
-      </c>
-      <c r="Q101">
-        <v>2.99</v>
-      </c>
-      <c r="R101">
-        <v>2.24</v>
-      </c>
       <c r="S101">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U101">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="V101">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W101">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z101">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="AA101">
+        <v>1.7</v>
+      </c>
+      <c r="AB101">
+        <v>2.02</v>
+      </c>
+      <c r="AC101">
+        <v>2.79</v>
+      </c>
+      <c r="AD101">
+        <v>1.36</v>
+      </c>
+      <c r="AE101">
+        <v>1.13</v>
+      </c>
+      <c r="AF101">
         <v>1.83</v>
       </c>
-      <c r="AB101">
-        <v>1.95</v>
-      </c>
-      <c r="AC101">
-        <v>3.17</v>
-      </c>
-      <c r="AD101">
-        <v>1.34</v>
-      </c>
-      <c r="AE101">
-        <v>1.12</v>
-      </c>
-      <c r="AF101">
-        <v>1.67</v>
-      </c>
       <c r="AG101">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK101">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q102">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R102">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="S102">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T102">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="U102">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="V102">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z102">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AA102">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AB102">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AC102">
-        <v>2.79</v>
+        <v>2.05</v>
       </c>
       <c r="AD102">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AE102">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF102">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AG102">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK102">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>4.6</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="P127">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="Q127">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="S127">
         <v>1.2</v>
@@ -21031,43 +21031,43 @@
         <v>4.4</v>
       </c>
       <c r="U127">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V127">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W127">
         <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z127">
         <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB127">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AC127">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AE127">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF127">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>2.27</v>
       </c>
       <c r="AK127">
-        <v>2.75</v>
+        <v>1.19</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="O128">
-        <v>4.66</v>
+        <v>8</v>
       </c>
       <c r="P128">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="Q128">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="R128">
-        <v>2.67</v>
+        <v>3.6</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T128">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="U128">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="V128">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y128">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z128">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA128">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AB128">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="AC128">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AD128">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="AE128">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AF128">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG128">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>2.27</v>
+        <v>1.07</v>
       </c>
       <c r="AK128">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>9</v>
+        <v>1.43</v>
       </c>
       <c r="O130">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P130">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="Q130">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="R130">
-        <v>3.6</v>
+        <v>2.61</v>
       </c>
       <c r="S130">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T130">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="U130">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="V130">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="W130">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z130">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA130">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AB130">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="AC130">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD130">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE130">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AF130">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG130">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="O154">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q154">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R154">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S154">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U154">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V154">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W154">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA154">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB154">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC154">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="AD154">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF154">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG154">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK154">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="O158">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P158">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q158">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R158">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U158">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V158">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W158">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z158">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA158">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB158">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC158">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AD158">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF158">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG158">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK158">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="O172">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="P172">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q172">
-        <v>3.28</v>
+        <v>2.73</v>
       </c>
       <c r="R172">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S172">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T172">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="U172">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="V172">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W172">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X172">
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z172">
-        <v>3.25</v>
+        <v>4.71</v>
       </c>
       <c r="AA172">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AB172">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AC172">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="AD172">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AE172">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF172">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AG172">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK172">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O173">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="P173">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q173">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R173">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T173">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="U173">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V173">
         <v>1.43</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X173">
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA173">
+        <v>1.8</v>
+      </c>
+      <c r="AB173">
         <v>1.9</v>
       </c>
-      <c r="AB173">
-        <v>1.98</v>
-      </c>
       <c r="AC173">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AD173">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE173">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF173">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG173">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
         <v>1.4</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,61 +28671,61 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O174">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P174">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q174">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="R174">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="S174">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T174">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="U174">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V174">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
         <v>1.19</v>
       </c>
       <c r="Z174">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="AA174">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB174">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AC174">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="AD174">
         <v>1.49</v>
       </c>
       <c r="AE174">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF174">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG174">
         <v>2.4</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK174">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P175">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q175">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R175">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T175">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U175">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V175">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W175">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z175">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA175">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB175">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC175">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD175">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE175">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF175">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG175">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
+        <v>2.05</v>
+      </c>
+      <c r="O177">
+        <v>3.4</v>
+      </c>
+      <c r="P177">
+        <v>3.5</v>
+      </c>
+      <c r="Q177">
         <v>2.6</v>
       </c>
-      <c r="O177">
-        <v>3.6</v>
-      </c>
-      <c r="P177">
-        <v>2.55</v>
-      </c>
-      <c r="Q177">
-        <v>2.9</v>
-      </c>
       <c r="R177">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T177">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X177">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z177">
-        <v>4.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA177">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AB177">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC177">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="AD177">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AG177">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,16 +30627,16 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O186">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P186">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q186">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="R186">
         <v>2.18</v>
@@ -30648,43 +30648,43 @@
         <v>3.3</v>
       </c>
       <c r="U186">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V186">
         <v>1.5</v>
       </c>
       <c r="W186">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X186">
         <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z186">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA186">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB186">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC186">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AD186">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE186">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG186">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O187">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P187">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Q187">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R187">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S187">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T187">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U187">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V187">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W187">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X187">
         <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z187">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA187">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB187">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC187">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AD187">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE187">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF187">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG187">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,61 +30953,61 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="O188">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="P188">
-        <v>3.3</v>
+        <v>6.25</v>
       </c>
       <c r="Q188">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="R188">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="S188">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T188">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U188">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V188">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W188">
+        <v>1.17</v>
+      </c>
+      <c r="X188">
+        <v>1.02</v>
+      </c>
+      <c r="Y188">
         <v>1.08</v>
       </c>
-      <c r="X188">
-        <v>1.01</v>
-      </c>
-      <c r="Y188">
-        <v>1.16</v>
-      </c>
       <c r="Z188">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA188">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AB188">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC188">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="AD188">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AE188">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF188">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
         <v>2.25</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK188">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="O189">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P189">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q189">
-        <v>3.13</v>
+        <v>2.1</v>
       </c>
       <c r="R189">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S189">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T189">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U189">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W189">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X189">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z189">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA189">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB189">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC189">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AD189">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE189">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF189">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG189">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK189">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="O190">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P190">
-        <v>4.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q190">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R190">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S190">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T190">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U190">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="V190">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z190">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="AA190">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB190">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC190">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="AD190">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE190">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF190">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG190">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK190">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,37 +31442,37 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="O191">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="P191">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q191">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R191">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S191">
         <v>1.2</v>
       </c>
       <c r="T191">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U191">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V191">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W191">
         <v>1.17</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
         <v>1.08</v>
@@ -31481,25 +31481,25 @@
         <v>5.45</v>
       </c>
       <c r="AA191">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB191">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC191">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD191">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AE191">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF191">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG191">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK191">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="O192">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P192">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q192">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="R192">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="S192">
         <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V192">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W192">
         <v>1.11</v>
       </c>
       <c r="X192">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y192">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z192">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="AA192">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB192">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC192">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="AD192">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE192">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF192">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG192">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK192">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O193">
+        <v>4</v>
+      </c>
+      <c r="P193">
+        <v>4.33</v>
+      </c>
+      <c r="Q193">
+        <v>2.2</v>
+      </c>
+      <c r="R193">
+        <v>2.49</v>
+      </c>
+      <c r="S193">
+        <v>1.29</v>
+      </c>
+      <c r="T193">
+        <v>3.4</v>
+      </c>
+      <c r="U193">
+        <v>2.27</v>
+      </c>
+      <c r="V193">
+        <v>1.57</v>
+      </c>
+      <c r="W193">
+        <v>1.11</v>
+      </c>
+      <c r="X193">
+        <v>1.03</v>
+      </c>
+      <c r="Y193">
+        <v>1.15</v>
+      </c>
+      <c r="Z193">
         <v>4.3</v>
       </c>
-      <c r="P193">
-        <v>4.8</v>
-      </c>
-      <c r="Q193">
-        <v>2</v>
-      </c>
-      <c r="R193">
-        <v>2.6</v>
-      </c>
-      <c r="S193">
-        <v>1.2</v>
-      </c>
-      <c r="T193">
-        <v>4</v>
-      </c>
-      <c r="U193">
-        <v>2.1</v>
-      </c>
-      <c r="V193">
-        <v>1.7</v>
-      </c>
-      <c r="W193">
+      <c r="AA193">
+        <v>1.59</v>
+      </c>
+      <c r="AB193">
+        <v>2.25</v>
+      </c>
+      <c r="AC193">
+        <v>2.36</v>
+      </c>
+      <c r="AD193">
+        <v>1.47</v>
+      </c>
+      <c r="AE193">
         <v>1.17</v>
       </c>
-      <c r="X193">
-        <v>1.01</v>
-      </c>
-      <c r="Y193">
-        <v>1.08</v>
-      </c>
-      <c r="Z193">
-        <v>5.45</v>
-      </c>
-      <c r="AA193">
-        <v>1.44</v>
-      </c>
-      <c r="AB193">
-        <v>2.75</v>
-      </c>
-      <c r="AC193">
-        <v>2.1</v>
-      </c>
-      <c r="AD193">
-        <v>1.68</v>
-      </c>
-      <c r="AE193">
-        <v>1.29</v>
-      </c>
       <c r="AF193">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG193">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK193">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -34059,55 +34059,55 @@
         <v>2.1</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="O219">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P219">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36045,10 +36045,10 @@
         <v>0</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC219">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="O237">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="P237">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="O238">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>3.35</v>
+        <v>1.89</v>
       </c>
       <c r="O239">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
-        <v>1.99</v>
+        <v>4.1</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="O240">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="P240">
-        <v>3.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -41231,55 +41231,55 @@
         <v>3.64</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -42046,55 +42046,55 @@
         <v>3.99</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42209,55 +42209,55 @@
         <v>2.72</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O259">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P259">
-        <v>6.73</v>
+        <v>7</v>
       </c>
       <c r="Q259">
         <v>1.92</v>
@@ -42565,7 +42565,7 @@
         <v>3.7</v>
       </c>
       <c r="AA259">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB259">
         <v>2.02</v>
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="O275">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P275">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -46278,61 +46278,61 @@
         <v>1.85</v>
       </c>
       <c r="O282">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
       <c r="P282">
-        <v>4.09</v>
+        <v>3.25</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X282">
         <v>0</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC282">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AD282">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O285">
-        <v>5.02</v>
+        <v>4.05</v>
       </c>
       <c r="P285">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="Q285">
         <v>1.85</v>
@@ -46779,10 +46779,10 @@
         <v>2.62</v>
       </c>
       <c r="S285">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T285">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U285">
         <v>2.07</v>
@@ -46791,7 +46791,7 @@
         <v>1.73</v>
       </c>
       <c r="W285">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X285">
         <v>1.01</v>
@@ -46800,28 +46800,28 @@
         <v>1.11</v>
       </c>
       <c r="Z285">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AA285">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB285">
         <v>2.83</v>
       </c>
       <c r="AC285">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD285">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AE285">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF285">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG285">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK285">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -48720,65 +48720,65 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.66</v>
+        <v>3.17</v>
       </c>
       <c r="O297">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P297">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA297">
+        <v>1.88</v>
+      </c>
+      <c r="AB297">
+        <v>1.79</v>
+      </c>
+      <c r="AC297">
+        <v>3.14</v>
+      </c>
+      <c r="AD297">
+        <v>1.27</v>
+      </c>
+      <c r="AE297">
+        <v>1.07</v>
+      </c>
+      <c r="AF297">
+        <v>1.73</v>
+      </c>
+      <c r="AG297">
         <v>1.98</v>
       </c>
-      <c r="AB297">
-        <v>1.83</v>
-      </c>
-      <c r="AC297">
-        <v>0</v>
-      </c>
-      <c r="AD297">
-        <v>0</v>
-      </c>
-      <c r="AE297">
-        <v>0</v>
-      </c>
-      <c r="AF297">
-        <v>0</v>
-      </c>
-      <c r="AG297">
-        <v>0</v>
-      </c>
       <c r="AH297" t="inlineStr">
         <is>
           <t>[]</t>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="O305">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="P305">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X305">
         <v>0</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC305">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD305">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="O334">
-        <v>4.24</v>
+        <v>3.65</v>
       </c>
       <c r="P334">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q334">
         <v>3.42</v>
@@ -54821,7 +54821,7 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AK334">
         <v>1.27</v>
@@ -55077,43 +55077,43 @@
         </is>
       </c>
       <c r="N336">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="O336">
-        <v>4.23</v>
+        <v>3.45</v>
       </c>
       <c r="P336">
-        <v>4.08</v>
+        <v>2.95</v>
       </c>
       <c r="Q336">
         <v>2.75</v>
       </c>
       <c r="R336">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="S336">
         <v>1.29</v>
       </c>
       <c r="T336">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="U336">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V336">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W336">
         <v>1.11</v>
       </c>
       <c r="X336">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y336">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z336">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA336">
         <v>1.66</v>
@@ -55125,16 +55125,16 @@
         <v>2.6</v>
       </c>
       <c r="AD336">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE336">
         <v>1.18</v>
       </c>
       <c r="AF336">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG336">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="O337">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P337">
-        <v>3.61</v>
+        <v>2.84</v>
       </c>
       <c r="Q337">
         <v>2.85</v>
@@ -55279,10 +55279,10 @@
         <v>3.04</v>
       </c>
       <c r="AA337">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB337">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AC337">
         <v>3.5</v>
@@ -55403,25 +55403,25 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="O338">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P338">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="Q338">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R338">
         <v>2</v>
       </c>
       <c r="S338">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T338">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="U338">
         <v>3.18</v>
@@ -55430,7 +55430,7 @@
         <v>1.27</v>
       </c>
       <c r="W338">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X338">
         <v>1.04</v>
@@ -55442,7 +55442,7 @@
         <v>2.66</v>
       </c>
       <c r="AA338">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB338">
         <v>1.56</v>
@@ -55460,7 +55460,7 @@
         <v>1.95</v>
       </c>
       <c r="AG338">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK338">
         <v>1.61</v>
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O339">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P339">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q339">
         <v>4.27</v>
       </c>
       <c r="R339">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S339">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T339">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="U339">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V339">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W339">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X339">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y339">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z339">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="AA339">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB339">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC339">
-        <v>3.07</v>
+        <v>3.26</v>
       </c>
       <c r="AD339">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE339">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF339">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG339">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55729,43 +55729,43 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="O340">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="P340">
-        <v>3.09</v>
+        <v>3.9</v>
       </c>
       <c r="Q340">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R340">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S340">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="T340">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U340">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V340">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W340">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X340">
         <v>1.02</v>
       </c>
       <c r="Y340">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z340">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="AA340">
         <v>1.61</v>
@@ -55774,19 +55774,19 @@
         <v>2.25</v>
       </c>
       <c r="AC340">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD340">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE340">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF340">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG340">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK340">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AL340">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O69">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P69">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="Q69">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="R69">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
         <v>1.2</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U69">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V69">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="W69">
         <v>1.2</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="AA69">
+        <v>1.37</v>
+      </c>
+      <c r="AB69">
+        <v>2.62</v>
+      </c>
+      <c r="AC69">
+        <v>2.02</v>
+      </c>
+      <c r="AD69">
+        <v>1.69</v>
+      </c>
+      <c r="AE69">
+        <v>1.25</v>
+      </c>
+      <c r="AF69">
         <v>1.4</v>
       </c>
-      <c r="AB69">
-        <v>3</v>
-      </c>
-      <c r="AC69">
-        <v>1.93</v>
-      </c>
-      <c r="AD69">
-        <v>1.75</v>
-      </c>
-      <c r="AE69">
-        <v>1.28</v>
-      </c>
-      <c r="AF69">
-        <v>1.44</v>
-      </c>
       <c r="AG69">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="O70">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="Q70">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="R70">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>3.46</v>
       </c>
       <c r="U70">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V70">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>5.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA70">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AB70">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="AC70">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AD70">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AE70">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="S71">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V71">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.45</v>
+        <v>5.15</v>
       </c>
       <c r="AA71">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB71">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="AC71">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="AD71">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK71">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P72">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q72">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="R72">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V72">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>5.15</v>
+        <v>6.01</v>
       </c>
       <c r="AA72">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AC72">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AD72">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -17753,10 +17753,10 @@
         <v>2.89</v>
       </c>
       <c r="O107">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P107">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q107">
         <v>3.2</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O126">
-        <v>3.8</v>
+        <v>4.66</v>
       </c>
       <c r="P126">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="Q126">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="R126">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="S126">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T126">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U126">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V126">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W126">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z126">
-        <v>5.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA126">
+        <v>1.36</v>
+      </c>
+      <c r="AB126">
+        <v>3.17</v>
+      </c>
+      <c r="AC126">
+        <v>2.02</v>
+      </c>
+      <c r="AD126">
+        <v>1.84</v>
+      </c>
+      <c r="AE126">
+        <v>1.38</v>
+      </c>
+      <c r="AF126">
         <v>1.44</v>
       </c>
-      <c r="AB126">
-        <v>2.64</v>
-      </c>
-      <c r="AC126">
-        <v>2.12</v>
-      </c>
-      <c r="AD126">
-        <v>1.74</v>
-      </c>
-      <c r="AE126">
-        <v>1.27</v>
-      </c>
-      <c r="AF126">
-        <v>1.36</v>
-      </c>
       <c r="AG126">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="AK126">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="O127">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="P127">
-        <v>1.58</v>
+        <v>6.25</v>
       </c>
       <c r="Q127">
-        <v>4.7</v>
+        <v>1.75</v>
       </c>
       <c r="R127">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="S127">
         <v>1.2</v>
       </c>
       <c r="T127">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U127">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V127">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="W127">
         <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z127">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB127">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AC127">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD127">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AE127">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF127">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG127">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK127">
-        <v>1.2</v>
+        <v>2.75</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="O129">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="P129">
-        <v>6.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q129">
-        <v>1.75</v>
+        <v>3.32</v>
       </c>
       <c r="R129">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
         <v>4</v>
       </c>
       <c r="U129">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AA129">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AD129">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AG129">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AK129">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.74</v>
+        <v>1.7</v>
       </c>
       <c r="O134">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P134">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q134">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R134">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="S134">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T134">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="U134">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X134">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z134">
-        <v>3.74</v>
+        <v>5.1</v>
       </c>
       <c r="AA134">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB134">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="AC134">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF134">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG134">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="O135">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P135">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q135">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R135">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S135">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="U135">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V135">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W135">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
+        <v>1.22</v>
+      </c>
+      <c r="Z135">
+        <v>3.74</v>
+      </c>
+      <c r="AA135">
+        <v>1.8</v>
+      </c>
+      <c r="AB135">
+        <v>2</v>
+      </c>
+      <c r="AC135">
+        <v>2.84</v>
+      </c>
+      <c r="AD135">
+        <v>1.36</v>
+      </c>
+      <c r="AE135">
         <v>1.1</v>
       </c>
-      <c r="Z135">
-        <v>5.1</v>
-      </c>
-      <c r="AA135">
-        <v>1.5</v>
-      </c>
-      <c r="AB135">
-        <v>2.59</v>
-      </c>
-      <c r="AC135">
-        <v>2.25</v>
-      </c>
-      <c r="AD135">
-        <v>1.68</v>
-      </c>
-      <c r="AE135">
-        <v>1.26</v>
-      </c>
       <c r="AF135">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG135">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK135">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="O154">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P154">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q154">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="R154">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="S154">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="T154">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="V154">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z154">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA154">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AB154">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC154">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="AD154">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF154">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AG154">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK154">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="O155">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q155">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R155">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S155">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T155">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U155">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V155">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W155">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X155">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z155">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA155">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB155">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC155">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="AD155">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE155">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF155">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG155">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK155">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>2.55</v>
+        <v>2.98</v>
       </c>
       <c r="Q156">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R156">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T156">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
+        <v>1.34</v>
+      </c>
+      <c r="Z156">
+        <v>2.78</v>
+      </c>
+      <c r="AA156">
+        <v>2.1</v>
+      </c>
+      <c r="AB156">
+        <v>1.7</v>
+      </c>
+      <c r="AC156">
+        <v>4</v>
+      </c>
+      <c r="AD156">
         <v>1.2</v>
       </c>
-      <c r="Z156">
-        <v>3.74</v>
-      </c>
-      <c r="AA156">
-        <v>1.78</v>
-      </c>
-      <c r="AB156">
-        <v>1.98</v>
-      </c>
-      <c r="AC156">
-        <v>2.81</v>
-      </c>
-      <c r="AD156">
-        <v>1.33</v>
-      </c>
       <c r="AE156">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
+        <v>1.84</v>
+      </c>
+      <c r="O157">
+        <v>3.55</v>
+      </c>
+      <c r="P157">
+        <v>3.6</v>
+      </c>
+      <c r="Q157">
         <v>2.3</v>
       </c>
-      <c r="O157">
-        <v>3.3</v>
-      </c>
-      <c r="P157">
-        <v>2.98</v>
-      </c>
-      <c r="Q157">
-        <v>2.69</v>
-      </c>
       <c r="R157">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S157">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V157">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W157">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z157">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AA157">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB157">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC157">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AD157">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG157">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
+        <v>3.8</v>
+      </c>
+      <c r="O158">
+        <v>3.7</v>
+      </c>
+      <c r="P158">
+        <v>1.83</v>
+      </c>
+      <c r="Q158">
         <v>4.2</v>
       </c>
-      <c r="O158">
+      <c r="R158">
+        <v>2.26</v>
+      </c>
+      <c r="S158">
+        <v>1.3</v>
+      </c>
+      <c r="T158">
+        <v>3.3</v>
+      </c>
+      <c r="U158">
+        <v>2.32</v>
+      </c>
+      <c r="V158">
+        <v>1.52</v>
+      </c>
+      <c r="W158">
+        <v>1.1</v>
+      </c>
+      <c r="X158">
+        <v>1.02</v>
+      </c>
+      <c r="Y158">
+        <v>1.16</v>
+      </c>
+      <c r="Z158">
         <v>4.1</v>
       </c>
-      <c r="P158">
+      <c r="AA158">
+        <v>1.67</v>
+      </c>
+      <c r="AB158">
+        <v>2.11</v>
+      </c>
+      <c r="AC158">
+        <v>2.72</v>
+      </c>
+      <c r="AD158">
+        <v>1.42</v>
+      </c>
+      <c r="AE158">
+        <v>1.11</v>
+      </c>
+      <c r="AF158">
         <v>1.62</v>
       </c>
-      <c r="Q158">
-        <v>3.72</v>
-      </c>
-      <c r="R158">
-        <v>2.27</v>
-      </c>
-      <c r="S158">
-        <v>1.23</v>
-      </c>
-      <c r="T158">
-        <v>3.5</v>
-      </c>
-      <c r="U158">
-        <v>2.21</v>
-      </c>
-      <c r="V158">
-        <v>1.57</v>
-      </c>
-      <c r="W158">
-        <v>1.13</v>
-      </c>
-      <c r="X158">
-        <v>1.03</v>
-      </c>
-      <c r="Y158">
-        <v>1.13</v>
-      </c>
-      <c r="Z158">
-        <v>4.6</v>
-      </c>
-      <c r="AA158">
-        <v>1.54</v>
-      </c>
-      <c r="AB158">
-        <v>2.3</v>
-      </c>
-      <c r="AC158">
-        <v>2.31</v>
-      </c>
-      <c r="AD158">
-        <v>1.54</v>
-      </c>
-      <c r="AE158">
-        <v>1.19</v>
-      </c>
-      <c r="AF158">
-        <v>1.56</v>
-      </c>
       <c r="AG158">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AK158">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="O172">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P172">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q172">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="R172">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="S172">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T172">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U172">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V172">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W172">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X172">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z172">
-        <v>3.04</v>
+        <v>4.71</v>
       </c>
       <c r="AA172">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="AB172">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AC172">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="AD172">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AE172">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF172">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AG172">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK172">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="O173">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="P173">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="Q173">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="R173">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T173">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U173">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V173">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X173">
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA173">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB173">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC173">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AD173">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE173">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF173">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG173">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O174">
-        <v>3.75</v>
+        <v>3.43</v>
       </c>
       <c r="P174">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q174">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="R174">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="S174">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T174">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="U174">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="V174">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W174">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X174">
         <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z174">
-        <v>4.71</v>
+        <v>3.14</v>
       </c>
       <c r="AA174">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AB174">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="AC174">
-        <v>2.59</v>
+        <v>3.28</v>
       </c>
       <c r="AD174">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE174">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF174">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG174">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK174">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="O175">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="P175">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="Q175">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="R175">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="S175">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T175">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U175">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="V175">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W175">
         <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z175">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA175">
+        <v>1.99</v>
+      </c>
+      <c r="AB175">
         <v>1.8</v>
       </c>
-      <c r="AB175">
-        <v>1.94</v>
-      </c>
       <c r="AC175">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AD175">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE175">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG175">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK175">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="O177">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="P177">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q177">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="R177">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S177">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T177">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="U177">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="V177">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W177">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z177">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA177">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB177">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC177">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD177">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE177">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF177">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG177">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK177">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,16 +30627,16 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O186">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P186">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q186">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="R186">
         <v>2.18</v>
@@ -30648,43 +30648,43 @@
         <v>3.3</v>
       </c>
       <c r="U186">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V186">
         <v>1.5</v>
       </c>
       <c r="W186">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X186">
         <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z186">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA186">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB186">
         <v>2.1</v>
       </c>
       <c r="AC186">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD186">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE186">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF186">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG186">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK186">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="P187">
-        <v>2.24</v>
+        <v>6.06</v>
       </c>
       <c r="Q187">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R187">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="S187">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T187">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U187">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="V187">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="W187">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X187">
         <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z187">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA187">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AB187">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AC187">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AD187">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AE187">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF187">
         <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK187">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="O188">
-        <v>4.95</v>
+        <v>3.6</v>
       </c>
       <c r="P188">
-        <v>6.06</v>
+        <v>2.39</v>
       </c>
       <c r="Q188">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="R188">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S188">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U188">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V188">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="W188">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y188">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z188">
-        <v>5.45</v>
+        <v>3.88</v>
       </c>
       <c r="AA188">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AB188">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AC188">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="AD188">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AE188">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG188">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O189">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P189">
-        <v>2.39</v>
+        <v>4.7</v>
       </c>
       <c r="Q189">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="R189">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S189">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T189">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U189">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W189">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X189">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z189">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA189">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB189">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC189">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="AD189">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE189">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF189">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AG189">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G190">
@@ -31282,61 +31282,61 @@
         <v>1.73</v>
       </c>
       <c r="O190">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P190">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q190">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R190">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S190">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T190">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U190">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V190">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W190">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X190">
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z190">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA190">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AB190">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC190">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="AD190">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE190">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF190">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG190">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK190">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,80 +31442,80 @@
         </is>
       </c>
       <c r="N191">
+        <v>1.59</v>
+      </c>
+      <c r="O191">
+        <v>4.5</v>
+      </c>
+      <c r="P191">
+        <v>4.9</v>
+      </c>
+      <c r="Q191">
+        <v>2</v>
+      </c>
+      <c r="R191">
+        <v>2.52</v>
+      </c>
+      <c r="S191">
+        <v>1.16</v>
+      </c>
+      <c r="T191">
+        <v>4.15</v>
+      </c>
+      <c r="U191">
+        <v>2</v>
+      </c>
+      <c r="V191">
+        <v>1.76</v>
+      </c>
+      <c r="W191">
+        <v>1.19</v>
+      </c>
+      <c r="X191">
+        <v>1.01</v>
+      </c>
+      <c r="Y191">
+        <v>1.07</v>
+      </c>
+      <c r="Z191">
+        <v>5.85</v>
+      </c>
+      <c r="AA191">
+        <v>1.35</v>
+      </c>
+      <c r="AB191">
+        <v>2.88</v>
+      </c>
+      <c r="AC191">
+        <v>2</v>
+      </c>
+      <c r="AD191">
         <v>1.73</v>
       </c>
-      <c r="O191">
-        <v>3.9</v>
-      </c>
-      <c r="P191">
-        <v>4.4</v>
-      </c>
-      <c r="Q191">
-        <v>2.1</v>
-      </c>
-      <c r="R191">
+      <c r="AE191">
+        <v>1.32</v>
+      </c>
+      <c r="AF191">
+        <v>1.47</v>
+      </c>
+      <c r="AG191">
+        <v>2.63</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ191">
+        <v>1.14</v>
+      </c>
+      <c r="AK191">
         <v>2.3</v>
-      </c>
-      <c r="S191">
-        <v>1.29</v>
-      </c>
-      <c r="T191">
-        <v>3.4</v>
-      </c>
-      <c r="U191">
-        <v>2.25</v>
-      </c>
-      <c r="V191">
-        <v>1.57</v>
-      </c>
-      <c r="W191">
-        <v>1.11</v>
-      </c>
-      <c r="X191">
-        <v>1.03</v>
-      </c>
-      <c r="Y191">
-        <v>1.15</v>
-      </c>
-      <c r="Z191">
-        <v>4.3</v>
-      </c>
-      <c r="AA191">
-        <v>1.59</v>
-      </c>
-      <c r="AB191">
-        <v>2.25</v>
-      </c>
-      <c r="AC191">
-        <v>2.32</v>
-      </c>
-      <c r="AD191">
-        <v>1.47</v>
-      </c>
-      <c r="AE191">
-        <v>1.18</v>
-      </c>
-      <c r="AF191">
-        <v>1.57</v>
-      </c>
-      <c r="AG191">
-        <v>2.26</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ191">
-        <v>1.2</v>
-      </c>
-      <c r="AK191">
-        <v>2.05</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,49 +31605,49 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="O192">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="P192">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="Q192">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R192">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S192">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V192">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W192">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X192">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
         <v>1.16</v>
       </c>
       <c r="Z192">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="AA192">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB192">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC192">
         <v>2.56</v>
@@ -31656,13 +31656,13 @@
         <v>1.4</v>
       </c>
       <c r="AE192">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF192">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG192">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK192">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,80 +31768,80 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="O193">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="P193">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q193">
+        <v>2.1</v>
+      </c>
+      <c r="R193">
+        <v>2.3</v>
+      </c>
+      <c r="S193">
+        <v>1.25</v>
+      </c>
+      <c r="T193">
+        <v>3.4</v>
+      </c>
+      <c r="U193">
+        <v>2.3</v>
+      </c>
+      <c r="V193">
+        <v>1.47</v>
+      </c>
+      <c r="W193">
+        <v>1.12</v>
+      </c>
+      <c r="X193">
+        <v>1.03</v>
+      </c>
+      <c r="Y193">
+        <v>1.16</v>
+      </c>
+      <c r="Z193">
+        <v>4.15</v>
+      </c>
+      <c r="AA193">
+        <v>1.65</v>
+      </c>
+      <c r="AB193">
+        <v>2.2</v>
+      </c>
+      <c r="AC193">
+        <v>2.56</v>
+      </c>
+      <c r="AD193">
+        <v>1.4</v>
+      </c>
+      <c r="AE193">
+        <v>1.12</v>
+      </c>
+      <c r="AF193">
+        <v>1.62</v>
+      </c>
+      <c r="AG193">
+        <v>2.2</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ193">
+        <v>1.2</v>
+      </c>
+      <c r="AK193">
         <v>2</v>
-      </c>
-      <c r="R193">
-        <v>2.52</v>
-      </c>
-      <c r="S193">
-        <v>1.16</v>
-      </c>
-      <c r="T193">
-        <v>4.15</v>
-      </c>
-      <c r="U193">
-        <v>2</v>
-      </c>
-      <c r="V193">
-        <v>1.76</v>
-      </c>
-      <c r="W193">
-        <v>1.19</v>
-      </c>
-      <c r="X193">
-        <v>1.01</v>
-      </c>
-      <c r="Y193">
-        <v>1.07</v>
-      </c>
-      <c r="Z193">
-        <v>5.85</v>
-      </c>
-      <c r="AA193">
-        <v>1.35</v>
-      </c>
-      <c r="AB193">
-        <v>2.88</v>
-      </c>
-      <c r="AC193">
-        <v>2</v>
-      </c>
-      <c r="AD193">
-        <v>1.73</v>
-      </c>
-      <c r="AE193">
-        <v>1.32</v>
-      </c>
-      <c r="AF193">
-        <v>1.47</v>
-      </c>
-      <c r="AG193">
-        <v>2.63</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ193">
-        <v>1.14</v>
-      </c>
-      <c r="AK193">
-        <v>2.3</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -41228,7 +41228,7 @@
         <v>3.5</v>
       </c>
       <c r="P251">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q251">
         <v>2.34</v>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="O262">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P262">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Q262">
-        <v>4.25</v>
+        <v>6.33</v>
       </c>
       <c r="R262">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S262">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T262">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U262">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V262">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W262">
         <v>1.08</v>
       </c>
       <c r="X262">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y262">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z262">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="AA262">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AB262">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AC262">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="AD262">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE262">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF262">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG262">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK262">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,80 +43178,80 @@
         </is>
       </c>
       <c r="N263">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="O263">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P263">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Q263">
-        <v>6.33</v>
+        <v>4.25</v>
       </c>
       <c r="R263">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="S263">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T263">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U263">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V263">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W263">
         <v>1.08</v>
       </c>
       <c r="X263">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y263">
+        <v>1.17</v>
+      </c>
+      <c r="Z263">
+        <v>4.12</v>
+      </c>
+      <c r="AA263">
+        <v>1.69</v>
+      </c>
+      <c r="AB263">
+        <v>2.13</v>
+      </c>
+      <c r="AC263">
+        <v>2.71</v>
+      </c>
+      <c r="AD263">
+        <v>1.43</v>
+      </c>
+      <c r="AE263">
+        <v>1.12</v>
+      </c>
+      <c r="AF263">
+        <v>1.67</v>
+      </c>
+      <c r="AG263">
+        <v>2.1</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ263">
+        <v>1.23</v>
+      </c>
+      <c r="AK263">
         <v>1.22</v>
-      </c>
-      <c r="Z263">
-        <v>3.9</v>
-      </c>
-      <c r="AA263">
-        <v>1.78</v>
-      </c>
-      <c r="AB263">
-        <v>1.94</v>
-      </c>
-      <c r="AC263">
-        <v>2.92</v>
-      </c>
-      <c r="AD263">
-        <v>1.38</v>
-      </c>
-      <c r="AE263">
-        <v>1.09</v>
-      </c>
-      <c r="AF263">
-        <v>1.87</v>
-      </c>
-      <c r="AG263">
-        <v>1.83</v>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ263">
-        <v>1.18</v>
-      </c>
-      <c r="AK263">
-        <v>1.09</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,80 +50839,80 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="O310">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="P310">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="Q310">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="R310">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="S310">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="T310">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="U310">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="V310">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="W310">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="X310">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y310">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Z310">
-        <v>9</v>
+        <v>4.75</v>
       </c>
       <c r="AA310">
+        <v>1.61</v>
+      </c>
+      <c r="AB310">
+        <v>2.42</v>
+      </c>
+      <c r="AC310">
+        <v>2.38</v>
+      </c>
+      <c r="AD310">
+        <v>1.5</v>
+      </c>
+      <c r="AE310">
+        <v>1.16</v>
+      </c>
+      <c r="AF310">
+        <v>1.62</v>
+      </c>
+      <c r="AG310">
+        <v>2.19</v>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ310">
         <v>1.22</v>
       </c>
-      <c r="AB310">
-        <v>4.15</v>
-      </c>
-      <c r="AC310">
-        <v>1.59</v>
-      </c>
-      <c r="AD310">
-        <v>2.39</v>
-      </c>
-      <c r="AE310">
-        <v>1.62</v>
-      </c>
-      <c r="AF310">
-        <v>2.15</v>
-      </c>
-      <c r="AG310">
-        <v>1.67</v>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ310">
-        <v>1.04</v>
-      </c>
       <c r="AK310">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
+        <v>1.08</v>
+      </c>
+      <c r="O311">
+        <v>13</v>
+      </c>
+      <c r="P311">
+        <v>23</v>
+      </c>
+      <c r="Q311">
+        <v>1.3</v>
+      </c>
+      <c r="R311">
+        <v>3.75</v>
+      </c>
+      <c r="S311">
+        <v>1.08</v>
+      </c>
+      <c r="T311">
+        <v>5.5</v>
+      </c>
+      <c r="U311">
         <v>1.6</v>
       </c>
-      <c r="O311">
-        <v>4.4</v>
-      </c>
-      <c r="P311">
-        <v>5.2</v>
-      </c>
-      <c r="Q311">
-        <v>2.06</v>
-      </c>
-      <c r="R311">
-        <v>2.4</v>
-      </c>
-      <c r="S311">
-        <v>1.27</v>
-      </c>
-      <c r="T311">
-        <v>3.5</v>
-      </c>
-      <c r="U311">
-        <v>2.24</v>
-      </c>
       <c r="V311">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="W311">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="X311">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y311">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Z311">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="AA311">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AB311">
-        <v>2.42</v>
+        <v>4.15</v>
       </c>
       <c r="AC311">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD311">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="AE311">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AF311">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG311">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK311">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="AL311">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>2.41</v>
       </c>
       <c r="Q52">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC52">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AD52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P53">
-        <v>2.41</v>
+        <v>5</v>
       </c>
       <c r="Q53">
-        <v>3.14</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="U53">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AA53">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB53">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC53">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AD53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG53">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK53">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,61 +11556,61 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="O69">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P69">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q69">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R69">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="S69">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T69">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="U69">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V69">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
         <v>1.12</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
+        <v>1.18</v>
+      </c>
+      <c r="Z69">
+        <v>4.45</v>
+      </c>
+      <c r="AA69">
+        <v>1.54</v>
+      </c>
+      <c r="AB69">
+        <v>2.19</v>
+      </c>
+      <c r="AC69">
+        <v>2.41</v>
+      </c>
+      <c r="AD69">
+        <v>1.48</v>
+      </c>
+      <c r="AE69">
         <v>1.15</v>
       </c>
-      <c r="Z69">
-        <v>4.3</v>
-      </c>
-      <c r="AA69">
-        <v>1.58</v>
-      </c>
-      <c r="AB69">
-        <v>2.18</v>
-      </c>
-      <c r="AC69">
-        <v>2.43</v>
-      </c>
-      <c r="AD69">
-        <v>1.44</v>
-      </c>
-      <c r="AE69">
-        <v>1.14</v>
-      </c>
       <c r="AF69">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG69">
         <v>2.3</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="R70">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="U70">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V70">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.45</v>
+        <v>5.15</v>
       </c>
       <c r="AA70">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB70">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="AC70">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="AD70">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AE70">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF70">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O71">
-        <v>5.05</v>
+        <v>3.55</v>
       </c>
       <c r="P71">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="Q71">
-        <v>2.02</v>
+        <v>2.47</v>
       </c>
       <c r="R71">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="S71">
         <v>1.2</v>
       </c>
       <c r="T71">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="W71">
         <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="AA71">
+        <v>1.47</v>
+      </c>
+      <c r="AB71">
+        <v>2.62</v>
+      </c>
+      <c r="AC71">
+        <v>2.02</v>
+      </c>
+      <c r="AD71">
+        <v>1.69</v>
+      </c>
+      <c r="AE71">
+        <v>1.25</v>
+      </c>
+      <c r="AF71">
         <v>1.4</v>
       </c>
-      <c r="AB71">
-        <v>3.1</v>
-      </c>
-      <c r="AC71">
-        <v>1.93</v>
-      </c>
-      <c r="AD71">
-        <v>1.75</v>
-      </c>
-      <c r="AE71">
-        <v>1.28</v>
-      </c>
-      <c r="AF71">
-        <v>1.44</v>
-      </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>2.18</v>
+        <v>1.64</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>5.05</v>
       </c>
       <c r="P72">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q72">
-        <v>2.62</v>
+        <v>2.02</v>
       </c>
       <c r="R72">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U72">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="V72">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>5.15</v>
+        <v>6.01</v>
       </c>
       <c r="AA72">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AC72">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AD72">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>2.99</v>
       </c>
       <c r="O73">
         <v>3.55</v>
       </c>
       <c r="P73">
-        <v>2.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q73">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="R73">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="S73">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U73">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V73">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z73">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA73">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AB73">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="AC73">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AD73">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AE73">
+        <v>1.14</v>
+      </c>
+      <c r="AF73">
+        <v>1.52</v>
+      </c>
+      <c r="AG73">
+        <v>2.3</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.19</v>
+      </c>
+      <c r="AK73">
         <v>1.25</v>
-      </c>
-      <c r="AF73">
-        <v>1.4</v>
-      </c>
-      <c r="AG73">
-        <v>2.7</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.3</v>
-      </c>
-      <c r="AK73">
-        <v>1.64</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O82">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q82">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T82">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="U82">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V82">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W82">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
+        <v>1.26</v>
+      </c>
+      <c r="Z82">
+        <v>3.2</v>
+      </c>
+      <c r="AA82">
+        <v>1.88</v>
+      </c>
+      <c r="AB82">
+        <v>1.79</v>
+      </c>
+      <c r="AC82">
+        <v>3.05</v>
+      </c>
+      <c r="AD82">
         <v>1.28</v>
       </c>
-      <c r="Z82">
-        <v>3.05</v>
-      </c>
-      <c r="AA82">
-        <v>1.99</v>
-      </c>
-      <c r="AB82">
-        <v>1.7</v>
-      </c>
-      <c r="AC82">
-        <v>3.5</v>
-      </c>
-      <c r="AD82">
-        <v>1.22</v>
-      </c>
       <c r="AE82">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG82">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,37 +13838,37 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="O83">
+        <v>4.6</v>
+      </c>
+      <c r="P83">
+        <v>6.4</v>
+      </c>
+      <c r="Q83">
+        <v>2.01</v>
+      </c>
+      <c r="R83">
+        <v>2.12</v>
+      </c>
+      <c r="S83">
+        <v>1.36</v>
+      </c>
+      <c r="T83">
         <v>3</v>
       </c>
-      <c r="P83">
-        <v>2.7</v>
-      </c>
-      <c r="Q83">
-        <v>3</v>
-      </c>
-      <c r="R83">
-        <v>2.1</v>
-      </c>
-      <c r="S83">
-        <v>1.38</v>
-      </c>
-      <c r="T83">
-        <v>2.65</v>
-      </c>
       <c r="U83">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="V83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
         <v>1.26</v>
@@ -13877,25 +13877,25 @@
         <v>3.2</v>
       </c>
       <c r="AA83">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB83">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC83">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD83">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE83">
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AG83">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,65 +14001,65 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.42</v>
+        <v>2.33</v>
       </c>
       <c r="O84">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="P84">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q84">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T84">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U84">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
+        <v>1.03</v>
+      </c>
+      <c r="Y84">
+        <v>1.35</v>
+      </c>
+      <c r="Z84">
+        <v>2.74</v>
+      </c>
+      <c r="AA84">
+        <v>2.15</v>
+      </c>
+      <c r="AB84">
+        <v>1.6</v>
+      </c>
+      <c r="AC84">
+        <v>3.84</v>
+      </c>
+      <c r="AD84">
+        <v>1.18</v>
+      </c>
+      <c r="AE84">
         <v>1.02</v>
       </c>
-      <c r="Y84">
-        <v>1.26</v>
-      </c>
-      <c r="Z84">
-        <v>3.2</v>
-      </c>
-      <c r="AA84">
+      <c r="AF84">
         <v>1.85</v>
       </c>
-      <c r="AB84">
+      <c r="AG84">
         <v>1.82</v>
       </c>
-      <c r="AC84">
-        <v>2.97</v>
-      </c>
-      <c r="AD84">
-        <v>1.3</v>
-      </c>
-      <c r="AE84">
-        <v>1.08</v>
-      </c>
-      <c r="AF84">
-        <v>1.99</v>
-      </c>
-      <c r="AG84">
-        <v>1.7</v>
-      </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK84">
-        <v>2.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O85">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q85">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="R85">
         <v>2</v>
@@ -14182,46 +14182,46 @@
         <v>1.4</v>
       </c>
       <c r="T85">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U85">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="V85">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W85">
+        <v>1.02</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.28</v>
+      </c>
+      <c r="Z85">
+        <v>3.05</v>
+      </c>
+      <c r="AA85">
+        <v>1.99</v>
+      </c>
+      <c r="AB85">
+        <v>1.7</v>
+      </c>
+      <c r="AC85">
+        <v>3.5</v>
+      </c>
+      <c r="AD85">
+        <v>1.22</v>
+      </c>
+      <c r="AE85">
         <v>1.04</v>
       </c>
-      <c r="X85">
-        <v>1.03</v>
-      </c>
-      <c r="Y85">
-        <v>1.35</v>
-      </c>
-      <c r="Z85">
-        <v>2.74</v>
-      </c>
-      <c r="AA85">
-        <v>2.15</v>
-      </c>
-      <c r="AB85">
-        <v>1.6</v>
-      </c>
-      <c r="AC85">
-        <v>3.84</v>
-      </c>
-      <c r="AD85">
-        <v>1.18</v>
-      </c>
-      <c r="AE85">
-        <v>1.02</v>
-      </c>
       <c r="AF85">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG85">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>4.8</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="P127">
-        <v>6.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q127">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="S127">
         <v>1.2</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U127">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V127">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W127">
         <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z127">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA127">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AB127">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="AC127">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AE127">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF127">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="AK127">
-        <v>2.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="O128">
-        <v>4.66</v>
+        <v>8.5</v>
       </c>
       <c r="P128">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="Q128">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="R128">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T128">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="U128">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="V128">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y128">
+        <v>1.04</v>
+      </c>
+      <c r="Z128">
+        <v>15</v>
+      </c>
+      <c r="AA128">
+        <v>1.14</v>
+      </c>
+      <c r="AB128">
+        <v>6</v>
+      </c>
+      <c r="AC128">
+        <v>1.38</v>
+      </c>
+      <c r="AD128">
+        <v>2.98</v>
+      </c>
+      <c r="AE128">
+        <v>1.89</v>
+      </c>
+      <c r="AF128">
+        <v>1.4</v>
+      </c>
+      <c r="AG128">
+        <v>2.73</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>1.07</v>
+      </c>
+      <c r="AK128">
         <v>1.05</v>
-      </c>
-      <c r="Z128">
-        <v>7.5</v>
-      </c>
-      <c r="AA128">
-        <v>1.37</v>
-      </c>
-      <c r="AB128">
-        <v>3.16</v>
-      </c>
-      <c r="AC128">
-        <v>1.96</v>
-      </c>
-      <c r="AD128">
-        <v>1.9</v>
-      </c>
-      <c r="AE128">
-        <v>1.38</v>
-      </c>
-      <c r="AF128">
-        <v>1.44</v>
-      </c>
-      <c r="AG128">
-        <v>2.66</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>2.26</v>
-      </c>
-      <c r="AK128">
-        <v>1.2</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>11</v>
+        <v>1.43</v>
       </c>
       <c r="O130">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="P130">
-        <v>1.17</v>
+        <v>6.25</v>
       </c>
       <c r="Q130">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="R130">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="S130">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T130">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U130">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="V130">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="W130">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z130">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA130">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AB130">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC130">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD130">
-        <v>2.98</v>
+        <v>1.79</v>
       </c>
       <c r="AE130">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="AF130">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG130">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>1.05</v>
+        <v>2.75</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="O139">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P139">
-        <v>1.91</v>
+        <v>2.72</v>
       </c>
       <c r="Q139">
-        <v>3.94</v>
+        <v>2.77</v>
       </c>
       <c r="R139">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S139">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T139">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U139">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V139">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W139">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X139">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z139">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA139">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB139">
         <v>2.2</v>
       </c>
       <c r="AC139">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="AD139">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE139">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF139">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AG139">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.22</v>
       </c>
       <c r="AK139">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="O140">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P140">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="Q140">
-        <v>2.77</v>
+        <v>3.94</v>
       </c>
       <c r="R140">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S140">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T140">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U140">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V140">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W140">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z140">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA140">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB140">
         <v>2.2</v>
       </c>
       <c r="AC140">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="AD140">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE140">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG140">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="O155">
+        <v>3.7</v>
+      </c>
+      <c r="P155">
+        <v>1.85</v>
+      </c>
+      <c r="Q155">
+        <v>4.2</v>
+      </c>
+      <c r="R155">
+        <v>2.26</v>
+      </c>
+      <c r="S155">
+        <v>1.3</v>
+      </c>
+      <c r="T155">
         <v>3.3</v>
       </c>
-      <c r="P155">
-        <v>2.98</v>
-      </c>
-      <c r="Q155">
-        <v>2.69</v>
-      </c>
-      <c r="R155">
-        <v>1.98</v>
-      </c>
-      <c r="S155">
-        <v>1.45</v>
-      </c>
-      <c r="T155">
-        <v>2.5</v>
-      </c>
       <c r="U155">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="V155">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W155">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z155">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA155">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="AB155">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AC155">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="AD155">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AE155">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG155">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK155">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="O156">
+        <v>4.2</v>
+      </c>
+      <c r="P156">
+        <v>1.62</v>
+      </c>
+      <c r="Q156">
+        <v>3.9</v>
+      </c>
+      <c r="R156">
+        <v>2.28</v>
+      </c>
+      <c r="S156">
+        <v>1.23</v>
+      </c>
+      <c r="T156">
         <v>3.5</v>
       </c>
-      <c r="P156">
-        <v>2.5</v>
-      </c>
-      <c r="Q156">
-        <v>3.1</v>
-      </c>
-      <c r="R156">
-        <v>2.18</v>
-      </c>
-      <c r="S156">
-        <v>1.36</v>
-      </c>
-      <c r="T156">
-        <v>2.82</v>
-      </c>
       <c r="U156">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="V156">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z156">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="AA156">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AB156">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AC156">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="AD156">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE156">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF156">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG156">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK156">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="O157">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
+        <v>2.98</v>
+      </c>
+      <c r="Q157">
+        <v>2.69</v>
+      </c>
+      <c r="R157">
+        <v>1.98</v>
+      </c>
+      <c r="S157">
+        <v>1.45</v>
+      </c>
+      <c r="T157">
+        <v>2.5</v>
+      </c>
+      <c r="U157">
+        <v>3</v>
+      </c>
+      <c r="V157">
+        <v>1.32</v>
+      </c>
+      <c r="W157">
+        <v>1.04</v>
+      </c>
+      <c r="X157">
+        <v>1.04</v>
+      </c>
+      <c r="Y157">
+        <v>1.34</v>
+      </c>
+      <c r="Z157">
+        <v>2.78</v>
+      </c>
+      <c r="AA157">
+        <v>2.22</v>
+      </c>
+      <c r="AB157">
+        <v>1.7</v>
+      </c>
+      <c r="AC157">
+        <v>4</v>
+      </c>
+      <c r="AD157">
+        <v>1.2</v>
+      </c>
+      <c r="AE157">
+        <v>1.04</v>
+      </c>
+      <c r="AF157">
         <v>1.85</v>
       </c>
-      <c r="Q157">
-        <v>4.2</v>
-      </c>
-      <c r="R157">
-        <v>2.26</v>
-      </c>
-      <c r="S157">
-        <v>1.3</v>
-      </c>
-      <c r="T157">
-        <v>3.3</v>
-      </c>
-      <c r="U157">
-        <v>2.32</v>
-      </c>
-      <c r="V157">
-        <v>1.52</v>
-      </c>
-      <c r="W157">
-        <v>1.1</v>
-      </c>
-      <c r="X157">
-        <v>1.02</v>
-      </c>
-      <c r="Y157">
-        <v>1.16</v>
-      </c>
-      <c r="Z157">
-        <v>4.1</v>
-      </c>
-      <c r="AA157">
-        <v>1.67</v>
-      </c>
-      <c r="AB157">
-        <v>2.11</v>
-      </c>
-      <c r="AC157">
-        <v>2.72</v>
-      </c>
-      <c r="AD157">
-        <v>1.42</v>
-      </c>
-      <c r="AE157">
-        <v>1.11</v>
-      </c>
-      <c r="AF157">
-        <v>1.62</v>
-      </c>
       <c r="AG157">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="O158">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q158">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S158">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U158">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="V158">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W158">
+        <v>1.09</v>
+      </c>
+      <c r="X158">
+        <v>1.01</v>
+      </c>
+      <c r="Y158">
+        <v>1.2</v>
+      </c>
+      <c r="Z158">
+        <v>3.74</v>
+      </c>
+      <c r="AA158">
+        <v>1.78</v>
+      </c>
+      <c r="AB158">
+        <v>1.98</v>
+      </c>
+      <c r="AC158">
+        <v>2.81</v>
+      </c>
+      <c r="AD158">
+        <v>1.33</v>
+      </c>
+      <c r="AE158">
         <v>1.13</v>
       </c>
-      <c r="X158">
-        <v>1.03</v>
-      </c>
-      <c r="Y158">
-        <v>1.13</v>
-      </c>
-      <c r="Z158">
-        <v>4.6</v>
-      </c>
-      <c r="AA158">
-        <v>1.54</v>
-      </c>
-      <c r="AB158">
-        <v>2.3</v>
-      </c>
-      <c r="AC158">
-        <v>2.31</v>
-      </c>
-      <c r="AD158">
-        <v>1.54</v>
-      </c>
-      <c r="AE158">
-        <v>1.19</v>
-      </c>
       <c r="AF158">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,65 +28508,65 @@
         </is>
       </c>
       <c r="N173">
+        <v>2.78</v>
+      </c>
+      <c r="O173">
+        <v>3.4</v>
+      </c>
+      <c r="P173">
+        <v>2.36</v>
+      </c>
+      <c r="Q173">
+        <v>3.2</v>
+      </c>
+      <c r="R173">
+        <v>2.11</v>
+      </c>
+      <c r="S173">
+        <v>1.33</v>
+      </c>
+      <c r="T173">
+        <v>2.96</v>
+      </c>
+      <c r="U173">
+        <v>2.53</v>
+      </c>
+      <c r="V173">
+        <v>1.43</v>
+      </c>
+      <c r="W173">
+        <v>1.07</v>
+      </c>
+      <c r="X173">
+        <v>1.04</v>
+      </c>
+      <c r="Y173">
+        <v>1.23</v>
+      </c>
+      <c r="Z173">
+        <v>3.42</v>
+      </c>
+      <c r="AA173">
+        <v>1.9</v>
+      </c>
+      <c r="AB173">
+        <v>1.98</v>
+      </c>
+      <c r="AC173">
+        <v>3.1</v>
+      </c>
+      <c r="AD173">
+        <v>1.37</v>
+      </c>
+      <c r="AE173">
+        <v>1.14</v>
+      </c>
+      <c r="AF173">
+        <v>1.67</v>
+      </c>
+      <c r="AG173">
         <v>2.1</v>
       </c>
-      <c r="O173">
-        <v>3.43</v>
-      </c>
-      <c r="P173">
-        <v>3.4</v>
-      </c>
-      <c r="Q173">
-        <v>2.65</v>
-      </c>
-      <c r="R173">
-        <v>2.08</v>
-      </c>
-      <c r="S173">
-        <v>1.38</v>
-      </c>
-      <c r="T173">
-        <v>2.74</v>
-      </c>
-      <c r="U173">
-        <v>2.82</v>
-      </c>
-      <c r="V173">
-        <v>1.36</v>
-      </c>
-      <c r="W173">
-        <v>1.04</v>
-      </c>
-      <c r="X173">
-        <v>1.01</v>
-      </c>
-      <c r="Y173">
-        <v>1.27</v>
-      </c>
-      <c r="Z173">
-        <v>3.14</v>
-      </c>
-      <c r="AA173">
-        <v>2.04</v>
-      </c>
-      <c r="AB173">
-        <v>1.8</v>
-      </c>
-      <c r="AC173">
-        <v>3.28</v>
-      </c>
-      <c r="AD173">
-        <v>1.25</v>
-      </c>
-      <c r="AE173">
-        <v>1.11</v>
-      </c>
-      <c r="AF173">
-        <v>1.76</v>
-      </c>
-      <c r="AG173">
-        <v>1.96</v>
-      </c>
       <c r="AH173" t="inlineStr">
         <is>
           <t>[]</t>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="O174">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P174">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q174">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="R174">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S174">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T174">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="U174">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V174">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W174">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X174">
         <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z174">
-        <v>4.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA174">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AB174">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AC174">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="AD174">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AE174">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF174">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AG174">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AK174">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="P175">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="Q175">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="R175">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="S175">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T175">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U175">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V175">
         <v>1.43</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z175">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA175">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB175">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC175">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AD175">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE175">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF175">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG175">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="O176">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P176">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q176">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="R176">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S176">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T176">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="U176">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V176">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z176">
-        <v>3.04</v>
+        <v>4.25</v>
       </c>
       <c r="AA176">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AB176">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AC176">
-        <v>3.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD176">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AE176">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF176">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AG176">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AK176">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,34 +29160,34 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O177">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="P177">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="Q177">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="R177">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="S177">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T177">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="U177">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="V177">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X177">
         <v>1.01</v>
@@ -29196,28 +29196,28 @@
         <v>1.27</v>
       </c>
       <c r="Z177">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA177">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AB177">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC177">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="AD177">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE177">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG177">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O187">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P187">
-        <v>6.06</v>
+        <v>4.33</v>
       </c>
       <c r="Q187">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R187">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S187">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T187">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U187">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="V187">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="W187">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z187">
-        <v>5.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA187">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AB187">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AC187">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="AD187">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE187">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF187">
         <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK187">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O188">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P188">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q188">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R188">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="S188">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T188">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U188">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V188">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X188">
         <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z188">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA188">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB188">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC188">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AD188">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE188">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF188">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG188">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,16 +31116,16 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="O189">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P189">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="Q189">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="R189">
         <v>2.18</v>
@@ -31137,43 +31137,43 @@
         <v>3.3</v>
       </c>
       <c r="U189">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V189">
         <v>1.5</v>
       </c>
       <c r="W189">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X189">
         <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z189">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="AA189">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB189">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC189">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD189">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE189">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF189">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG189">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O190">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P190">
-        <v>4.33</v>
+        <v>6.06</v>
       </c>
       <c r="Q190">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R190">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S190">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T190">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U190">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V190">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="W190">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z190">
-        <v>4.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA190">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB190">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AC190">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AD190">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AE190">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF190">
         <v>1.57</v>
       </c>
       <c r="AG190">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK190">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,49 +31605,49 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="O192">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="P192">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q192">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="R192">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T192">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U192">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V192">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W192">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y192">
         <v>1.16</v>
       </c>
       <c r="Z192">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA192">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB192">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC192">
         <v>2.56</v>
@@ -31656,13 +31656,13 @@
         <v>1.4</v>
       </c>
       <c r="AE192">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF192">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG192">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>1.22</v>
       </c>
       <c r="AK192">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,80 +31768,80 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O193">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P193">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q193">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="R193">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S193">
+        <v>1.29</v>
+      </c>
+      <c r="T193">
+        <v>3.3</v>
+      </c>
+      <c r="U193">
+        <v>2.31</v>
+      </c>
+      <c r="V193">
+        <v>1.5</v>
+      </c>
+      <c r="W193">
+        <v>1.09</v>
+      </c>
+      <c r="X193">
+        <v>1.01</v>
+      </c>
+      <c r="Y193">
+        <v>1.19</v>
+      </c>
+      <c r="Z193">
+        <v>4.15</v>
+      </c>
+      <c r="AA193">
+        <v>1.67</v>
+      </c>
+      <c r="AB193">
+        <v>2.15</v>
+      </c>
+      <c r="AC193">
+        <v>2.5</v>
+      </c>
+      <c r="AD193">
+        <v>1.49</v>
+      </c>
+      <c r="AE193">
+        <v>1.19</v>
+      </c>
+      <c r="AF193">
+        <v>1.57</v>
+      </c>
+      <c r="AG193">
+        <v>2.38</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ193">
+        <v>1.27</v>
+      </c>
+      <c r="AK193">
         <v>1.33</v>
-      </c>
-      <c r="T193">
-        <v>3</v>
-      </c>
-      <c r="U193">
-        <v>2.75</v>
-      </c>
-      <c r="V193">
-        <v>1.4</v>
-      </c>
-      <c r="W193">
-        <v>1.06</v>
-      </c>
-      <c r="X193">
-        <v>1.03</v>
-      </c>
-      <c r="Y193">
-        <v>1.23</v>
-      </c>
-      <c r="Z193">
-        <v>3.42</v>
-      </c>
-      <c r="AA193">
-        <v>1.9</v>
-      </c>
-      <c r="AB193">
-        <v>1.82</v>
-      </c>
-      <c r="AC193">
-        <v>2.96</v>
-      </c>
-      <c r="AD193">
-        <v>1.3</v>
-      </c>
-      <c r="AE193">
-        <v>1.08</v>
-      </c>
-      <c r="AF193">
-        <v>1.87</v>
-      </c>
-      <c r="AG193">
-        <v>1.9</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ193">
-        <v>1.22</v>
-      </c>
-      <c r="AK193">
-        <v>2</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.64</v>
+        <v>1.89</v>
       </c>
       <c r="O239">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
+        <v>4.1</v>
+      </c>
+      <c r="Q239">
         <v>2.5</v>
       </c>
-      <c r="Q239">
-        <v>3.06</v>
-      </c>
       <c r="R239">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S239">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T239">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="U239">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V239">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W239">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X239">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z239">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
       <c r="AA239">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB239">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AC239">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="AD239">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE239">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF239">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG239">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK239">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.89</v>
+        <v>2.64</v>
       </c>
       <c r="O240">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="P240">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q240">
-        <v>2.5</v>
+        <v>3.06</v>
       </c>
       <c r="R240">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S240">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T240">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U240">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V240">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W240">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X240">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y240">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z240">
-        <v>3.04</v>
+        <v>2.66</v>
       </c>
       <c r="AA240">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AB240">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC240">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="AD240">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE240">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF240">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG240">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK240">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="O261">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P261">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="Q261">
-        <v>4.33</v>
+        <v>6.33</v>
       </c>
       <c r="R261">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S261">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T261">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U261">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V261">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W261">
         <v>1.08</v>
       </c>
       <c r="X261">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y261">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z261">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="AA261">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AB261">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC261">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AD261">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE261">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF261">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG261">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK261">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,80 +43015,80 @@
         </is>
       </c>
       <c r="N262">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="O262">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P262">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="Q262">
-        <v>6.33</v>
+        <v>4.33</v>
       </c>
       <c r="R262">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="S262">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T262">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U262">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V262">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W262">
         <v>1.08</v>
       </c>
       <c r="X262">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y262">
+        <v>1.17</v>
+      </c>
+      <c r="Z262">
+        <v>4.16</v>
+      </c>
+      <c r="AA262">
+        <v>1.68</v>
+      </c>
+      <c r="AB262">
+        <v>2.15</v>
+      </c>
+      <c r="AC262">
+        <v>2.69</v>
+      </c>
+      <c r="AD262">
+        <v>1.44</v>
+      </c>
+      <c r="AE262">
+        <v>1.12</v>
+      </c>
+      <c r="AF262">
+        <v>1.67</v>
+      </c>
+      <c r="AG262">
+        <v>2.1</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ262">
         <v>1.22</v>
       </c>
-      <c r="Z262">
-        <v>3.9</v>
-      </c>
-      <c r="AA262">
-        <v>1.78</v>
-      </c>
-      <c r="AB262">
-        <v>1.94</v>
-      </c>
-      <c r="AC262">
-        <v>2.92</v>
-      </c>
-      <c r="AD262">
-        <v>1.38</v>
-      </c>
-      <c r="AE262">
-        <v>1.09</v>
-      </c>
-      <c r="AF262">
-        <v>1.87</v>
-      </c>
-      <c r="AG262">
-        <v>1.83</v>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ262">
-        <v>1.18</v>
-      </c>
       <c r="AK262">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="O309">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="P309">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="Q309">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="R309">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="S309">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="T309">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="U309">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="V309">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="W309">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="X309">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Z309">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="AA309">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AB309">
-        <v>2.43</v>
+        <v>4.15</v>
       </c>
       <c r="AC309">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD309">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="AE309">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="AF309">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG309">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK309">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="O310">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="P310">
-        <v>23</v>
+        <v>5.1</v>
       </c>
       <c r="Q310">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="R310">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="S310">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="T310">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="U310">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="V310">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="W310">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="X310">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y310">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Z310">
-        <v>9</v>
+        <v>4.75</v>
       </c>
       <c r="AA310">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AB310">
-        <v>4.15</v>
+        <v>2.43</v>
       </c>
       <c r="AC310">
-        <v>1.59</v>
+        <v>2.38</v>
       </c>
       <c r="AD310">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE310">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="AF310">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG310">
-        <v>1.67</v>
+        <v>2.19</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK310">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="AL310">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
         <v>2.68</v>
       </c>
       <c r="U15">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R16">
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
         <v>2.68</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC16">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
         <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
+        <v>1.73</v>
+      </c>
+      <c r="AK16">
         <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.45</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.62</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R86">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T86">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="U86">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="V86">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W86">
         <v>1.01</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z86">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA86">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AB86">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC86">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AD86">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
+        <v>1.81</v>
+      </c>
+      <c r="AG86">
         <v>1.86</v>
-      </c>
-      <c r="AG86">
-        <v>1.81</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O101">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.36</v>
+        <v>2.59</v>
       </c>
       <c r="Q101">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R101">
-        <v>2.76</v>
+        <v>2.08</v>
       </c>
       <c r="S101">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="V101">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y101">
+        <v>1.27</v>
+      </c>
+      <c r="Z101">
+        <v>3.61</v>
+      </c>
+      <c r="AA101">
+        <v>1.83</v>
+      </c>
+      <c r="AB101">
+        <v>1.93</v>
+      </c>
+      <c r="AC101">
+        <v>3.17</v>
+      </c>
+      <c r="AD101">
+        <v>1.34</v>
+      </c>
+      <c r="AE101">
         <v>1.12</v>
       </c>
-      <c r="Z101">
-        <v>6</v>
-      </c>
-      <c r="AA101">
-        <v>1.38</v>
-      </c>
-      <c r="AB101">
-        <v>2.62</v>
-      </c>
-      <c r="AC101">
-        <v>2.05</v>
-      </c>
-      <c r="AD101">
-        <v>1.75</v>
-      </c>
-      <c r="AE101">
-        <v>1.29</v>
-      </c>
       <c r="AF101">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
+        <v>1.48</v>
+      </c>
+      <c r="O102">
+        <v>4.6</v>
+      </c>
+      <c r="P102">
+        <v>5.36</v>
+      </c>
+      <c r="Q102">
+        <v>1.91</v>
+      </c>
+      <c r="R102">
+        <v>2.76</v>
+      </c>
+      <c r="S102">
+        <v>1.2</v>
+      </c>
+      <c r="T102">
+        <v>4</v>
+      </c>
+      <c r="U102">
+        <v>2.01</v>
+      </c>
+      <c r="V102">
+        <v>1.7</v>
+      </c>
+      <c r="W102">
+        <v>1.16</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.12</v>
+      </c>
+      <c r="Z102">
+        <v>6</v>
+      </c>
+      <c r="AA102">
+        <v>1.38</v>
+      </c>
+      <c r="AB102">
+        <v>2.62</v>
+      </c>
+      <c r="AC102">
+        <v>2.05</v>
+      </c>
+      <c r="AD102">
+        <v>1.75</v>
+      </c>
+      <c r="AE102">
+        <v>1.29</v>
+      </c>
+      <c r="AF102">
+        <v>1.52</v>
+      </c>
+      <c r="AG102">
+        <v>2.45</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.12</v>
+      </c>
+      <c r="AK102">
         <v>2.4</v>
-      </c>
-      <c r="O102">
-        <v>3.2</v>
-      </c>
-      <c r="P102">
-        <v>2.59</v>
-      </c>
-      <c r="Q102">
-        <v>2.99</v>
-      </c>
-      <c r="R102">
-        <v>2.08</v>
-      </c>
-      <c r="S102">
-        <v>1.33</v>
-      </c>
-      <c r="T102">
-        <v>2.88</v>
-      </c>
-      <c r="U102">
-        <v>2.56</v>
-      </c>
-      <c r="V102">
-        <v>1.41</v>
-      </c>
-      <c r="W102">
-        <v>1.07</v>
-      </c>
-      <c r="X102">
-        <v>1</v>
-      </c>
-      <c r="Y102">
-        <v>1.27</v>
-      </c>
-      <c r="Z102">
-        <v>3.61</v>
-      </c>
-      <c r="AA102">
-        <v>1.83</v>
-      </c>
-      <c r="AB102">
-        <v>1.93</v>
-      </c>
-      <c r="AC102">
-        <v>3.17</v>
-      </c>
-      <c r="AD102">
-        <v>1.34</v>
-      </c>
-      <c r="AE102">
-        <v>1.12</v>
-      </c>
-      <c r="AF102">
-        <v>1.67</v>
-      </c>
-      <c r="AG102">
-        <v>2.11</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.3</v>
-      </c>
-      <c r="AK102">
-        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,80 +21010,80 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="O127">
-        <v>4.66</v>
+        <v>8.5</v>
       </c>
       <c r="P127">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="Q127">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="R127">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="S127">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T127">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="U127">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="V127">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="W127">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y127">
+        <v>1.04</v>
+      </c>
+      <c r="Z127">
+        <v>15</v>
+      </c>
+      <c r="AA127">
+        <v>1.14</v>
+      </c>
+      <c r="AB127">
+        <v>6</v>
+      </c>
+      <c r="AC127">
+        <v>1.38</v>
+      </c>
+      <c r="AD127">
+        <v>2.98</v>
+      </c>
+      <c r="AE127">
+        <v>1.89</v>
+      </c>
+      <c r="AF127">
+        <v>1.4</v>
+      </c>
+      <c r="AG127">
+        <v>2.73</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>1.07</v>
+      </c>
+      <c r="AK127">
         <v>1.05</v>
-      </c>
-      <c r="Z127">
-        <v>7.5</v>
-      </c>
-      <c r="AA127">
-        <v>1.37</v>
-      </c>
-      <c r="AB127">
-        <v>3.16</v>
-      </c>
-      <c r="AC127">
-        <v>1.96</v>
-      </c>
-      <c r="AD127">
-        <v>1.9</v>
-      </c>
-      <c r="AE127">
-        <v>1.38</v>
-      </c>
-      <c r="AF127">
-        <v>1.44</v>
-      </c>
-      <c r="AG127">
-        <v>2.66</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>2.26</v>
-      </c>
-      <c r="AK127">
-        <v>1.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>11</v>
+        <v>2.9</v>
       </c>
       <c r="O128">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="P128">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q128">
-        <v>7.5</v>
+        <v>3.32</v>
       </c>
       <c r="R128">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="S128">
+        <v>1.22</v>
+      </c>
+      <c r="T128">
+        <v>4</v>
+      </c>
+      <c r="U128">
+        <v>2.1</v>
+      </c>
+      <c r="V128">
+        <v>1.67</v>
+      </c>
+      <c r="W128">
+        <v>1.18</v>
+      </c>
+      <c r="X128">
+        <v>1.02</v>
+      </c>
+      <c r="Y128">
         <v>1.11</v>
       </c>
-      <c r="T128">
-        <v>6</v>
-      </c>
-      <c r="U128">
-        <v>1.53</v>
-      </c>
-      <c r="V128">
-        <v>2.38</v>
-      </c>
-      <c r="W128">
+      <c r="Z128">
+        <v>5.45</v>
+      </c>
+      <c r="AA128">
         <v>1.44</v>
       </c>
-      <c r="X128">
-        <v>1</v>
-      </c>
-      <c r="Y128">
-        <v>1.04</v>
-      </c>
-      <c r="Z128">
-        <v>15</v>
-      </c>
-      <c r="AA128">
-        <v>1.14</v>
-      </c>
       <c r="AB128">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AD128">
-        <v>2.98</v>
+        <v>1.74</v>
       </c>
       <c r="AE128">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="AF128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG128">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.07</v>
+        <v>1.62</v>
       </c>
       <c r="AK128">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O129">
-        <v>3.75</v>
+        <v>4.66</v>
       </c>
       <c r="P129">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="Q129">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T129">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z129">
-        <v>5.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA129">
+        <v>1.37</v>
+      </c>
+      <c r="AB129">
+        <v>3.16</v>
+      </c>
+      <c r="AC129">
+        <v>1.96</v>
+      </c>
+      <c r="AD129">
+        <v>1.9</v>
+      </c>
+      <c r="AE129">
+        <v>1.38</v>
+      </c>
+      <c r="AF129">
         <v>1.44</v>
       </c>
-      <c r="AB129">
-        <v>2.64</v>
-      </c>
-      <c r="AC129">
-        <v>2.13</v>
-      </c>
-      <c r="AD129">
-        <v>1.74</v>
-      </c>
-      <c r="AE129">
-        <v>1.27</v>
-      </c>
-      <c r="AF129">
-        <v>1.36</v>
-      </c>
       <c r="AG129">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AK129">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.74</v>
+        <v>1.7</v>
       </c>
       <c r="O134">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P134">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q134">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R134">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="S134">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T134">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="U134">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="V134">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X134">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z134">
-        <v>3.74</v>
+        <v>5.1</v>
       </c>
       <c r="AA134">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB134">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AC134">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF134">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG134">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="O135">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q135">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R135">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S135">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="U135">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V135">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W135">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
+        <v>1.22</v>
+      </c>
+      <c r="Z135">
+        <v>3.74</v>
+      </c>
+      <c r="AA135">
+        <v>1.8</v>
+      </c>
+      <c r="AB135">
+        <v>1.95</v>
+      </c>
+      <c r="AC135">
+        <v>2.84</v>
+      </c>
+      <c r="AD135">
+        <v>1.36</v>
+      </c>
+      <c r="AE135">
         <v>1.1</v>
       </c>
-      <c r="Z135">
-        <v>5.1</v>
-      </c>
-      <c r="AA135">
-        <v>1.5</v>
-      </c>
-      <c r="AB135">
-        <v>2.6</v>
-      </c>
-      <c r="AC135">
-        <v>2.25</v>
-      </c>
-      <c r="AD135">
-        <v>1.69</v>
-      </c>
-      <c r="AE135">
-        <v>1.26</v>
-      </c>
       <c r="AF135">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG135">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK135">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.72</v>
+        <v>2.26</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P145">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Q145">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S145">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T145">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="U145">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V145">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X145">
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z145">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA145">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AB145">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC145">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE145">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF145">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG145">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="O146">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="Q146">
+        <v>2.36</v>
+      </c>
+      <c r="R146">
+        <v>2.2</v>
+      </c>
+      <c r="S146">
+        <v>1.36</v>
+      </c>
+      <c r="T146">
+        <v>2.56</v>
+      </c>
+      <c r="U146">
         <v>2.88</v>
       </c>
-      <c r="R146">
-        <v>2.09</v>
-      </c>
-      <c r="S146">
-        <v>1.32</v>
-      </c>
-      <c r="T146">
-        <v>2.89</v>
-      </c>
-      <c r="U146">
-        <v>2.5</v>
-      </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W146">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z146">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA146">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AB146">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC146">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD146">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.87</v>
+        <v>4.2</v>
       </c>
       <c r="O154">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P154">
+        <v>1.62</v>
+      </c>
+      <c r="Q154">
+        <v>3.9</v>
+      </c>
+      <c r="R154">
+        <v>2.28</v>
+      </c>
+      <c r="S154">
+        <v>1.23</v>
+      </c>
+      <c r="T154">
         <v>3.5</v>
       </c>
-      <c r="Q154">
-        <v>2.29</v>
-      </c>
-      <c r="R154">
-        <v>2.04</v>
-      </c>
-      <c r="S154">
-        <v>1.4</v>
-      </c>
-      <c r="T154">
-        <v>2.66</v>
-      </c>
       <c r="U154">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="V154">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z154">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA154">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AB154">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC154">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="AD154">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF154">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AG154">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK154">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.2</v>
+        <v>1.87</v>
       </c>
       <c r="O156">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="Q156">
-        <v>3.9</v>
+        <v>2.29</v>
       </c>
       <c r="R156">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="S156">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="U156">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="V156">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="W156">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X156">
         <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z156">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AB156">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC156">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="AD156">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AE156">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF156">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG156">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="O157">
         <v>3.3</v>
       </c>
       <c r="P157">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="Q157">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="R157">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S157">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="V157">
+        <v>1.4</v>
+      </c>
+      <c r="W157">
+        <v>1.05</v>
+      </c>
+      <c r="X157">
+        <v>1.01</v>
+      </c>
+      <c r="Y157">
+        <v>1.24</v>
+      </c>
+      <c r="Z157">
+        <v>3.51</v>
+      </c>
+      <c r="AA157">
+        <v>1.93</v>
+      </c>
+      <c r="AB157">
+        <v>1.85</v>
+      </c>
+      <c r="AC157">
+        <v>3.05</v>
+      </c>
+      <c r="AD157">
         <v>1.32</v>
       </c>
-      <c r="W157">
-        <v>1.04</v>
-      </c>
-      <c r="X157">
-        <v>1.04</v>
-      </c>
-      <c r="Y157">
-        <v>1.34</v>
-      </c>
-      <c r="Z157">
-        <v>2.78</v>
-      </c>
-      <c r="AA157">
-        <v>2.22</v>
-      </c>
-      <c r="AB157">
-        <v>1.7</v>
-      </c>
-      <c r="AC157">
-        <v>4</v>
-      </c>
-      <c r="AD157">
-        <v>1.2</v>
-      </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF157">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG157">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O158">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P158">
+        <v>2.98</v>
+      </c>
+      <c r="Q158">
+        <v>2.69</v>
+      </c>
+      <c r="R158">
+        <v>1.98</v>
+      </c>
+      <c r="S158">
+        <v>1.45</v>
+      </c>
+      <c r="T158">
         <v>2.5</v>
       </c>
-      <c r="Q158">
-        <v>3.1</v>
-      </c>
-      <c r="R158">
-        <v>2.18</v>
-      </c>
-      <c r="S158">
-        <v>1.36</v>
-      </c>
-      <c r="T158">
-        <v>2.82</v>
-      </c>
       <c r="U158">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V158">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W158">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y158">
+        <v>1.34</v>
+      </c>
+      <c r="Z158">
+        <v>2.78</v>
+      </c>
+      <c r="AA158">
+        <v>2.22</v>
+      </c>
+      <c r="AB158">
+        <v>1.7</v>
+      </c>
+      <c r="AC158">
+        <v>4</v>
+      </c>
+      <c r="AD158">
         <v>1.2</v>
       </c>
-      <c r="Z158">
-        <v>3.74</v>
-      </c>
-      <c r="AA158">
-        <v>1.78</v>
-      </c>
-      <c r="AB158">
-        <v>1.98</v>
-      </c>
-      <c r="AC158">
-        <v>2.81</v>
-      </c>
-      <c r="AD158">
-        <v>1.33</v>
-      </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF158">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG158">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="O159">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P159">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q159">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="R159">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S159">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T159">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U159">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V159">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z159">
-        <v>3.51</v>
+        <v>3.74</v>
       </c>
       <c r="AA159">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AB159">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC159">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AD159">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF159">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG159">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK159">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>3.95</v>
       </c>
       <c r="AA162">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB162">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC162">
         <v>2.7</v>
@@ -26887,22 +26887,22 @@
         <v>12.7</v>
       </c>
       <c r="Q163">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R163">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="S163">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T163">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U163">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V163">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W163">
         <v>1.11</v>
@@ -26911,31 +26911,31 @@
         <v>1.02</v>
       </c>
       <c r="Y163">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z163">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA163">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB163">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC163">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD163">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE163">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF163">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG163">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK163">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="O173">
+        <v>3.43</v>
+      </c>
+      <c r="P173">
         <v>3.4</v>
       </c>
-      <c r="P173">
-        <v>2.36</v>
-      </c>
       <c r="Q173">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="R173">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T173">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="U173">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="V173">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X173">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA173">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AB173">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC173">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD173">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE173">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF173">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG173">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="O174">
+        <v>3.47</v>
+      </c>
+      <c r="P174">
+        <v>2.49</v>
+      </c>
+      <c r="Q174">
+        <v>3.31</v>
+      </c>
+      <c r="R174">
+        <v>2.27</v>
+      </c>
+      <c r="S174">
+        <v>1.37</v>
+      </c>
+      <c r="T174">
         <v>3.3</v>
       </c>
-      <c r="P174">
-        <v>2.6</v>
-      </c>
-      <c r="Q174">
-        <v>3.34</v>
-      </c>
-      <c r="R174">
-        <v>2.05</v>
-      </c>
-      <c r="S174">
-        <v>1.41</v>
-      </c>
-      <c r="T174">
-        <v>2.62</v>
-      </c>
       <c r="U174">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="V174">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W174">
         <v>1.06</v>
       </c>
       <c r="X174">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z174">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA174">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AB174">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC174">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AD174">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE174">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF174">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG174">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="O175">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P175">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="Q175">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="R175">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="S175">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T175">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U175">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="V175">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W175">
         <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z175">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA175">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB175">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC175">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="AD175">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE175">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG175">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK175">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,65 +29160,65 @@
         </is>
       </c>
       <c r="N177">
+        <v>2.78</v>
+      </c>
+      <c r="O177">
+        <v>3.4</v>
+      </c>
+      <c r="P177">
+        <v>2.36</v>
+      </c>
+      <c r="Q177">
+        <v>3.2</v>
+      </c>
+      <c r="R177">
+        <v>2.11</v>
+      </c>
+      <c r="S177">
+        <v>1.33</v>
+      </c>
+      <c r="T177">
+        <v>2.96</v>
+      </c>
+      <c r="U177">
+        <v>2.53</v>
+      </c>
+      <c r="V177">
+        <v>1.43</v>
+      </c>
+      <c r="W177">
+        <v>1.07</v>
+      </c>
+      <c r="X177">
+        <v>1.04</v>
+      </c>
+      <c r="Y177">
+        <v>1.23</v>
+      </c>
+      <c r="Z177">
+        <v>3.42</v>
+      </c>
+      <c r="AA177">
+        <v>1.9</v>
+      </c>
+      <c r="AB177">
+        <v>1.98</v>
+      </c>
+      <c r="AC177">
+        <v>3.1</v>
+      </c>
+      <c r="AD177">
+        <v>1.37</v>
+      </c>
+      <c r="AE177">
+        <v>1.14</v>
+      </c>
+      <c r="AF177">
+        <v>1.67</v>
+      </c>
+      <c r="AG177">
         <v>2.1</v>
       </c>
-      <c r="O177">
-        <v>3.43</v>
-      </c>
-      <c r="P177">
-        <v>3.4</v>
-      </c>
-      <c r="Q177">
-        <v>2.65</v>
-      </c>
-      <c r="R177">
-        <v>2.08</v>
-      </c>
-      <c r="S177">
-        <v>1.38</v>
-      </c>
-      <c r="T177">
-        <v>2.74</v>
-      </c>
-      <c r="U177">
-        <v>2.82</v>
-      </c>
-      <c r="V177">
-        <v>1.36</v>
-      </c>
-      <c r="W177">
-        <v>1.04</v>
-      </c>
-      <c r="X177">
-        <v>1.01</v>
-      </c>
-      <c r="Y177">
-        <v>1.27</v>
-      </c>
-      <c r="Z177">
-        <v>3.14</v>
-      </c>
-      <c r="AA177">
-        <v>2.04</v>
-      </c>
-      <c r="AB177">
-        <v>1.8</v>
-      </c>
-      <c r="AC177">
-        <v>3.28</v>
-      </c>
-      <c r="AD177">
-        <v>1.25</v>
-      </c>
-      <c r="AE177">
-        <v>1.11</v>
-      </c>
-      <c r="AF177">
-        <v>1.76</v>
-      </c>
-      <c r="AG177">
-        <v>1.96</v>
-      </c>
       <c r="AH177" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK177">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,80 +31442,80 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="O191">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="P191">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q191">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R191">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S191">
+        <v>1.25</v>
+      </c>
+      <c r="T191">
+        <v>3.4</v>
+      </c>
+      <c r="U191">
+        <v>2.3</v>
+      </c>
+      <c r="V191">
+        <v>1.47</v>
+      </c>
+      <c r="W191">
+        <v>1.12</v>
+      </c>
+      <c r="X191">
+        <v>1.03</v>
+      </c>
+      <c r="Y191">
         <v>1.16</v>
       </c>
-      <c r="T191">
+      <c r="Z191">
         <v>4.15</v>
       </c>
-      <c r="U191">
+      <c r="AA191">
+        <v>1.65</v>
+      </c>
+      <c r="AB191">
+        <v>2.3</v>
+      </c>
+      <c r="AC191">
+        <v>2.56</v>
+      </c>
+      <c r="AD191">
+        <v>1.4</v>
+      </c>
+      <c r="AE191">
+        <v>1.12</v>
+      </c>
+      <c r="AF191">
+        <v>1.62</v>
+      </c>
+      <c r="AG191">
+        <v>2.2</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ191">
+        <v>1.22</v>
+      </c>
+      <c r="AK191">
         <v>2</v>
-      </c>
-      <c r="V191">
-        <v>1.76</v>
-      </c>
-      <c r="W191">
-        <v>1.19</v>
-      </c>
-      <c r="X191">
-        <v>1.01</v>
-      </c>
-      <c r="Y191">
-        <v>1.07</v>
-      </c>
-      <c r="Z191">
-        <v>5.85</v>
-      </c>
-      <c r="AA191">
-        <v>1.35</v>
-      </c>
-      <c r="AB191">
-        <v>2.88</v>
-      </c>
-      <c r="AC191">
-        <v>2</v>
-      </c>
-      <c r="AD191">
-        <v>1.73</v>
-      </c>
-      <c r="AE191">
-        <v>1.32</v>
-      </c>
-      <c r="AF191">
-        <v>1.47</v>
-      </c>
-      <c r="AG191">
-        <v>2.63</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ191">
-        <v>1.13</v>
-      </c>
-      <c r="AK191">
-        <v>2.4</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="O192">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P192">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q192">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R192">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S192">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="U192">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V192">
+        <v>1.76</v>
+      </c>
+      <c r="W192">
+        <v>1.19</v>
+      </c>
+      <c r="X192">
+        <v>1.01</v>
+      </c>
+      <c r="Y192">
+        <v>1.07</v>
+      </c>
+      <c r="Z192">
+        <v>5.85</v>
+      </c>
+      <c r="AA192">
+        <v>1.35</v>
+      </c>
+      <c r="AB192">
+        <v>2.88</v>
+      </c>
+      <c r="AC192">
+        <v>2</v>
+      </c>
+      <c r="AD192">
+        <v>1.73</v>
+      </c>
+      <c r="AE192">
+        <v>1.32</v>
+      </c>
+      <c r="AF192">
         <v>1.47</v>
       </c>
-      <c r="W192">
-        <v>1.12</v>
-      </c>
-      <c r="X192">
-        <v>1.03</v>
-      </c>
-      <c r="Y192">
-        <v>1.16</v>
-      </c>
-      <c r="Z192">
-        <v>4.15</v>
-      </c>
-      <c r="AA192">
-        <v>1.65</v>
-      </c>
-      <c r="AB192">
-        <v>2.3</v>
-      </c>
-      <c r="AC192">
-        <v>2.56</v>
-      </c>
-      <c r="AD192">
-        <v>1.4</v>
-      </c>
-      <c r="AE192">
-        <v>1.12</v>
-      </c>
-      <c r="AF192">
-        <v>1.62</v>
-      </c>
       <c r="AG192">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK192">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -34059,13 +34059,13 @@
         <v>2.1</v>
       </c>
       <c r="Q207">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="R207">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S207">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T207">
         <v>2.75</v>
@@ -34089,7 +34089,7 @@
         <v>2.92</v>
       </c>
       <c r="AA207">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB207">
         <v>1.7</v>
@@ -34104,10 +34104,10 @@
         <v>1.05</v>
       </c>
       <c r="AF207">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG207">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>1.25</v>
       </c>
       <c r="AK207">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34551,7 +34551,7 @@
         <v>1.57</v>
       </c>
       <c r="R210">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S210">
         <v>1.28</v>
@@ -34578,7 +34578,7 @@
         <v>3.5</v>
       </c>
       <c r="AA210">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB210">
         <v>2</v>
@@ -34612,7 +34612,7 @@
         <v>1.05</v>
       </c>
       <c r="AK210">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O211">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="P211">
-        <v>3.38</v>
+        <v>2.68</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,80 +37636,80 @@
         </is>
       </c>
       <c r="N229">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="O229">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P229">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q229">
-        <v>4.23</v>
+        <v>2.8</v>
       </c>
       <c r="R229">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S229">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T229">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U229">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V229">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W229">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
+        <v>1.27</v>
+      </c>
+      <c r="Z229">
+        <v>3.14</v>
+      </c>
+      <c r="AA229">
+        <v>1.95</v>
+      </c>
+      <c r="AB229">
+        <v>1.73</v>
+      </c>
+      <c r="AC229">
+        <v>3.34</v>
+      </c>
+      <c r="AD229">
+        <v>1.24</v>
+      </c>
+      <c r="AE229">
+        <v>1.04</v>
+      </c>
+      <c r="AF229">
+        <v>1.74</v>
+      </c>
+      <c r="AG229">
+        <v>1.94</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
         <v>1.29</v>
       </c>
-      <c r="Z229">
-        <v>3.04</v>
-      </c>
-      <c r="AA229">
-        <v>2.01</v>
-      </c>
-      <c r="AB229">
-        <v>1.69</v>
-      </c>
-      <c r="AC229">
-        <v>3.58</v>
-      </c>
-      <c r="AD229">
-        <v>1.21</v>
-      </c>
-      <c r="AE229">
-        <v>1.03</v>
-      </c>
-      <c r="AF229">
-        <v>1.8</v>
-      </c>
-      <c r="AG229">
-        <v>1.87</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ229">
-        <v>1.24</v>
-      </c>
       <c r="AK229">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,80 +37799,80 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="O230">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P230">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q230">
-        <v>2.8</v>
+        <v>4.23</v>
       </c>
       <c r="R230">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S230">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T230">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U230">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V230">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W230">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z230">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA230">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB230">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC230">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD230">
+        <v>1.21</v>
+      </c>
+      <c r="AE230">
+        <v>1.03</v>
+      </c>
+      <c r="AF230">
+        <v>1.8</v>
+      </c>
+      <c r="AG230">
+        <v>1.87</v>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ230">
         <v>1.24</v>
       </c>
-      <c r="AE230">
-        <v>1.04</v>
-      </c>
-      <c r="AF230">
-        <v>1.74</v>
-      </c>
-      <c r="AG230">
-        <v>1.94</v>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ230">
-        <v>1.29</v>
-      </c>
       <c r="AK230">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38949,7 +38949,7 @@
         <v>2.05</v>
       </c>
       <c r="Q237">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="R237">
         <v>1.99</v>
@@ -38961,10 +38961,10 @@
         <v>2.57</v>
       </c>
       <c r="U237">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="V237">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W237">
         <v>1.03</v>
@@ -38973,31 +38973,31 @@
         <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z237">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA237">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AB237">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC237">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="AD237">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE237">
         <v>1.04</v>
       </c>
       <c r="AF237">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG237">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.26</v>
       </c>
       <c r="AK237">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O239">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P239">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q239">
         <v>2.5</v>
@@ -39281,16 +39281,16 @@
         <v>2.1</v>
       </c>
       <c r="S239">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U239">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V239">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W239">
         <v>1.06</v>
@@ -39299,31 +39299,31 @@
         <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z239">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA239">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB239">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC239">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD239">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE239">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF239">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AG239">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39438,55 +39438,55 @@
         <v>2.5</v>
       </c>
       <c r="Q240">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R240">
         <v>2</v>
       </c>
       <c r="S240">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T240">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="U240">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V240">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W240">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X240">
         <v>1.04</v>
       </c>
       <c r="Y240">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z240">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA240">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB240">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC240">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="AD240">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE240">
         <v>1.03</v>
       </c>
       <c r="AF240">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG240">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>1.3</v>
       </c>
       <c r="AK240">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -42046,22 +42046,22 @@
         <v>3.99</v>
       </c>
       <c r="Q256">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="R256">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S256">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T256">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="U256">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V256">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W256">
         <v>1.05</v>
@@ -42070,31 +42070,31 @@
         <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z256">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA256">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB256">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC256">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD256">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE256">
         <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG256">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK256">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -45173,25 +45173,25 @@
         <v>2.88</v>
       </c>
       <c r="AA275">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB275">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC275">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD275">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE275">
         <v>1.05</v>
       </c>
       <c r="AF275">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG275">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK275">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -46278,7 +46278,7 @@
         <v>1.85</v>
       </c>
       <c r="O282">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P282">
         <v>3.25</v>
@@ -46770,7 +46770,7 @@
         <v>4.05</v>
       </c>
       <c r="P285">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q285">
         <v>1.85</v>
@@ -46803,7 +46803,7 @@
         <v>5.7</v>
       </c>
       <c r="AA285">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB285">
         <v>2.83</v>
@@ -48729,16 +48729,16 @@
         <v>2.03</v>
       </c>
       <c r="Q297">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="R297">
         <v>2.13</v>
       </c>
       <c r="S297">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T297">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="U297">
         <v>2.72</v>
@@ -48759,10 +48759,10 @@
         <v>3.2</v>
       </c>
       <c r="AA297">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB297">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC297">
         <v>3.14</v>
@@ -48774,10 +48774,10 @@
         <v>1.07</v>
       </c>
       <c r="AF297">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG297">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK297">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -50024,34 +50024,34 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="O305">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P305">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q305">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R305">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S305">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T305">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="U305">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V305">
         <v>1.62</v>
       </c>
       <c r="W305">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X305">
         <v>0</v>
@@ -50060,28 +50060,28 @@
         <v>1.11</v>
       </c>
       <c r="Z305">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA305">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB305">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC305">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AD305">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE305">
         <v>1.2</v>
       </c>
       <c r="AF305">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG305">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK305">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50187,31 +50187,31 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O306">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P306">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q306">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="R306">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S306">
         <v>1.29</v>
       </c>
       <c r="T306">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="U306">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V306">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W306">
         <v>1.09</v>
@@ -50226,25 +50226,25 @@
         <v>4.5</v>
       </c>
       <c r="AA306">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB306">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC306">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AD306">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE306">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF306">
         <v>1.7</v>
       </c>
       <c r="AG306">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>1.14</v>
       </c>
       <c r="AK306">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -56218,64 +56218,64 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="O343">
-        <v>4.03</v>
+        <v>3.6</v>
       </c>
       <c r="P343">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="Q343">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R343">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S343">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T343">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U343">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V343">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W343">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X343">
         <v>0</v>
       </c>
       <c r="Y343">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z343">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA343">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB343">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC343">
         <v>1.9</v>
       </c>
       <c r="AD343">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE343">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF343">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG343">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH343" t="inlineStr">
         <is>
@@ -56288,10 +56288,10 @@
         </is>
       </c>
       <c r="AJ343">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK343">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56384,61 +56384,61 @@
         <v>2.12</v>
       </c>
       <c r="O344">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="P344">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="Q344">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R344">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S344">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T344">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U344">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V344">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W344">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X344">
         <v>0</v>
       </c>
       <c r="Y344">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z344">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="AA344">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB344">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC344">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AD344">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE344">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF344">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG344">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK344">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56544,64 +56544,64 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O345">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="P345">
-        <v>4.12</v>
+        <v>3.19</v>
       </c>
       <c r="Q345">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R345">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S345">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T345">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U345">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V345">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W345">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X345">
         <v>0</v>
       </c>
       <c r="Y345">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z345">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA345">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB345">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC345">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AD345">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE345">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF345">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG345">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH345" t="inlineStr">
         <is>
@@ -56614,10 +56614,10 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK345">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56707,64 +56707,64 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="O346">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="P346">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q346">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R346">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S346">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T346">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U346">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V346">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W346">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X346">
         <v>0</v>
       </c>
       <c r="Y346">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z346">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="AA346">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB346">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC346">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AD346">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE346">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF346">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG346">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK346">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,64 +56870,64 @@
         </is>
       </c>
       <c r="N347">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O347">
-        <v>6.46</v>
+        <v>4.6</v>
       </c>
       <c r="P347">
-        <v>8.949999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="Q347">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R347">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S347">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T347">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U347">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V347">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W347">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X347">
         <v>0</v>
       </c>
       <c r="Y347">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z347">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="AA347">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB347">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AC347">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AD347">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AE347">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF347">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG347">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH347" t="inlineStr">
         <is>
@@ -56940,10 +56940,10 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK347">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,64 +57033,64 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O348">
-        <v>5.76</v>
+        <v>3.5</v>
       </c>
       <c r="P348">
-        <v>8.449999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="Q348">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R348">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S348">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T348">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U348">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V348">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W348">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X348">
         <v>0</v>
       </c>
       <c r="Y348">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z348">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA348">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB348">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC348">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AD348">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AE348">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF348">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG348">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57103,10 +57103,10 @@
         </is>
       </c>
       <c r="AJ348">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK348">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL348">
         <v>0</v>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,64 +57196,64 @@
         </is>
       </c>
       <c r="N349">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="O349">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="P349">
-        <v>3.67</v>
+        <v>7.25</v>
       </c>
       <c r="Q349">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R349">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S349">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T349">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U349">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V349">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W349">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X349">
         <v>0</v>
       </c>
       <c r="Y349">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z349">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA349">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB349">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AC349">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD349">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="AE349">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF349">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG349">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH349" t="inlineStr">
         <is>
@@ -57266,10 +57266,10 @@
         </is>
       </c>
       <c r="AJ349">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK349">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL349">
         <v>0</v>
@@ -57522,64 +57522,64 @@
         </is>
       </c>
       <c r="N351">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="O351">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="P351">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Q351">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R351">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S351">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T351">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U351">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V351">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W351">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X351">
         <v>0</v>
       </c>
       <c r="Y351">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z351">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA351">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB351">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC351">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD351">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE351">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF351">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG351">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57592,10 +57592,10 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK351">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,64 +57685,64 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="O352">
-        <v>4.11</v>
+        <v>3.69</v>
       </c>
       <c r="P352">
-        <v>2.41</v>
+        <v>3.34</v>
       </c>
       <c r="Q352">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R352">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S352">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T352">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U352">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V352">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W352">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X352">
         <v>0</v>
       </c>
       <c r="Y352">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z352">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA352">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB352">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC352">
-        <v>1.87</v>
+        <v>2.64</v>
       </c>
       <c r="AD352">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AE352">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF352">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG352">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57755,10 +57755,10 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK352">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>2.11</v>
+        <v>2.51</v>
       </c>
       <c r="O353">
-        <v>3.74</v>
+        <v>4.08</v>
       </c>
       <c r="P353">
-        <v>3.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q353">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R353">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S353">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T353">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U353">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V353">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W353">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X353">
         <v>0</v>
       </c>
       <c r="Y353">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z353">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA353">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="AB353">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AC353">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD353">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE353">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF353">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG353">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57918,10 +57918,10 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK353">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -58337,64 +58337,64 @@
         </is>
       </c>
       <c r="N356">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O356">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="P356">
-        <v>4.17</v>
+        <v>3.76</v>
       </c>
       <c r="Q356">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R356">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S356">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T356">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U356">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V356">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W356">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X356">
         <v>0</v>
       </c>
       <c r="Y356">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z356">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA356">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB356">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC356">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD356">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE356">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF356">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG356">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK356">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58989,64 +58989,64 @@
         </is>
       </c>
       <c r="N360">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="O360">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P360">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q360">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R360">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S360">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T360">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U360">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V360">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W360">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X360">
         <v>0</v>
       </c>
       <c r="Y360">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z360">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA360">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB360">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC360">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD360">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE360">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF360">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG360">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -59059,10 +59059,10 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK360">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL360">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O2">
         <v>3.8</v>
       </c>
       <c r="P2">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q2">
         <v>2.05</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="O5">
         <v>3.38</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1797,7 +1797,7 @@
         <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -1812,7 +1812,7 @@
         <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>4.34</v>
+        <v>4.19</v>
       </c>
       <c r="AA9">
         <v>1.66</v>
@@ -1824,10 +1824,10 @@
         <v>2.52</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.57</v>
@@ -1993,7 +1993,7 @@
         <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
         <v>1.76</v>
@@ -2108,7 +2108,7 @@
         <v>4.1</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q11">
         <v>2.2</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
         <v>3.05</v>
@@ -2597,19 +2597,19 @@
         <v>3.4</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="Q14">
         <v>2.42</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="S14">
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
         <v>2.61</v>
@@ -2618,7 +2618,7 @@
         <v>1.47</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2630,10 +2630,10 @@
         <v>3.82</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB14">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC14">
         <v>2.78</v>
@@ -2664,7 +2664,7 @@
         <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q21">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="U21">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC21">
-        <v>3.43</v>
+        <v>3.15</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="O30">
         <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
         <v>2.87</v>
@@ -5238,10 +5238,10 @@
         <v>3.78</v>
       </c>
       <c r="AA30">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>2.74</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O31">
         <v>3.8</v>
@@ -5392,7 +5392,7 @@
         <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
         <v>1.17</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P36">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q36">
         <v>5.93</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O38">
         <v>3.8</v>
@@ -6859,7 +6859,7 @@
         <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.12</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>5.75</v>
       </c>
       <c r="P42">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q42">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="R42">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="S42">
         <v>1.17</v>
       </c>
       <c r="T42">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -7194,25 +7194,25 @@
         <v>5.9</v>
       </c>
       <c r="AA42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AD42">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE42">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>7.9</v>
       </c>
       <c r="Q49">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R49">
         <v>2.4</v>
@@ -8320,7 +8320,7 @@
         <v>2.44</v>
       </c>
       <c r="V49">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
         <v>1.08</v>
@@ -8341,7 +8341,7 @@
         <v>2.14</v>
       </c>
       <c r="AC49">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AD49">
         <v>1.36</v>
@@ -8369,7 +8369,7 @@
         <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O53">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q53">
         <v>2.05</v>
@@ -8966,7 +8966,7 @@
         <v>1.35</v>
       </c>
       <c r="T53">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U53">
         <v>2.44</v>
@@ -8984,28 +8984,28 @@
         <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AA53">
         <v>1.79</v>
       </c>
       <c r="AB53">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC53">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AD53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF53">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9286,13 +9286,13 @@
         <v>2.73</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U55">
         <v>2.21</v>
@@ -9347,7 +9347,7 @@
         <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9455,10 +9455,10 @@
         <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V56">
         <v>1.44</v>
@@ -9510,7 +9510,7 @@
         <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q58">
         <v>2.67</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="O64">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P64">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q64">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="R64">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="T64">
+        <v>5.4</v>
+      </c>
+      <c r="U64">
+        <v>1.65</v>
+      </c>
+      <c r="V64">
+        <v>2.21</v>
+      </c>
+      <c r="W64">
+        <v>1.32</v>
+      </c>
+      <c r="X64">
+        <v>1</v>
+      </c>
+      <c r="Y64">
+        <v>1.01</v>
+      </c>
+      <c r="Z64">
+        <v>9.9</v>
+      </c>
+      <c r="AA64">
+        <v>1.17</v>
+      </c>
+      <c r="AB64">
+        <v>4.25</v>
+      </c>
+      <c r="AC64">
+        <v>1.51</v>
+      </c>
+      <c r="AD64">
+        <v>2.43</v>
+      </c>
+      <c r="AE64">
+        <v>1.69</v>
+      </c>
+      <c r="AF64">
+        <v>1.26</v>
+      </c>
+      <c r="AG64">
         <v>3.3</v>
       </c>
-      <c r="U64">
-        <v>2.45</v>
-      </c>
-      <c r="V64">
-        <v>1.44</v>
-      </c>
-      <c r="W64">
-        <v>1.11</v>
-      </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.18</v>
       </c>
-      <c r="Z64">
-        <v>3.9</v>
-      </c>
-      <c r="AA64">
-        <v>1.67</v>
-      </c>
-      <c r="AB64">
-        <v>2.1</v>
-      </c>
-      <c r="AC64">
-        <v>2.7</v>
-      </c>
-      <c r="AD64">
-        <v>1.45</v>
-      </c>
-      <c r="AE64">
-        <v>1.12</v>
-      </c>
-      <c r="AF64">
-        <v>1.73</v>
-      </c>
-      <c r="AG64">
-        <v>2</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.22</v>
-      </c>
       <c r="AK64">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="O65">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q65">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="S65">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="V65">
-        <v>2.21</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA65">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC65">
-        <v>1.51</v>
+        <v>2.7</v>
       </c>
       <c r="AD65">
-        <v>2.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE65">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="AF65">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AG65">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O69">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -11577,10 +11577,10 @@
         <v>3.46</v>
       </c>
       <c r="U69">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V69">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
         <v>1.12</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q70">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R70">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA70">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB70">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD70">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.05</v>
+        <v>2.99</v>
       </c>
       <c r="O71">
         <v>3.55</v>
       </c>
       <c r="P71">
-        <v>2.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q71">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V71">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z71">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AB71">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="AC71">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AD71">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AE71">
+        <v>1.14</v>
+      </c>
+      <c r="AF71">
+        <v>1.52</v>
+      </c>
+      <c r="AG71">
+        <v>2.3</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.19</v>
+      </c>
+      <c r="AK71">
         <v>1.25</v>
-      </c>
-      <c r="AF71">
-        <v>1.4</v>
-      </c>
-      <c r="AG71">
-        <v>2.7</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.3</v>
-      </c>
-      <c r="AK71">
-        <v>1.64</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O72">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q72">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="R72">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U72">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>6.01</v>
+        <v>5.15</v>
       </c>
       <c r="AA72">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB72">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="AC72">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AD72">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE72">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.99</v>
+        <v>1.62</v>
       </c>
       <c r="O73">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P73">
-        <v>1.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q73">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="R73">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="S73">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T73">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="U73">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="V73">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>4.3</v>
+        <v>6.01</v>
       </c>
       <c r="AA73">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
+        <v>3.1</v>
+      </c>
+      <c r="AC73">
+        <v>1.93</v>
+      </c>
+      <c r="AD73">
+        <v>1.75</v>
+      </c>
+      <c r="AE73">
+        <v>1.28</v>
+      </c>
+      <c r="AF73">
+        <v>1.44</v>
+      </c>
+      <c r="AG73">
+        <v>2.62</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.2</v>
+      </c>
+      <c r="AK73">
         <v>2.18</v>
-      </c>
-      <c r="AC73">
-        <v>2.43</v>
-      </c>
-      <c r="AD73">
-        <v>1.44</v>
-      </c>
-      <c r="AE73">
-        <v>1.14</v>
-      </c>
-      <c r="AF73">
-        <v>1.52</v>
-      </c>
-      <c r="AG73">
-        <v>2.3</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.19</v>
-      </c>
-      <c r="AK73">
-        <v>1.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13521,10 +13521,10 @@
         <v>2.1</v>
       </c>
       <c r="Q81">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S81">
         <v>1.33</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P82">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="O83">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q83">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R83">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.36</v>
@@ -13871,16 +13871,16 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA83">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB83">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC83">
         <v>2.97</v>
@@ -13892,10 +13892,10 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AG83">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>3.36</v>
       </c>
       <c r="R85">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
         <v>1.4</v>
@@ -14188,7 +14188,7 @@
         <v>2.89</v>
       </c>
       <c r="V85">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W85">
         <v>1.02</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>1.7</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
         <v>3.9</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O89">
         <v>3.4</v>
@@ -14846,7 +14846,7 @@
         <v>1.09</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.22</v>
@@ -14873,7 +14873,7 @@
         <v>1.58</v>
       </c>
       <c r="AG89">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P90">
         <v>3.55</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O92">
         <v>3.25</v>
@@ -15812,7 +15812,7 @@
         <v>1.44</v>
       </c>
       <c r="T95">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U95">
         <v>3.24</v>
@@ -15963,10 +15963,10 @@
         <v>3.7</v>
       </c>
       <c r="P96">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q96">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="R96">
         <v>2.26</v>
@@ -16292,10 +16292,10 @@
         <v>4.44</v>
       </c>
       <c r="Q98">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -16307,13 +16307,13 @@
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W98">
         <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y98">
         <v>1.32</v>
@@ -16328,19 +16328,19 @@
         <v>1.7</v>
       </c>
       <c r="AC98">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD98">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE98">
         <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AG98">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16449,10 +16449,10 @@
         <v>3.9</v>
       </c>
       <c r="O99">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q99">
         <v>4.4</v>
@@ -16630,7 +16630,7 @@
         <v>3.22</v>
       </c>
       <c r="U100">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V100">
         <v>1.49</v>
@@ -16938,7 +16938,7 @@
         <v>1.48</v>
       </c>
       <c r="O102">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P102">
         <v>5.36</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O104">
         <v>3.4</v>
       </c>
       <c r="P104">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="Q104">
         <v>2.32</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="O105">
         <v>3.54</v>
       </c>
       <c r="P105">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="Q105">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R105">
         <v>2.34</v>
@@ -17497,7 +17497,7 @@
         <v>1.26</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17593,7 +17593,7 @@
         <v>3.25</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q106">
         <v>3.02</v>
@@ -17949,13 +17949,13 @@
         <v>1.22</v>
       </c>
       <c r="Z108">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA108">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB108">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC108">
         <v>3</v>
@@ -17967,10 +17967,10 @@
         <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG108">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="O127">
-        <v>8.5</v>
+        <v>4.66</v>
       </c>
       <c r="P127">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="Q127">
+        <v>4.7</v>
+      </c>
+      <c r="R127">
+        <v>2.67</v>
+      </c>
+      <c r="S127">
+        <v>1.2</v>
+      </c>
+      <c r="T127">
+        <v>4.4</v>
+      </c>
+      <c r="U127">
+        <v>1.91</v>
+      </c>
+      <c r="V127">
+        <v>1.76</v>
+      </c>
+      <c r="W127">
+        <v>1.2</v>
+      </c>
+      <c r="X127">
+        <v>1.01</v>
+      </c>
+      <c r="Y127">
+        <v>1.05</v>
+      </c>
+      <c r="Z127">
         <v>7.5</v>
       </c>
-      <c r="R127">
-        <v>3.5</v>
-      </c>
-      <c r="S127">
-        <v>1.11</v>
-      </c>
-      <c r="T127">
-        <v>6</v>
-      </c>
-      <c r="U127">
-        <v>1.53</v>
-      </c>
-      <c r="V127">
-        <v>2.38</v>
-      </c>
-      <c r="W127">
+      <c r="AA127">
+        <v>1.37</v>
+      </c>
+      <c r="AB127">
+        <v>3.16</v>
+      </c>
+      <c r="AC127">
+        <v>1.96</v>
+      </c>
+      <c r="AD127">
+        <v>1.9</v>
+      </c>
+      <c r="AE127">
+        <v>1.38</v>
+      </c>
+      <c r="AF127">
         <v>1.44</v>
       </c>
-      <c r="X127">
-        <v>1</v>
-      </c>
-      <c r="Y127">
-        <v>1.04</v>
-      </c>
-      <c r="Z127">
-        <v>15</v>
-      </c>
-      <c r="AA127">
-        <v>1.14</v>
-      </c>
-      <c r="AB127">
-        <v>6</v>
-      </c>
-      <c r="AC127">
-        <v>1.38</v>
-      </c>
-      <c r="AD127">
-        <v>2.98</v>
-      </c>
-      <c r="AE127">
-        <v>1.89</v>
-      </c>
-      <c r="AF127">
-        <v>1.4</v>
-      </c>
       <c r="AG127">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
       <c r="AK127">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O128">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="P128">
-        <v>2.16</v>
+        <v>6.25</v>
       </c>
       <c r="Q128">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="R128">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S128">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T128">
         <v>4</v>
       </c>
       <c r="U128">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V128">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W128">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z128">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="AA128">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB128">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AC128">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD128">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE128">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF128">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AG128">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK128">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O129">
-        <v>4.66</v>
+        <v>3.84</v>
       </c>
       <c r="P129">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q129">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="R129">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U129">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>7.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA129">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>3.16</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AD129">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG129">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AK129">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.43</v>
+        <v>9.75</v>
       </c>
       <c r="O130">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="P130">
-        <v>6.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q130">
-        <v>1.75</v>
+        <v>7.5</v>
       </c>
       <c r="R130">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="S130">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U130">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="V130">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="W130">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y130">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z130">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA130">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AB130">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC130">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AD130">
-        <v>1.79</v>
+        <v>2.99</v>
       </c>
       <c r="AE130">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="AF130">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG130">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>2.75</v>
+        <v>1.05</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21991,7 +21991,7 @@
         <v>2.62</v>
       </c>
       <c r="O133">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="P133">
         <v>2.5</v>
@@ -22027,19 +22027,19 @@
         <v>4.2</v>
       </c>
       <c r="AA133">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB133">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC133">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AD133">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE133">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF133">
         <v>1.54</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK133">
         <v>1.44</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="O134">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q134">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R134">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S134">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T134">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="U134">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="V134">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
+        <v>1.22</v>
+      </c>
+      <c r="Z134">
+        <v>3.74</v>
+      </c>
+      <c r="AA134">
+        <v>1.8</v>
+      </c>
+      <c r="AB134">
+        <v>1.95</v>
+      </c>
+      <c r="AC134">
+        <v>3</v>
+      </c>
+      <c r="AD134">
+        <v>1.36</v>
+      </c>
+      <c r="AE134">
         <v>1.1</v>
       </c>
-      <c r="Z134">
-        <v>5.1</v>
-      </c>
-      <c r="AA134">
-        <v>1.5</v>
-      </c>
-      <c r="AB134">
-        <v>2.6</v>
-      </c>
-      <c r="AC134">
-        <v>2.25</v>
-      </c>
-      <c r="AD134">
-        <v>1.69</v>
-      </c>
-      <c r="AE134">
-        <v>1.26</v>
-      </c>
       <c r="AF134">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG134">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK134">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.74</v>
+        <v>1.68</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P135">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q135">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R135">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="S135">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T135">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="U135">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="V135">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z135">
-        <v>3.74</v>
+        <v>5.1</v>
       </c>
       <c r="AA135">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB135">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AC135">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD135">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF135">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG135">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK135">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23171,7 +23171,7 @@
         <v>1.61</v>
       </c>
       <c r="AB140">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC140">
         <v>2.61</v>
@@ -23509,7 +23509,7 @@
         <v>1.1</v>
       </c>
       <c r="AF142">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG142">
         <v>1.73</v>
@@ -23950,7 +23950,7 @@
         <v>3.3</v>
       </c>
       <c r="P145">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q145">
         <v>2.88</v>
@@ -23992,7 +23992,7 @@
         <v>2.92</v>
       </c>
       <c r="AD145">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE145">
         <v>1.08</v>
@@ -24762,7 +24762,7 @@
         <v>2.15</v>
       </c>
       <c r="O150">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P150">
         <v>3</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O151">
         <v>3.4</v>
@@ -24940,7 +24940,7 @@
         <v>1.4</v>
       </c>
       <c r="T151">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U151">
         <v>2.82</v>
@@ -25088,7 +25088,7 @@
         <v>1.67</v>
       </c>
       <c r="O152">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P152">
         <v>4.8</v>
@@ -25257,19 +25257,19 @@
         <v>3.1</v>
       </c>
       <c r="Q153">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R153">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S153">
         <v>1.32</v>
       </c>
       <c r="T153">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="U153">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V153">
         <v>1.48</v>
@@ -25293,7 +25293,7 @@
         <v>1.95</v>
       </c>
       <c r="AC153">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="AD153">
         <v>1.33</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
+        <v>3.8</v>
+      </c>
+      <c r="O154">
+        <v>3.7</v>
+      </c>
+      <c r="P154">
+        <v>1.85</v>
+      </c>
+      <c r="Q154">
         <v>4.2</v>
       </c>
-      <c r="O154">
-        <v>4.2</v>
-      </c>
-      <c r="P154">
-        <v>1.62</v>
-      </c>
-      <c r="Q154">
-        <v>3.9</v>
-      </c>
       <c r="R154">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S154">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="V154">
+        <v>1.52</v>
+      </c>
+      <c r="W154">
+        <v>1.1</v>
+      </c>
+      <c r="X154">
+        <v>1.02</v>
+      </c>
+      <c r="Y154">
+        <v>1.16</v>
+      </c>
+      <c r="Z154">
+        <v>4.1</v>
+      </c>
+      <c r="AA154">
+        <v>1.67</v>
+      </c>
+      <c r="AB154">
+        <v>2.11</v>
+      </c>
+      <c r="AC154">
+        <v>2.72</v>
+      </c>
+      <c r="AD154">
+        <v>1.42</v>
+      </c>
+      <c r="AE154">
+        <v>1.11</v>
+      </c>
+      <c r="AF154">
         <v>1.57</v>
       </c>
-      <c r="W154">
-        <v>1.13</v>
-      </c>
-      <c r="X154">
-        <v>1.03</v>
-      </c>
-      <c r="Y154">
-        <v>1.13</v>
-      </c>
-      <c r="Z154">
-        <v>4.6</v>
-      </c>
-      <c r="AA154">
-        <v>1.54</v>
-      </c>
-      <c r="AB154">
-        <v>2.3</v>
-      </c>
-      <c r="AC154">
-        <v>2.31</v>
-      </c>
-      <c r="AD154">
-        <v>1.54</v>
-      </c>
-      <c r="AE154">
-        <v>1.19</v>
-      </c>
-      <c r="AF154">
-        <v>1.56</v>
-      </c>
       <c r="AG154">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AK154">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="O155">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P155">
+        <v>3.25</v>
+      </c>
+      <c r="Q155">
+        <v>2.55</v>
+      </c>
+      <c r="R155">
+        <v>2.25</v>
+      </c>
+      <c r="S155">
+        <v>1.34</v>
+      </c>
+      <c r="T155">
+        <v>2.7</v>
+      </c>
+      <c r="U155">
+        <v>2.67</v>
+      </c>
+      <c r="V155">
+        <v>1.4</v>
+      </c>
+      <c r="W155">
+        <v>1.05</v>
+      </c>
+      <c r="X155">
+        <v>1.01</v>
+      </c>
+      <c r="Y155">
+        <v>1.24</v>
+      </c>
+      <c r="Z155">
+        <v>3.51</v>
+      </c>
+      <c r="AA155">
+        <v>1.93</v>
+      </c>
+      <c r="AB155">
         <v>1.85</v>
       </c>
-      <c r="Q155">
-        <v>4.2</v>
-      </c>
-      <c r="R155">
-        <v>2.26</v>
-      </c>
-      <c r="S155">
-        <v>1.3</v>
-      </c>
-      <c r="T155">
-        <v>3.3</v>
-      </c>
-      <c r="U155">
-        <v>2.32</v>
-      </c>
-      <c r="V155">
-        <v>1.52</v>
-      </c>
-      <c r="W155">
-        <v>1.1</v>
-      </c>
-      <c r="X155">
-        <v>1.02</v>
-      </c>
-      <c r="Y155">
-        <v>1.16</v>
-      </c>
-      <c r="Z155">
-        <v>4.1</v>
-      </c>
-      <c r="AA155">
-        <v>1.67</v>
-      </c>
-      <c r="AB155">
-        <v>2.11</v>
-      </c>
       <c r="AC155">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AD155">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE155">
         <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG155">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK155">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="Q156">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="R156">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T156">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W156">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z156">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AA156">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AB156">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC156">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="AD156">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE156">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="O157">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q157">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="R157">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S157">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T157">
+        <v>2.66</v>
+      </c>
+      <c r="U157">
         <v>2.7</v>
       </c>
-      <c r="U157">
-        <v>2.67</v>
-      </c>
       <c r="V157">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z157">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="AA157">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB157">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC157">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD157">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE157">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG157">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
+        <v>4.15</v>
+      </c>
+      <c r="O158">
+        <v>4.2</v>
+      </c>
+      <c r="P158">
+        <v>1.63</v>
+      </c>
+      <c r="Q158">
+        <v>3.9</v>
+      </c>
+      <c r="R158">
+        <v>2.28</v>
+      </c>
+      <c r="S158">
+        <v>1.23</v>
+      </c>
+      <c r="T158">
+        <v>3.5</v>
+      </c>
+      <c r="U158">
+        <v>2.21</v>
+      </c>
+      <c r="V158">
+        <v>1.57</v>
+      </c>
+      <c r="W158">
+        <v>1.13</v>
+      </c>
+      <c r="X158">
+        <v>1.03</v>
+      </c>
+      <c r="Y158">
+        <v>1.13</v>
+      </c>
+      <c r="Z158">
+        <v>4.6</v>
+      </c>
+      <c r="AA158">
+        <v>1.54</v>
+      </c>
+      <c r="AB158">
         <v>2.3</v>
       </c>
-      <c r="O158">
-        <v>3.3</v>
-      </c>
-      <c r="P158">
-        <v>2.98</v>
-      </c>
-      <c r="Q158">
-        <v>2.69</v>
-      </c>
-      <c r="R158">
-        <v>1.98</v>
-      </c>
-      <c r="S158">
-        <v>1.45</v>
-      </c>
-      <c r="T158">
-        <v>2.5</v>
-      </c>
-      <c r="U158">
-        <v>3</v>
-      </c>
-      <c r="V158">
-        <v>1.32</v>
-      </c>
-      <c r="W158">
-        <v>1.04</v>
-      </c>
-      <c r="X158">
-        <v>1.04</v>
-      </c>
-      <c r="Y158">
-        <v>1.34</v>
-      </c>
-      <c r="Z158">
-        <v>2.78</v>
-      </c>
-      <c r="AA158">
-        <v>2.22</v>
-      </c>
-      <c r="AB158">
-        <v>1.7</v>
-      </c>
       <c r="AC158">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="AD158">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE158">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AF158">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG158">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK158">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27874,7 +27874,7 @@
         <v>1.15</v>
       </c>
       <c r="T169">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="U169">
         <v>1.83</v>
@@ -27910,7 +27910,7 @@
         <v>1.4</v>
       </c>
       <c r="AF169">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG169">
         <v>3.25</v>
@@ -28182,7 +28182,7 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O171">
         <v>3.57</v>
@@ -28348,10 +28348,10 @@
         <v>2.25</v>
       </c>
       <c r="O172">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P172">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q172">
         <v>2.73</v>
@@ -28396,7 +28396,7 @@
         <v>1.49</v>
       </c>
       <c r="AE172">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF172">
         <v>1.49</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O173">
         <v>3.43</v>
@@ -28550,7 +28550,7 @@
         <v>2.04</v>
       </c>
       <c r="AB173">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC173">
         <v>3.28</v>
@@ -28692,7 +28692,7 @@
         <v>3.3</v>
       </c>
       <c r="U174">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="V174">
         <v>1.43</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="O175">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P175">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q175">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="R175">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S175">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T175">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="U175">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X175">
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z175">
-        <v>3.04</v>
+        <v>4.25</v>
       </c>
       <c r="AA175">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AB175">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AC175">
-        <v>3.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD175">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AE175">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF175">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AG175">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AK175">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="O176">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P176">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q176">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="R176">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S176">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T176">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="U176">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V176">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W176">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z176">
-        <v>4.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA176">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AB176">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AC176">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="AD176">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AE176">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF176">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AG176">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AK176">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>1.14</v>
       </c>
       <c r="AF177">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG177">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>3.5</v>
       </c>
       <c r="P180">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q180">
         <v>2.4</v>
@@ -29667,7 +29667,7 @@
         <v>1.3</v>
       </c>
       <c r="T180">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U180">
         <v>2.59</v>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="O181">
         <v>8.25</v>
@@ -29869,7 +29869,7 @@
         <v>1.9</v>
       </c>
       <c r="AG181">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29978,16 +29978,16 @@
         <v>2.67</v>
       </c>
       <c r="O182">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P182">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q182">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R182">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S182">
         <v>1.29</v>
@@ -30023,16 +30023,16 @@
         <v>2.61</v>
       </c>
       <c r="AD182">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE182">
         <v>1.14</v>
       </c>
       <c r="AF182">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG182">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30159,10 +30159,10 @@
         <v>3.78</v>
       </c>
       <c r="U183">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V183">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W183">
         <v>1.16</v>
@@ -30340,7 +30340,7 @@
         <v>2.74</v>
       </c>
       <c r="AA184">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB184">
         <v>1.64</v>
@@ -30666,7 +30666,7 @@
         <v>3.88</v>
       </c>
       <c r="AA186">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB186">
         <v>2.09</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O187">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P187">
-        <v>4.33</v>
+        <v>6.06</v>
       </c>
       <c r="Q187">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R187">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S187">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T187">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U187">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V187">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="W187">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X187">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z187">
-        <v>4.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA187">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB187">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AC187">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AD187">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AE187">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF187">
         <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK187">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,80 +30953,80 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O188">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q188">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="R188">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S188">
+        <v>1.29</v>
+      </c>
+      <c r="T188">
+        <v>3.3</v>
+      </c>
+      <c r="U188">
+        <v>2.31</v>
+      </c>
+      <c r="V188">
+        <v>1.5</v>
+      </c>
+      <c r="W188">
+        <v>1.09</v>
+      </c>
+      <c r="X188">
+        <v>1.01</v>
+      </c>
+      <c r="Y188">
+        <v>1.19</v>
+      </c>
+      <c r="Z188">
+        <v>4.15</v>
+      </c>
+      <c r="AA188">
+        <v>1.67</v>
+      </c>
+      <c r="AB188">
+        <v>2.15</v>
+      </c>
+      <c r="AC188">
+        <v>2.5</v>
+      </c>
+      <c r="AD188">
+        <v>1.49</v>
+      </c>
+      <c r="AE188">
+        <v>1.19</v>
+      </c>
+      <c r="AF188">
+        <v>1.57</v>
+      </c>
+      <c r="AG188">
+        <v>2.38</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ188">
+        <v>1.27</v>
+      </c>
+      <c r="AK188">
         <v>1.33</v>
-      </c>
-      <c r="T188">
-        <v>3</v>
-      </c>
-      <c r="U188">
-        <v>2.75</v>
-      </c>
-      <c r="V188">
-        <v>1.4</v>
-      </c>
-      <c r="W188">
-        <v>1.06</v>
-      </c>
-      <c r="X188">
-        <v>1.03</v>
-      </c>
-      <c r="Y188">
-        <v>1.23</v>
-      </c>
-      <c r="Z188">
-        <v>3.42</v>
-      </c>
-      <c r="AA188">
-        <v>1.9</v>
-      </c>
-      <c r="AB188">
-        <v>1.82</v>
-      </c>
-      <c r="AC188">
-        <v>2.96</v>
-      </c>
-      <c r="AD188">
-        <v>1.3</v>
-      </c>
-      <c r="AE188">
-        <v>1.08</v>
-      </c>
-      <c r="AF188">
-        <v>1.87</v>
-      </c>
-      <c r="AG188">
-        <v>1.9</v>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ188">
-        <v>1.22</v>
-      </c>
-      <c r="AK188">
-        <v>2</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,80 +31279,80 @@
         </is>
       </c>
       <c r="N190">
+        <v>1.71</v>
+      </c>
+      <c r="O190">
+        <v>3.7</v>
+      </c>
+      <c r="P190">
+        <v>4.4</v>
+      </c>
+      <c r="Q190">
+        <v>2.16</v>
+      </c>
+      <c r="R190">
+        <v>2.11</v>
+      </c>
+      <c r="S190">
         <v>1.33</v>
       </c>
-      <c r="O190">
-        <v>5</v>
-      </c>
-      <c r="P190">
-        <v>6.06</v>
-      </c>
-      <c r="Q190">
-        <v>1.8</v>
-      </c>
-      <c r="R190">
-        <v>2.7</v>
-      </c>
-      <c r="S190">
-        <v>1.2</v>
-      </c>
       <c r="T190">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="U190">
+        <v>2.75</v>
+      </c>
+      <c r="V190">
+        <v>1.4</v>
+      </c>
+      <c r="W190">
+        <v>1.06</v>
+      </c>
+      <c r="X190">
+        <v>1.03</v>
+      </c>
+      <c r="Y190">
+        <v>1.23</v>
+      </c>
+      <c r="Z190">
+        <v>3.42</v>
+      </c>
+      <c r="AA190">
+        <v>1.9</v>
+      </c>
+      <c r="AB190">
+        <v>1.82</v>
+      </c>
+      <c r="AC190">
+        <v>2.95</v>
+      </c>
+      <c r="AD190">
+        <v>1.3</v>
+      </c>
+      <c r="AE190">
+        <v>1.08</v>
+      </c>
+      <c r="AF190">
+        <v>1.87</v>
+      </c>
+      <c r="AG190">
+        <v>1.9</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
+        <v>1.22</v>
+      </c>
+      <c r="AK190">
         <v>2</v>
-      </c>
-      <c r="V190">
-        <v>1.71</v>
-      </c>
-      <c r="W190">
-        <v>1.17</v>
-      </c>
-      <c r="X190">
-        <v>1.01</v>
-      </c>
-      <c r="Y190">
-        <v>1.08</v>
-      </c>
-      <c r="Z190">
-        <v>5.45</v>
-      </c>
-      <c r="AA190">
-        <v>1.38</v>
-      </c>
-      <c r="AB190">
-        <v>3</v>
-      </c>
-      <c r="AC190">
-        <v>2.03</v>
-      </c>
-      <c r="AD190">
-        <v>1.83</v>
-      </c>
-      <c r="AE190">
-        <v>1.33</v>
-      </c>
-      <c r="AF190">
-        <v>1.57</v>
-      </c>
-      <c r="AG190">
-        <v>2.25</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ190">
-        <v>1.17</v>
-      </c>
-      <c r="AK190">
-        <v>2.7</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O191">
         <v>3.9</v>
@@ -31451,55 +31451,55 @@
         <v>4.33</v>
       </c>
       <c r="Q191">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R191">
         <v>2.38</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T191">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U191">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V191">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W191">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X191">
         <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z191">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA191">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB191">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC191">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="AD191">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE191">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF191">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG191">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK191">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,80 +31605,80 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="O192">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="P192">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q192">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R192">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S192">
+        <v>1.25</v>
+      </c>
+      <c r="T192">
+        <v>3.4</v>
+      </c>
+      <c r="U192">
+        <v>2.3</v>
+      </c>
+      <c r="V192">
+        <v>1.47</v>
+      </c>
+      <c r="W192">
+        <v>1.12</v>
+      </c>
+      <c r="X192">
+        <v>1.03</v>
+      </c>
+      <c r="Y192">
         <v>1.16</v>
       </c>
-      <c r="T192">
+      <c r="Z192">
         <v>4.15</v>
       </c>
-      <c r="U192">
+      <c r="AA192">
+        <v>1.65</v>
+      </c>
+      <c r="AB192">
+        <v>2.3</v>
+      </c>
+      <c r="AC192">
+        <v>2.56</v>
+      </c>
+      <c r="AD192">
+        <v>1.4</v>
+      </c>
+      <c r="AE192">
+        <v>1.12</v>
+      </c>
+      <c r="AF192">
+        <v>1.62</v>
+      </c>
+      <c r="AG192">
+        <v>2.2</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ192">
+        <v>1.22</v>
+      </c>
+      <c r="AK192">
         <v>2</v>
-      </c>
-      <c r="V192">
-        <v>1.76</v>
-      </c>
-      <c r="W192">
-        <v>1.19</v>
-      </c>
-      <c r="X192">
-        <v>1.01</v>
-      </c>
-      <c r="Y192">
-        <v>1.07</v>
-      </c>
-      <c r="Z192">
-        <v>5.85</v>
-      </c>
-      <c r="AA192">
-        <v>1.35</v>
-      </c>
-      <c r="AB192">
-        <v>2.88</v>
-      </c>
-      <c r="AC192">
-        <v>2</v>
-      </c>
-      <c r="AD192">
-        <v>1.73</v>
-      </c>
-      <c r="AE192">
-        <v>1.32</v>
-      </c>
-      <c r="AF192">
-        <v>1.47</v>
-      </c>
-      <c r="AG192">
-        <v>2.63</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ192">
-        <v>1.13</v>
-      </c>
-      <c r="AK192">
-        <v>2.4</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P193">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="Q193">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="R193">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S193">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T193">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="U193">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="V193">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W193">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X193">
         <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z193">
-        <v>4.15</v>
+        <v>5.85</v>
       </c>
       <c r="AA193">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AB193">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AC193">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD193">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE193">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AF193">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG193">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK193">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31934,7 +31934,7 @@
         <v>2.45</v>
       </c>
       <c r="O194">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P194">
         <v>2.37</v>
@@ -31958,7 +31958,7 @@
         <v>1.51</v>
       </c>
       <c r="W194">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X194">
         <v>1.01</v>
@@ -31967,7 +31967,7 @@
         <v>1.14</v>
       </c>
       <c r="Z194">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="AA194">
         <v>1.58</v>
@@ -31988,7 +31988,7 @@
         <v>1.55</v>
       </c>
       <c r="AG194">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>3</v>
       </c>
       <c r="U195">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="V195">
         <v>1.44</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O198">
         <v>3.7</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK198">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32770,7 +32770,7 @@
         <v>2.8</v>
       </c>
       <c r="V199">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W199">
         <v>1.07</v>
@@ -32909,16 +32909,16 @@
         </is>
       </c>
       <c r="N200">
-        <v>4.16</v>
+        <v>4.33</v>
       </c>
       <c r="O200">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P200">
         <v>1.8</v>
       </c>
       <c r="Q200">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="R200">
         <v>2.32</v>
@@ -32954,7 +32954,7 @@
         <v>2.02</v>
       </c>
       <c r="AC200">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AD200">
         <v>1.34</v>
@@ -32979,7 +32979,7 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AK200">
         <v>1.22</v>
@@ -33754,7 +33754,7 @@
         <v>1.09</v>
       </c>
       <c r="X205">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
         <v>1.17</v>
@@ -34213,7 +34213,7 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O208">
         <v>3.3</v>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK208">
         <v>1.83</v>
@@ -34379,10 +34379,10 @@
         <v>1.76</v>
       </c>
       <c r="O209">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P209">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -34403,7 +34403,7 @@
         <v>1.7</v>
       </c>
       <c r="W209">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X209">
         <v>1.01</v>
@@ -34421,7 +34421,7 @@
         <v>2.87</v>
       </c>
       <c r="AC209">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD209">
         <v>1.84</v>
@@ -34433,7 +34433,7 @@
         <v>1.39</v>
       </c>
       <c r="AG209">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -35037,55 +35037,55 @@
         <v>5.36</v>
       </c>
       <c r="Q213">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R213">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S213">
         <v>1.28</v>
       </c>
       <c r="T213">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U213">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="V213">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W213">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
         <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z213">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA213">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB213">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC213">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AD213">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE213">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF213">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG213">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK213">
         <v>3.3</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,80 +35680,80 @@
         </is>
       </c>
       <c r="N217">
+        <v>5</v>
+      </c>
+      <c r="O217">
+        <v>4.6</v>
+      </c>
+      <c r="P217">
+        <v>1.44</v>
+      </c>
+      <c r="Q217">
+        <v>4.62</v>
+      </c>
+      <c r="R217">
+        <v>2.4</v>
+      </c>
+      <c r="S217">
+        <v>1.19</v>
+      </c>
+      <c r="T217">
+        <v>3.82</v>
+      </c>
+      <c r="U217">
+        <v>2.13</v>
+      </c>
+      <c r="V217">
+        <v>1.67</v>
+      </c>
+      <c r="W217">
+        <v>1.13</v>
+      </c>
+      <c r="X217">
+        <v>1.02</v>
+      </c>
+      <c r="Y217">
+        <v>1.09</v>
+      </c>
+      <c r="Z217">
+        <v>5.3</v>
+      </c>
+      <c r="AA217">
+        <v>1.42</v>
+      </c>
+      <c r="AB217">
+        <v>2.49</v>
+      </c>
+      <c r="AC217">
+        <v>2.19</v>
+      </c>
+      <c r="AD217">
+        <v>1.65</v>
+      </c>
+      <c r="AE217">
+        <v>1.21</v>
+      </c>
+      <c r="AF217">
+        <v>1.57</v>
+      </c>
+      <c r="AG217">
+        <v>2.26</v>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ217">
         <v>2.5</v>
       </c>
-      <c r="O217">
-        <v>3.4</v>
-      </c>
-      <c r="P217">
-        <v>2.4</v>
-      </c>
-      <c r="Q217">
-        <v>3.24</v>
-      </c>
-      <c r="R217">
-        <v>2.28</v>
-      </c>
-      <c r="S217">
-        <v>1.27</v>
-      </c>
-      <c r="T217">
-        <v>3.4</v>
-      </c>
-      <c r="U217">
-        <v>2.29</v>
-      </c>
-      <c r="V217">
-        <v>1.53</v>
-      </c>
-      <c r="W217">
-        <v>1.11</v>
-      </c>
-      <c r="X217">
-        <v>1.01</v>
-      </c>
-      <c r="Y217">
-        <v>1.2</v>
-      </c>
-      <c r="Z217">
-        <v>4.58</v>
-      </c>
-      <c r="AA217">
-        <v>1.61</v>
-      </c>
-      <c r="AB217">
-        <v>2.25</v>
-      </c>
-      <c r="AC217">
-        <v>2.55</v>
-      </c>
-      <c r="AD217">
-        <v>1.47</v>
-      </c>
-      <c r="AE217">
-        <v>1.18</v>
-      </c>
-      <c r="AF217">
-        <v>1.5</v>
-      </c>
-      <c r="AG217">
-        <v>2.4</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ217">
-        <v>1.25</v>
-      </c>
       <c r="AK217">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,80 +35843,80 @@
         </is>
       </c>
       <c r="N218">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O218">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P218">
+        <v>2.4</v>
+      </c>
+      <c r="Q218">
+        <v>3.24</v>
+      </c>
+      <c r="R218">
+        <v>2.28</v>
+      </c>
+      <c r="S218">
+        <v>1.27</v>
+      </c>
+      <c r="T218">
+        <v>3.4</v>
+      </c>
+      <c r="U218">
+        <v>2.29</v>
+      </c>
+      <c r="V218">
+        <v>1.53</v>
+      </c>
+      <c r="W218">
+        <v>1.1</v>
+      </c>
+      <c r="X218">
+        <v>1.01</v>
+      </c>
+      <c r="Y218">
+        <v>1.2</v>
+      </c>
+      <c r="Z218">
+        <v>4.58</v>
+      </c>
+      <c r="AA218">
+        <v>1.61</v>
+      </c>
+      <c r="AB218">
+        <v>2.25</v>
+      </c>
+      <c r="AC218">
+        <v>2.55</v>
+      </c>
+      <c r="AD218">
+        <v>1.47</v>
+      </c>
+      <c r="AE218">
+        <v>1.18</v>
+      </c>
+      <c r="AF218">
+        <v>1.5</v>
+      </c>
+      <c r="AG218">
+        <v>2.4</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ218">
+        <v>1.25</v>
+      </c>
+      <c r="AK218">
         <v>1.44</v>
-      </c>
-      <c r="Q218">
-        <v>4.62</v>
-      </c>
-      <c r="R218">
-        <v>2.4</v>
-      </c>
-      <c r="S218">
-        <v>1.19</v>
-      </c>
-      <c r="T218">
-        <v>3.82</v>
-      </c>
-      <c r="U218">
-        <v>2.13</v>
-      </c>
-      <c r="V218">
-        <v>1.67</v>
-      </c>
-      <c r="W218">
-        <v>1.13</v>
-      </c>
-      <c r="X218">
-        <v>1.02</v>
-      </c>
-      <c r="Y218">
-        <v>1.09</v>
-      </c>
-      <c r="Z218">
-        <v>5.3</v>
-      </c>
-      <c r="AA218">
-        <v>1.42</v>
-      </c>
-      <c r="AB218">
-        <v>2.49</v>
-      </c>
-      <c r="AC218">
-        <v>2.19</v>
-      </c>
-      <c r="AD218">
-        <v>1.65</v>
-      </c>
-      <c r="AE218">
-        <v>1.21</v>
-      </c>
-      <c r="AF218">
-        <v>1.57</v>
-      </c>
-      <c r="AG218">
-        <v>2.26</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ218">
-        <v>2.5</v>
-      </c>
-      <c r="AK218">
-        <v>1.14</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36537,7 +36537,7 @@
         <v>1.89</v>
       </c>
       <c r="AB222">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC222">
         <v>3.2</v>
@@ -37334,7 +37334,7 @@
         <v>2.45</v>
       </c>
       <c r="V227">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W227">
         <v>1.12</v>
@@ -37367,7 +37367,7 @@
         <v>1.83</v>
       </c>
       <c r="AG227">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O229">
         <v>3.1</v>
@@ -37648,19 +37648,19 @@
         <v>2.8</v>
       </c>
       <c r="R229">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S229">
         <v>1.37</v>
       </c>
       <c r="T229">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U229">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V229">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W229">
         <v>1.06</v>
@@ -37675,7 +37675,7 @@
         <v>3.14</v>
       </c>
       <c r="AA229">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB229">
         <v>1.73</v>
@@ -37706,7 +37706,7 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK229">
         <v>1.62</v>
@@ -37965,10 +37965,10 @@
         <v>2.36</v>
       </c>
       <c r="O231">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P231">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38798,7 +38798,7 @@
         <v>3</v>
       </c>
       <c r="U236">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V236">
         <v>1.44</v>
@@ -38819,7 +38819,7 @@
         <v>1.8</v>
       </c>
       <c r="AB236">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC236">
         <v>2.97</v>
@@ -39595,10 +39595,10 @@
         <v>4.4</v>
       </c>
       <c r="O241">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P241">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q241">
         <v>4.55</v>
@@ -39613,13 +39613,13 @@
         <v>3.4</v>
       </c>
       <c r="U241">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V241">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W241">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -40123,7 +40123,7 @@
         <v>1.53</v>
       </c>
       <c r="AB244">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC244">
         <v>2.27</v>
@@ -40135,7 +40135,7 @@
         <v>1.27</v>
       </c>
       <c r="AF244">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG244">
         <v>2.7</v>
@@ -40256,7 +40256,7 @@
         <v>2.69</v>
       </c>
       <c r="R245">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S245">
         <v>1.14</v>
@@ -40271,31 +40271,31 @@
         <v>1.8</v>
       </c>
       <c r="W245">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X245">
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z245">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="AA245">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB245">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC245">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AD245">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AE245">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AF245">
         <v>1.33</v>
@@ -40464,7 +40464,7 @@
         <v>1.58</v>
       </c>
       <c r="AG246">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="O250">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P250">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q250">
         <v>2.34</v>
@@ -41557,7 +41557,7 @@
         <v>5.75</v>
       </c>
       <c r="Q253">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R253">
         <v>2.31</v>
@@ -41593,19 +41593,19 @@
         <v>2.24</v>
       </c>
       <c r="AC253">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AD253">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE253">
         <v>1.17</v>
       </c>
       <c r="AF253">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG253">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -42372,10 +42372,10 @@
         <v>2.8</v>
       </c>
       <c r="Q258">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R258">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S258">
         <v>1.3</v>
@@ -42436,7 +42436,7 @@
         <v>1.3</v>
       </c>
       <c r="AK258">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42692,7 +42692,7 @@
         <v>1.07</v>
       </c>
       <c r="O260">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P260">
         <v>15</v>
@@ -42701,16 +42701,16 @@
         <v>1.4</v>
       </c>
       <c r="R260">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S260">
         <v>1.17</v>
       </c>
       <c r="T260">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U260">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V260">
         <v>1.85</v>
@@ -42725,7 +42725,7 @@
         <v>1.06</v>
       </c>
       <c r="Z260">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AA260">
         <v>1.34</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O262">
         <v>3.7</v>
       </c>
       <c r="P262">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q262">
         <v>4.33</v>
@@ -43187,10 +43187,10 @@
         <v>1.39</v>
       </c>
       <c r="Q263">
-        <v>6.61</v>
+        <v>6.85</v>
       </c>
       <c r="R263">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="S263">
         <v>1.22</v>
@@ -43199,7 +43199,7 @@
         <v>3.55</v>
       </c>
       <c r="U263">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V263">
         <v>1.62</v>
@@ -43217,10 +43217,10 @@
         <v>5.5</v>
       </c>
       <c r="AA263">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB263">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AC263">
         <v>2.22</v>
@@ -43380,16 +43380,16 @@
         <v>5.25</v>
       </c>
       <c r="AA264">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB264">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC264">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AD264">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE264">
         <v>1.23</v>
@@ -43398,7 +43398,7 @@
         <v>1.5</v>
       </c>
       <c r="AG264">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43682,22 +43682,22 @@
         <v>2.3</v>
       </c>
       <c r="S266">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T266">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U266">
         <v>2.38</v>
       </c>
       <c r="V266">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W266">
         <v>1.11</v>
       </c>
       <c r="X266">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
         <v>1.13</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43996,7 +43996,7 @@
         <v>1.22</v>
       </c>
       <c r="O268">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="P268">
         <v>11</v>
@@ -44014,7 +44014,7 @@
         <v>3.92</v>
       </c>
       <c r="U268">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V268">
         <v>1.62</v>
@@ -44035,7 +44035,7 @@
         <v>1.44</v>
       </c>
       <c r="AB268">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC268">
         <v>2.2</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="O269">
         <v>3.08</v>
       </c>
       <c r="P269">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q269">
         <v>3</v>
@@ -44195,7 +44195,7 @@
         <v>2.94</v>
       </c>
       <c r="AA269">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB269">
         <v>1.57</v>
@@ -44346,7 +44346,7 @@
         <v>1.43</v>
       </c>
       <c r="W270">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X270">
         <v>1</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O271">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="P271">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q271">
         <v>1.28</v>
@@ -44497,10 +44497,10 @@
         <v>3.76</v>
       </c>
       <c r="S271">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T271">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="U271">
         <v>1.71</v>
@@ -44518,28 +44518,28 @@
         <v>1.01</v>
       </c>
       <c r="Z271">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="AA271">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB271">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AC271">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AD271">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AE271">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF271">
         <v>2.15</v>
       </c>
       <c r="AG271">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK271">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O274">
         <v>7</v>
@@ -45336,10 +45336,10 @@
         <v>7.4</v>
       </c>
       <c r="AA276">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB276">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC276">
         <v>1.76</v>
@@ -45469,16 +45469,16 @@
         <v>2.41</v>
       </c>
       <c r="Q277">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="R277">
         <v>2.01</v>
       </c>
       <c r="S277">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T277">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U277">
         <v>2.77</v>
@@ -45487,28 +45487,28 @@
         <v>1.35</v>
       </c>
       <c r="W277">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y277">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z277">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA277">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB277">
         <v>1.72</v>
       </c>
       <c r="AC277">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD277">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE277">
         <v>1.05</v>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK277">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45641,16 +45641,16 @@
         <v>1.36</v>
       </c>
       <c r="T278">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U278">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V278">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W278">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X278">
         <v>1.02</v>
@@ -45662,16 +45662,16 @@
         <v>2.92</v>
       </c>
       <c r="AA278">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB278">
         <v>1.72</v>
       </c>
       <c r="AC278">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD278">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE278">
         <v>1.05</v>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK278">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45789,10 +45789,10 @@
         <v>1.82</v>
       </c>
       <c r="O279">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P279">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q279">
         <v>2.1</v>
@@ -45813,7 +45813,7 @@
         <v>1.7</v>
       </c>
       <c r="W279">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X279">
         <v>1.01</v>
@@ -46438,7 +46438,7 @@
         </is>
       </c>
       <c r="N283">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="O283">
         <v>4.8</v>
@@ -46456,7 +46456,7 @@
         <v>1.35</v>
       </c>
       <c r="T283">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U283">
         <v>2.55</v>
@@ -46465,7 +46465,7 @@
         <v>1.46</v>
       </c>
       <c r="W283">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X283">
         <v>1.02</v>
@@ -46480,7 +46480,7 @@
         <v>1.74</v>
       </c>
       <c r="AB283">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC283">
         <v>2.74</v>
@@ -46508,7 +46508,7 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.13</v>
+        <v>3.3</v>
       </c>
       <c r="AK283">
         <v>1.04</v>
@@ -46674,7 +46674,7 @@
         <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47262,10 +47262,10 @@
         <v>2.95</v>
       </c>
       <c r="Q288">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="R288">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S288">
         <v>1.14</v>
@@ -47274,10 +47274,10 @@
         <v>5</v>
       </c>
       <c r="U288">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V288">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="W288">
         <v>1.25</v>
@@ -47286,25 +47286,25 @@
         <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z288">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AA288">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB288">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC288">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AD288">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AE288">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF288">
         <v>1.29</v>
@@ -47326,7 +47326,7 @@
         <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="O291">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P291">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47947,7 +47947,7 @@
         <v>2.07</v>
       </c>
       <c r="AB292">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC292">
         <v>3.42</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK293">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48261,7 +48261,7 @@
         <v>1.11</v>
       </c>
       <c r="X294">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y294">
         <v>1.22</v>
@@ -48922,10 +48922,10 @@
         <v>5.6</v>
       </c>
       <c r="AA298">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB298">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AC298">
         <v>2.05</v>
@@ -49046,10 +49046,10 @@
         </is>
       </c>
       <c r="N299">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O299">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P299">
         <v>1.42</v>
@@ -49209,7 +49209,7 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="O300">
         <v>3.5</v>
@@ -49535,25 +49535,25 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O302">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P302">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q302">
         <v>1.67</v>
       </c>
       <c r="R302">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="S302">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T302">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U302">
         <v>2.5</v>
@@ -49562,16 +49562,16 @@
         <v>1.5</v>
       </c>
       <c r="W302">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X302">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y302">
         <v>1.19</v>
       </c>
       <c r="Z302">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AA302">
         <v>1.68</v>
@@ -49580,19 +49580,19 @@
         <v>2.02</v>
       </c>
       <c r="AC302">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD302">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE302">
         <v>1.12</v>
       </c>
       <c r="AF302">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AG302">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>1.1</v>
       </c>
       <c r="AK302">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49867,7 +49867,7 @@
         <v>3.8</v>
       </c>
       <c r="P304">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q304">
         <v>2.8</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O308">
         <v>3.25</v>
       </c>
       <c r="P308">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q308">
         <v>3.34</v>
@@ -50531,7 +50531,7 @@
         <v>1.35</v>
       </c>
       <c r="T308">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="U308">
         <v>2.62</v>
@@ -50549,10 +50549,10 @@
         <v>1.27</v>
       </c>
       <c r="Z308">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA308">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB308">
         <v>1.9</v>
@@ -50570,7 +50570,7 @@
         <v>1.73</v>
       </c>
       <c r="AG308">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50709,10 +50709,10 @@
         <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z309">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA309">
         <v>1.18</v>
@@ -50845,7 +50845,7 @@
         <v>4.2</v>
       </c>
       <c r="P310">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q310">
         <v>2.04</v>
@@ -51038,10 +51038,10 @@
         <v>1.11</v>
       </c>
       <c r="Z311">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA311">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB311">
         <v>2.5</v>
@@ -51056,10 +51056,10 @@
         <v>1.25</v>
       </c>
       <c r="AF311">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG311">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>6</v>
       </c>
       <c r="Q312">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R312">
         <v>2.71</v>
@@ -51331,16 +51331,16 @@
         <v>2.61</v>
       </c>
       <c r="O313">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P313">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q313">
         <v>3.13</v>
       </c>
       <c r="R313">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S313">
         <v>1.36</v>
@@ -51355,7 +51355,7 @@
         <v>1.35</v>
       </c>
       <c r="W313">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X313">
         <v>1.01</v>
@@ -51693,10 +51693,10 @@
         <v>6.1</v>
       </c>
       <c r="AA315">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB315">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC315">
         <v>1.88</v>
@@ -51711,7 +51711,7 @@
         <v>1.4</v>
       </c>
       <c r="AG315">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51998,13 +51998,13 @@
         <v>1.3</v>
       </c>
       <c r="T317">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U317">
         <v>2.5</v>
       </c>
       <c r="V317">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W317">
         <v>1.11</v>
@@ -52022,7 +52022,7 @@
         <v>1.72</v>
       </c>
       <c r="AB317">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC317">
         <v>2.59</v>
@@ -52167,7 +52167,7 @@
         <v>3.2</v>
       </c>
       <c r="V318">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W318">
         <v>1.03</v>
@@ -52339,25 +52339,25 @@
         <v>1.01</v>
       </c>
       <c r="Y319">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z319">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA319">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB319">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AC319">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD319">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AE319">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AF319">
         <v>1.5</v>
@@ -52632,7 +52632,7 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="O321">
         <v>6</v>
@@ -52647,10 +52647,10 @@
         <v>3</v>
       </c>
       <c r="S321">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T321">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="U321">
         <v>1.83</v>
@@ -53290,7 +53290,7 @@
         <v>3.4</v>
       </c>
       <c r="P325">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q325">
         <v>2.69</v>
@@ -53308,7 +53308,7 @@
         <v>2.59</v>
       </c>
       <c r="V325">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W325">
         <v>1.06</v>
@@ -53323,10 +53323,10 @@
         <v>3.66</v>
       </c>
       <c r="AA325">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB325">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC325">
         <v>3.04</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q327">
         <v>0</v>
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q328">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="O331">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P331">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q331">
         <v>0</v>
@@ -54588,10 +54588,10 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O333">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P333">
         <v>8.5</v>
@@ -54926,7 +54926,7 @@
         <v>3.74</v>
       </c>
       <c r="R335">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S335">
         <v>1.47</v>
@@ -54956,7 +54956,7 @@
         <v>2.38</v>
       </c>
       <c r="AB335">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC335">
         <v>4.34</v>
@@ -55077,7 +55077,7 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="O336">
         <v>3.45</v>
@@ -55596,7 +55596,7 @@
         <v>1.25</v>
       </c>
       <c r="X339">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y339">
         <v>1.14</v>
@@ -55732,13 +55732,13 @@
         <v>3.3</v>
       </c>
       <c r="O340">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P340">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q340">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="R340">
         <v>2.2</v>
@@ -55762,19 +55762,19 @@
         <v>1.01</v>
       </c>
       <c r="Y340">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z340">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="AA340">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB340">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC340">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AD340">
         <v>1.31</v>
@@ -55931,7 +55931,7 @@
         <v>3.9</v>
       </c>
       <c r="AA341">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB341">
         <v>2.03</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,19 +56381,19 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="O344">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P344">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q344">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R344">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S344">
         <v>1.2</v>
@@ -56402,43 +56402,43 @@
         <v>4</v>
       </c>
       <c r="U344">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="V344">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="W344">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X344">
         <v>0</v>
       </c>
       <c r="Y344">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z344">
-        <v>6.17</v>
+        <v>4.8</v>
       </c>
       <c r="AA344">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB344">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC344">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="AD344">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE344">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF344">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AG344">
-        <v>2.84</v>
+        <v>2.49</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK344">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,64 +56544,64 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.91</v>
+        <v>2.51</v>
       </c>
       <c r="O345">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="P345">
-        <v>3.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q345">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R345">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="S345">
         <v>1.2</v>
       </c>
       <c r="T345">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U345">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="V345">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="W345">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X345">
         <v>0</v>
       </c>
       <c r="Y345">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z345">
-        <v>4.8</v>
+        <v>6.26</v>
       </c>
       <c r="AA345">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB345">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="AC345">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AD345">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE345">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AF345">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AG345">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AH345" t="inlineStr">
         <is>
@@ -56617,7 +56617,7 @@
         <v>1.24</v>
       </c>
       <c r="AK345">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,65 +56707,65 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="O346">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P346">
+        <v>3.16</v>
+      </c>
+      <c r="Q346">
+        <v>2.63</v>
+      </c>
+      <c r="R346">
+        <v>2.38</v>
+      </c>
+      <c r="S346">
+        <v>1.22</v>
+      </c>
+      <c r="T346">
+        <v>3.8</v>
+      </c>
+      <c r="U346">
+        <v>2.12</v>
+      </c>
+      <c r="V346">
+        <v>1.65</v>
+      </c>
+      <c r="W346">
+        <v>1.14</v>
+      </c>
+      <c r="X346">
+        <v>0</v>
+      </c>
+      <c r="Y346">
+        <v>1.13</v>
+      </c>
+      <c r="Z346">
+        <v>5.25</v>
+      </c>
+      <c r="AA346">
+        <v>1.52</v>
+      </c>
+      <c r="AB346">
+        <v>2.31</v>
+      </c>
+      <c r="AC346">
+        <v>2.39</v>
+      </c>
+      <c r="AD346">
+        <v>1.56</v>
+      </c>
+      <c r="AE346">
+        <v>1.23</v>
+      </c>
+      <c r="AF346">
+        <v>1.44</v>
+      </c>
+      <c r="AG346">
         <v>2.5</v>
       </c>
-      <c r="Q346">
-        <v>2.75</v>
-      </c>
-      <c r="R346">
-        <v>2.43</v>
-      </c>
-      <c r="S346">
-        <v>1.2</v>
-      </c>
-      <c r="T346">
-        <v>4.33</v>
-      </c>
-      <c r="U346">
-        <v>2.06</v>
-      </c>
-      <c r="V346">
-        <v>1.77</v>
-      </c>
-      <c r="W346">
-        <v>1.19</v>
-      </c>
-      <c r="X346">
-        <v>0</v>
-      </c>
-      <c r="Y346">
-        <v>1.08</v>
-      </c>
-      <c r="Z346">
-        <v>6.26</v>
-      </c>
-      <c r="AA346">
-        <v>1.4</v>
-      </c>
-      <c r="AB346">
-        <v>2.87</v>
-      </c>
-      <c r="AC346">
-        <v>2.11</v>
-      </c>
-      <c r="AD346">
-        <v>1.8</v>
-      </c>
-      <c r="AE346">
-        <v>1.34</v>
-      </c>
-      <c r="AF346">
-        <v>1.35</v>
-      </c>
-      <c r="AG346">
-        <v>2.88</v>
-      </c>
       <c r="AH346" t="inlineStr">
         <is>
           <t>[]</t>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK346">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,80 +56870,80 @@
         </is>
       </c>
       <c r="N347">
+        <v>1.36</v>
+      </c>
+      <c r="O347">
+        <v>5.2</v>
+      </c>
+      <c r="P347">
+        <v>7.25</v>
+      </c>
+      <c r="Q347">
+        <v>1.7</v>
+      </c>
+      <c r="R347">
+        <v>2.9</v>
+      </c>
+      <c r="S347">
+        <v>1.11</v>
+      </c>
+      <c r="T347">
+        <v>4.95</v>
+      </c>
+      <c r="U347">
+        <v>1.75</v>
+      </c>
+      <c r="V347">
+        <v>1.91</v>
+      </c>
+      <c r="W347">
+        <v>1.28</v>
+      </c>
+      <c r="X347">
+        <v>0</v>
+      </c>
+      <c r="Y347">
+        <v>1.05</v>
+      </c>
+      <c r="Z347">
+        <v>9</v>
+      </c>
+      <c r="AA347">
+        <v>1.25</v>
+      </c>
+      <c r="AB347">
+        <v>3.7</v>
+      </c>
+      <c r="AC347">
+        <v>1.71</v>
+      </c>
+      <c r="AD347">
+        <v>2.14</v>
+      </c>
+      <c r="AE347">
+        <v>1.45</v>
+      </c>
+      <c r="AF347">
         <v>1.4</v>
       </c>
-      <c r="O347">
-        <v>4.6</v>
-      </c>
-      <c r="P347">
-        <v>6.55</v>
-      </c>
-      <c r="Q347">
-        <v>1.83</v>
-      </c>
-      <c r="R347">
-        <v>2.88</v>
-      </c>
-      <c r="S347">
-        <v>1.2</v>
-      </c>
-      <c r="T347">
-        <v>4.2</v>
-      </c>
-      <c r="U347">
-        <v>1.95</v>
-      </c>
-      <c r="V347">
-        <v>1.75</v>
-      </c>
-      <c r="W347">
-        <v>1.2</v>
-      </c>
-      <c r="X347">
-        <v>0</v>
-      </c>
-      <c r="Y347">
+      <c r="AG347">
+        <v>2.6</v>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ347">
         <v>1.12</v>
       </c>
-      <c r="Z347">
-        <v>6.32</v>
-      </c>
-      <c r="AA347">
-        <v>1.4</v>
-      </c>
-      <c r="AB347">
-        <v>2.96</v>
-      </c>
-      <c r="AC347">
-        <v>1.89</v>
-      </c>
-      <c r="AD347">
-        <v>1.79</v>
-      </c>
-      <c r="AE347">
-        <v>1.33</v>
-      </c>
-      <c r="AF347">
-        <v>1.52</v>
-      </c>
-      <c r="AG347">
-        <v>2.4</v>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI347" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ347">
-        <v>1.18</v>
-      </c>
       <c r="AK347">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,64 +57033,64 @@
         </is>
       </c>
       <c r="N348">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="O348">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P348">
-        <v>3.16</v>
+        <v>6.55</v>
       </c>
       <c r="Q348">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="R348">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="S348">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T348">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U348">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V348">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W348">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X348">
         <v>0</v>
       </c>
       <c r="Y348">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z348">
-        <v>5.25</v>
+        <v>6.32</v>
       </c>
       <c r="AA348">
+        <v>1.4</v>
+      </c>
+      <c r="AB348">
+        <v>2.96</v>
+      </c>
+      <c r="AC348">
+        <v>1.89</v>
+      </c>
+      <c r="AD348">
+        <v>1.79</v>
+      </c>
+      <c r="AE348">
+        <v>1.33</v>
+      </c>
+      <c r="AF348">
         <v>1.52</v>
       </c>
-      <c r="AB348">
-        <v>2.31</v>
-      </c>
-      <c r="AC348">
-        <v>2.39</v>
-      </c>
-      <c r="AD348">
-        <v>1.56</v>
-      </c>
-      <c r="AE348">
-        <v>1.23</v>
-      </c>
-      <c r="AF348">
-        <v>1.44</v>
-      </c>
       <c r="AG348">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57103,10 +57103,10 @@
         </is>
       </c>
       <c r="AJ348">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK348">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL348">
         <v>0</v>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,64 +57196,64 @@
         </is>
       </c>
       <c r="N349">
+        <v>2.12</v>
+      </c>
+      <c r="O349">
+        <v>3.9</v>
+      </c>
+      <c r="P349">
+        <v>2.8</v>
+      </c>
+      <c r="Q349">
+        <v>2.41</v>
+      </c>
+      <c r="R349">
+        <v>2.45</v>
+      </c>
+      <c r="S349">
+        <v>1.2</v>
+      </c>
+      <c r="T349">
+        <v>4</v>
+      </c>
+      <c r="U349">
+        <v>1.97</v>
+      </c>
+      <c r="V349">
+        <v>1.72</v>
+      </c>
+      <c r="W349">
+        <v>1.2</v>
+      </c>
+      <c r="X349">
+        <v>0</v>
+      </c>
+      <c r="Y349">
+        <v>1.12</v>
+      </c>
+      <c r="Z349">
+        <v>6.17</v>
+      </c>
+      <c r="AA349">
+        <v>1.4</v>
+      </c>
+      <c r="AB349">
+        <v>2.87</v>
+      </c>
+      <c r="AC349">
+        <v>2.01</v>
+      </c>
+      <c r="AD349">
+        <v>1.75</v>
+      </c>
+      <c r="AE349">
+        <v>1.33</v>
+      </c>
+      <c r="AF349">
         <v>1.36</v>
       </c>
-      <c r="O349">
-        <v>5.2</v>
-      </c>
-      <c r="P349">
-        <v>7.25</v>
-      </c>
-      <c r="Q349">
-        <v>1.7</v>
-      </c>
-      <c r="R349">
-        <v>2.9</v>
-      </c>
-      <c r="S349">
-        <v>1.11</v>
-      </c>
-      <c r="T349">
-        <v>4.95</v>
-      </c>
-      <c r="U349">
-        <v>1.75</v>
-      </c>
-      <c r="V349">
-        <v>1.91</v>
-      </c>
-      <c r="W349">
-        <v>1.28</v>
-      </c>
-      <c r="X349">
-        <v>0</v>
-      </c>
-      <c r="Y349">
-        <v>1.05</v>
-      </c>
-      <c r="Z349">
-        <v>9</v>
-      </c>
-      <c r="AA349">
-        <v>1.25</v>
-      </c>
-      <c r="AB349">
-        <v>3.7</v>
-      </c>
-      <c r="AC349">
-        <v>1.71</v>
-      </c>
-      <c r="AD349">
-        <v>2.14</v>
-      </c>
-      <c r="AE349">
-        <v>1.45</v>
-      </c>
-      <c r="AF349">
-        <v>1.4</v>
-      </c>
       <c r="AG349">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="AH349" t="inlineStr">
         <is>
@@ -57266,10 +57266,10 @@
         </is>
       </c>
       <c r="AJ349">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK349">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AL349">
         <v>0</v>
@@ -57359,16 +57359,16 @@
         </is>
       </c>
       <c r="N350">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O350">
         <v>3.8</v>
       </c>
       <c r="P350">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q350">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R350">
         <v>2.2</v>
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,64 +57522,64 @@
         </is>
       </c>
       <c r="N351">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="O351">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="P351">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="Q351">
-        <v>4.3</v>
+        <v>2.56</v>
       </c>
       <c r="R351">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S351">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T351">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U351">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V351">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W351">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X351">
         <v>0</v>
       </c>
       <c r="Y351">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z351">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="AA351">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB351">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC351">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD351">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE351">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF351">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG351">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57592,10 +57592,10 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK351">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,64 +57685,64 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="O352">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="P352">
-        <v>3.34</v>
+        <v>1.87</v>
       </c>
       <c r="Q352">
+        <v>4.3</v>
+      </c>
+      <c r="R352">
+        <v>2.22</v>
+      </c>
+      <c r="S352">
+        <v>1.3</v>
+      </c>
+      <c r="T352">
+        <v>3.3</v>
+      </c>
+      <c r="U352">
         <v>2.56</v>
       </c>
-      <c r="R352">
-        <v>2.23</v>
-      </c>
-      <c r="S352">
-        <v>1.29</v>
-      </c>
-      <c r="T352">
-        <v>3.4</v>
-      </c>
-      <c r="U352">
-        <v>2.47</v>
-      </c>
       <c r="V352">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W352">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X352">
         <v>0</v>
       </c>
       <c r="Y352">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z352">
-        <v>4.4</v>
+        <v>3.86</v>
       </c>
       <c r="AA352">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB352">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AC352">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AD352">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE352">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF352">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG352">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57755,10 +57755,10 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK352">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,64 +58663,64 @@
         </is>
       </c>
       <c r="N358">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="O358">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P358">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q358">
+        <v>2.25</v>
+      </c>
+      <c r="R358">
         <v>2.4</v>
       </c>
-      <c r="R358">
-        <v>2.15</v>
-      </c>
       <c r="S358">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T358">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U358">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="V358">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W358">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X358">
         <v>1.02</v>
       </c>
       <c r="Y358">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z358">
-        <v>3.08</v>
+        <v>4.41</v>
       </c>
       <c r="AA358">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AB358">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC358">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD358">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE358">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF358">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG358">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK358">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G359">
@@ -58826,64 +58826,64 @@
         </is>
       </c>
       <c r="N359">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="O359">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P359">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q359">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R359">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S359">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T359">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U359">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="V359">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W359">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X359">
         <v>1.02</v>
       </c>
       <c r="Y359">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z359">
-        <v>4.41</v>
+        <v>3.08</v>
       </c>
       <c r="AA359">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AB359">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC359">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="AD359">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE359">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF359">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG359">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AH359" t="inlineStr">
         <is>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="AJ359">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK359">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL359">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
         <v>2.68</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AD15">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
+        <v>1.73</v>
+      </c>
+      <c r="AK15">
         <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.45</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="R16">
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
         <v>2.68</v>
       </c>
       <c r="U16">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q52">
-        <v>3.14</v>
+        <v>2.05</v>
       </c>
       <c r="R52">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA52">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB52">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AC52">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>4.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q53">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="U53">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AC53">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="R70">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U70">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V70">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="AA70">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB70">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AC70">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AD70">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.99</v>
+        <v>1.62</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P71">
-        <v>1.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="R71">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="V71">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>4.3</v>
+        <v>6.01</v>
       </c>
       <c r="AA71">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
+        <v>3.1</v>
+      </c>
+      <c r="AC71">
+        <v>1.93</v>
+      </c>
+      <c r="AD71">
+        <v>1.75</v>
+      </c>
+      <c r="AE71">
+        <v>1.28</v>
+      </c>
+      <c r="AF71">
+        <v>1.44</v>
+      </c>
+      <c r="AG71">
+        <v>2.62</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.2</v>
+      </c>
+      <c r="AK71">
         <v>2.18</v>
-      </c>
-      <c r="AC71">
-        <v>2.43</v>
-      </c>
-      <c r="AD71">
-        <v>1.44</v>
-      </c>
-      <c r="AE71">
-        <v>1.14</v>
-      </c>
-      <c r="AF71">
-        <v>1.52</v>
-      </c>
-      <c r="AG71">
-        <v>2.3</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.19</v>
-      </c>
-      <c r="AK71">
-        <v>1.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P72">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q72">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R72">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V72">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z72">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA72">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB72">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC72">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD72">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="O73">
-        <v>5.05</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
-        <v>4.33</v>
+        <v>1.98</v>
       </c>
       <c r="Q73">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="S73">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="U73">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V73">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z73">
-        <v>6.01</v>
+        <v>4.3</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB73">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="AC73">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AD73">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AE73">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG73">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.48</v>
+      </c>
+      <c r="O101">
+        <v>4.75</v>
+      </c>
+      <c r="P101">
+        <v>5.36</v>
+      </c>
+      <c r="Q101">
+        <v>1.91</v>
+      </c>
+      <c r="R101">
+        <v>2.76</v>
+      </c>
+      <c r="S101">
+        <v>1.2</v>
+      </c>
+      <c r="T101">
+        <v>4</v>
+      </c>
+      <c r="U101">
+        <v>2.01</v>
+      </c>
+      <c r="V101">
+        <v>1.7</v>
+      </c>
+      <c r="W101">
+        <v>1.16</v>
+      </c>
+      <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.12</v>
+      </c>
+      <c r="Z101">
+        <v>6</v>
+      </c>
+      <c r="AA101">
+        <v>1.38</v>
+      </c>
+      <c r="AB101">
+        <v>2.62</v>
+      </c>
+      <c r="AC101">
+        <v>2.05</v>
+      </c>
+      <c r="AD101">
+        <v>1.75</v>
+      </c>
+      <c r="AE101">
+        <v>1.29</v>
+      </c>
+      <c r="AF101">
+        <v>1.52</v>
+      </c>
+      <c r="AG101">
+        <v>2.45</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.12</v>
+      </c>
+      <c r="AK101">
         <v>2.4</v>
-      </c>
-      <c r="O101">
-        <v>3.2</v>
-      </c>
-      <c r="P101">
-        <v>2.59</v>
-      </c>
-      <c r="Q101">
-        <v>2.99</v>
-      </c>
-      <c r="R101">
-        <v>2.08</v>
-      </c>
-      <c r="S101">
-        <v>1.33</v>
-      </c>
-      <c r="T101">
-        <v>2.88</v>
-      </c>
-      <c r="U101">
-        <v>2.56</v>
-      </c>
-      <c r="V101">
-        <v>1.41</v>
-      </c>
-      <c r="W101">
-        <v>1.07</v>
-      </c>
-      <c r="X101">
-        <v>1</v>
-      </c>
-      <c r="Y101">
-        <v>1.27</v>
-      </c>
-      <c r="Z101">
-        <v>3.61</v>
-      </c>
-      <c r="AA101">
-        <v>1.83</v>
-      </c>
-      <c r="AB101">
-        <v>1.93</v>
-      </c>
-      <c r="AC101">
-        <v>3.17</v>
-      </c>
-      <c r="AD101">
-        <v>1.34</v>
-      </c>
-      <c r="AE101">
-        <v>1.12</v>
-      </c>
-      <c r="AF101">
-        <v>1.67</v>
-      </c>
-      <c r="AG101">
-        <v>2.11</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.3</v>
-      </c>
-      <c r="AK101">
-        <v>1.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O102">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>5.36</v>
+        <v>2.59</v>
       </c>
       <c r="Q102">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R102">
-        <v>2.76</v>
+        <v>2.08</v>
       </c>
       <c r="S102">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="V102">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W102">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y102">
+        <v>1.27</v>
+      </c>
+      <c r="Z102">
+        <v>3.61</v>
+      </c>
+      <c r="AA102">
+        <v>1.83</v>
+      </c>
+      <c r="AB102">
+        <v>1.93</v>
+      </c>
+      <c r="AC102">
+        <v>3.17</v>
+      </c>
+      <c r="AD102">
+        <v>1.34</v>
+      </c>
+      <c r="AE102">
         <v>1.12</v>
       </c>
-      <c r="Z102">
-        <v>6</v>
-      </c>
-      <c r="AA102">
-        <v>1.38</v>
-      </c>
-      <c r="AB102">
-        <v>2.62</v>
-      </c>
-      <c r="AC102">
-        <v>2.05</v>
-      </c>
-      <c r="AD102">
-        <v>1.75</v>
-      </c>
-      <c r="AE102">
-        <v>1.29</v>
-      </c>
       <c r="AF102">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG102">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O127">
-        <v>4.66</v>
+        <v>3.84</v>
       </c>
       <c r="P127">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q127">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="R127">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S127">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U127">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V127">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W127">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z127">
-        <v>7.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA127">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB127">
-        <v>3.16</v>
+        <v>2.64</v>
       </c>
       <c r="AC127">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AD127">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE127">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG127">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AK127">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.43</v>
+        <v>9.75</v>
       </c>
       <c r="O128">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="P128">
-        <v>6.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q128">
-        <v>1.75</v>
+        <v>7.5</v>
       </c>
       <c r="R128">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T128">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U128">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="V128">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y128">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z128">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA128">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AB128">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC128">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AD128">
-        <v>1.79</v>
+        <v>2.99</v>
       </c>
       <c r="AE128">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="AF128">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AG128">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK128">
-        <v>2.75</v>
+        <v>1.05</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O129">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="P129">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="Q129">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T129">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z129">
-        <v>5.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA129">
+        <v>1.37</v>
+      </c>
+      <c r="AB129">
+        <v>3.16</v>
+      </c>
+      <c r="AC129">
+        <v>1.96</v>
+      </c>
+      <c r="AD129">
+        <v>1.9</v>
+      </c>
+      <c r="AE129">
+        <v>1.38</v>
+      </c>
+      <c r="AF129">
         <v>1.44</v>
       </c>
-      <c r="AB129">
-        <v>2.64</v>
-      </c>
-      <c r="AC129">
-        <v>2.13</v>
-      </c>
-      <c r="AD129">
-        <v>1.74</v>
-      </c>
-      <c r="AE129">
-        <v>1.27</v>
-      </c>
-      <c r="AF129">
-        <v>1.36</v>
-      </c>
       <c r="AG129">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AK129">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>9.75</v>
+        <v>1.43</v>
       </c>
       <c r="O130">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="P130">
+        <v>6.25</v>
+      </c>
+      <c r="Q130">
+        <v>1.75</v>
+      </c>
+      <c r="R130">
+        <v>2.61</v>
+      </c>
+      <c r="S130">
         <v>1.2</v>
       </c>
-      <c r="Q130">
-        <v>7.5</v>
-      </c>
-      <c r="R130">
-        <v>3.5</v>
-      </c>
-      <c r="S130">
-        <v>1.11</v>
-      </c>
       <c r="T130">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U130">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="V130">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="W130">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z130">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA130">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AB130">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC130">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD130">
-        <v>2.99</v>
+        <v>1.79</v>
       </c>
       <c r="AE130">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="AF130">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AG130">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>1.05</v>
+        <v>2.75</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.74</v>
+        <v>1.68</v>
       </c>
       <c r="O134">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P134">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q134">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R134">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="S134">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T134">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="U134">
+        <v>2.05</v>
+      </c>
+      <c r="V134">
+        <v>1.66</v>
+      </c>
+      <c r="W134">
+        <v>1.14</v>
+      </c>
+      <c r="X134">
+        <v>1.02</v>
+      </c>
+      <c r="Y134">
+        <v>1.1</v>
+      </c>
+      <c r="Z134">
+        <v>5.1</v>
+      </c>
+      <c r="AA134">
+        <v>1.5</v>
+      </c>
+      <c r="AB134">
         <v>2.6</v>
       </c>
-      <c r="V134">
-        <v>1.48</v>
-      </c>
-      <c r="W134">
-        <v>1.07</v>
-      </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
-      <c r="Y134">
-        <v>1.22</v>
-      </c>
-      <c r="Z134">
-        <v>3.74</v>
-      </c>
-      <c r="AA134">
-        <v>1.8</v>
-      </c>
-      <c r="AB134">
-        <v>1.95</v>
-      </c>
       <c r="AC134">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF134">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG134">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="O135">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q135">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R135">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S135">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="U135">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="V135">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W135">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
+        <v>1.22</v>
+      </c>
+      <c r="Z135">
+        <v>3.74</v>
+      </c>
+      <c r="AA135">
+        <v>1.8</v>
+      </c>
+      <c r="AB135">
+        <v>1.95</v>
+      </c>
+      <c r="AC135">
+        <v>3</v>
+      </c>
+      <c r="AD135">
+        <v>1.36</v>
+      </c>
+      <c r="AE135">
         <v>1.1</v>
       </c>
-      <c r="Z135">
-        <v>5.1</v>
-      </c>
-      <c r="AA135">
-        <v>1.5</v>
-      </c>
-      <c r="AB135">
-        <v>2.6</v>
-      </c>
-      <c r="AC135">
-        <v>2.25</v>
-      </c>
-      <c r="AD135">
-        <v>1.69</v>
-      </c>
-      <c r="AE135">
-        <v>1.26</v>
-      </c>
       <c r="AF135">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG135">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK135">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="O154">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P154">
+        <v>3.25</v>
+      </c>
+      <c r="Q154">
+        <v>2.55</v>
+      </c>
+      <c r="R154">
+        <v>2.25</v>
+      </c>
+      <c r="S154">
+        <v>1.34</v>
+      </c>
+      <c r="T154">
+        <v>2.7</v>
+      </c>
+      <c r="U154">
+        <v>2.67</v>
+      </c>
+      <c r="V154">
+        <v>1.4</v>
+      </c>
+      <c r="W154">
+        <v>1.05</v>
+      </c>
+      <c r="X154">
+        <v>1.01</v>
+      </c>
+      <c r="Y154">
+        <v>1.24</v>
+      </c>
+      <c r="Z154">
+        <v>3.51</v>
+      </c>
+      <c r="AA154">
+        <v>1.93</v>
+      </c>
+      <c r="AB154">
         <v>1.85</v>
       </c>
-      <c r="Q154">
-        <v>4.2</v>
-      </c>
-      <c r="R154">
-        <v>2.26</v>
-      </c>
-      <c r="S154">
-        <v>1.3</v>
-      </c>
-      <c r="T154">
-        <v>3.3</v>
-      </c>
-      <c r="U154">
-        <v>2.32</v>
-      </c>
-      <c r="V154">
-        <v>1.52</v>
-      </c>
-      <c r="W154">
-        <v>1.1</v>
-      </c>
-      <c r="X154">
-        <v>1.02</v>
-      </c>
-      <c r="Y154">
-        <v>1.16</v>
-      </c>
-      <c r="Z154">
-        <v>4.1</v>
-      </c>
-      <c r="AA154">
-        <v>1.67</v>
-      </c>
-      <c r="AB154">
-        <v>2.11</v>
-      </c>
       <c r="AC154">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AD154">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE154">
         <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG154">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="O155">
         <v>3.3</v>
       </c>
       <c r="P155">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="Q155">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="R155">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S155">
+        <v>1.45</v>
+      </c>
+      <c r="T155">
+        <v>2.5</v>
+      </c>
+      <c r="U155">
+        <v>3</v>
+      </c>
+      <c r="V155">
+        <v>1.32</v>
+      </c>
+      <c r="W155">
+        <v>1.04</v>
+      </c>
+      <c r="X155">
+        <v>1.04</v>
+      </c>
+      <c r="Y155">
         <v>1.34</v>
       </c>
-      <c r="T155">
-        <v>2.7</v>
-      </c>
-      <c r="U155">
-        <v>2.67</v>
-      </c>
-      <c r="V155">
-        <v>1.4</v>
-      </c>
-      <c r="W155">
-        <v>1.05</v>
-      </c>
-      <c r="X155">
-        <v>1.01</v>
-      </c>
-      <c r="Y155">
-        <v>1.24</v>
-      </c>
       <c r="Z155">
-        <v>3.51</v>
+        <v>2.78</v>
       </c>
       <c r="AA155">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="AB155">
+        <v>1.7</v>
+      </c>
+      <c r="AC155">
+        <v>4.1</v>
+      </c>
+      <c r="AD155">
+        <v>1.2</v>
+      </c>
+      <c r="AE155">
+        <v>1.04</v>
+      </c>
+      <c r="AF155">
         <v>1.85</v>
       </c>
-      <c r="AC155">
-        <v>3.05</v>
-      </c>
-      <c r="AD155">
-        <v>1.32</v>
-      </c>
-      <c r="AE155">
-        <v>1.11</v>
-      </c>
-      <c r="AF155">
-        <v>1.71</v>
-      </c>
       <c r="AG155">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK155">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="Q156">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="R156">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S156">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U156">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V156">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W156">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z156">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="AB156">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC156">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD156">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE156">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG156">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.87</v>
+        <v>4.15</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P157">
+        <v>1.63</v>
+      </c>
+      <c r="Q157">
+        <v>3.9</v>
+      </c>
+      <c r="R157">
+        <v>2.28</v>
+      </c>
+      <c r="S157">
+        <v>1.23</v>
+      </c>
+      <c r="T157">
         <v>3.5</v>
       </c>
-      <c r="Q157">
-        <v>2.29</v>
-      </c>
-      <c r="R157">
-        <v>2.04</v>
-      </c>
-      <c r="S157">
-        <v>1.4</v>
-      </c>
-      <c r="T157">
-        <v>2.66</v>
-      </c>
       <c r="U157">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="V157">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W157">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X157">
         <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z157">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA157">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AB157">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC157">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="AD157">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE157">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF157">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AG157">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK157">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.15</v>
+        <v>2.62</v>
       </c>
       <c r="O158">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q158">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S158">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U158">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="V158">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W158">
+        <v>1.09</v>
+      </c>
+      <c r="X158">
+        <v>1.01</v>
+      </c>
+      <c r="Y158">
+        <v>1.2</v>
+      </c>
+      <c r="Z158">
+        <v>3.74</v>
+      </c>
+      <c r="AA158">
+        <v>1.78</v>
+      </c>
+      <c r="AB158">
+        <v>1.98</v>
+      </c>
+      <c r="AC158">
+        <v>2.81</v>
+      </c>
+      <c r="AD158">
+        <v>1.33</v>
+      </c>
+      <c r="AE158">
         <v>1.13</v>
       </c>
-      <c r="X158">
-        <v>1.03</v>
-      </c>
-      <c r="Y158">
-        <v>1.13</v>
-      </c>
-      <c r="Z158">
-        <v>4.6</v>
-      </c>
-      <c r="AA158">
-        <v>1.54</v>
-      </c>
-      <c r="AB158">
-        <v>2.3</v>
-      </c>
-      <c r="AC158">
-        <v>2.31</v>
-      </c>
-      <c r="AD158">
-        <v>1.54</v>
-      </c>
-      <c r="AE158">
-        <v>1.19</v>
-      </c>
       <c r="AF158">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="O159">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P159">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q159">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R159">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S159">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U159">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V159">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W159">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA159">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB159">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC159">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AD159">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF159">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG159">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK159">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O187">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P187">
-        <v>6.06</v>
+        <v>4.33</v>
       </c>
       <c r="Q187">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R187">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S187">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T187">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U187">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="V187">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="W187">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z187">
-        <v>5.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA187">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AB187">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AC187">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="AD187">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE187">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF187">
         <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK187">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O190">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P190">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q190">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R190">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="S190">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T190">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U190">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="V190">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W190">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X190">
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z190">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="AA190">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB190">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC190">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="AD190">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE190">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF190">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG190">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O191">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P191">
-        <v>4.33</v>
+        <v>6.06</v>
       </c>
       <c r="Q191">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R191">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S191">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T191">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U191">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V191">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="W191">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X191">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z191">
-        <v>4.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA191">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB191">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AC191">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AD191">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AE191">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF191">
         <v>1.57</v>
       </c>
       <c r="AG191">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK191">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O192">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P192">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q192">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R192">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="S192">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U192">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V192">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W192">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X192">
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z192">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA192">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB192">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC192">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="AD192">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE192">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF192">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG192">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,80 +37636,80 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="O229">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P229">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q229">
-        <v>2.8</v>
+        <v>4.23</v>
       </c>
       <c r="R229">
         <v>2</v>
       </c>
       <c r="S229">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T229">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U229">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V229">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W229">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z229">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA229">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB229">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC229">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD229">
+        <v>1.21</v>
+      </c>
+      <c r="AE229">
+        <v>1.03</v>
+      </c>
+      <c r="AF229">
+        <v>1.8</v>
+      </c>
+      <c r="AG229">
+        <v>1.87</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
         <v>1.24</v>
       </c>
-      <c r="AE229">
-        <v>1.04</v>
-      </c>
-      <c r="AF229">
-        <v>1.74</v>
-      </c>
-      <c r="AG229">
-        <v>1.94</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ229">
-        <v>1.3</v>
-      </c>
       <c r="AK229">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="O230">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P230">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q230">
-        <v>4.23</v>
+        <v>2.8</v>
       </c>
       <c r="R230">
         <v>2</v>
       </c>
       <c r="S230">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T230">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U230">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V230">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W230">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z230">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA230">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB230">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC230">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD230">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE230">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF230">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG230">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O354">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P354">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q354">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R354">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="S354">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="T354">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="U354">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V354">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W354">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X354">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y354">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z354">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA354">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB354">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AC354">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="AD354">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AE354">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF354">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AG354">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,64 +58174,64 @@
         </is>
       </c>
       <c r="N355">
+        <v>1.59</v>
+      </c>
+      <c r="O355">
+        <v>3.9</v>
+      </c>
+      <c r="P355">
+        <v>4.25</v>
+      </c>
+      <c r="Q355">
+        <v>2</v>
+      </c>
+      <c r="R355">
+        <v>2.46</v>
+      </c>
+      <c r="S355">
+        <v>1.19</v>
+      </c>
+      <c r="T355">
+        <v>3.7</v>
+      </c>
+      <c r="U355">
+        <v>2.2</v>
+      </c>
+      <c r="V355">
+        <v>1.62</v>
+      </c>
+      <c r="W355">
+        <v>1.15</v>
+      </c>
+      <c r="X355">
+        <v>1.02</v>
+      </c>
+      <c r="Y355">
+        <v>1.15</v>
+      </c>
+      <c r="Z355">
+        <v>4.75</v>
+      </c>
+      <c r="AA355">
+        <v>1.47</v>
+      </c>
+      <c r="AB355">
+        <v>2.5</v>
+      </c>
+      <c r="AC355">
+        <v>2.28</v>
+      </c>
+      <c r="AD355">
         <v>1.6</v>
       </c>
-      <c r="O355">
-        <v>3.65</v>
-      </c>
-      <c r="P355">
-        <v>4.5</v>
-      </c>
-      <c r="Q355">
-        <v>2.1</v>
-      </c>
-      <c r="R355">
-        <v>2.33</v>
-      </c>
-      <c r="S355">
-        <v>1.26</v>
-      </c>
-      <c r="T355">
-        <v>3.24</v>
-      </c>
-      <c r="U355">
-        <v>2.34</v>
-      </c>
-      <c r="V355">
-        <v>1.48</v>
-      </c>
-      <c r="W355">
-        <v>1.1</v>
-      </c>
-      <c r="X355">
-        <v>1</v>
-      </c>
-      <c r="Y355">
-        <v>1.21</v>
-      </c>
-      <c r="Z355">
-        <v>3.58</v>
-      </c>
-      <c r="AA355">
-        <v>1.73</v>
-      </c>
-      <c r="AB355">
-        <v>2.03</v>
-      </c>
-      <c r="AC355">
-        <v>2.78</v>
-      </c>
-      <c r="AD355">
-        <v>1.34</v>
-      </c>
       <c r="AE355">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF355">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AG355">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="AH355" t="inlineStr">
         <is>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>4.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q52">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB52">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AC52">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q53">
-        <v>3.14</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="U53">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA53">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB53">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AC53">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="AD53">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK53">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q70">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R70">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA70">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB70">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD70">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="R71">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U71">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V71">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>6.01</v>
+        <v>5.15</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB71">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="AC71">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AD71">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE71">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
         <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P72">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q72">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="R72">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S72">
         <v>1.2</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U72">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V72">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
         <v>1.2</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>5.8</v>
+        <v>6.01</v>
       </c>
       <c r="AA72">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
+        <v>3.1</v>
+      </c>
+      <c r="AC72">
+        <v>1.93</v>
+      </c>
+      <c r="AD72">
+        <v>1.75</v>
+      </c>
+      <c r="AE72">
+        <v>1.28</v>
+      </c>
+      <c r="AF72">
+        <v>1.44</v>
+      </c>
+      <c r="AG72">
         <v>2.62</v>
       </c>
-      <c r="AC72">
-        <v>2.02</v>
-      </c>
-      <c r="AD72">
-        <v>1.69</v>
-      </c>
-      <c r="AE72">
-        <v>1.25</v>
-      </c>
-      <c r="AF72">
-        <v>1.4</v>
-      </c>
-      <c r="AG72">
-        <v>2.7</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O101">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.36</v>
+        <v>2.59</v>
       </c>
       <c r="Q101">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R101">
-        <v>2.76</v>
+        <v>2.08</v>
       </c>
       <c r="S101">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="V101">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y101">
+        <v>1.27</v>
+      </c>
+      <c r="Z101">
+        <v>3.61</v>
+      </c>
+      <c r="AA101">
+        <v>1.83</v>
+      </c>
+      <c r="AB101">
+        <v>1.93</v>
+      </c>
+      <c r="AC101">
+        <v>3.17</v>
+      </c>
+      <c r="AD101">
+        <v>1.34</v>
+      </c>
+      <c r="AE101">
         <v>1.12</v>
       </c>
-      <c r="Z101">
-        <v>6</v>
-      </c>
-      <c r="AA101">
-        <v>1.38</v>
-      </c>
-      <c r="AB101">
-        <v>2.62</v>
-      </c>
-      <c r="AC101">
-        <v>2.05</v>
-      </c>
-      <c r="AD101">
-        <v>1.75</v>
-      </c>
-      <c r="AE101">
-        <v>1.29</v>
-      </c>
       <c r="AF101">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
+        <v>1.48</v>
+      </c>
+      <c r="O102">
+        <v>4.75</v>
+      </c>
+      <c r="P102">
+        <v>5.36</v>
+      </c>
+      <c r="Q102">
+        <v>1.91</v>
+      </c>
+      <c r="R102">
+        <v>2.76</v>
+      </c>
+      <c r="S102">
+        <v>1.2</v>
+      </c>
+      <c r="T102">
+        <v>4</v>
+      </c>
+      <c r="U102">
+        <v>2.01</v>
+      </c>
+      <c r="V102">
+        <v>1.7</v>
+      </c>
+      <c r="W102">
+        <v>1.16</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.12</v>
+      </c>
+      <c r="Z102">
+        <v>6</v>
+      </c>
+      <c r="AA102">
+        <v>1.38</v>
+      </c>
+      <c r="AB102">
+        <v>2.62</v>
+      </c>
+      <c r="AC102">
+        <v>2.05</v>
+      </c>
+      <c r="AD102">
+        <v>1.75</v>
+      </c>
+      <c r="AE102">
+        <v>1.29</v>
+      </c>
+      <c r="AF102">
+        <v>1.52</v>
+      </c>
+      <c r="AG102">
+        <v>2.45</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.12</v>
+      </c>
+      <c r="AK102">
         <v>2.4</v>
-      </c>
-      <c r="O102">
-        <v>3.2</v>
-      </c>
-      <c r="P102">
-        <v>2.59</v>
-      </c>
-      <c r="Q102">
-        <v>2.99</v>
-      </c>
-      <c r="R102">
-        <v>2.08</v>
-      </c>
-      <c r="S102">
-        <v>1.33</v>
-      </c>
-      <c r="T102">
-        <v>2.88</v>
-      </c>
-      <c r="U102">
-        <v>2.56</v>
-      </c>
-      <c r="V102">
-        <v>1.41</v>
-      </c>
-      <c r="W102">
-        <v>1.07</v>
-      </c>
-      <c r="X102">
-        <v>1</v>
-      </c>
-      <c r="Y102">
-        <v>1.27</v>
-      </c>
-      <c r="Z102">
-        <v>3.61</v>
-      </c>
-      <c r="AA102">
-        <v>1.83</v>
-      </c>
-      <c r="AB102">
-        <v>1.93</v>
-      </c>
-      <c r="AC102">
-        <v>3.17</v>
-      </c>
-      <c r="AD102">
-        <v>1.34</v>
-      </c>
-      <c r="AE102">
-        <v>1.12</v>
-      </c>
-      <c r="AF102">
-        <v>1.67</v>
-      </c>
-      <c r="AG102">
-        <v>2.11</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.3</v>
-      </c>
-      <c r="AK102">
-        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O127">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="P127">
-        <v>2.16</v>
+        <v>6.25</v>
       </c>
       <c r="Q127">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="R127">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S127">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T127">
         <v>4</v>
       </c>
       <c r="U127">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V127">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W127">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z127">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="AA127">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB127">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AC127">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD127">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE127">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF127">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AG127">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK127">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="O130">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="P130">
-        <v>6.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q130">
-        <v>1.75</v>
+        <v>3.32</v>
       </c>
       <c r="R130">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S130">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T130">
         <v>4</v>
       </c>
       <c r="U130">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V130">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W130">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X130">
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z130">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AA130">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB130">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AC130">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AD130">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE130">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF130">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AG130">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AK130">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.96</v>
+        <v>4.15</v>
       </c>
       <c r="O154">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P154">
-        <v>3.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q154">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="R154">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S154">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T154">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z154">
-        <v>3.51</v>
+        <v>4.6</v>
       </c>
       <c r="AA154">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AB154">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AC154">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="AD154">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF154">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AG154">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK154">
-        <v>1.74</v>
+        <v>1.12</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O155">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q155">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="R155">
+        <v>2.18</v>
+      </c>
+      <c r="S155">
+        <v>1.36</v>
+      </c>
+      <c r="T155">
+        <v>2.82</v>
+      </c>
+      <c r="U155">
+        <v>2.5</v>
+      </c>
+      <c r="V155">
+        <v>1.44</v>
+      </c>
+      <c r="W155">
+        <v>1.09</v>
+      </c>
+      <c r="X155">
+        <v>1.01</v>
+      </c>
+      <c r="Y155">
+        <v>1.2</v>
+      </c>
+      <c r="Z155">
+        <v>3.74</v>
+      </c>
+      <c r="AA155">
+        <v>1.78</v>
+      </c>
+      <c r="AB155">
         <v>1.98</v>
       </c>
-      <c r="S155">
-        <v>1.45</v>
-      </c>
-      <c r="T155">
-        <v>2.5</v>
-      </c>
-      <c r="U155">
-        <v>3</v>
-      </c>
-      <c r="V155">
-        <v>1.32</v>
-      </c>
-      <c r="W155">
-        <v>1.04</v>
-      </c>
-      <c r="X155">
-        <v>1.04</v>
-      </c>
-      <c r="Y155">
-        <v>1.34</v>
-      </c>
-      <c r="Z155">
-        <v>2.78</v>
-      </c>
-      <c r="AA155">
-        <v>2.22</v>
-      </c>
-      <c r="AB155">
-        <v>1.7</v>
-      </c>
       <c r="AC155">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD155">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE155">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG155">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.26</v>
       </c>
       <c r="AK155">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="Q156">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="R156">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T156">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W156">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z156">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AA156">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="AB156">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC156">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="AD156">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE156">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.15</v>
+        <v>1.96</v>
       </c>
       <c r="O157">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q157">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="R157">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S157">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T157">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U157">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="V157">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W157">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z157">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="AA157">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AB157">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC157">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="AD157">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AE157">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF157">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG157">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="O158">
+        <v>3.6</v>
+      </c>
+      <c r="P158">
         <v>3.5</v>
       </c>
-      <c r="P158">
-        <v>2.5</v>
-      </c>
       <c r="Q158">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="R158">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T158">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="U158">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V158">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W158">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z158">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA158">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB158">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AC158">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AD158">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF158">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG158">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,65 +28508,65 @@
         </is>
       </c>
       <c r="N173">
+        <v>2.78</v>
+      </c>
+      <c r="O173">
+        <v>3.4</v>
+      </c>
+      <c r="P173">
+        <v>2.36</v>
+      </c>
+      <c r="Q173">
+        <v>3.2</v>
+      </c>
+      <c r="R173">
+        <v>2.11</v>
+      </c>
+      <c r="S173">
+        <v>1.33</v>
+      </c>
+      <c r="T173">
+        <v>2.96</v>
+      </c>
+      <c r="U173">
+        <v>2.53</v>
+      </c>
+      <c r="V173">
+        <v>1.43</v>
+      </c>
+      <c r="W173">
+        <v>1.07</v>
+      </c>
+      <c r="X173">
+        <v>1.04</v>
+      </c>
+      <c r="Y173">
+        <v>1.23</v>
+      </c>
+      <c r="Z173">
+        <v>3.42</v>
+      </c>
+      <c r="AA173">
+        <v>1.9</v>
+      </c>
+      <c r="AB173">
+        <v>1.98</v>
+      </c>
+      <c r="AC173">
+        <v>3.1</v>
+      </c>
+      <c r="AD173">
+        <v>1.37</v>
+      </c>
+      <c r="AE173">
+        <v>1.14</v>
+      </c>
+      <c r="AF173">
+        <v>1.62</v>
+      </c>
+      <c r="AG173">
         <v>2.15</v>
       </c>
-      <c r="O173">
-        <v>3.43</v>
-      </c>
-      <c r="P173">
-        <v>3.4</v>
-      </c>
-      <c r="Q173">
-        <v>2.65</v>
-      </c>
-      <c r="R173">
-        <v>2.08</v>
-      </c>
-      <c r="S173">
-        <v>1.38</v>
-      </c>
-      <c r="T173">
-        <v>2.74</v>
-      </c>
-      <c r="U173">
-        <v>2.82</v>
-      </c>
-      <c r="V173">
-        <v>1.36</v>
-      </c>
-      <c r="W173">
-        <v>1.04</v>
-      </c>
-      <c r="X173">
-        <v>1.01</v>
-      </c>
-      <c r="Y173">
-        <v>1.27</v>
-      </c>
-      <c r="Z173">
-        <v>3.14</v>
-      </c>
-      <c r="AA173">
-        <v>2.04</v>
-      </c>
-      <c r="AB173">
-        <v>1.87</v>
-      </c>
-      <c r="AC173">
-        <v>3.28</v>
-      </c>
-      <c r="AD173">
-        <v>1.25</v>
-      </c>
-      <c r="AE173">
-        <v>1.11</v>
-      </c>
-      <c r="AF173">
-        <v>1.76</v>
-      </c>
-      <c r="AG173">
-        <v>1.96</v>
-      </c>
       <c r="AH173" t="inlineStr">
         <is>
           <t>[]</t>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
+        <v>2.6</v>
+      </c>
+      <c r="O174">
+        <v>3.7</v>
+      </c>
+      <c r="P174">
         <v>2.45</v>
       </c>
-      <c r="O174">
-        <v>3.47</v>
-      </c>
-      <c r="P174">
-        <v>2.49</v>
-      </c>
       <c r="Q174">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="R174">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S174">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U174">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V174">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z174">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="AA174">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB174">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="AC174">
-        <v>3.16</v>
+        <v>2.39</v>
       </c>
       <c r="AD174">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AE174">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF174">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG174">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK174">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O175">
-        <v>3.7</v>
+        <v>3.47</v>
       </c>
       <c r="P175">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q175">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
       <c r="R175">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T175">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U175">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W175">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z175">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA175">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB175">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="AC175">
-        <v>2.39</v>
+        <v>3.16</v>
       </c>
       <c r="AD175">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AE175">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF175">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AG175">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK175">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
+        <v>2.15</v>
+      </c>
+      <c r="O176">
+        <v>3.43</v>
+      </c>
+      <c r="P176">
+        <v>3.4</v>
+      </c>
+      <c r="Q176">
         <v>2.65</v>
       </c>
-      <c r="O176">
-        <v>3.3</v>
-      </c>
-      <c r="P176">
-        <v>2.6</v>
-      </c>
-      <c r="Q176">
-        <v>3.34</v>
-      </c>
       <c r="R176">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S176">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T176">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="U176">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="V176">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X176">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z176">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA176">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AB176">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC176">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD176">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE176">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF176">
         <v>1.76</v>
       </c>
       <c r="AG176">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.28</v>
       </c>
       <c r="AK176">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="O177">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="Q177">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R177">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S177">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T177">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U177">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V177">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W177">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z177">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA177">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB177">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC177">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD177">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE177">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF177">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="O188">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P188">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="Q188">
+        <v>2.1</v>
+      </c>
+      <c r="R188">
+        <v>2.38</v>
+      </c>
+      <c r="S188">
+        <v>1.25</v>
+      </c>
+      <c r="T188">
         <v>3.4</v>
       </c>
-      <c r="R188">
-        <v>2.18</v>
-      </c>
-      <c r="S188">
-        <v>1.29</v>
-      </c>
-      <c r="T188">
-        <v>3.3</v>
-      </c>
       <c r="U188">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V188">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W188">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z188">
         <v>4.15</v>
       </c>
       <c r="AA188">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB188">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC188">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD188">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE188">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="O189">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q189">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="R189">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S189">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T189">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="U189">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W189">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X189">
         <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z189">
-        <v>4.24</v>
+        <v>5.85</v>
       </c>
       <c r="AA189">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AB189">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC189">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="AD189">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE189">
+        <v>1.32</v>
+      </c>
+      <c r="AF189">
+        <v>1.47</v>
+      </c>
+      <c r="AG189">
+        <v>2.63</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
         <v>1.13</v>
       </c>
-      <c r="AF189">
-        <v>1.6</v>
-      </c>
-      <c r="AG189">
-        <v>2.25</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.22</v>
-      </c>
       <c r="AK189">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="O190">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P190">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q190">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R190">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S190">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T190">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U190">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V190">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z190">
         <v>4.15</v>
       </c>
       <c r="AA190">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB190">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC190">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD190">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE190">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF190">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG190">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK190">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="O192">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="P192">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q192">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="R192">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S192">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V192">
+        <v>1.5</v>
+      </c>
+      <c r="W192">
+        <v>1.08</v>
+      </c>
+      <c r="X192">
+        <v>1.01</v>
+      </c>
+      <c r="Y192">
+        <v>1.16</v>
+      </c>
+      <c r="Z192">
+        <v>4.24</v>
+      </c>
+      <c r="AA192">
+        <v>1.7</v>
+      </c>
+      <c r="AB192">
+        <v>2.1</v>
+      </c>
+      <c r="AC192">
+        <v>2.56</v>
+      </c>
+      <c r="AD192">
         <v>1.4</v>
       </c>
-      <c r="W192">
-        <v>1.06</v>
-      </c>
-      <c r="X192">
-        <v>1.03</v>
-      </c>
-      <c r="Y192">
-        <v>1.23</v>
-      </c>
-      <c r="Z192">
-        <v>3.42</v>
-      </c>
-      <c r="AA192">
-        <v>1.9</v>
-      </c>
-      <c r="AB192">
-        <v>1.82</v>
-      </c>
-      <c r="AC192">
-        <v>2.95</v>
-      </c>
-      <c r="AD192">
-        <v>1.3</v>
-      </c>
       <c r="AE192">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF192">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG192">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>1.22</v>
       </c>
       <c r="AK192">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,80 +31768,80 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O193">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P193">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q193">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="R193">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="S193">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="T193">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="U193">
+        <v>2.75</v>
+      </c>
+      <c r="V193">
+        <v>1.4</v>
+      </c>
+      <c r="W193">
+        <v>1.06</v>
+      </c>
+      <c r="X193">
+        <v>1.03</v>
+      </c>
+      <c r="Y193">
+        <v>1.23</v>
+      </c>
+      <c r="Z193">
+        <v>3.42</v>
+      </c>
+      <c r="AA193">
+        <v>1.9</v>
+      </c>
+      <c r="AB193">
+        <v>1.82</v>
+      </c>
+      <c r="AC193">
+        <v>2.95</v>
+      </c>
+      <c r="AD193">
+        <v>1.3</v>
+      </c>
+      <c r="AE193">
+        <v>1.08</v>
+      </c>
+      <c r="AF193">
+        <v>1.87</v>
+      </c>
+      <c r="AG193">
+        <v>1.9</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ193">
+        <v>1.22</v>
+      </c>
+      <c r="AK193">
         <v>2</v>
-      </c>
-      <c r="V193">
-        <v>1.76</v>
-      </c>
-      <c r="W193">
-        <v>1.19</v>
-      </c>
-      <c r="X193">
-        <v>1.01</v>
-      </c>
-      <c r="Y193">
-        <v>1.07</v>
-      </c>
-      <c r="Z193">
-        <v>5.85</v>
-      </c>
-      <c r="AA193">
-        <v>1.35</v>
-      </c>
-      <c r="AB193">
-        <v>2.88</v>
-      </c>
-      <c r="AC193">
-        <v>2</v>
-      </c>
-      <c r="AD193">
-        <v>1.73</v>
-      </c>
-      <c r="AE193">
-        <v>1.32</v>
-      </c>
-      <c r="AF193">
-        <v>1.47</v>
-      </c>
-      <c r="AG193">
-        <v>2.63</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ193">
-        <v>1.13</v>
-      </c>
-      <c r="AK193">
-        <v>2.4</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="O229">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P229">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q229">
-        <v>4.23</v>
+        <v>2.8</v>
       </c>
       <c r="R229">
         <v>2</v>
       </c>
       <c r="S229">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T229">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U229">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V229">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W229">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z229">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA229">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB229">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC229">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD229">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE229">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF229">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG229">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK229">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,80 +37799,80 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="O230">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P230">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q230">
-        <v>2.8</v>
+        <v>4.23</v>
       </c>
       <c r="R230">
         <v>2</v>
       </c>
       <c r="S230">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T230">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U230">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V230">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W230">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z230">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA230">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB230">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC230">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD230">
+        <v>1.21</v>
+      </c>
+      <c r="AE230">
+        <v>1.03</v>
+      </c>
+      <c r="AF230">
+        <v>1.8</v>
+      </c>
+      <c r="AG230">
+        <v>1.87</v>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ230">
         <v>1.24</v>
       </c>
-      <c r="AE230">
-        <v>1.04</v>
-      </c>
-      <c r="AF230">
-        <v>1.74</v>
-      </c>
-      <c r="AG230">
-        <v>1.94</v>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ230">
-        <v>1.3</v>
-      </c>
       <c r="AK230">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,80 +42852,80 @@
         </is>
       </c>
       <c r="N261">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="O261">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P261">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="Q261">
-        <v>6.33</v>
+        <v>4.33</v>
       </c>
       <c r="R261">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="S261">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T261">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U261">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V261">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W261">
         <v>1.08</v>
       </c>
       <c r="X261">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
+        <v>1.17</v>
+      </c>
+      <c r="Z261">
+        <v>4.16</v>
+      </c>
+      <c r="AA261">
+        <v>1.68</v>
+      </c>
+      <c r="AB261">
+        <v>2.15</v>
+      </c>
+      <c r="AC261">
+        <v>2.69</v>
+      </c>
+      <c r="AD261">
+        <v>1.44</v>
+      </c>
+      <c r="AE261">
+        <v>1.12</v>
+      </c>
+      <c r="AF261">
+        <v>1.67</v>
+      </c>
+      <c r="AG261">
+        <v>2.1</v>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ261">
         <v>1.22</v>
       </c>
-      <c r="Z261">
-        <v>3.9</v>
-      </c>
-      <c r="AA261">
-        <v>1.78</v>
-      </c>
-      <c r="AB261">
-        <v>1.94</v>
-      </c>
-      <c r="AC261">
-        <v>2.92</v>
-      </c>
-      <c r="AD261">
-        <v>1.38</v>
-      </c>
-      <c r="AE261">
-        <v>1.09</v>
-      </c>
-      <c r="AF261">
-        <v>1.87</v>
-      </c>
-      <c r="AG261">
-        <v>1.83</v>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ261">
-        <v>1.18</v>
-      </c>
       <c r="AK261">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="O262">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P262">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="Q262">
-        <v>4.33</v>
+        <v>6.33</v>
       </c>
       <c r="R262">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S262">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T262">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U262">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V262">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W262">
         <v>1.08</v>
       </c>
       <c r="X262">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y262">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z262">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="AA262">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AB262">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC262">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AD262">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE262">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF262">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG262">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK262">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>3.17</v>
+        <v>2.25</v>
       </c>
       <c r="O297">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="P297">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="Q297">
         <v>3.7</v>
@@ -48741,10 +48741,10 @@
         <v>2.8</v>
       </c>
       <c r="U297">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="V297">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W297">
         <v>1.06</v>
@@ -48753,13 +48753,13 @@
         <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z297">
         <v>3.2</v>
       </c>
       <c r="AA297">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB297">
         <v>1.85</v>
@@ -48774,7 +48774,7 @@
         <v>1.07</v>
       </c>
       <c r="AF297">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AG297">
         <v>2</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
         <v>3.2</v>
@@ -3436,7 +3436,7 @@
         <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.21</v>
@@ -3454,16 +3454,16 @@
         <v>2.85</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.62</v>
@@ -5534,55 +5534,55 @@
         <v>3.12</v>
       </c>
       <c r="Q32">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>2.72</v>
+        <v>3.09</v>
       </c>
       <c r="U32">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AC32">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AD32">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O35">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="P35">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="O45">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
         <v>2.3</v>
       </c>
       <c r="R45">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S45">
         <v>1.3</v>
@@ -7668,7 +7668,7 @@
         <v>2.75</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W45">
         <v>1.07</v>
@@ -7692,10 +7692,10 @@
         <v>2.92</v>
       </c>
       <c r="AD45">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
         <v>1.71</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="O50">
-        <v>6.4</v>
+        <v>6.52</v>
       </c>
       <c r="P50">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q52">
-        <v>3.14</v>
+        <v>2.05</v>
       </c>
       <c r="R52">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA52">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB52">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AC52">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>4.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q53">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="U53">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AC53">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="O64">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="P64">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q64">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="S64">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="V64">
-        <v>2.21</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA64">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC64">
-        <v>1.51</v>
+        <v>2.7</v>
       </c>
       <c r="AD64">
-        <v>2.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE64">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AG64">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="O65">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P65">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q65">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="R65">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="T65">
+        <v>5.4</v>
+      </c>
+      <c r="U65">
+        <v>1.65</v>
+      </c>
+      <c r="V65">
+        <v>2.21</v>
+      </c>
+      <c r="W65">
+        <v>1.32</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>1.01</v>
+      </c>
+      <c r="Z65">
+        <v>9.9</v>
+      </c>
+      <c r="AA65">
+        <v>1.17</v>
+      </c>
+      <c r="AB65">
+        <v>4.25</v>
+      </c>
+      <c r="AC65">
+        <v>1.51</v>
+      </c>
+      <c r="AD65">
+        <v>2.43</v>
+      </c>
+      <c r="AE65">
+        <v>1.69</v>
+      </c>
+      <c r="AF65">
+        <v>1.26</v>
+      </c>
+      <c r="AG65">
         <v>3.3</v>
       </c>
-      <c r="U65">
-        <v>2.45</v>
-      </c>
-      <c r="V65">
-        <v>1.44</v>
-      </c>
-      <c r="W65">
-        <v>1.11</v>
-      </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
-      <c r="Y65">
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.18</v>
       </c>
-      <c r="Z65">
-        <v>3.9</v>
-      </c>
-      <c r="AA65">
-        <v>1.67</v>
-      </c>
-      <c r="AB65">
-        <v>2.1</v>
-      </c>
-      <c r="AC65">
-        <v>2.7</v>
-      </c>
-      <c r="AD65">
-        <v>1.45</v>
-      </c>
-      <c r="AE65">
-        <v>1.12</v>
-      </c>
-      <c r="AF65">
-        <v>1.73</v>
-      </c>
-      <c r="AG65">
-        <v>2</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.22</v>
-      </c>
       <c r="AK65">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O70">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P70">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q70">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="R70">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S70">
         <v>1.2</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U70">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V70">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="W70">
         <v>1.2</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
-        <v>5.8</v>
+        <v>6.01</v>
       </c>
       <c r="AA70">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB70">
+        <v>3.1</v>
+      </c>
+      <c r="AC70">
+        <v>1.93</v>
+      </c>
+      <c r="AD70">
+        <v>1.75</v>
+      </c>
+      <c r="AE70">
+        <v>1.28</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AC70">
-        <v>2.02</v>
-      </c>
-      <c r="AD70">
-        <v>1.69</v>
-      </c>
-      <c r="AE70">
-        <v>1.25</v>
-      </c>
-      <c r="AF70">
-        <v>1.4</v>
-      </c>
-      <c r="AG70">
-        <v>2.7</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P71">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q71">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R71">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA71">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB71">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC71">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD71">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O72">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q72">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="R72">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U72">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>6.01</v>
+        <v>5.15</v>
       </c>
       <c r="AA72">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB72">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="AC72">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AD72">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE72">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>1.29</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X76">
         <v>1.03</v>
@@ -12751,7 +12751,7 @@
         <v>1.01</v>
       </c>
       <c r="AF76">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
         <v>1.8</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,37 +13675,37 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="O82">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>2.62</v>
+        <v>5.75</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.26</v>
@@ -13714,25 +13714,25 @@
         <v>3.2</v>
       </c>
       <c r="AA82">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB82">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD82">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
         <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG82">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P83">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
-        <v>2.02</v>
+        <v>2.81</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
+        <v>1.33</v>
+      </c>
+      <c r="Z83">
+        <v>2.9</v>
+      </c>
+      <c r="AA83">
+        <v>2.08</v>
+      </c>
+      <c r="AB83">
+        <v>1.64</v>
+      </c>
+      <c r="AC83">
+        <v>4.1</v>
+      </c>
+      <c r="AD83">
+        <v>1.2</v>
+      </c>
+      <c r="AE83">
+        <v>1.04</v>
+      </c>
+      <c r="AF83">
+        <v>1.85</v>
+      </c>
+      <c r="AG83">
+        <v>1.83</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.25</v>
       </c>
-      <c r="Z83">
-        <v>3.28</v>
-      </c>
-      <c r="AA83">
-        <v>1.84</v>
-      </c>
-      <c r="AB83">
-        <v>1.83</v>
-      </c>
-      <c r="AC83">
-        <v>2.97</v>
-      </c>
-      <c r="AD83">
-        <v>1.3</v>
-      </c>
-      <c r="AE83">
-        <v>1.08</v>
-      </c>
-      <c r="AF83">
-        <v>1.97</v>
-      </c>
-      <c r="AG83">
-        <v>1.72</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.17</v>
-      </c>
       <c r="AK83">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,65 +14001,65 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O84">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q84">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T84">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U84">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="V84">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
         <v>1.04</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z84">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA84">
+        <v>1.8</v>
+      </c>
+      <c r="AB84">
+        <v>1.87</v>
+      </c>
+      <c r="AC84">
+        <v>2.92</v>
+      </c>
+      <c r="AD84">
+        <v>1.31</v>
+      </c>
+      <c r="AE84">
+        <v>1.1</v>
+      </c>
+      <c r="AF84">
+        <v>1.62</v>
+      </c>
+      <c r="AG84">
         <v>2.15</v>
       </c>
-      <c r="AB84">
-        <v>1.6</v>
-      </c>
-      <c r="AC84">
-        <v>3.84</v>
-      </c>
-      <c r="AD84">
-        <v>1.18</v>
-      </c>
-      <c r="AE84">
-        <v>1.02</v>
-      </c>
-      <c r="AF84">
-        <v>1.85</v>
-      </c>
-      <c r="AG84">
-        <v>1.82</v>
-      </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O85">
         <v>3.1</v>
       </c>
       <c r="P85">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="R85">
         <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T85">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="U85">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V85">
         <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
+        <v>1.3</v>
+      </c>
+      <c r="Z85">
+        <v>3.25</v>
+      </c>
+      <c r="AA85">
+        <v>1.92</v>
+      </c>
+      <c r="AB85">
+        <v>1.76</v>
+      </c>
+      <c r="AC85">
+        <v>3.6</v>
+      </c>
+      <c r="AD85">
         <v>1.28</v>
       </c>
-      <c r="Z85">
-        <v>3.05</v>
-      </c>
-      <c r="AA85">
-        <v>1.99</v>
-      </c>
-      <c r="AB85">
-        <v>1.7</v>
-      </c>
-      <c r="AC85">
-        <v>3.5</v>
-      </c>
-      <c r="AD85">
-        <v>1.22</v>
-      </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK85">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O110">
+        <v>3.4</v>
+      </c>
+      <c r="P110">
+        <v>2.62</v>
+      </c>
+      <c r="Q110">
+        <v>2.7</v>
+      </c>
+      <c r="R110">
+        <v>2.38</v>
+      </c>
+      <c r="S110">
+        <v>1.25</v>
+      </c>
+      <c r="T110">
         <v>3.5</v>
       </c>
-      <c r="P110">
-        <v>2.65</v>
-      </c>
-      <c r="Q110">
-        <v>2.75</v>
-      </c>
-      <c r="R110">
-        <v>2.45</v>
-      </c>
-      <c r="S110">
-        <v>1.22</v>
-      </c>
-      <c r="T110">
-        <v>3.75</v>
-      </c>
       <c r="U110">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V110">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W110">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z110">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA110">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AB110">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC110">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AD110">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF110">
         <v>1.44</v>
       </c>
       <c r="AG110">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,7 +18411,7 @@
         <v>2.2</v>
       </c>
       <c r="Q111">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="R111">
         <v>2.07</v>
@@ -18438,7 +18438,7 @@
         <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AA111">
         <v>2</v>
@@ -18453,13 +18453,13 @@
         <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG111">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -20530,22 +20530,22 @@
         <v>3.31</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W124">
         <v>0</v>
@@ -20554,16 +20554,16 @@
         <v>0</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -20575,10 +20575,10 @@
         <v>0</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20865,7 +20865,7 @@
         <v>1.26</v>
       </c>
       <c r="T126">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U126">
         <v>2.3</v>
@@ -20883,28 +20883,28 @@
         <v>1.12</v>
       </c>
       <c r="Z126">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AA126">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB126">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC126">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD126">
         <v>1.58</v>
       </c>
       <c r="AE126">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF126">
         <v>1.46</v>
       </c>
       <c r="AG126">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>9.75</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="P127">
-        <v>6.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q127">
-        <v>1.75</v>
+        <v>7.9</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>3.72</v>
       </c>
       <c r="S127">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U127">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="V127">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="W127">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Z127">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA127">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AB127">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="AC127">
-        <v>2.05</v>
+        <v>1.39</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>2.91</v>
       </c>
       <c r="AE127">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="AF127">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK127">
-        <v>2.75</v>
+        <v>1.05</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>9.75</v>
+        <v>4.8</v>
       </c>
       <c r="O128">
-        <v>8.5</v>
+        <v>4.66</v>
       </c>
       <c r="P128">
+        <v>1.6</v>
+      </c>
+      <c r="Q128">
+        <v>4.7</v>
+      </c>
+      <c r="R128">
+        <v>2.67</v>
+      </c>
+      <c r="S128">
         <v>1.2</v>
       </c>
-      <c r="Q128">
+      <c r="T128">
+        <v>4.4</v>
+      </c>
+      <c r="U128">
+        <v>1.95</v>
+      </c>
+      <c r="V128">
+        <v>1.76</v>
+      </c>
+      <c r="W128">
+        <v>1.2</v>
+      </c>
+      <c r="X128">
+        <v>1.01</v>
+      </c>
+      <c r="Y128">
+        <v>1.1</v>
+      </c>
+      <c r="Z128">
         <v>7.5</v>
       </c>
-      <c r="R128">
-        <v>3.5</v>
-      </c>
-      <c r="S128">
-        <v>1.11</v>
-      </c>
-      <c r="T128">
-        <v>6</v>
-      </c>
-      <c r="U128">
-        <v>1.53</v>
-      </c>
-      <c r="V128">
-        <v>2.38</v>
-      </c>
-      <c r="W128">
-        <v>1.45</v>
-      </c>
-      <c r="X128">
-        <v>1</v>
-      </c>
-      <c r="Y128">
-        <v>1.04</v>
-      </c>
-      <c r="Z128">
-        <v>15</v>
-      </c>
       <c r="AA128">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AB128">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AC128">
+        <v>1.96</v>
+      </c>
+      <c r="AD128">
+        <v>1.9</v>
+      </c>
+      <c r="AE128">
         <v>1.38</v>
       </c>
-      <c r="AD128">
-        <v>2.99</v>
-      </c>
-      <c r="AE128">
-        <v>1.89</v>
-      </c>
       <c r="AF128">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG128">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
       <c r="AK128">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O129">
-        <v>4.66</v>
+        <v>3.84</v>
       </c>
       <c r="P129">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q129">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="R129">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U129">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z129">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>3.16</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AD129">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG129">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AK129">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O130">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="P130">
-        <v>2.16</v>
+        <v>6.25</v>
       </c>
       <c r="Q130">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="R130">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T130">
         <v>4</v>
       </c>
       <c r="U130">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V130">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W130">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z130">
         <v>5.45</v>
       </c>
       <c r="AA130">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB130">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AC130">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD130">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE130">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF130">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AG130">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21692,31 +21692,31 @@
         <v>1.11</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z131">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA131">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB131">
         <v>2</v>
       </c>
       <c r="AC131">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD131">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE131">
         <v>1.1</v>
       </c>
       <c r="AF131">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG131">
         <v>2.05</v>
@@ -21735,7 +21735,7 @@
         <v>1.22</v>
       </c>
       <c r="AK131">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="O134">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q134">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R134">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S134">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T134">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="U134">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="V134">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
+        <v>1.22</v>
+      </c>
+      <c r="Z134">
+        <v>3.74</v>
+      </c>
+      <c r="AA134">
+        <v>1.8</v>
+      </c>
+      <c r="AB134">
+        <v>1.95</v>
+      </c>
+      <c r="AC134">
+        <v>3</v>
+      </c>
+      <c r="AD134">
+        <v>1.36</v>
+      </c>
+      <c r="AE134">
         <v>1.1</v>
       </c>
-      <c r="Z134">
-        <v>5.1</v>
-      </c>
-      <c r="AA134">
-        <v>1.5</v>
-      </c>
-      <c r="AB134">
-        <v>2.6</v>
-      </c>
-      <c r="AC134">
-        <v>2.25</v>
-      </c>
-      <c r="AD134">
-        <v>1.69</v>
-      </c>
-      <c r="AE134">
-        <v>1.26</v>
-      </c>
       <c r="AF134">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG134">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK134">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.74</v>
+        <v>1.68</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P135">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q135">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R135">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="S135">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T135">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="U135">
+        <v>2.05</v>
+      </c>
+      <c r="V135">
+        <v>1.66</v>
+      </c>
+      <c r="W135">
+        <v>1.14</v>
+      </c>
+      <c r="X135">
+        <v>1.02</v>
+      </c>
+      <c r="Y135">
+        <v>1.1</v>
+      </c>
+      <c r="Z135">
+        <v>5.1</v>
+      </c>
+      <c r="AA135">
+        <v>1.5</v>
+      </c>
+      <c r="AB135">
         <v>2.6</v>
       </c>
-      <c r="V135">
-        <v>1.48</v>
-      </c>
-      <c r="W135">
-        <v>1.07</v>
-      </c>
-      <c r="X135">
-        <v>1.01</v>
-      </c>
-      <c r="Y135">
-        <v>1.22</v>
-      </c>
-      <c r="Z135">
-        <v>3.74</v>
-      </c>
-      <c r="AA135">
-        <v>1.8</v>
-      </c>
-      <c r="AB135">
-        <v>1.95</v>
-      </c>
       <c r="AC135">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AD135">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF135">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG135">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK135">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="O139">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P139">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="Q139">
-        <v>2.77</v>
+        <v>3.94</v>
       </c>
       <c r="R139">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S139">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T139">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U139">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V139">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W139">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y139">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z139">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA139">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB139">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC139">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="AD139">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE139">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG139">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.22</v>
       </c>
       <c r="AK139">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="O140">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P140">
-        <v>1.91</v>
+        <v>2.72</v>
       </c>
       <c r="Q140">
-        <v>3.94</v>
+        <v>2.77</v>
       </c>
       <c r="R140">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S140">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U140">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V140">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W140">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X140">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA140">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB140">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC140">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="AD140">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE140">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF140">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AG140">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.15</v>
+        <v>2.3</v>
       </c>
       <c r="O154">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P154">
-        <v>1.63</v>
+        <v>2.98</v>
       </c>
       <c r="Q154">
-        <v>3.9</v>
+        <v>2.69</v>
       </c>
       <c r="R154">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S154">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="T154">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="U154">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="V154">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W154">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y154">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="Z154">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="AA154">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="AB154">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC154">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="AD154">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="AE154">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AF154">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG154">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK154">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="O155">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P155">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q155">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R155">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S155">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T155">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U155">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V155">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W155">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z155">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA155">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB155">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC155">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AD155">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE155">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG155">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK155">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
+        <v>4.15</v>
+      </c>
+      <c r="O156">
+        <v>4.2</v>
+      </c>
+      <c r="P156">
+        <v>1.63</v>
+      </c>
+      <c r="Q156">
+        <v>3.9</v>
+      </c>
+      <c r="R156">
+        <v>2.28</v>
+      </c>
+      <c r="S156">
+        <v>1.23</v>
+      </c>
+      <c r="T156">
+        <v>3.5</v>
+      </c>
+      <c r="U156">
+        <v>2.21</v>
+      </c>
+      <c r="V156">
+        <v>1.57</v>
+      </c>
+      <c r="W156">
+        <v>1.13</v>
+      </c>
+      <c r="X156">
+        <v>1.03</v>
+      </c>
+      <c r="Y156">
+        <v>1.13</v>
+      </c>
+      <c r="Z156">
+        <v>4.6</v>
+      </c>
+      <c r="AA156">
+        <v>1.54</v>
+      </c>
+      <c r="AB156">
         <v>2.3</v>
       </c>
-      <c r="O156">
-        <v>3.3</v>
-      </c>
-      <c r="P156">
-        <v>2.98</v>
-      </c>
-      <c r="Q156">
-        <v>2.69</v>
-      </c>
-      <c r="R156">
-        <v>1.98</v>
-      </c>
-      <c r="S156">
-        <v>1.45</v>
-      </c>
-      <c r="T156">
-        <v>2.5</v>
-      </c>
-      <c r="U156">
-        <v>3</v>
-      </c>
-      <c r="V156">
-        <v>1.32</v>
-      </c>
-      <c r="W156">
-        <v>1.04</v>
-      </c>
-      <c r="X156">
-        <v>1.04</v>
-      </c>
-      <c r="Y156">
-        <v>1.34</v>
-      </c>
-      <c r="Z156">
-        <v>2.78</v>
-      </c>
-      <c r="AA156">
-        <v>2.22</v>
-      </c>
-      <c r="AB156">
-        <v>1.7</v>
-      </c>
       <c r="AC156">
-        <v>4.1</v>
+        <v>2.31</v>
       </c>
       <c r="AD156">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE156">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG156">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK156">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="O159">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P159">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q159">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R159">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S159">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T159">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U159">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z159">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA159">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB159">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC159">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="AD159">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF159">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG159">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK159">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26715,80 +26715,80 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="O162">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="P162">
-        <v>9.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q162">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="R162">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S162">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U162">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V162">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W162">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y162">
+        <v>1.18</v>
+      </c>
+      <c r="Z162">
+        <v>3.85</v>
+      </c>
+      <c r="AA162">
+        <v>1.75</v>
+      </c>
+      <c r="AB162">
+        <v>2.03</v>
+      </c>
+      <c r="AC162">
+        <v>2.78</v>
+      </c>
+      <c r="AD162">
+        <v>1.34</v>
+      </c>
+      <c r="AE162">
+        <v>1.09</v>
+      </c>
+      <c r="AF162">
+        <v>1.85</v>
+      </c>
+      <c r="AG162">
+        <v>1.85</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
         <v>1.17</v>
       </c>
-      <c r="Z162">
-        <v>3.95</v>
-      </c>
-      <c r="AA162">
-        <v>1.7</v>
-      </c>
-      <c r="AB162">
-        <v>2.1</v>
-      </c>
-      <c r="AC162">
-        <v>2.7</v>
-      </c>
-      <c r="AD162">
-        <v>1.36</v>
-      </c>
-      <c r="AE162">
-        <v>1.1</v>
-      </c>
-      <c r="AF162">
-        <v>2.09</v>
-      </c>
-      <c r="AG162">
-        <v>1.65</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>1.09</v>
-      </c>
       <c r="AK162">
-        <v>3.22</v>
+        <v>2.42</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
+        <v>1.2</v>
+      </c>
+      <c r="O163">
+        <v>5.75</v>
+      </c>
+      <c r="P163">
+        <v>10</v>
+      </c>
+      <c r="Q163">
+        <v>1.62</v>
+      </c>
+      <c r="R163">
+        <v>2.62</v>
+      </c>
+      <c r="S163">
+        <v>1.27</v>
+      </c>
+      <c r="T163">
+        <v>3.5</v>
+      </c>
+      <c r="U163">
+        <v>2.19</v>
+      </c>
+      <c r="V163">
+        <v>1.58</v>
+      </c>
+      <c r="W163">
+        <v>1.15</v>
+      </c>
+      <c r="X163">
+        <v>1.01</v>
+      </c>
+      <c r="Y163">
+        <v>1.12</v>
+      </c>
+      <c r="Z163">
+        <v>4.65</v>
+      </c>
+      <c r="AA163">
+        <v>1.51</v>
+      </c>
+      <c r="AB163">
+        <v>2.26</v>
+      </c>
+      <c r="AC163">
+        <v>2.33</v>
+      </c>
+      <c r="AD163">
+        <v>1.52</v>
+      </c>
+      <c r="AE163">
         <v>1.17</v>
-      </c>
-      <c r="O163">
-        <v>5.65</v>
-      </c>
-      <c r="P163">
-        <v>12.7</v>
-      </c>
-      <c r="Q163">
-        <v>1.71</v>
-      </c>
-      <c r="R163">
-        <v>2.47</v>
-      </c>
-      <c r="S163">
-        <v>1.26</v>
-      </c>
-      <c r="T163">
-        <v>3.24</v>
-      </c>
-      <c r="U163">
-        <v>2.34</v>
-      </c>
-      <c r="V163">
-        <v>1.48</v>
-      </c>
-      <c r="W163">
-        <v>1.11</v>
-      </c>
-      <c r="X163">
-        <v>1.02</v>
-      </c>
-      <c r="Y163">
-        <v>1.18</v>
-      </c>
-      <c r="Z163">
-        <v>3.9</v>
-      </c>
-      <c r="AA163">
-        <v>1.67</v>
-      </c>
-      <c r="AB163">
-        <v>2.04</v>
-      </c>
-      <c r="AC163">
-        <v>2.62</v>
-      </c>
-      <c r="AD163">
-        <v>1.38</v>
-      </c>
-      <c r="AE163">
-        <v>1.11</v>
       </c>
       <c r="AF163">
         <v>2.15</v>
       </c>
       <c r="AG163">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK163">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="O173">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P173">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="Q173">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R173">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T173">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U173">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V173">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X173">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA173">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB173">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC173">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD173">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE173">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF173">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG173">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="O177">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q177">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R177">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S177">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T177">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="U177">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V177">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y177">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z177">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA177">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB177">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC177">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD177">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AE177">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF177">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG177">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK177">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29495,55 +29495,55 @@
         <v>5.15</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA179">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB179">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O185">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q185">
-        <v>2.16</v>
+        <v>3.13</v>
       </c>
       <c r="R185">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S185">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T185">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U185">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V185">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W185">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X185">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y185">
         <v>1.18</v>
       </c>
       <c r="Z185">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AA185">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB185">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC185">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="AD185">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE185">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF185">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG185">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK185">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,80 +30627,80 @@
         </is>
       </c>
       <c r="N186">
+        <v>1.59</v>
+      </c>
+      <c r="O186">
+        <v>4.5</v>
+      </c>
+      <c r="P186">
+        <v>4.8</v>
+      </c>
+      <c r="Q186">
+        <v>1.91</v>
+      </c>
+      <c r="R186">
         <v>2.6</v>
       </c>
-      <c r="O186">
-        <v>3.5</v>
-      </c>
-      <c r="P186">
-        <v>2.5</v>
-      </c>
-      <c r="Q186">
-        <v>3.13</v>
-      </c>
-      <c r="R186">
-        <v>2.25</v>
-      </c>
       <c r="S186">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T186">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="U186">
+        <v>2</v>
+      </c>
+      <c r="V186">
+        <v>1.76</v>
+      </c>
+      <c r="W186">
+        <v>1.19</v>
+      </c>
+      <c r="X186">
+        <v>1.01</v>
+      </c>
+      <c r="Y186">
+        <v>1.07</v>
+      </c>
+      <c r="Z186">
+        <v>5.85</v>
+      </c>
+      <c r="AA186">
+        <v>1.35</v>
+      </c>
+      <c r="AB186">
+        <v>2.88</v>
+      </c>
+      <c r="AC186">
+        <v>2</v>
+      </c>
+      <c r="AD186">
+        <v>1.73</v>
+      </c>
+      <c r="AE186">
+        <v>1.32</v>
+      </c>
+      <c r="AF186">
+        <v>1.47</v>
+      </c>
+      <c r="AG186">
+        <v>2.63</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ186">
+        <v>1.13</v>
+      </c>
+      <c r="AK186">
         <v>2.4</v>
-      </c>
-      <c r="V186">
-        <v>1.5</v>
-      </c>
-      <c r="W186">
-        <v>1.11</v>
-      </c>
-      <c r="X186">
-        <v>1</v>
-      </c>
-      <c r="Y186">
-        <v>1.18</v>
-      </c>
-      <c r="Z186">
-        <v>3.88</v>
-      </c>
-      <c r="AA186">
-        <v>1.65</v>
-      </c>
-      <c r="AB186">
-        <v>2.09</v>
-      </c>
-      <c r="AC186">
-        <v>2.53</v>
-      </c>
-      <c r="AD186">
-        <v>1.44</v>
-      </c>
-      <c r="AE186">
-        <v>1.13</v>
-      </c>
-      <c r="AF186">
-        <v>1.55</v>
-      </c>
-      <c r="AG186">
-        <v>2.38</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ186">
-        <v>1.28</v>
-      </c>
-      <c r="AK186">
-        <v>1.44</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="O187">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P187">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q187">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="R187">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S187">
         <v>1.29</v>
       </c>
       <c r="T187">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U187">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V187">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z187">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="AA187">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB187">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC187">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AD187">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE187">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF187">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG187">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="O188">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q188">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R188">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S188">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U188">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V188">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X188">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z188">
         <v>4.15</v>
       </c>
       <c r="AA188">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB188">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC188">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD188">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE188">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF188">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK188">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="O189">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P189">
-        <v>4.8</v>
+        <v>6.06</v>
       </c>
       <c r="Q189">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R189">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S189">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T189">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U189">
         <v>2</v>
       </c>
       <c r="V189">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="W189">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X189">
         <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z189">
-        <v>5.85</v>
+        <v>5.45</v>
       </c>
       <c r="AA189">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AB189">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AC189">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AD189">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE189">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF189">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG189">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK189">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="O190">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P190">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="Q190">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="R190">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S190">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T190">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U190">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="V190">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W190">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X190">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z190">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA190">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB190">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AC190">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="AD190">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE190">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF190">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG190">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK190">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O191">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P191">
-        <v>6.06</v>
+        <v>4.33</v>
       </c>
       <c r="Q191">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R191">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S191">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T191">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U191">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="V191">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="W191">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z191">
-        <v>5.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA191">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AB191">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AC191">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="AD191">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE191">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF191">
         <v>1.57</v>
       </c>
       <c r="AG191">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK191">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,49 +31605,49 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="O192">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="P192">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q192">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="R192">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T192">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U192">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V192">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W192">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y192">
         <v>1.16</v>
       </c>
       <c r="Z192">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA192">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB192">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC192">
         <v>2.56</v>
@@ -31656,13 +31656,13 @@
         <v>1.4</v>
       </c>
       <c r="AE192">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF192">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG192">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>1.22</v>
       </c>
       <c r="AK192">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O193">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P193">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q193">
         <v>2.16</v>
       </c>
       <c r="R193">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S193">
         <v>1.33</v>
       </c>
       <c r="T193">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U193">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V193">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W193">
         <v>1.06</v>
       </c>
       <c r="X193">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z193">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="AA193">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB193">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AC193">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AD193">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE193">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF193">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG193">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK193">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O198">
         <v>3.7</v>
@@ -32616,7 +32616,7 @@
         <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z198">
         <v>4.1</v>
@@ -32625,7 +32625,7 @@
         <v>1.68</v>
       </c>
       <c r="AB198">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AC198">
         <v>2.46</v>
@@ -32634,7 +32634,7 @@
         <v>1.43</v>
       </c>
       <c r="AE198">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF198">
         <v>1.53</v>
@@ -33244,55 +33244,55 @@
         <v>2.47</v>
       </c>
       <c r="Q202">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R202">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S202">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T202">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U202">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V202">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W202">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X202">
         <v>1.03</v>
       </c>
       <c r="Y202">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z202">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AA202">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB202">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC202">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AD202">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE202">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF202">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG202">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK202">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -34053,25 +34053,25 @@
         <v>3.2</v>
       </c>
       <c r="O207">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P207">
         <v>2.1</v>
       </c>
       <c r="Q207">
-        <v>3.84</v>
+        <v>4.16</v>
       </c>
       <c r="R207">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S207">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T207">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U207">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V207">
         <v>1.33</v>
@@ -34080,35 +34080,35 @@
         <v>1.06</v>
       </c>
       <c r="X207">
+        <v>1.05</v>
+      </c>
+      <c r="Y207">
+        <v>1.4</v>
+      </c>
+      <c r="Z207">
+        <v>2.77</v>
+      </c>
+      <c r="AA207">
+        <v>2.28</v>
+      </c>
+      <c r="AB207">
+        <v>1.6</v>
+      </c>
+      <c r="AC207">
+        <v>3.98</v>
+      </c>
+      <c r="AD207">
+        <v>1.17</v>
+      </c>
+      <c r="AE207">
         <v>1.03</v>
       </c>
-      <c r="Y207">
-        <v>1.31</v>
-      </c>
-      <c r="Z207">
-        <v>2.92</v>
-      </c>
-      <c r="AA207">
-        <v>2.02</v>
-      </c>
-      <c r="AB207">
-        <v>1.7</v>
-      </c>
-      <c r="AC207">
-        <v>3.58</v>
-      </c>
-      <c r="AD207">
-        <v>1.21</v>
-      </c>
-      <c r="AE207">
-        <v>1.05</v>
-      </c>
       <c r="AF207">
+        <v>1.91</v>
+      </c>
+      <c r="AG207">
         <v>1.8</v>
       </c>
-      <c r="AG207">
-        <v>1.89</v>
-      </c>
       <c r="AH207" t="inlineStr">
         <is>
           <t>[]</t>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
+        <v>1.26</v>
+      </c>
+      <c r="AK207">
         <v>1.25</v>
-      </c>
-      <c r="AK207">
-        <v>1.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34216,22 +34216,22 @@
         <v>1.9</v>
       </c>
       <c r="O208">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P208">
         <v>3.5</v>
       </c>
       <c r="Q208">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R208">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S208">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T208">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U208">
         <v>2.88</v>
@@ -34249,19 +34249,19 @@
         <v>1.37</v>
       </c>
       <c r="Z208">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AA208">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB208">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC208">
         <v>3.78</v>
       </c>
       <c r="AD208">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE208">
         <v>1.03</v>
@@ -34382,13 +34382,13 @@
         <v>4</v>
       </c>
       <c r="P209">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q209">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R209">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S209">
         <v>1.17</v>
@@ -34397,7 +34397,7 @@
         <v>4.1</v>
       </c>
       <c r="U209">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V209">
         <v>1.7</v>
@@ -34415,25 +34415,25 @@
         <v>6.05</v>
       </c>
       <c r="AA209">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB209">
         <v>2.87</v>
       </c>
       <c r="AC209">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD209">
         <v>1.84</v>
       </c>
       <c r="AE209">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF209">
         <v>1.39</v>
       </c>
       <c r="AG209">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
         <v>2</v>
@@ -34539,80 +34539,80 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="O210">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="P210">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q210">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="R210">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="S210">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T210">
+        <v>2.7</v>
+      </c>
+      <c r="U210">
+        <v>2.9</v>
+      </c>
+      <c r="V210">
+        <v>1.35</v>
+      </c>
+      <c r="W210">
+        <v>1.07</v>
+      </c>
+      <c r="X210">
+        <v>1.03</v>
+      </c>
+      <c r="Y210">
+        <v>1.37</v>
+      </c>
+      <c r="Z210">
+        <v>2.97</v>
+      </c>
+      <c r="AA210">
+        <v>1.99</v>
+      </c>
+      <c r="AB210">
+        <v>1.8</v>
+      </c>
+      <c r="AC210">
+        <v>3.5</v>
+      </c>
+      <c r="AD210">
+        <v>1.22</v>
+      </c>
+      <c r="AE210">
+        <v>1.03</v>
+      </c>
+      <c r="AF210">
         <v>3.08</v>
       </c>
-      <c r="U210">
-        <v>2.63</v>
-      </c>
-      <c r="V210">
-        <v>1.44</v>
-      </c>
-      <c r="W210">
+      <c r="AG210">
+        <v>1.3</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ210">
         <v>1.08</v>
       </c>
-      <c r="X210">
-        <v>1</v>
-      </c>
-      <c r="Y210">
-        <v>1.22</v>
-      </c>
-      <c r="Z210">
-        <v>3.5</v>
-      </c>
-      <c r="AA210">
-        <v>1.77</v>
-      </c>
-      <c r="AB210">
-        <v>2</v>
-      </c>
-      <c r="AC210">
-        <v>2.88</v>
-      </c>
-      <c r="AD210">
-        <v>1.32</v>
-      </c>
-      <c r="AE210">
-        <v>1.1</v>
-      </c>
-      <c r="AF210">
-        <v>2.93</v>
-      </c>
-      <c r="AG210">
-        <v>1.33</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ210">
-        <v>1.05</v>
-      </c>
       <c r="AK210">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34702,16 +34702,16 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O211">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P211">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="Q211">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R211">
         <v>2.3</v>
@@ -34723,13 +34723,13 @@
         <v>3.6</v>
       </c>
       <c r="U211">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="V211">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W211">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X211">
         <v>1.02</v>
@@ -34738,28 +34738,28 @@
         <v>1.13</v>
       </c>
       <c r="Z211">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA211">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB211">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AC211">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD211">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE211">
         <v>1.16</v>
       </c>
       <c r="AF211">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG211">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK211">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34874,13 +34874,13 @@
         <v>3.3</v>
       </c>
       <c r="Q212">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R212">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S212">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T212">
         <v>3.18</v>
@@ -34889,7 +34889,7 @@
         <v>2.38</v>
       </c>
       <c r="V212">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W212">
         <v>1.12</v>
@@ -34904,19 +34904,19 @@
         <v>4.05</v>
       </c>
       <c r="AA212">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB212">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AC212">
         <v>2.56</v>
       </c>
       <c r="AD212">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE212">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF212">
         <v>1.56</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK212">
         <v>1.75</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O219">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P219">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="O220">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P220">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q220">
         <v>2.82</v>
@@ -36184,13 +36184,13 @@
         <v>1.98</v>
       </c>
       <c r="S220">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T220">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U220">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V220">
         <v>1.31</v>
@@ -36211,7 +36211,7 @@
         <v>2.15</v>
       </c>
       <c r="AB220">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC220">
         <v>3.95</v>
@@ -36239,7 +36239,7 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK220">
         <v>1.54</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O221">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P221">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="Q221">
         <v>3.62</v>
@@ -36347,13 +36347,13 @@
         <v>2.18</v>
       </c>
       <c r="S221">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T221">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U221">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V221">
         <v>1.44</v>
@@ -36380,7 +36380,7 @@
         <v>2.88</v>
       </c>
       <c r="AD221">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE221">
         <v>1.09</v>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK221">
         <v>1.3</v>
@@ -36495,22 +36495,22 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O222">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P222">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q222">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R222">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S222">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T222">
         <v>2.68</v>
@@ -36534,7 +36534,7 @@
         <v>3.2</v>
       </c>
       <c r="AA222">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB222">
         <v>1.78</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="O223">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q223">
         <v>2.63</v>
@@ -36673,7 +36673,7 @@
         <v>2.06</v>
       </c>
       <c r="S223">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T223">
         <v>2.77</v>
@@ -36715,7 +36715,7 @@
         <v>1.75</v>
       </c>
       <c r="AG223">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.24</v>
       </c>
       <c r="AK223">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,80 +37636,80 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="O229">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P229">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q229">
-        <v>2.8</v>
+        <v>4.23</v>
       </c>
       <c r="R229">
         <v>2</v>
       </c>
       <c r="S229">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T229">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U229">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V229">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W229">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z229">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA229">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB229">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC229">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD229">
+        <v>1.21</v>
+      </c>
+      <c r="AE229">
+        <v>1.03</v>
+      </c>
+      <c r="AF229">
+        <v>1.8</v>
+      </c>
+      <c r="AG229">
+        <v>1.87</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
         <v>1.24</v>
       </c>
-      <c r="AE229">
-        <v>1.04</v>
-      </c>
-      <c r="AF229">
-        <v>1.74</v>
-      </c>
-      <c r="AG229">
-        <v>1.94</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ229">
-        <v>1.3</v>
-      </c>
       <c r="AK229">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="O230">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P230">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q230">
-        <v>4.23</v>
+        <v>2.8</v>
       </c>
       <c r="R230">
         <v>2</v>
       </c>
       <c r="S230">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T230">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U230">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V230">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W230">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z230">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA230">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB230">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC230">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD230">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE230">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF230">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG230">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="O231">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P231">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O236">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P236">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q236">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R236">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S236">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T236">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U236">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="V236">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W236">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X236">
         <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z236">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA236">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB236">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC236">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD236">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE236">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF236">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG236">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38940,31 +38940,31 @@
         </is>
       </c>
       <c r="N237">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O237">
         <v>3.1</v>
       </c>
       <c r="P237">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q237">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="R237">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="S237">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T237">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="U237">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V237">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W237">
         <v>1.03</v>
@@ -38973,31 +38973,31 @@
         <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z237">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA237">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB237">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC237">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD237">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE237">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF237">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG237">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK237">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,34 +39103,34 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O238">
         <v>3.1</v>
       </c>
       <c r="P238">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q238">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R238">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S238">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T238">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="U238">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V238">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X238">
         <v>1.02</v>
@@ -39148,19 +39148,19 @@
         <v>1.67</v>
       </c>
       <c r="AC238">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD238">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE238">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF238">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG238">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK238">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,31 +39266,31 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O239">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q239">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R239">
         <v>2.1</v>
       </c>
       <c r="S239">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T239">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U239">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V239">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W239">
         <v>1.06</v>
@@ -39299,31 +39299,31 @@
         <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z239">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA239">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB239">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC239">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AD239">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE239">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF239">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG239">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK239">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39438,55 +39438,55 @@
         <v>2.5</v>
       </c>
       <c r="Q240">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R240">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S240">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T240">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="U240">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V240">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W240">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X240">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y240">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z240">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA240">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB240">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC240">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AD240">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE240">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF240">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG240">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>1.3</v>
       </c>
       <c r="AK240">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="O247">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P247">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q247">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R247">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S247">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T247">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="U247">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V247">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W247">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X247">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z247">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA247">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB247">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC247">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD247">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE247">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF247">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG247">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK247">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O248">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P248">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="Q248">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="R248">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S248">
+        <v>1.36</v>
+      </c>
+      <c r="T248">
+        <v>2.85</v>
+      </c>
+      <c r="U248">
+        <v>2.76</v>
+      </c>
+      <c r="V248">
         <v>1.39</v>
       </c>
-      <c r="T248">
-        <v>2.61</v>
-      </c>
-      <c r="U248">
-        <v>2.86</v>
-      </c>
-      <c r="V248">
-        <v>1.33</v>
-      </c>
       <c r="W248">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X248">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z248">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AA248">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AB248">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC248">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD248">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE248">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF248">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG248">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK248">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41231,55 +41231,55 @@
         <v>3.64</v>
       </c>
       <c r="Q251">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="R251">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S251">
+        <v>1.4</v>
+      </c>
+      <c r="T251">
+        <v>2.7</v>
+      </c>
+      <c r="U251">
+        <v>3</v>
+      </c>
+      <c r="V251">
+        <v>1.35</v>
+      </c>
+      <c r="W251">
+        <v>1.07</v>
+      </c>
+      <c r="X251">
+        <v>1.04</v>
+      </c>
+      <c r="Y251">
         <v>1.38</v>
       </c>
-      <c r="T251">
-        <v>2.65</v>
-      </c>
-      <c r="U251">
+      <c r="Z251">
         <v>2.86</v>
       </c>
-      <c r="V251">
-        <v>1.33</v>
-      </c>
-      <c r="W251">
-        <v>1.04</v>
-      </c>
-      <c r="X251">
+      <c r="AA251">
+        <v>2.11</v>
+      </c>
+      <c r="AB251">
+        <v>1.62</v>
+      </c>
+      <c r="AC251">
+        <v>3.75</v>
+      </c>
+      <c r="AD251">
+        <v>1.19</v>
+      </c>
+      <c r="AE251">
         <v>1.03</v>
       </c>
-      <c r="Y251">
-        <v>1.33</v>
-      </c>
-      <c r="Z251">
-        <v>2.81</v>
-      </c>
-      <c r="AA251">
-        <v>2.08</v>
-      </c>
-      <c r="AB251">
-        <v>1.64</v>
-      </c>
-      <c r="AC251">
-        <v>3.72</v>
-      </c>
-      <c r="AD251">
-        <v>1.2</v>
-      </c>
-      <c r="AE251">
-        <v>1.04</v>
-      </c>
       <c r="AF251">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG251">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>1.24</v>
       </c>
       <c r="AK251">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="O256">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="P256">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="Q256">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="R256">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S256">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T256">
         <v>2.57</v>
       </c>
       <c r="U256">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="V256">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W256">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X256">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y256">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z256">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AA256">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB256">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC256">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AD256">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE256">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF256">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG256">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK256">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,65 +42200,65 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="O257">
         <v>3.1</v>
       </c>
       <c r="P257">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q257">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="R257">
+        <v>2.1</v>
+      </c>
+      <c r="S257">
+        <v>1.36</v>
+      </c>
+      <c r="T257">
+        <v>2.71</v>
+      </c>
+      <c r="U257">
+        <v>2.85</v>
+      </c>
+      <c r="V257">
+        <v>1.33</v>
+      </c>
+      <c r="W257">
+        <v>1.06</v>
+      </c>
+      <c r="X257">
+        <v>1.02</v>
+      </c>
+      <c r="Y257">
+        <v>1.38</v>
+      </c>
+      <c r="Z257">
+        <v>2.87</v>
+      </c>
+      <c r="AA257">
+        <v>1.96</v>
+      </c>
+      <c r="AB257">
+        <v>1.83</v>
+      </c>
+      <c r="AC257">
+        <v>3.42</v>
+      </c>
+      <c r="AD257">
+        <v>1.23</v>
+      </c>
+      <c r="AE257">
+        <v>1.07</v>
+      </c>
+      <c r="AF257">
+        <v>1.7</v>
+      </c>
+      <c r="AG257">
         <v>2</v>
       </c>
-      <c r="S257">
-        <v>1.41</v>
-      </c>
-      <c r="T257">
-        <v>2.54</v>
-      </c>
-      <c r="U257">
-        <v>3.2</v>
-      </c>
-      <c r="V257">
-        <v>1.28</v>
-      </c>
-      <c r="W257">
-        <v>1.04</v>
-      </c>
-      <c r="X257">
-        <v>1.03</v>
-      </c>
-      <c r="Y257">
-        <v>1.32</v>
-      </c>
-      <c r="Z257">
-        <v>2.88</v>
-      </c>
-      <c r="AA257">
-        <v>2.15</v>
-      </c>
-      <c r="AB257">
-        <v>1.66</v>
-      </c>
-      <c r="AC257">
-        <v>3.86</v>
-      </c>
-      <c r="AD257">
-        <v>1.18</v>
-      </c>
-      <c r="AE257">
-        <v>1.04</v>
-      </c>
-      <c r="AF257">
-        <v>1.83</v>
-      </c>
-      <c r="AG257">
-        <v>1.83</v>
-      </c>
       <c r="AH257" t="inlineStr">
         <is>
           <t>[]</t>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK257">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42363,37 +42363,37 @@
         </is>
       </c>
       <c r="N258">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O258">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P258">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="Q258">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="R258">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S258">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T258">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U258">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V258">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W258">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X258">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y258">
         <v>1.21</v>
@@ -42402,25 +42402,25 @@
         <v>3.58</v>
       </c>
       <c r="AA258">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB258">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC258">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD258">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE258">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF258">
         <v>1.62</v>
       </c>
       <c r="AG258">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK258">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="O259">
-        <v>4.86</v>
+        <v>3.85</v>
       </c>
       <c r="P259">
-        <v>6.95</v>
+        <v>5.2</v>
       </c>
       <c r="Q259">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R259">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S259">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T259">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U259">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="V259">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W259">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X259">
         <v>1</v>
       </c>
       <c r="Y259">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z259">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AA259">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB259">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AC259">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AD259">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE259">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF259">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG259">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK259">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42698,10 +42698,10 @@
         <v>15</v>
       </c>
       <c r="Q260">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R260">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S260">
         <v>1.17</v>
@@ -42731,22 +42731,22 @@
         <v>1.34</v>
       </c>
       <c r="AB260">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AC260">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AD260">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AE260">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF260">
         <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK260">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43187,10 +43187,10 @@
         <v>1.39</v>
       </c>
       <c r="Q263">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="R263">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="S263">
         <v>1.22</v>
@@ -43199,7 +43199,7 @@
         <v>3.55</v>
       </c>
       <c r="U263">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="V263">
         <v>1.62</v>
@@ -43211,19 +43211,19 @@
         <v>1.02</v>
       </c>
       <c r="Y263">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z263">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA263">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB263">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AC263">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AD263">
         <v>1.62</v>
@@ -43248,7 +43248,7 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK263">
         <v>1.11</v>
@@ -43996,61 +43996,61 @@
         <v>1.22</v>
       </c>
       <c r="O268">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="P268">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q268">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R268">
         <v>2.8</v>
       </c>
       <c r="S268">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T268">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="U268">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V268">
         <v>1.62</v>
       </c>
       <c r="W268">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X268">
         <v>1.02</v>
       </c>
       <c r="Y268">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z268">
-        <v>5.49</v>
+        <v>5.08</v>
       </c>
       <c r="AA268">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB268">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC268">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD268">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AE268">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF268">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG268">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>1.11</v>
       </c>
       <c r="AK268">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44165,16 +44165,16 @@
         <v>2.8</v>
       </c>
       <c r="Q269">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R269">
         <v>2</v>
       </c>
       <c r="S269">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T269">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U269">
         <v>3.1</v>
@@ -44183,7 +44183,7 @@
         <v>1.28</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X269">
         <v>1.04</v>
@@ -44204,7 +44204,7 @@
         <v>4</v>
       </c>
       <c r="AD269">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE269">
         <v>1.02</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O272">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P272">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O275">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P275">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q275">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R275">
         <v>2.1</v>
       </c>
       <c r="S275">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="U275">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="V275">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W275">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X275">
         <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z275">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AA275">
         <v>2.04</v>
       </c>
       <c r="AB275">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC275">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD275">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE275">
         <v>1.05</v>
       </c>
       <c r="AF275">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AG275">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK275">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45330,16 +45330,16 @@
         <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z276">
         <v>7.4</v>
       </c>
       <c r="AA276">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AB276">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AC276">
         <v>1.76</v>
@@ -45348,7 +45348,7 @@
         <v>2.11</v>
       </c>
       <c r="AE276">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AF276">
         <v>1.33</v>
@@ -45460,40 +45460,40 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="O277">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="Q277">
-        <v>3.69</v>
+        <v>4.4</v>
       </c>
       <c r="R277">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T277">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U277">
         <v>2.77</v>
       </c>
       <c r="V277">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W277">
+        <v>1.07</v>
+      </c>
+      <c r="X277">
         <v>1.06</v>
       </c>
-      <c r="X277">
-        <v>1.02</v>
-      </c>
       <c r="Y277">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z277">
         <v>3.25</v>
@@ -45505,19 +45505,19 @@
         <v>1.72</v>
       </c>
       <c r="AC277">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD277">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE277">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF277">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG277">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK277">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.27</v>
+        <v>1.79</v>
       </c>
       <c r="O278">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P278">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q278">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="R278">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S278">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T278">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U278">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V278">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W278">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X278">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y278">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z278">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AA278">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AB278">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC278">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AD278">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE278">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF278">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG278">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK278">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45795,10 +45795,10 @@
         <v>3.3</v>
       </c>
       <c r="Q279">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R279">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="S279">
         <v>1.19</v>
@@ -45810,10 +45810,10 @@
         <v>2.05</v>
       </c>
       <c r="V279">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="W279">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X279">
         <v>1.01</v>
@@ -45831,10 +45831,10 @@
         <v>2.87</v>
       </c>
       <c r="AC279">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD279">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE279">
         <v>1.28</v>
@@ -45859,7 +45859,7 @@
         <v>1.19</v>
       </c>
       <c r="AK279">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46674,7 +46674,7 @@
         <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,22 +46764,22 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="O285">
         <v>4.05</v>
       </c>
       <c r="P285">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Q285">
         <v>1.85</v>
       </c>
       <c r="R285">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="S285">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T285">
         <v>3.86</v>
@@ -46803,7 +46803,7 @@
         <v>5.7</v>
       </c>
       <c r="AA285">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB285">
         <v>2.83</v>
@@ -46818,10 +46818,10 @@
         <v>1.26</v>
       </c>
       <c r="AF285">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG285">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -47914,71 +47914,71 @@
         <v>2.66</v>
       </c>
       <c r="Q292">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="R292">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S292">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T292">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U292">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="V292">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W292">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X292">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
+        <v>1.23</v>
+      </c>
+      <c r="Z292">
+        <v>3.42</v>
+      </c>
+      <c r="AA292">
+        <v>1.8</v>
+      </c>
+      <c r="AB292">
+        <v>1.72</v>
+      </c>
+      <c r="AC292">
+        <v>2.92</v>
+      </c>
+      <c r="AD292">
+        <v>1.31</v>
+      </c>
+      <c r="AE292">
+        <v>1.1</v>
+      </c>
+      <c r="AF292">
+        <v>1.73</v>
+      </c>
+      <c r="AG292">
+        <v>2.1</v>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ292">
         <v>1.3</v>
       </c>
-      <c r="Z292">
-        <v>2.97</v>
-      </c>
-      <c r="AA292">
-        <v>2.07</v>
-      </c>
-      <c r="AB292">
-        <v>1.69</v>
-      </c>
-      <c r="AC292">
-        <v>3.42</v>
-      </c>
-      <c r="AD292">
-        <v>1.23</v>
-      </c>
-      <c r="AE292">
-        <v>1.05</v>
-      </c>
-      <c r="AF292">
-        <v>1.77</v>
-      </c>
-      <c r="AG292">
-        <v>1.92</v>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ292">
-        <v>1.27</v>
-      </c>
       <c r="AK292">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48107,25 +48107,25 @@
         <v>7</v>
       </c>
       <c r="AA293">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB293">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AC293">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD293">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE293">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AF293">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG293">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48720,25 +48720,25 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="O297">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P297">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q297">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R297">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="S297">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T297">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U297">
         <v>3.1</v>
@@ -48750,50 +48750,50 @@
         <v>1.06</v>
       </c>
       <c r="X297">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y297">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z297">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA297">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB297">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC297">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="AD297">
+        <v>1.19</v>
+      </c>
+      <c r="AE297">
+        <v>1.02</v>
+      </c>
+      <c r="AF297">
+        <v>1.84</v>
+      </c>
+      <c r="AG297">
+        <v>1.75</v>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ297">
         <v>1.27</v>
       </c>
-      <c r="AE297">
-        <v>1.07</v>
-      </c>
-      <c r="AF297">
-        <v>1.88</v>
-      </c>
-      <c r="AG297">
-        <v>2</v>
-      </c>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI297" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ297">
-        <v>1.23</v>
-      </c>
       <c r="AK297">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>6.3</v>
       </c>
       <c r="AA299">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB299">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="AC299">
         <v>1.97</v>
@@ -49097,7 +49097,7 @@
         <v>1.85</v>
       </c>
       <c r="AE299">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF299">
         <v>1.47</v>
@@ -51038,10 +51038,10 @@
         <v>1.11</v>
       </c>
       <c r="Z311">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA311">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB311">
         <v>2.5</v>
@@ -51059,7 +51059,7 @@
         <v>1.57</v>
       </c>
       <c r="AG311">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51177,13 +51177,13 @@
         <v>1.83</v>
       </c>
       <c r="R312">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="S312">
         <v>1.25</v>
       </c>
       <c r="T312">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="U312">
         <v>2.25</v>
@@ -51198,31 +51198,31 @@
         <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z312">
-        <v>5.07</v>
+        <v>4.5</v>
       </c>
       <c r="AA312">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AB312">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AC312">
         <v>2.38</v>
       </c>
       <c r="AD312">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE312">
         <v>1.18</v>
       </c>
       <c r="AF312">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG312">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51328,22 +51328,22 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="O313">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P313">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q313">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="R313">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S313">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T313">
         <v>2.78</v>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AK313">
         <v>1.37</v>
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O314">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P314">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q314">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R314">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="S314">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T314">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="U314">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V314">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W314">
         <v>1.04</v>
       </c>
       <c r="X314">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y314">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z314">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA314">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB314">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC314">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AD314">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE314">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF314">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG314">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -52632,31 +52632,31 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O321">
         <v>6</v>
       </c>
       <c r="P321">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q321">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R321">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="S321">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T321">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="U321">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V321">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W321">
         <v>1.25</v>
@@ -52668,7 +52668,7 @@
         <v>1.05</v>
       </c>
       <c r="Z321">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA321">
         <v>1.26</v>
@@ -52677,19 +52677,19 @@
         <v>3.2</v>
       </c>
       <c r="AC321">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD321">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE321">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF321">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG321">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>1.08</v>
       </c>
       <c r="AK321">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O330">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P330">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q330">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="O64">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="Q64">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="S64">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="V64">
-        <v>2.21</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>9.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA64">
-        <v>1.17</v>
+        <v>1.72</v>
       </c>
       <c r="AB64">
-        <v>4.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC64">
-        <v>1.48</v>
+        <v>2.71</v>
       </c>
       <c r="AD64">
-        <v>2.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.74</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AG64">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="O65">
+        <v>4.75</v>
+      </c>
+      <c r="P65">
+        <v>4.45</v>
+      </c>
+      <c r="Q65">
+        <v>1.85</v>
+      </c>
+      <c r="R65">
+        <v>3</v>
+      </c>
+      <c r="S65">
+        <v>1.09</v>
+      </c>
+      <c r="T65">
+        <v>6.1</v>
+      </c>
+      <c r="U65">
+        <v>1.6</v>
+      </c>
+      <c r="V65">
+        <v>2.21</v>
+      </c>
+      <c r="W65">
+        <v>1.35</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>1.01</v>
+      </c>
+      <c r="Z65">
+        <v>9.9</v>
+      </c>
+      <c r="AA65">
+        <v>1.17</v>
+      </c>
+      <c r="AB65">
+        <v>4.45</v>
+      </c>
+      <c r="AC65">
+        <v>1.48</v>
+      </c>
+      <c r="AD65">
+        <v>2.51</v>
+      </c>
+      <c r="AE65">
+        <v>1.74</v>
+      </c>
+      <c r="AF65">
+        <v>1.24</v>
+      </c>
+      <c r="AG65">
         <v>3.3</v>
       </c>
-      <c r="P65">
-        <v>3.8</v>
-      </c>
-      <c r="Q65">
-        <v>2.17</v>
-      </c>
-      <c r="R65">
-        <v>2.38</v>
-      </c>
-      <c r="S65">
-        <v>1.3</v>
-      </c>
-      <c r="T65">
-        <v>3.3</v>
-      </c>
-      <c r="U65">
-        <v>2.45</v>
-      </c>
-      <c r="V65">
-        <v>1.44</v>
-      </c>
-      <c r="W65">
-        <v>1.11</v>
-      </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
-      <c r="Y65">
-        <v>1.18</v>
-      </c>
-      <c r="Z65">
-        <v>3.88</v>
-      </c>
-      <c r="AA65">
-        <v>1.72</v>
-      </c>
-      <c r="AB65">
-        <v>2.1</v>
-      </c>
-      <c r="AC65">
-        <v>2.71</v>
-      </c>
-      <c r="AD65">
-        <v>1.44</v>
-      </c>
-      <c r="AE65">
-        <v>1.12</v>
-      </c>
-      <c r="AF65">
-        <v>1.67</v>
-      </c>
-      <c r="AG65">
-        <v>2.1</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK65">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="R70">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U70">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V70">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z70">
-        <v>6.5</v>
+        <v>5.39</v>
       </c>
       <c r="AA70">
+        <v>1.43</v>
+      </c>
+      <c r="AB70">
+        <v>2.46</v>
+      </c>
+      <c r="AC70">
+        <v>2.2</v>
+      </c>
+      <c r="AD70">
+        <v>1.61</v>
+      </c>
+      <c r="AE70">
+        <v>1.26</v>
+      </c>
+      <c r="AF70">
         <v>1.4</v>
       </c>
-      <c r="AB70">
-        <v>3.1</v>
-      </c>
-      <c r="AC70">
-        <v>1.9</v>
-      </c>
-      <c r="AD70">
-        <v>1.79</v>
-      </c>
-      <c r="AE70">
-        <v>1.33</v>
-      </c>
-      <c r="AF70">
-        <v>1.44</v>
-      </c>
       <c r="AG70">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P71">
-        <v>1.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="R71">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="V71">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA71">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="AC71">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AD71">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF71">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="O72">
+        <v>3.55</v>
+      </c>
+      <c r="P72">
+        <v>1.98</v>
+      </c>
+      <c r="Q72">
+        <v>3.75</v>
+      </c>
+      <c r="R72">
+        <v>2.26</v>
+      </c>
+      <c r="S72">
+        <v>1.25</v>
+      </c>
+      <c r="T72">
         <v>3.5</v>
       </c>
-      <c r="P72">
-        <v>2.6</v>
-      </c>
-      <c r="Q72">
-        <v>2.68</v>
-      </c>
-      <c r="R72">
-        <v>2.32</v>
-      </c>
-      <c r="S72">
-        <v>1.22</v>
-      </c>
-      <c r="T72">
-        <v>3.8</v>
-      </c>
       <c r="U72">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="V72">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
+        <v>1.15</v>
+      </c>
+      <c r="Z72">
+        <v>4.25</v>
+      </c>
+      <c r="AA72">
+        <v>1.59</v>
+      </c>
+      <c r="AB72">
+        <v>2.17</v>
+      </c>
+      <c r="AC72">
+        <v>2.46</v>
+      </c>
+      <c r="AD72">
+        <v>1.43</v>
+      </c>
+      <c r="AE72">
         <v>1.14</v>
       </c>
-      <c r="Z72">
-        <v>5.39</v>
-      </c>
-      <c r="AA72">
-        <v>1.43</v>
-      </c>
-      <c r="AB72">
-        <v>2.46</v>
-      </c>
-      <c r="AC72">
-        <v>2.2</v>
-      </c>
-      <c r="AD72">
-        <v>1.61</v>
-      </c>
-      <c r="AE72">
-        <v>1.26</v>
-      </c>
       <c r="AF72">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG72">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="Q89">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="R89">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="T89">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="U89">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="V89">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W89">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z89">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA89">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AB89">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC89">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AD89">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE89">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,58 +14979,58 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P90">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q90">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U90">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W90">
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z90">
-        <v>3.46</v>
+        <v>3.87</v>
       </c>
       <c r="AA90">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB90">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC90">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="AD90">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
         <v>1.73</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK90">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,65 +15142,65 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="O91">
         <v>3.25</v>
       </c>
       <c r="P91">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U91">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="V91">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
         <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z91">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="AA91">
+        <v>1.91</v>
+      </c>
+      <c r="AB91">
+        <v>1.83</v>
+      </c>
+      <c r="AC91">
+        <v>3.5</v>
+      </c>
+      <c r="AD91">
+        <v>1.29</v>
+      </c>
+      <c r="AE91">
+        <v>1.08</v>
+      </c>
+      <c r="AF91">
+        <v>1.73</v>
+      </c>
+      <c r="AG91">
         <v>2.1</v>
       </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.28</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.07</v>
-      </c>
-      <c r="AF91">
-        <v>1.85</v>
-      </c>
-      <c r="AG91">
-        <v>1.85</v>
-      </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,61 +15305,61 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O92">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>3.5</v>
+        <v>1.97</v>
       </c>
       <c r="Q92">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="R92">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.87</v>
+        <v>4.2</v>
       </c>
       <c r="AA92">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB92">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC92">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AD92">
         <v>1.38</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG92">
         <v>2.1</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>4.8</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="P127">
-        <v>6.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q127">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="S127">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U127">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V127">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W127">
         <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z127">
-        <v>5.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA127">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AB127">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AC127">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AE127">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF127">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="AK127">
-        <v>2.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O128">
-        <v>4.66</v>
+        <v>3.84</v>
       </c>
       <c r="P128">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q128">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="R128">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T128">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U128">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V128">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W128">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
         <v>1.1</v>
       </c>
       <c r="Z128">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA128">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB128">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AD128">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE128">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF128">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG128">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AK128">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O129">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="P129">
-        <v>2.16</v>
+        <v>6.25</v>
       </c>
       <c r="Q129">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T129">
         <v>4</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA129">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB129">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AC129">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD129">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE129">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF129">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG129">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK129">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O150">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P150">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q150">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="R150">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S150">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T150">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="U150">
-        <v>2.39</v>
+        <v>2.82</v>
       </c>
       <c r="V150">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W150">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X150">
         <v>1.02</v>
       </c>
       <c r="Y150">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z150">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA150">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AB150">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AC150">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="AD150">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE150">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF150">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG150">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O151">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P151">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q151">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="R151">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T151">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="U151">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="V151">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W151">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X151">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z151">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA151">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB151">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC151">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AD151">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE151">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF151">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG151">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK151">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,37 +25085,37 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q152">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="R152">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="S152">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T152">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="U152">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="V152">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W152">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X152">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
         <v>1.22</v>
@@ -25124,25 +25124,25 @@
         <v>3.5</v>
       </c>
       <c r="AA152">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB152">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC152">
         <v>2.88</v>
       </c>
       <c r="AD152">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF152">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG152">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK152">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,28 +25248,28 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="O153">
         <v>3.5</v>
       </c>
       <c r="P153">
+        <v>2.5</v>
+      </c>
+      <c r="Q153">
         <v>3.1</v>
       </c>
-      <c r="Q153">
-        <v>2.74</v>
-      </c>
       <c r="R153">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="S153">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T153">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U153">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="V153">
         <v>1.48</v>
@@ -25278,34 +25278,34 @@
         <v>1.09</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y153">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z153">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA153">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB153">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC153">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD153">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE153">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF153">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG153">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK153">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O154">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P154">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="Q154">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="R154">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="S154">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
         <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V154">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W154">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
         <v>1.02</v>
       </c>
       <c r="Y154">
+        <v>1.18</v>
+      </c>
+      <c r="Z154">
+        <v>4.1</v>
+      </c>
+      <c r="AA154">
+        <v>1.67</v>
+      </c>
+      <c r="AB154">
+        <v>2.11</v>
+      </c>
+      <c r="AC154">
+        <v>2.73</v>
+      </c>
+      <c r="AD154">
+        <v>1.43</v>
+      </c>
+      <c r="AE154">
         <v>1.16</v>
       </c>
-      <c r="Z154">
-        <v>4.15</v>
-      </c>
-      <c r="AA154">
-        <v>1.66</v>
-      </c>
-      <c r="AB154">
-        <v>2.12</v>
-      </c>
-      <c r="AC154">
-        <v>2.72</v>
-      </c>
-      <c r="AD154">
-        <v>1.42</v>
-      </c>
-      <c r="AE154">
-        <v>1.14</v>
-      </c>
       <c r="AF154">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG154">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="O156">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
+        <v>3.25</v>
+      </c>
+      <c r="Q156">
+        <v>2.55</v>
+      </c>
+      <c r="R156">
+        <v>2.15</v>
+      </c>
+      <c r="S156">
+        <v>1.34</v>
+      </c>
+      <c r="T156">
+        <v>2.7</v>
+      </c>
+      <c r="U156">
+        <v>2.67</v>
+      </c>
+      <c r="V156">
+        <v>1.4</v>
+      </c>
+      <c r="W156">
+        <v>1.05</v>
+      </c>
+      <c r="X156">
+        <v>1.04</v>
+      </c>
+      <c r="Y156">
+        <v>1.29</v>
+      </c>
+      <c r="Z156">
         <v>3.5</v>
       </c>
-      <c r="Q156">
-        <v>2.29</v>
-      </c>
-      <c r="R156">
-        <v>2.04</v>
-      </c>
-      <c r="S156">
-        <v>1.4</v>
-      </c>
-      <c r="T156">
-        <v>2.66</v>
-      </c>
-      <c r="U156">
-        <v>2.7</v>
-      </c>
-      <c r="V156">
-        <v>1.39</v>
-      </c>
-      <c r="W156">
-        <v>1.06</v>
-      </c>
-      <c r="X156">
-        <v>1.03</v>
-      </c>
-      <c r="Y156">
-        <v>1.26</v>
-      </c>
-      <c r="Z156">
-        <v>3.4</v>
-      </c>
       <c r="AA156">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB156">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC156">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AD156">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE156">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
+        <v>1.71</v>
+      </c>
+      <c r="AG156">
+        <v>1.99</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>1.29</v>
+      </c>
+      <c r="AK156">
         <v>1.75</v>
-      </c>
-      <c r="AG156">
-        <v>1.95</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.26</v>
-      </c>
-      <c r="AK156">
-        <v>1.9</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O157">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="Q157">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R157">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="S157">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T157">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="U157">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="V157">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="W157">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X157">
         <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z157">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA157">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB157">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AC157">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="AD157">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE157">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG157">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="O158">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P158">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q158">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="R158">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S158">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T158">
+        <v>2.66</v>
+      </c>
+      <c r="U158">
         <v>2.7</v>
       </c>
-      <c r="U158">
-        <v>2.67</v>
-      </c>
       <c r="V158">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W158">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X158">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z158">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA158">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB158">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC158">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD158">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE158">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF158">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG158">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
+        <v>3.8</v>
+      </c>
+      <c r="O159">
+        <v>3.7</v>
+      </c>
+      <c r="P159">
+        <v>1.85</v>
+      </c>
+      <c r="Q159">
+        <v>4.2</v>
+      </c>
+      <c r="R159">
+        <v>2.27</v>
+      </c>
+      <c r="S159">
+        <v>1.29</v>
+      </c>
+      <c r="T159">
+        <v>3.3</v>
+      </c>
+      <c r="U159">
         <v>2.3</v>
       </c>
-      <c r="O159">
-        <v>3.3</v>
-      </c>
-      <c r="P159">
-        <v>2.98</v>
-      </c>
-      <c r="Q159">
-        <v>2.69</v>
-      </c>
-      <c r="R159">
-        <v>1.98</v>
-      </c>
-      <c r="S159">
-        <v>1.45</v>
-      </c>
-      <c r="T159">
-        <v>2.49</v>
-      </c>
-      <c r="U159">
-        <v>3</v>
-      </c>
       <c r="V159">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W159">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>2.78</v>
+        <v>4.15</v>
       </c>
       <c r="AA159">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AB159">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="AC159">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD159">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF159">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG159">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AK159">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,80 +28508,80 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O173">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="P173">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="Q173">
-        <v>3.41</v>
+        <v>3.31</v>
       </c>
       <c r="R173">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S173">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T173">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U173">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V173">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W173">
         <v>1.06</v>
       </c>
       <c r="X173">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z173">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA173">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AB173">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC173">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD173">
+        <v>1.31</v>
+      </c>
+      <c r="AE173">
+        <v>1.14</v>
+      </c>
+      <c r="AF173">
+        <v>1.57</v>
+      </c>
+      <c r="AG173">
+        <v>2.08</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ173">
         <v>1.3</v>
       </c>
-      <c r="AE173">
-        <v>1.1</v>
-      </c>
-      <c r="AF173">
-        <v>1.76</v>
-      </c>
-      <c r="AG173">
-        <v>1.93</v>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ173">
-        <v>1.28</v>
-      </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O174">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="P174">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q174">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="R174">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="S174">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="U174">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="V174">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z174">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA174">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB174">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AC174">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD174">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE174">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF174">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG174">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK174">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O175">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q175">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R175">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
+        <v>1.33</v>
+      </c>
+      <c r="T175">
+        <v>2.96</v>
+      </c>
+      <c r="U175">
+        <v>2.52</v>
+      </c>
+      <c r="V175">
+        <v>1.44</v>
+      </c>
+      <c r="W175">
+        <v>1.07</v>
+      </c>
+      <c r="X175">
+        <v>1.04</v>
+      </c>
+      <c r="Y175">
+        <v>1.23</v>
+      </c>
+      <c r="Z175">
+        <v>3.8</v>
+      </c>
+      <c r="AA175">
+        <v>1.8</v>
+      </c>
+      <c r="AB175">
+        <v>1.92</v>
+      </c>
+      <c r="AC175">
+        <v>3.25</v>
+      </c>
+      <c r="AD175">
+        <v>1.33</v>
+      </c>
+      <c r="AE175">
+        <v>1.14</v>
+      </c>
+      <c r="AF175">
+        <v>1.67</v>
+      </c>
+      <c r="AG175">
+        <v>2.15</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
         <v>1.29</v>
       </c>
-      <c r="T175">
-        <v>3.18</v>
-      </c>
-      <c r="U175">
-        <v>2.45</v>
-      </c>
-      <c r="V175">
-        <v>1.52</v>
-      </c>
-      <c r="W175">
-        <v>1.1</v>
-      </c>
-      <c r="X175">
-        <v>1.02</v>
-      </c>
-      <c r="Y175">
-        <v>1.2</v>
-      </c>
-      <c r="Z175">
-        <v>4.5</v>
-      </c>
-      <c r="AA175">
-        <v>1.6</v>
-      </c>
-      <c r="AB175">
-        <v>2.2</v>
-      </c>
-      <c r="AC175">
-        <v>2.39</v>
-      </c>
-      <c r="AD175">
-        <v>1.47</v>
-      </c>
-      <c r="AE175">
-        <v>1.17</v>
-      </c>
-      <c r="AF175">
-        <v>1.53</v>
-      </c>
-      <c r="AG175">
-        <v>2.45</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.27</v>
-      </c>
       <c r="AK175">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O176">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P176">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="Q176">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="R176">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S176">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T176">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U176">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="V176">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W176">
         <v>1.06</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z176">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA176">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB176">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC176">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD176">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE176">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF176">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG176">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK176">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="O177">
+        <v>3.43</v>
+      </c>
+      <c r="P177">
         <v>3.4</v>
       </c>
-      <c r="P177">
-        <v>2.35</v>
-      </c>
       <c r="Q177">
+        <v>2.7</v>
+      </c>
+      <c r="R177">
+        <v>2.08</v>
+      </c>
+      <c r="S177">
+        <v>1.38</v>
+      </c>
+      <c r="T177">
+        <v>2.74</v>
+      </c>
+      <c r="U177">
+        <v>2.82</v>
+      </c>
+      <c r="V177">
+        <v>1.36</v>
+      </c>
+      <c r="W177">
+        <v>1.04</v>
+      </c>
+      <c r="X177">
+        <v>1.01</v>
+      </c>
+      <c r="Y177">
+        <v>1.29</v>
+      </c>
+      <c r="Z177">
+        <v>3.5</v>
+      </c>
+      <c r="AA177">
+        <v>2.04</v>
+      </c>
+      <c r="AB177">
+        <v>1.87</v>
+      </c>
+      <c r="AC177">
         <v>3.4</v>
       </c>
-      <c r="R177">
-        <v>2.2</v>
-      </c>
-      <c r="S177">
-        <v>1.33</v>
-      </c>
-      <c r="T177">
-        <v>2.96</v>
-      </c>
-      <c r="U177">
-        <v>2.52</v>
-      </c>
-      <c r="V177">
-        <v>1.44</v>
-      </c>
-      <c r="W177">
-        <v>1.07</v>
-      </c>
-      <c r="X177">
-        <v>1.04</v>
-      </c>
-      <c r="Y177">
-        <v>1.23</v>
-      </c>
-      <c r="Z177">
-        <v>3.8</v>
-      </c>
-      <c r="AA177">
-        <v>1.8</v>
-      </c>
-      <c r="AB177">
-        <v>1.92</v>
-      </c>
-      <c r="AC177">
-        <v>3.25</v>
-      </c>
       <c r="AD177">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE177">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF177">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="O182">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="P182">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q182">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="R182">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="S182">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T182">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="U182">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V182">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="W182">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X182">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z182">
-        <v>4.85</v>
+        <v>6.35</v>
       </c>
       <c r="AA182">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AB182">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="AC182">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AD182">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AE182">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AF182">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG182">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK182">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="O183">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="P183">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q183">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="R183">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="S183">
+        <v>1.2</v>
+      </c>
+      <c r="T183">
+        <v>3.78</v>
+      </c>
+      <c r="U183">
+        <v>2.1</v>
+      </c>
+      <c r="V183">
+        <v>1.63</v>
+      </c>
+      <c r="W183">
         <v>1.16</v>
       </c>
-      <c r="T183">
-        <v>4.2</v>
-      </c>
-      <c r="U183">
-        <v>1.89</v>
-      </c>
-      <c r="V183">
-        <v>1.93</v>
-      </c>
-      <c r="W183">
+      <c r="X183">
+        <v>1.02</v>
+      </c>
+      <c r="Y183">
+        <v>1.11</v>
+      </c>
+      <c r="Z183">
+        <v>4.85</v>
+      </c>
+      <c r="AA183">
+        <v>1.45</v>
+      </c>
+      <c r="AB183">
+        <v>2.41</v>
+      </c>
+      <c r="AC183">
+        <v>2.3</v>
+      </c>
+      <c r="AD183">
+        <v>1.61</v>
+      </c>
+      <c r="AE183">
         <v>1.21</v>
       </c>
-      <c r="X183">
-        <v>1.01</v>
-      </c>
-      <c r="Y183">
-        <v>1.07</v>
-      </c>
-      <c r="Z183">
-        <v>6.35</v>
-      </c>
-      <c r="AA183">
-        <v>1.3</v>
-      </c>
-      <c r="AB183">
-        <v>3.25</v>
-      </c>
-      <c r="AC183">
-        <v>1.82</v>
-      </c>
-      <c r="AD183">
-        <v>2</v>
-      </c>
-      <c r="AE183">
-        <v>1.34</v>
-      </c>
       <c r="AF183">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG183">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK183">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O184">
+        <v>3.5</v>
+      </c>
+      <c r="P184">
+        <v>2.5</v>
+      </c>
+      <c r="Q184">
+        <v>3.2</v>
+      </c>
+      <c r="R184">
+        <v>2.19</v>
+      </c>
+      <c r="S184">
+        <v>1.29</v>
+      </c>
+      <c r="T184">
         <v>3.3</v>
       </c>
-      <c r="P184">
-        <v>3.5</v>
-      </c>
-      <c r="Q184">
-        <v>2.62</v>
-      </c>
-      <c r="R184">
-        <v>2.1</v>
-      </c>
-      <c r="S184">
-        <v>1.4</v>
-      </c>
-      <c r="T184">
+      <c r="U184">
+        <v>2.4</v>
+      </c>
+      <c r="V184">
+        <v>1.5</v>
+      </c>
+      <c r="W184">
+        <v>1.11</v>
+      </c>
+      <c r="X184">
+        <v>1.02</v>
+      </c>
+      <c r="Y184">
+        <v>1.2</v>
+      </c>
+      <c r="Z184">
+        <v>4.33</v>
+      </c>
+      <c r="AA184">
+        <v>1.69</v>
+      </c>
+      <c r="AB184">
+        <v>2.09</v>
+      </c>
+      <c r="AC184">
         <v>2.7</v>
       </c>
-      <c r="U184">
-        <v>3.2</v>
-      </c>
-      <c r="V184">
-        <v>1.3</v>
-      </c>
-      <c r="W184">
-        <v>1.05</v>
-      </c>
-      <c r="X184">
-        <v>1.06</v>
-      </c>
-      <c r="Y184">
-        <v>1.35</v>
-      </c>
-      <c r="Z184">
-        <v>2.74</v>
-      </c>
-      <c r="AA184">
-        <v>2.15</v>
-      </c>
-      <c r="AB184">
-        <v>1.67</v>
-      </c>
-      <c r="AC184">
-        <v>4.1</v>
-      </c>
       <c r="AD184">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE184">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF184">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AG184">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK184">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,80 +30464,80 @@
         </is>
       </c>
       <c r="N185">
+        <v>1.59</v>
+      </c>
+      <c r="O185">
+        <v>4.6</v>
+      </c>
+      <c r="P185">
+        <v>4.8</v>
+      </c>
+      <c r="Q185">
+        <v>1.91</v>
+      </c>
+      <c r="R185">
         <v>2.6</v>
       </c>
-      <c r="O185">
-        <v>3.5</v>
-      </c>
-      <c r="P185">
-        <v>2.5</v>
-      </c>
-      <c r="Q185">
-        <v>3.2</v>
-      </c>
-      <c r="R185">
-        <v>2.19</v>
-      </c>
       <c r="S185">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T185">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="U185">
+        <v>2</v>
+      </c>
+      <c r="V185">
+        <v>1.76</v>
+      </c>
+      <c r="W185">
+        <v>1.19</v>
+      </c>
+      <c r="X185">
+        <v>1.01</v>
+      </c>
+      <c r="Y185">
+        <v>1.07</v>
+      </c>
+      <c r="Z185">
+        <v>5.85</v>
+      </c>
+      <c r="AA185">
+        <v>1.37</v>
+      </c>
+      <c r="AB185">
+        <v>2.88</v>
+      </c>
+      <c r="AC185">
+        <v>2</v>
+      </c>
+      <c r="AD185">
+        <v>1.73</v>
+      </c>
+      <c r="AE185">
+        <v>1.32</v>
+      </c>
+      <c r="AF185">
+        <v>1.47</v>
+      </c>
+      <c r="AG185">
+        <v>2.63</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>1.13</v>
+      </c>
+      <c r="AK185">
         <v>2.4</v>
-      </c>
-      <c r="V185">
-        <v>1.5</v>
-      </c>
-      <c r="W185">
-        <v>1.11</v>
-      </c>
-      <c r="X185">
-        <v>1.02</v>
-      </c>
-      <c r="Y185">
-        <v>1.2</v>
-      </c>
-      <c r="Z185">
-        <v>4.33</v>
-      </c>
-      <c r="AA185">
-        <v>1.69</v>
-      </c>
-      <c r="AB185">
-        <v>2.09</v>
-      </c>
-      <c r="AC185">
-        <v>2.7</v>
-      </c>
-      <c r="AD185">
-        <v>1.44</v>
-      </c>
-      <c r="AE185">
-        <v>1.13</v>
-      </c>
-      <c r="AF185">
-        <v>1.55</v>
-      </c>
-      <c r="AG185">
-        <v>2.38</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ185">
-        <v>1.29</v>
-      </c>
-      <c r="AK185">
-        <v>1.44</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,80 +30627,80 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="O186">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="P186">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q186">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="R186">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="S186">
         <v>1.29</v>
       </c>
       <c r="T186">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U186">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="V186">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W186">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X186">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
+        <v>1.14</v>
+      </c>
+      <c r="Z186">
+        <v>5.5</v>
+      </c>
+      <c r="AA186">
+        <v>1.59</v>
+      </c>
+      <c r="AB186">
+        <v>2.45</v>
+      </c>
+      <c r="AC186">
+        <v>2.32</v>
+      </c>
+      <c r="AD186">
+        <v>1.57</v>
+      </c>
+      <c r="AE186">
+        <v>1.18</v>
+      </c>
+      <c r="AF186">
+        <v>1.57</v>
+      </c>
+      <c r="AG186">
+        <v>2.26</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ186">
         <v>1.2</v>
       </c>
-      <c r="Z186">
-        <v>4.5</v>
-      </c>
-      <c r="AA186">
-        <v>1.7</v>
-      </c>
-      <c r="AB186">
-        <v>2.1</v>
-      </c>
-      <c r="AC186">
-        <v>2.56</v>
-      </c>
-      <c r="AD186">
-        <v>1.44</v>
-      </c>
-      <c r="AE186">
-        <v>1.13</v>
-      </c>
-      <c r="AF186">
-        <v>1.6</v>
-      </c>
-      <c r="AG186">
-        <v>2.25</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ186">
-        <v>1.22</v>
-      </c>
       <c r="AK186">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
+        <v>1.33</v>
+      </c>
+      <c r="O187">
+        <v>5</v>
+      </c>
+      <c r="P187">
+        <v>6.06</v>
+      </c>
+      <c r="Q187">
+        <v>1.8</v>
+      </c>
+      <c r="R187">
+        <v>2.7</v>
+      </c>
+      <c r="S187">
+        <v>1.2</v>
+      </c>
+      <c r="T187">
+        <v>4.2</v>
+      </c>
+      <c r="U187">
+        <v>2</v>
+      </c>
+      <c r="V187">
         <v>1.71</v>
       </c>
-      <c r="O187">
-        <v>3.7</v>
-      </c>
-      <c r="P187">
-        <v>4.4</v>
-      </c>
-      <c r="Q187">
-        <v>2.16</v>
-      </c>
-      <c r="R187">
-        <v>2.11</v>
-      </c>
-      <c r="S187">
+      <c r="W187">
+        <v>1.18</v>
+      </c>
+      <c r="X187">
+        <v>1.01</v>
+      </c>
+      <c r="Y187">
+        <v>1.08</v>
+      </c>
+      <c r="Z187">
+        <v>5.45</v>
+      </c>
+      <c r="AA187">
+        <v>1.38</v>
+      </c>
+      <c r="AB187">
+        <v>3</v>
+      </c>
+      <c r="AC187">
+        <v>2.03</v>
+      </c>
+      <c r="AD187">
+        <v>1.8</v>
+      </c>
+      <c r="AE187">
         <v>1.3</v>
       </c>
-      <c r="T187">
-        <v>3.2</v>
-      </c>
-      <c r="U187">
-        <v>2.6</v>
-      </c>
-      <c r="V187">
-        <v>1.44</v>
-      </c>
-      <c r="W187">
-        <v>1.07</v>
-      </c>
-      <c r="X187">
-        <v>1.03</v>
-      </c>
-      <c r="Y187">
-        <v>1.23</v>
-      </c>
-      <c r="Z187">
-        <v>3.42</v>
-      </c>
-      <c r="AA187">
-        <v>1.87</v>
-      </c>
-      <c r="AB187">
-        <v>1.82</v>
-      </c>
-      <c r="AC187">
-        <v>2.96</v>
-      </c>
-      <c r="AD187">
-        <v>1.3</v>
-      </c>
-      <c r="AE187">
-        <v>1.1</v>
-      </c>
       <c r="AF187">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK187">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="O188">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P188">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q188">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="R188">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S188">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T188">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="U188">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V188">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="W188">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="X188">
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="Z188">
-        <v>5.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA188">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AB188">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC188">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AD188">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AE188">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="O189">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P189">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q189">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="R189">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S189">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T189">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U189">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V189">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W189">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X189">
         <v>1.02</v>
       </c>
       <c r="Y189">
+        <v>1.2</v>
+      </c>
+      <c r="Z189">
+        <v>4.5</v>
+      </c>
+      <c r="AA189">
+        <v>1.7</v>
+      </c>
+      <c r="AB189">
+        <v>2.1</v>
+      </c>
+      <c r="AC189">
+        <v>2.56</v>
+      </c>
+      <c r="AD189">
+        <v>1.44</v>
+      </c>
+      <c r="AE189">
+        <v>1.13</v>
+      </c>
+      <c r="AF189">
+        <v>1.6</v>
+      </c>
+      <c r="AG189">
+        <v>2.25</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
         <v>1.22</v>
       </c>
-      <c r="Z189">
-        <v>4.2</v>
-      </c>
-      <c r="AA189">
-        <v>1.8</v>
-      </c>
-      <c r="AB189">
-        <v>2.02</v>
-      </c>
-      <c r="AC189">
-        <v>2.73</v>
-      </c>
-      <c r="AD189">
-        <v>1.4</v>
-      </c>
-      <c r="AE189">
-        <v>1.11</v>
-      </c>
-      <c r="AF189">
-        <v>1.73</v>
-      </c>
-      <c r="AG189">
-        <v>1.98</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.14</v>
-      </c>
       <c r="AK189">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,80 +31279,80 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="O190">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P190">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Q190">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="R190">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S190">
+        <v>1.4</v>
+      </c>
+      <c r="T190">
+        <v>2.7</v>
+      </c>
+      <c r="U190">
+        <v>3.2</v>
+      </c>
+      <c r="V190">
+        <v>1.3</v>
+      </c>
+      <c r="W190">
+        <v>1.05</v>
+      </c>
+      <c r="X190">
+        <v>1.06</v>
+      </c>
+      <c r="Y190">
+        <v>1.35</v>
+      </c>
+      <c r="Z190">
+        <v>2.74</v>
+      </c>
+      <c r="AA190">
+        <v>2.15</v>
+      </c>
+      <c r="AB190">
+        <v>1.67</v>
+      </c>
+      <c r="AC190">
+        <v>4.1</v>
+      </c>
+      <c r="AD190">
+        <v>1.23</v>
+      </c>
+      <c r="AE190">
+        <v>1.03</v>
+      </c>
+      <c r="AF190">
+        <v>1.89</v>
+      </c>
+      <c r="AG190">
+        <v>1.81</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
         <v>1.25</v>
       </c>
-      <c r="T190">
-        <v>3.4</v>
-      </c>
-      <c r="U190">
-        <v>2.3</v>
-      </c>
-      <c r="V190">
-        <v>1.47</v>
-      </c>
-      <c r="W190">
-        <v>1.12</v>
-      </c>
-      <c r="X190">
-        <v>1.01</v>
-      </c>
-      <c r="Y190">
-        <v>1.2</v>
-      </c>
-      <c r="Z190">
-        <v>4.5</v>
-      </c>
-      <c r="AA190">
-        <v>1.7</v>
-      </c>
-      <c r="AB190">
-        <v>2.3</v>
-      </c>
-      <c r="AC190">
-        <v>2.63</v>
-      </c>
-      <c r="AD190">
-        <v>1.47</v>
-      </c>
-      <c r="AE190">
-        <v>1.11</v>
-      </c>
-      <c r="AF190">
-        <v>1.62</v>
-      </c>
-      <c r="AG190">
-        <v>2.2</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ190">
-        <v>1.22</v>
-      </c>
       <c r="AK190">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="O191">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P191">
-        <v>6.06</v>
+        <v>4.4</v>
       </c>
       <c r="Q191">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="R191">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="S191">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T191">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="U191">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="V191">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="W191">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z191">
-        <v>5.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA191">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AB191">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="AC191">
-        <v>2.03</v>
+        <v>2.96</v>
       </c>
       <c r="AD191">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AE191">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AF191">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG191">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK191">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O192">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P192">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q192">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R192">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="S192">
         <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V192">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W192">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z192">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA192">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB192">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC192">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AD192">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AE192">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF192">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG192">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK192">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P193">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="Q193">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="R193">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S193">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T193">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U193">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="V193">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W193">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X193">
         <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z193">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA193">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB193">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC193">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AD193">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE193">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF193">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG193">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK193">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,80 +35680,80 @@
         </is>
       </c>
       <c r="N217">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O217">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P217">
+        <v>2.42</v>
+      </c>
+      <c r="Q217">
+        <v>3.12</v>
+      </c>
+      <c r="R217">
+        <v>2.28</v>
+      </c>
+      <c r="S217">
+        <v>1.27</v>
+      </c>
+      <c r="T217">
+        <v>3.32</v>
+      </c>
+      <c r="U217">
+        <v>2.29</v>
+      </c>
+      <c r="V217">
+        <v>1.53</v>
+      </c>
+      <c r="W217">
+        <v>1.11</v>
+      </c>
+      <c r="X217">
+        <v>1.01</v>
+      </c>
+      <c r="Y217">
+        <v>1.2</v>
+      </c>
+      <c r="Z217">
+        <v>4.58</v>
+      </c>
+      <c r="AA217">
+        <v>1.65</v>
+      </c>
+      <c r="AB217">
+        <v>2.25</v>
+      </c>
+      <c r="AC217">
+        <v>2.55</v>
+      </c>
+      <c r="AD217">
+        <v>1.47</v>
+      </c>
+      <c r="AE217">
+        <v>1.18</v>
+      </c>
+      <c r="AF217">
+        <v>1.5</v>
+      </c>
+      <c r="AG217">
+        <v>2.4</v>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ217">
+        <v>1.25</v>
+      </c>
+      <c r="AK217">
         <v>1.44</v>
-      </c>
-      <c r="Q217">
-        <v>5.53</v>
-      </c>
-      <c r="R217">
-        <v>2.4</v>
-      </c>
-      <c r="S217">
-        <v>1.19</v>
-      </c>
-      <c r="T217">
-        <v>3.82</v>
-      </c>
-      <c r="U217">
-        <v>2.13</v>
-      </c>
-      <c r="V217">
-        <v>1.67</v>
-      </c>
-      <c r="W217">
-        <v>1.13</v>
-      </c>
-      <c r="X217">
-        <v>1.02</v>
-      </c>
-      <c r="Y217">
-        <v>1.09</v>
-      </c>
-      <c r="Z217">
-        <v>5.3</v>
-      </c>
-      <c r="AA217">
-        <v>1.42</v>
-      </c>
-      <c r="AB217">
-        <v>2.49</v>
-      </c>
-      <c r="AC217">
-        <v>2.19</v>
-      </c>
-      <c r="AD217">
-        <v>1.65</v>
-      </c>
-      <c r="AE217">
-        <v>1.21</v>
-      </c>
-      <c r="AF217">
-        <v>1.57</v>
-      </c>
-      <c r="AG217">
-        <v>2.22</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ217">
-        <v>2.5</v>
-      </c>
-      <c r="AK217">
-        <v>1.14</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,80 +35843,80 @@
         </is>
       </c>
       <c r="N218">
+        <v>5</v>
+      </c>
+      <c r="O218">
+        <v>4.6</v>
+      </c>
+      <c r="P218">
+        <v>1.44</v>
+      </c>
+      <c r="Q218">
+        <v>5.53</v>
+      </c>
+      <c r="R218">
+        <v>2.4</v>
+      </c>
+      <c r="S218">
+        <v>1.19</v>
+      </c>
+      <c r="T218">
+        <v>3.82</v>
+      </c>
+      <c r="U218">
+        <v>2.13</v>
+      </c>
+      <c r="V218">
+        <v>1.67</v>
+      </c>
+      <c r="W218">
+        <v>1.13</v>
+      </c>
+      <c r="X218">
+        <v>1.02</v>
+      </c>
+      <c r="Y218">
+        <v>1.09</v>
+      </c>
+      <c r="Z218">
+        <v>5.3</v>
+      </c>
+      <c r="AA218">
+        <v>1.42</v>
+      </c>
+      <c r="AB218">
+        <v>2.49</v>
+      </c>
+      <c r="AC218">
+        <v>2.19</v>
+      </c>
+      <c r="AD218">
+        <v>1.65</v>
+      </c>
+      <c r="AE218">
+        <v>1.21</v>
+      </c>
+      <c r="AF218">
+        <v>1.57</v>
+      </c>
+      <c r="AG218">
+        <v>2.22</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ218">
         <v>2.5</v>
       </c>
-      <c r="O218">
-        <v>3.4</v>
-      </c>
-      <c r="P218">
-        <v>2.42</v>
-      </c>
-      <c r="Q218">
-        <v>3.12</v>
-      </c>
-      <c r="R218">
-        <v>2.28</v>
-      </c>
-      <c r="S218">
-        <v>1.27</v>
-      </c>
-      <c r="T218">
-        <v>3.32</v>
-      </c>
-      <c r="U218">
-        <v>2.29</v>
-      </c>
-      <c r="V218">
-        <v>1.53</v>
-      </c>
-      <c r="W218">
-        <v>1.11</v>
-      </c>
-      <c r="X218">
-        <v>1.01</v>
-      </c>
-      <c r="Y218">
-        <v>1.2</v>
-      </c>
-      <c r="Z218">
-        <v>4.58</v>
-      </c>
-      <c r="AA218">
-        <v>1.65</v>
-      </c>
-      <c r="AB218">
-        <v>2.25</v>
-      </c>
-      <c r="AC218">
-        <v>2.55</v>
-      </c>
-      <c r="AD218">
-        <v>1.47</v>
-      </c>
-      <c r="AE218">
-        <v>1.18</v>
-      </c>
-      <c r="AF218">
-        <v>1.5</v>
-      </c>
-      <c r="AG218">
-        <v>2.4</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ218">
-        <v>1.25</v>
-      </c>
       <c r="AK218">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
+        <v>2.15</v>
+      </c>
+      <c r="O229">
         <v>3.2</v>
       </c>
-      <c r="O229">
-        <v>3</v>
-      </c>
       <c r="P229">
+        <v>2.95</v>
+      </c>
+      <c r="Q229">
+        <v>2.77</v>
+      </c>
+      <c r="R229">
+        <v>2.2</v>
+      </c>
+      <c r="S229">
+        <v>1.37</v>
+      </c>
+      <c r="T229">
+        <v>2.88</v>
+      </c>
+      <c r="U229">
+        <v>2.88</v>
+      </c>
+      <c r="V229">
+        <v>1.36</v>
+      </c>
+      <c r="W229">
+        <v>1.06</v>
+      </c>
+      <c r="X229">
+        <v>1.01</v>
+      </c>
+      <c r="Y229">
+        <v>1.23</v>
+      </c>
+      <c r="Z229">
+        <v>3.42</v>
+      </c>
+      <c r="AA229">
         <v>2.1</v>
       </c>
-      <c r="Q229">
-        <v>4.24</v>
-      </c>
-      <c r="R229">
-        <v>1.9</v>
-      </c>
-      <c r="S229">
-        <v>1.45</v>
-      </c>
-      <c r="T229">
-        <v>2.42</v>
-      </c>
-      <c r="U229">
-        <v>3.18</v>
-      </c>
-      <c r="V229">
-        <v>1.27</v>
-      </c>
-      <c r="W229">
-        <v>1.05</v>
-      </c>
-      <c r="X229">
-        <v>1.03</v>
-      </c>
-      <c r="Y229">
-        <v>1.35</v>
-      </c>
-      <c r="Z229">
-        <v>2.74</v>
-      </c>
-      <c r="AA229">
-        <v>2.18</v>
-      </c>
       <c r="AB229">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AC229">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AD229">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE229">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF229">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG229">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AK229">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O230">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P230">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q230">
-        <v>2.77</v>
+        <v>4.24</v>
       </c>
       <c r="R230">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S230">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T230">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="U230">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="V230">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W230">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X230">
+        <v>1.03</v>
+      </c>
+      <c r="Y230">
+        <v>1.35</v>
+      </c>
+      <c r="Z230">
+        <v>2.74</v>
+      </c>
+      <c r="AA230">
+        <v>2.18</v>
+      </c>
+      <c r="AB230">
+        <v>1.58</v>
+      </c>
+      <c r="AC230">
+        <v>4.05</v>
+      </c>
+      <c r="AD230">
+        <v>1.16</v>
+      </c>
+      <c r="AE230">
         <v>1.01</v>
       </c>
-      <c r="Y230">
-        <v>1.23</v>
-      </c>
-      <c r="Z230">
-        <v>3.42</v>
-      </c>
-      <c r="AA230">
-        <v>2.1</v>
-      </c>
-      <c r="AB230">
+      <c r="AF230">
         <v>1.88</v>
       </c>
-      <c r="AC230">
-        <v>3.05</v>
-      </c>
-      <c r="AD230">
-        <v>1.28</v>
-      </c>
-      <c r="AE230">
-        <v>1.06</v>
-      </c>
-      <c r="AF230">
-        <v>1.7</v>
-      </c>
       <c r="AG230">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AK230">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O277">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P277">
+        <v>3.85</v>
+      </c>
+      <c r="Q277">
+        <v>2.51</v>
+      </c>
+      <c r="R277">
+        <v>2.2</v>
+      </c>
+      <c r="S277">
+        <v>1.33</v>
+      </c>
+      <c r="T277">
+        <v>2.9</v>
+      </c>
+      <c r="U277">
+        <v>2.62</v>
+      </c>
+      <c r="V277">
+        <v>1.4</v>
+      </c>
+      <c r="W277">
+        <v>1.08</v>
+      </c>
+      <c r="X277">
+        <v>1.04</v>
+      </c>
+      <c r="Y277">
+        <v>1.25</v>
+      </c>
+      <c r="Z277">
+        <v>3.28</v>
+      </c>
+      <c r="AA277">
         <v>1.85</v>
       </c>
-      <c r="Q277">
-        <v>4.4</v>
-      </c>
-      <c r="R277">
-        <v>2.1</v>
-      </c>
-      <c r="S277">
-        <v>1.4</v>
-      </c>
-      <c r="T277">
-        <v>2.7</v>
-      </c>
-      <c r="U277">
-        <v>2.77</v>
-      </c>
-      <c r="V277">
-        <v>1.36</v>
-      </c>
-      <c r="W277">
-        <v>1.07</v>
-      </c>
-      <c r="X277">
-        <v>1.06</v>
-      </c>
-      <c r="Y277">
-        <v>1.34</v>
-      </c>
-      <c r="Z277">
-        <v>3.25</v>
-      </c>
-      <c r="AA277">
-        <v>2.1</v>
-      </c>
       <c r="AB277">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC277">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="AD277">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE277">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF277">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG277">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,80 +45623,80 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="O278">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P278">
-        <v>3.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q278">
-        <v>2.51</v>
+        <v>4.4</v>
       </c>
       <c r="R278">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S278">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T278">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U278">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V278">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W278">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X278">
+        <v>1.06</v>
+      </c>
+      <c r="Y278">
+        <v>1.34</v>
+      </c>
+      <c r="Z278">
+        <v>3.25</v>
+      </c>
+      <c r="AA278">
+        <v>2.1</v>
+      </c>
+      <c r="AB278">
+        <v>1.72</v>
+      </c>
+      <c r="AC278">
+        <v>3.58</v>
+      </c>
+      <c r="AD278">
+        <v>1.25</v>
+      </c>
+      <c r="AE278">
         <v>1.04</v>
       </c>
-      <c r="Y278">
+      <c r="AF278">
+        <v>1.83</v>
+      </c>
+      <c r="AG278">
+        <v>1.83</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
+        <v>1.22</v>
+      </c>
+      <c r="AK278">
         <v>1.25</v>
-      </c>
-      <c r="Z278">
-        <v>3.28</v>
-      </c>
-      <c r="AA278">
-        <v>1.85</v>
-      </c>
-      <c r="AB278">
-        <v>1.9</v>
-      </c>
-      <c r="AC278">
-        <v>3.04</v>
-      </c>
-      <c r="AD278">
-        <v>1.29</v>
-      </c>
-      <c r="AE278">
-        <v>1.08</v>
-      </c>
-      <c r="AF278">
-        <v>1.67</v>
-      </c>
-      <c r="AG278">
-        <v>2.05</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.24</v>
-      </c>
-      <c r="AK278">
-        <v>1.71</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
+        <v>2.58</v>
+      </c>
+      <c r="O312">
+        <v>3.15</v>
+      </c>
+      <c r="P312">
+        <v>2.37</v>
+      </c>
+      <c r="Q312">
+        <v>3.45</v>
+      </c>
+      <c r="R312">
+        <v>2.1</v>
+      </c>
+      <c r="S312">
+        <v>1.37</v>
+      </c>
+      <c r="T312">
+        <v>2.78</v>
+      </c>
+      <c r="U312">
+        <v>2.88</v>
+      </c>
+      <c r="V312">
         <v>1.35</v>
       </c>
-      <c r="O312">
-        <v>4.65</v>
-      </c>
-      <c r="P312">
-        <v>6</v>
-      </c>
-      <c r="Q312">
-        <v>1.83</v>
-      </c>
-      <c r="R312">
-        <v>2.72</v>
-      </c>
-      <c r="S312">
-        <v>1.25</v>
-      </c>
-      <c r="T312">
-        <v>3.32</v>
-      </c>
-      <c r="U312">
-        <v>2.25</v>
-      </c>
-      <c r="V312">
-        <v>1.57</v>
-      </c>
       <c r="W312">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X312">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z312">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA312">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AB312">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="AC312">
-        <v>2.38</v>
+        <v>3.34</v>
       </c>
       <c r="AD312">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AE312">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF312">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG312">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AK312">
-        <v>2.66</v>
+        <v>1.37</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.58</v>
+        <v>1.35</v>
       </c>
       <c r="O313">
-        <v>3.15</v>
+        <v>4.65</v>
       </c>
       <c r="P313">
-        <v>2.37</v>
+        <v>6</v>
       </c>
       <c r="Q313">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="R313">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="S313">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T313">
-        <v>2.78</v>
+        <v>3.32</v>
       </c>
       <c r="U313">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V313">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W313">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X313">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z313">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA313">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="AB313">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="AC313">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD313">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AE313">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF313">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG313">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="AK313">
-        <v>1.37</v>
+        <v>2.66</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O327">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P327">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q327">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="R327">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S327">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T327">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="U327">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V327">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W327">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X327">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y327">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z327">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AA327">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB327">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC327">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AD327">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE327">
         <v>1.01</v>
       </c>
       <c r="AF327">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG327">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK327">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O329">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P329">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q329">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="R329">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S329">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T329">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="U329">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V329">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W329">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X329">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y329">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z329">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AA329">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB329">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AC329">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AD329">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE329">
         <v>1.01</v>
       </c>
       <c r="AF329">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG329">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK329">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AL329">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="U15">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC16">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AK16">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P52">
+        <v>4.8</v>
+      </c>
+      <c r="Q52">
+        <v>2.05</v>
+      </c>
+      <c r="R52">
+        <v>2.21</v>
+      </c>
+      <c r="S52">
+        <v>1.35</v>
+      </c>
+      <c r="T52">
+        <v>2.87</v>
+      </c>
+      <c r="U52">
         <v>2.44</v>
       </c>
-      <c r="Q52">
-        <v>2.9</v>
-      </c>
-      <c r="R52">
-        <v>2.16</v>
-      </c>
-      <c r="S52">
-        <v>1.3</v>
-      </c>
-      <c r="T52">
-        <v>3.2</v>
-      </c>
-      <c r="U52">
-        <v>2.38</v>
-      </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA52">
+        <v>1.77</v>
+      </c>
+      <c r="AB52">
+        <v>1.97</v>
+      </c>
+      <c r="AC52">
+        <v>2.73</v>
+      </c>
+      <c r="AD52">
+        <v>1.32</v>
+      </c>
+      <c r="AE52">
+        <v>1.13</v>
+      </c>
+      <c r="AF52">
         <v>1.73</v>
       </c>
-      <c r="AB52">
-        <v>2.1</v>
-      </c>
-      <c r="AC52">
-        <v>2.88</v>
-      </c>
-      <c r="AD52">
-        <v>1.4</v>
-      </c>
-      <c r="AE52">
-        <v>1.14</v>
-      </c>
-      <c r="AF52">
-        <v>1.57</v>
-      </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>4.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q53">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.05</v>
+      </c>
+      <c r="O70">
+        <v>3.55</v>
+      </c>
+      <c r="P70">
+        <v>2.95</v>
+      </c>
+      <c r="Q70">
+        <v>2.47</v>
+      </c>
+      <c r="R70">
+        <v>2.42</v>
+      </c>
+      <c r="S70">
+        <v>1.2</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70">
+        <v>2.05</v>
+      </c>
+      <c r="V70">
+        <v>1.66</v>
+      </c>
+      <c r="W70">
+        <v>1.13</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.1</v>
+      </c>
+      <c r="Z70">
+        <v>5.8</v>
+      </c>
+      <c r="AA70">
+        <v>1.37</v>
+      </c>
+      <c r="AB70">
         <v>2.2</v>
       </c>
-      <c r="O70">
-        <v>3.5</v>
-      </c>
-      <c r="P70">
-        <v>2.6</v>
-      </c>
-      <c r="Q70">
-        <v>2.68</v>
-      </c>
-      <c r="R70">
-        <v>2.32</v>
-      </c>
-      <c r="S70">
-        <v>1.22</v>
-      </c>
-      <c r="T70">
-        <v>3.8</v>
-      </c>
-      <c r="U70">
-        <v>2.12</v>
-      </c>
-      <c r="V70">
-        <v>1.62</v>
-      </c>
-      <c r="W70">
-        <v>1.11</v>
-      </c>
-      <c r="X70">
-        <v>1.01</v>
-      </c>
-      <c r="Y70">
-        <v>1.14</v>
-      </c>
-      <c r="Z70">
-        <v>5.39</v>
-      </c>
-      <c r="AA70">
-        <v>1.43</v>
-      </c>
-      <c r="AB70">
-        <v>2.46</v>
-      </c>
       <c r="AC70">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD70">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF70">
         <v>1.4</v>
       </c>
       <c r="AG70">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="R71">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U71">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V71">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z71">
-        <v>6.5</v>
+        <v>5.39</v>
       </c>
       <c r="AA71">
+        <v>1.43</v>
+      </c>
+      <c r="AB71">
+        <v>2.46</v>
+      </c>
+      <c r="AC71">
+        <v>2.2</v>
+      </c>
+      <c r="AD71">
+        <v>1.61</v>
+      </c>
+      <c r="AE71">
+        <v>1.26</v>
+      </c>
+      <c r="AF71">
         <v>1.4</v>
       </c>
-      <c r="AB71">
-        <v>3.1</v>
-      </c>
-      <c r="AC71">
-        <v>1.9</v>
-      </c>
-      <c r="AD71">
-        <v>1.79</v>
-      </c>
-      <c r="AE71">
-        <v>1.33</v>
-      </c>
-      <c r="AF71">
-        <v>1.44</v>
-      </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK71">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="P72">
-        <v>1.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q72">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="R72">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="S72">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U72">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="V72">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA72">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="AC72">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AD72">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF72">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O73">
         <v>3.55</v>
       </c>
       <c r="P73">
-        <v>2.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q73">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="S73">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U73">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V73">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z73">
-        <v>5.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA73">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AB73">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC73">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AD73">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AE73">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.2</v>
       </c>
       <c r="AK73">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O101">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>5.36</v>
+        <v>2.61</v>
       </c>
       <c r="Q101">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="R101">
-        <v>2.79</v>
+        <v>2.08</v>
       </c>
       <c r="S101">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="V101">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AA101">
+        <v>1.83</v>
+      </c>
+      <c r="AB101">
+        <v>1.93</v>
+      </c>
+      <c r="AC101">
+        <v>3.2</v>
+      </c>
+      <c r="AD101">
+        <v>1.33</v>
+      </c>
+      <c r="AE101">
+        <v>1.08</v>
+      </c>
+      <c r="AF101">
+        <v>1.67</v>
+      </c>
+      <c r="AG101">
+        <v>2.15</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.33</v>
+      </c>
+      <c r="AK101">
         <v>1.44</v>
-      </c>
-      <c r="AB101">
-        <v>2.62</v>
-      </c>
-      <c r="AC101">
-        <v>2.05</v>
-      </c>
-      <c r="AD101">
-        <v>1.78</v>
-      </c>
-      <c r="AE101">
-        <v>1.3</v>
-      </c>
-      <c r="AF101">
-        <v>1.52</v>
-      </c>
-      <c r="AG101">
-        <v>2.45</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.12</v>
-      </c>
-      <c r="AK101">
-        <v>2.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
+        <v>1.48</v>
+      </c>
+      <c r="O102">
+        <v>4.75</v>
+      </c>
+      <c r="P102">
+        <v>5.36</v>
+      </c>
+      <c r="Q102">
+        <v>1.91</v>
+      </c>
+      <c r="R102">
+        <v>2.79</v>
+      </c>
+      <c r="S102">
+        <v>1.2</v>
+      </c>
+      <c r="T102">
+        <v>4</v>
+      </c>
+      <c r="U102">
+        <v>2</v>
+      </c>
+      <c r="V102">
+        <v>1.72</v>
+      </c>
+      <c r="W102">
+        <v>1.16</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.13</v>
+      </c>
+      <c r="Z102">
+        <v>6</v>
+      </c>
+      <c r="AA102">
+        <v>1.44</v>
+      </c>
+      <c r="AB102">
+        <v>2.62</v>
+      </c>
+      <c r="AC102">
+        <v>2.05</v>
+      </c>
+      <c r="AD102">
+        <v>1.78</v>
+      </c>
+      <c r="AE102">
+        <v>1.3</v>
+      </c>
+      <c r="AF102">
+        <v>1.52</v>
+      </c>
+      <c r="AG102">
+        <v>2.45</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.12</v>
+      </c>
+      <c r="AK102">
         <v>2.4</v>
-      </c>
-      <c r="O102">
-        <v>3.2</v>
-      </c>
-      <c r="P102">
-        <v>2.61</v>
-      </c>
-      <c r="Q102">
-        <v>2.99</v>
-      </c>
-      <c r="R102">
-        <v>2.08</v>
-      </c>
-      <c r="S102">
-        <v>1.33</v>
-      </c>
-      <c r="T102">
-        <v>2.88</v>
-      </c>
-      <c r="U102">
-        <v>2.56</v>
-      </c>
-      <c r="V102">
-        <v>1.41</v>
-      </c>
-      <c r="W102">
-        <v>1.07</v>
-      </c>
-      <c r="X102">
-        <v>1.04</v>
-      </c>
-      <c r="Y102">
-        <v>1.27</v>
-      </c>
-      <c r="Z102">
-        <v>3.6</v>
-      </c>
-      <c r="AA102">
-        <v>1.83</v>
-      </c>
-      <c r="AB102">
-        <v>1.93</v>
-      </c>
-      <c r="AC102">
-        <v>3.2</v>
-      </c>
-      <c r="AD102">
-        <v>1.33</v>
-      </c>
-      <c r="AE102">
-        <v>1.08</v>
-      </c>
-      <c r="AF102">
-        <v>1.67</v>
-      </c>
-      <c r="AG102">
-        <v>2.15</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.33</v>
-      </c>
-      <c r="AK102">
-        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="O127">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="P127">
-        <v>1.6</v>
+        <v>6.25</v>
       </c>
       <c r="Q127">
-        <v>4.7</v>
+        <v>1.75</v>
       </c>
       <c r="R127">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="S127">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T127">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U127">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V127">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W127">
         <v>1.2</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z127">
-        <v>7.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA127">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AB127">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AC127">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD127">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AE127">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF127">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG127">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>2.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK127">
-        <v>1.2</v>
+        <v>2.75</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O128">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="P128">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="Q128">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="R128">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="S128">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T128">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U128">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V128">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W128">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
         <v>1.1</v>
       </c>
       <c r="Z128">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA128">
+        <v>1.37</v>
+      </c>
+      <c r="AB128">
+        <v>3.15</v>
+      </c>
+      <c r="AC128">
+        <v>1.96</v>
+      </c>
+      <c r="AD128">
+        <v>1.9</v>
+      </c>
+      <c r="AE128">
+        <v>1.38</v>
+      </c>
+      <c r="AF128">
         <v>1.44</v>
       </c>
-      <c r="AB128">
-        <v>2.64</v>
-      </c>
-      <c r="AC128">
-        <v>2.13</v>
-      </c>
-      <c r="AD128">
-        <v>1.74</v>
-      </c>
-      <c r="AE128">
-        <v>1.27</v>
-      </c>
-      <c r="AF128">
-        <v>1.33</v>
-      </c>
       <c r="AG128">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AK128">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="O129">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="P129">
-        <v>6.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q129">
-        <v>1.75</v>
+        <v>3.32</v>
       </c>
       <c r="R129">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S129">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
         <v>4</v>
       </c>
       <c r="U129">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z129">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AC129">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AD129">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG129">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AK129">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="O134">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q134">
-        <v>2.24</v>
+        <v>3.64</v>
       </c>
       <c r="R134">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S134">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>4.2</v>
+        <v>3.27</v>
       </c>
       <c r="U134">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="V134">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
+        <v>1.22</v>
+      </c>
+      <c r="Z134">
+        <v>3.74</v>
+      </c>
+      <c r="AA134">
+        <v>1.8</v>
+      </c>
+      <c r="AB134">
+        <v>1.95</v>
+      </c>
+      <c r="AC134">
+        <v>2.84</v>
+      </c>
+      <c r="AD134">
+        <v>1.36</v>
+      </c>
+      <c r="AE134">
         <v>1.1</v>
       </c>
-      <c r="Z134">
-        <v>5.1</v>
-      </c>
-      <c r="AA134">
-        <v>1.5</v>
-      </c>
-      <c r="AB134">
-        <v>2.57</v>
-      </c>
-      <c r="AC134">
-        <v>2.25</v>
-      </c>
-      <c r="AD134">
-        <v>1.67</v>
-      </c>
-      <c r="AE134">
-        <v>1.26</v>
-      </c>
       <c r="AF134">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AG134">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK134">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P135">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q135">
-        <v>3.64</v>
+        <v>2.24</v>
       </c>
       <c r="R135">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="S135">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T135">
-        <v>3.27</v>
+        <v>4.2</v>
       </c>
       <c r="U135">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="V135">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z135">
-        <v>3.74</v>
+        <v>5.1</v>
       </c>
       <c r="AA135">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB135">
-        <v>1.95</v>
+        <v>2.57</v>
       </c>
       <c r="AC135">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD135">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AE135">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF135">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG135">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK135">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="O154">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P154">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="Q154">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="R154">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S154">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V154">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z154">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA154">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AB154">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AC154">
-        <v>2.73</v>
+        <v>2.31</v>
       </c>
       <c r="AD154">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE154">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF154">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG154">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK154">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="O155">
+        <v>3.7</v>
+      </c>
+      <c r="P155">
+        <v>1.85</v>
+      </c>
+      <c r="Q155">
         <v>4.2</v>
       </c>
-      <c r="P155">
+      <c r="R155">
+        <v>2.27</v>
+      </c>
+      <c r="S155">
+        <v>1.29</v>
+      </c>
+      <c r="T155">
+        <v>3.3</v>
+      </c>
+      <c r="U155">
+        <v>2.3</v>
+      </c>
+      <c r="V155">
+        <v>1.53</v>
+      </c>
+      <c r="W155">
+        <v>1.1</v>
+      </c>
+      <c r="X155">
+        <v>1.02</v>
+      </c>
+      <c r="Y155">
+        <v>1.16</v>
+      </c>
+      <c r="Z155">
+        <v>4.15</v>
+      </c>
+      <c r="AA155">
+        <v>1.66</v>
+      </c>
+      <c r="AB155">
+        <v>2.12</v>
+      </c>
+      <c r="AC155">
+        <v>2.72</v>
+      </c>
+      <c r="AD155">
+        <v>1.42</v>
+      </c>
+      <c r="AE155">
+        <v>1.14</v>
+      </c>
+      <c r="AF155">
         <v>1.65</v>
       </c>
-      <c r="Q155">
-        <v>3.9</v>
-      </c>
-      <c r="R155">
-        <v>2.28</v>
-      </c>
-      <c r="S155">
-        <v>1.23</v>
-      </c>
-      <c r="T155">
-        <v>3.5</v>
-      </c>
-      <c r="U155">
-        <v>2.21</v>
-      </c>
-      <c r="V155">
-        <v>1.57</v>
-      </c>
-      <c r="W155">
-        <v>1.13</v>
-      </c>
-      <c r="X155">
-        <v>1.01</v>
-      </c>
-      <c r="Y155">
-        <v>1.17</v>
-      </c>
-      <c r="Z155">
-        <v>4.6</v>
-      </c>
-      <c r="AA155">
-        <v>1.54</v>
-      </c>
-      <c r="AB155">
-        <v>2.3</v>
-      </c>
-      <c r="AC155">
-        <v>2.31</v>
-      </c>
-      <c r="AD155">
-        <v>1.54</v>
-      </c>
-      <c r="AE155">
-        <v>1.19</v>
-      </c>
-      <c r="AF155">
-        <v>1.56</v>
-      </c>
       <c r="AG155">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AK155">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="O156">
+        <v>3.6</v>
+      </c>
+      <c r="P156">
+        <v>3</v>
+      </c>
+      <c r="Q156">
+        <v>2.7</v>
+      </c>
+      <c r="R156">
+        <v>2.18</v>
+      </c>
+      <c r="S156">
+        <v>1.3</v>
+      </c>
+      <c r="T156">
         <v>3.3</v>
       </c>
-      <c r="P156">
-        <v>3.25</v>
-      </c>
-      <c r="Q156">
-        <v>2.55</v>
-      </c>
-      <c r="R156">
-        <v>2.15</v>
-      </c>
-      <c r="S156">
-        <v>1.34</v>
-      </c>
-      <c r="T156">
-        <v>2.7</v>
-      </c>
       <c r="U156">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="V156">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z156">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA156">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AB156">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AC156">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="AD156">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF156">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG156">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.29</v>
       </c>
       <c r="AK156">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.8</v>
+        <v>1.97</v>
       </c>
       <c r="O159">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P159">
+        <v>3.25</v>
+      </c>
+      <c r="Q159">
+        <v>2.55</v>
+      </c>
+      <c r="R159">
+        <v>2.15</v>
+      </c>
+      <c r="S159">
+        <v>1.34</v>
+      </c>
+      <c r="T159">
+        <v>2.7</v>
+      </c>
+      <c r="U159">
+        <v>2.67</v>
+      </c>
+      <c r="V159">
+        <v>1.4</v>
+      </c>
+      <c r="W159">
+        <v>1.05</v>
+      </c>
+      <c r="X159">
+        <v>1.04</v>
+      </c>
+      <c r="Y159">
+        <v>1.29</v>
+      </c>
+      <c r="Z159">
+        <v>3.5</v>
+      </c>
+      <c r="AA159">
+        <v>1.93</v>
+      </c>
+      <c r="AB159">
         <v>1.85</v>
       </c>
-      <c r="Q159">
-        <v>4.2</v>
-      </c>
-      <c r="R159">
-        <v>2.27</v>
-      </c>
-      <c r="S159">
+      <c r="AC159">
+        <v>3.05</v>
+      </c>
+      <c r="AD159">
+        <v>1.33</v>
+      </c>
+      <c r="AE159">
+        <v>1.11</v>
+      </c>
+      <c r="AF159">
+        <v>1.71</v>
+      </c>
+      <c r="AG159">
+        <v>1.99</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.29</v>
       </c>
-      <c r="T159">
-        <v>3.3</v>
-      </c>
-      <c r="U159">
-        <v>2.3</v>
-      </c>
-      <c r="V159">
-        <v>1.53</v>
-      </c>
-      <c r="W159">
-        <v>1.1</v>
-      </c>
-      <c r="X159">
-        <v>1.02</v>
-      </c>
-      <c r="Y159">
-        <v>1.16</v>
-      </c>
-      <c r="Z159">
-        <v>4.15</v>
-      </c>
-      <c r="AA159">
-        <v>1.66</v>
-      </c>
-      <c r="AB159">
-        <v>2.12</v>
-      </c>
-      <c r="AC159">
-        <v>2.72</v>
-      </c>
-      <c r="AD159">
-        <v>1.42</v>
-      </c>
-      <c r="AE159">
-        <v>1.14</v>
-      </c>
-      <c r="AF159">
-        <v>1.65</v>
-      </c>
-      <c r="AG159">
-        <v>2.2</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.88</v>
-      </c>
       <c r="AK159">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,80 +28671,80 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O174">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P174">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q174">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R174">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="S174">
+        <v>1.33</v>
+      </c>
+      <c r="T174">
+        <v>2.96</v>
+      </c>
+      <c r="U174">
+        <v>2.52</v>
+      </c>
+      <c r="V174">
+        <v>1.44</v>
+      </c>
+      <c r="W174">
+        <v>1.07</v>
+      </c>
+      <c r="X174">
+        <v>1.04</v>
+      </c>
+      <c r="Y174">
+        <v>1.23</v>
+      </c>
+      <c r="Z174">
+        <v>3.8</v>
+      </c>
+      <c r="AA174">
+        <v>1.8</v>
+      </c>
+      <c r="AB174">
+        <v>1.92</v>
+      </c>
+      <c r="AC174">
+        <v>3.25</v>
+      </c>
+      <c r="AD174">
+        <v>1.33</v>
+      </c>
+      <c r="AE174">
+        <v>1.14</v>
+      </c>
+      <c r="AF174">
+        <v>1.67</v>
+      </c>
+      <c r="AG174">
+        <v>2.15</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ174">
         <v>1.29</v>
       </c>
-      <c r="T174">
-        <v>3.18</v>
-      </c>
-      <c r="U174">
-        <v>2.45</v>
-      </c>
-      <c r="V174">
-        <v>1.52</v>
-      </c>
-      <c r="W174">
-        <v>1.1</v>
-      </c>
-      <c r="X174">
-        <v>1.02</v>
-      </c>
-      <c r="Y174">
-        <v>1.2</v>
-      </c>
-      <c r="Z174">
-        <v>4.5</v>
-      </c>
-      <c r="AA174">
-        <v>1.6</v>
-      </c>
-      <c r="AB174">
-        <v>2.2</v>
-      </c>
-      <c r="AC174">
-        <v>2.39</v>
-      </c>
-      <c r="AD174">
-        <v>1.47</v>
-      </c>
-      <c r="AE174">
-        <v>1.17</v>
-      </c>
-      <c r="AF174">
-        <v>1.53</v>
-      </c>
-      <c r="AG174">
-        <v>2.45</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ174">
-        <v>1.27</v>
-      </c>
       <c r="AK174">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="O175">
+        <v>3.43</v>
+      </c>
+      <c r="P175">
         <v>3.4</v>
       </c>
-      <c r="P175">
-        <v>2.35</v>
-      </c>
       <c r="Q175">
+        <v>2.7</v>
+      </c>
+      <c r="R175">
+        <v>2.08</v>
+      </c>
+      <c r="S175">
+        <v>1.38</v>
+      </c>
+      <c r="T175">
+        <v>2.74</v>
+      </c>
+      <c r="U175">
+        <v>2.82</v>
+      </c>
+      <c r="V175">
+        <v>1.36</v>
+      </c>
+      <c r="W175">
+        <v>1.04</v>
+      </c>
+      <c r="X175">
+        <v>1.01</v>
+      </c>
+      <c r="Y175">
+        <v>1.29</v>
+      </c>
+      <c r="Z175">
+        <v>3.5</v>
+      </c>
+      <c r="AA175">
+        <v>2.04</v>
+      </c>
+      <c r="AB175">
+        <v>1.87</v>
+      </c>
+      <c r="AC175">
         <v>3.4</v>
       </c>
-      <c r="R175">
-        <v>2.2</v>
-      </c>
-      <c r="S175">
-        <v>1.33</v>
-      </c>
-      <c r="T175">
-        <v>2.96</v>
-      </c>
-      <c r="U175">
-        <v>2.52</v>
-      </c>
-      <c r="V175">
-        <v>1.44</v>
-      </c>
-      <c r="W175">
-        <v>1.07</v>
-      </c>
-      <c r="X175">
-        <v>1.04</v>
-      </c>
-      <c r="Y175">
-        <v>1.23</v>
-      </c>
-      <c r="Z175">
-        <v>3.8</v>
-      </c>
-      <c r="AA175">
-        <v>1.8</v>
-      </c>
-      <c r="AB175">
-        <v>1.92</v>
-      </c>
-      <c r="AC175">
-        <v>3.25</v>
-      </c>
       <c r="AD175">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE175">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG175">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK175">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O177">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="P177">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q177">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="R177">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="S177">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T177">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="U177">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="V177">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z177">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA177">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AC177">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD177">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE177">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF177">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG177">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK177">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,80 +29812,80 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.67</v>
+        <v>1.48</v>
       </c>
       <c r="O181">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P181">
-        <v>2.37</v>
+        <v>6</v>
       </c>
       <c r="Q181">
-        <v>3.22</v>
+        <v>1.92</v>
       </c>
       <c r="R181">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="S181">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T181">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="U181">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V181">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W181">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X181">
         <v>1.02</v>
       </c>
       <c r="Y181">
+        <v>1.11</v>
+      </c>
+      <c r="Z181">
+        <v>4.85</v>
+      </c>
+      <c r="AA181">
+        <v>1.45</v>
+      </c>
+      <c r="AB181">
+        <v>2.41</v>
+      </c>
+      <c r="AC181">
+        <v>2.3</v>
+      </c>
+      <c r="AD181">
+        <v>1.61</v>
+      </c>
+      <c r="AE181">
+        <v>1.21</v>
+      </c>
+      <c r="AF181">
+        <v>1.65</v>
+      </c>
+      <c r="AG181">
+        <v>2.15</v>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ181">
         <v>1.14</v>
       </c>
-      <c r="Z181">
-        <v>4.35</v>
-      </c>
-      <c r="AA181">
-        <v>1.62</v>
-      </c>
-      <c r="AB181">
-        <v>2.2</v>
-      </c>
-      <c r="AC181">
-        <v>2.6</v>
-      </c>
-      <c r="AD181">
-        <v>1.44</v>
-      </c>
-      <c r="AE181">
-        <v>1.14</v>
-      </c>
-      <c r="AF181">
-        <v>1.5</v>
-      </c>
-      <c r="AG181">
-        <v>2.42</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ181">
-        <v>1.3</v>
-      </c>
       <c r="AK181">
-        <v>1.44</v>
+        <v>2.58</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.48</v>
+        <v>2.67</v>
       </c>
       <c r="O183">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P183">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="Q183">
-        <v>1.92</v>
+        <v>3.22</v>
       </c>
       <c r="R183">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="S183">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T183">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="U183">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V183">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W183">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X183">
         <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z183">
-        <v>4.85</v>
+        <v>4.35</v>
       </c>
       <c r="AA183">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AB183">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="AC183">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD183">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AE183">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG183">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK183">
-        <v>2.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="O185">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P185">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q185">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R185">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="S185">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="T185">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="U185">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="V185">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="W185">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X185">
         <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z185">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA185">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AB185">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AC185">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AD185">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE185">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AF185">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG185">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK185">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O186">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P186">
-        <v>4.33</v>
+        <v>6.06</v>
       </c>
       <c r="Q186">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="R186">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="S186">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T186">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U186">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V186">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="W186">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X186">
         <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z186">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA186">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB186">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AC186">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AD186">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE186">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF186">
         <v>1.57</v>
       </c>
       <c r="AG186">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK186">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,80 +30790,80 @@
         </is>
       </c>
       <c r="N187">
+        <v>2.8</v>
+      </c>
+      <c r="O187">
+        <v>3.5</v>
+      </c>
+      <c r="P187">
+        <v>2.36</v>
+      </c>
+      <c r="Q187">
+        <v>3.4</v>
+      </c>
+      <c r="R187">
+        <v>2.18</v>
+      </c>
+      <c r="S187">
+        <v>1.29</v>
+      </c>
+      <c r="T187">
+        <v>3.3</v>
+      </c>
+      <c r="U187">
+        <v>2.31</v>
+      </c>
+      <c r="V187">
+        <v>1.5</v>
+      </c>
+      <c r="W187">
+        <v>1.08</v>
+      </c>
+      <c r="X187">
+        <v>1.02</v>
+      </c>
+      <c r="Y187">
+        <v>1.19</v>
+      </c>
+      <c r="Z187">
+        <v>4.5</v>
+      </c>
+      <c r="AA187">
+        <v>1.65</v>
+      </c>
+      <c r="AB187">
+        <v>2.2</v>
+      </c>
+      <c r="AC187">
+        <v>2.5</v>
+      </c>
+      <c r="AD187">
+        <v>1.45</v>
+      </c>
+      <c r="AE187">
+        <v>1.19</v>
+      </c>
+      <c r="AF187">
+        <v>1.5</v>
+      </c>
+      <c r="AG187">
+        <v>2.38</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ187">
+        <v>1.27</v>
+      </c>
+      <c r="AK187">
         <v>1.33</v>
-      </c>
-      <c r="O187">
-        <v>5</v>
-      </c>
-      <c r="P187">
-        <v>6.06</v>
-      </c>
-      <c r="Q187">
-        <v>1.8</v>
-      </c>
-      <c r="R187">
-        <v>2.7</v>
-      </c>
-      <c r="S187">
-        <v>1.2</v>
-      </c>
-      <c r="T187">
-        <v>4.2</v>
-      </c>
-      <c r="U187">
-        <v>2</v>
-      </c>
-      <c r="V187">
-        <v>1.71</v>
-      </c>
-      <c r="W187">
-        <v>1.18</v>
-      </c>
-      <c r="X187">
-        <v>1.01</v>
-      </c>
-      <c r="Y187">
-        <v>1.08</v>
-      </c>
-      <c r="Z187">
-        <v>5.45</v>
-      </c>
-      <c r="AA187">
-        <v>1.38</v>
-      </c>
-      <c r="AB187">
-        <v>3</v>
-      </c>
-      <c r="AC187">
-        <v>2.03</v>
-      </c>
-      <c r="AD187">
-        <v>1.8</v>
-      </c>
-      <c r="AE187">
-        <v>1.3</v>
-      </c>
-      <c r="AF187">
-        <v>1.57</v>
-      </c>
-      <c r="AG187">
-        <v>2.3</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ187">
-        <v>1.17</v>
-      </c>
-      <c r="AK187">
-        <v>2.7</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="O188">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P188">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q188">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="R188">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="S188">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T188">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U188">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V188">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y188">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z188">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA188">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB188">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC188">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="AD188">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AE188">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF188">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG188">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O189">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P189">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q189">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="R189">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S189">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T189">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U189">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W189">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X189">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y189">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z189">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA189">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB189">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC189">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="AD189">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE189">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF189">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AG189">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK189">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
+        <v>2.05</v>
+      </c>
+      <c r="O190">
+        <v>3.54</v>
+      </c>
+      <c r="P190">
+        <v>3.3</v>
+      </c>
+      <c r="Q190">
+        <v>2.41</v>
+      </c>
+      <c r="R190">
+        <v>2.18</v>
+      </c>
+      <c r="S190">
+        <v>1.29</v>
+      </c>
+      <c r="T190">
+        <v>3.3</v>
+      </c>
+      <c r="U190">
+        <v>2.4</v>
+      </c>
+      <c r="V190">
+        <v>1.5</v>
+      </c>
+      <c r="W190">
+        <v>1.08</v>
+      </c>
+      <c r="X190">
+        <v>1.02</v>
+      </c>
+      <c r="Y190">
+        <v>1.2</v>
+      </c>
+      <c r="Z190">
+        <v>4.5</v>
+      </c>
+      <c r="AA190">
+        <v>1.7</v>
+      </c>
+      <c r="AB190">
         <v>2.1</v>
       </c>
-      <c r="O190">
-        <v>3.3</v>
-      </c>
-      <c r="P190">
-        <v>3.5</v>
-      </c>
-      <c r="Q190">
-        <v>2.62</v>
-      </c>
-      <c r="R190">
-        <v>2.1</v>
-      </c>
-      <c r="S190">
-        <v>1.4</v>
-      </c>
-      <c r="T190">
-        <v>2.7</v>
-      </c>
-      <c r="U190">
-        <v>3.2</v>
-      </c>
-      <c r="V190">
-        <v>1.3</v>
-      </c>
-      <c r="W190">
-        <v>1.05</v>
-      </c>
-      <c r="X190">
-        <v>1.06</v>
-      </c>
-      <c r="Y190">
-        <v>1.35</v>
-      </c>
-      <c r="Z190">
-        <v>2.74</v>
-      </c>
-      <c r="AA190">
-        <v>2.15</v>
-      </c>
-      <c r="AB190">
-        <v>1.67</v>
-      </c>
       <c r="AC190">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD190">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE190">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AG190">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK190">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O191">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P191">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q191">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="R191">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="S191">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T191">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U191">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="V191">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W191">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X191">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z191">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AA191">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB191">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC191">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="AD191">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE191">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF191">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG191">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>1.22</v>
       </c>
       <c r="AK191">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="O192">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P192">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="Q192">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="R192">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T192">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="U192">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="V192">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W192">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X192">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z192">
-        <v>4.5</v>
+        <v>5.85</v>
       </c>
       <c r="AA192">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AB192">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AC192">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD192">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AE192">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AF192">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG192">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK192">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,31 +40081,31 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="O244">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P244">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="Q244">
-        <v>2.69</v>
+        <v>2.02</v>
       </c>
       <c r="R244">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="S244">
         <v>1.14</v>
       </c>
       <c r="T244">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U244">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V244">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W244">
         <v>1.2</v>
@@ -40114,31 +40114,31 @@
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z244">
-        <v>6.15</v>
+        <v>6.9</v>
       </c>
       <c r="AA244">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB244">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC244">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD244">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE244">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF244">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AG244">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.2</v>
       </c>
       <c r="AK244">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,31 +40244,31 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="O245">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P245">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="Q245">
-        <v>2.02</v>
+        <v>2.69</v>
       </c>
       <c r="R245">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="S245">
         <v>1.14</v>
       </c>
       <c r="T245">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U245">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V245">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="W245">
         <v>1.2</v>
@@ -40277,31 +40277,31 @@
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z245">
-        <v>6.9</v>
+        <v>6.15</v>
       </c>
       <c r="AA245">
+        <v>1.36</v>
+      </c>
+      <c r="AB245">
+        <v>2.87</v>
+      </c>
+      <c r="AC245">
+        <v>1.92</v>
+      </c>
+      <c r="AD245">
+        <v>1.82</v>
+      </c>
+      <c r="AE245">
+        <v>1.31</v>
+      </c>
+      <c r="AF245">
         <v>1.33</v>
       </c>
-      <c r="AB245">
+      <c r="AG245">
         <v>3.1</v>
-      </c>
-      <c r="AC245">
-        <v>1.84</v>
-      </c>
-      <c r="AD245">
-        <v>1.84</v>
-      </c>
-      <c r="AE245">
-        <v>1.33</v>
-      </c>
-      <c r="AF245">
-        <v>1.38</v>
-      </c>
-      <c r="AG245">
-        <v>2.76</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>1.2</v>
       </c>
       <c r="AK245">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,80 +45460,80 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="O277">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>3.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q277">
-        <v>2.51</v>
+        <v>4.4</v>
       </c>
       <c r="R277">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T277">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U277">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V277">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W277">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X277">
+        <v>1.06</v>
+      </c>
+      <c r="Y277">
+        <v>1.34</v>
+      </c>
+      <c r="Z277">
+        <v>3.25</v>
+      </c>
+      <c r="AA277">
+        <v>2.1</v>
+      </c>
+      <c r="AB277">
+        <v>1.72</v>
+      </c>
+      <c r="AC277">
+        <v>3.58</v>
+      </c>
+      <c r="AD277">
+        <v>1.25</v>
+      </c>
+      <c r="AE277">
         <v>1.04</v>
       </c>
-      <c r="Y277">
+      <c r="AF277">
+        <v>1.83</v>
+      </c>
+      <c r="AG277">
+        <v>1.83</v>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ277">
+        <v>1.22</v>
+      </c>
+      <c r="AK277">
         <v>1.25</v>
-      </c>
-      <c r="Z277">
-        <v>3.28</v>
-      </c>
-      <c r="AA277">
-        <v>1.85</v>
-      </c>
-      <c r="AB277">
-        <v>1.9</v>
-      </c>
-      <c r="AC277">
-        <v>3.04</v>
-      </c>
-      <c r="AD277">
-        <v>1.29</v>
-      </c>
-      <c r="AE277">
-        <v>1.08</v>
-      </c>
-      <c r="AF277">
-        <v>1.67</v>
-      </c>
-      <c r="AG277">
-        <v>2.05</v>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ277">
-        <v>1.24</v>
-      </c>
-      <c r="AK277">
-        <v>1.71</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O278">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P278">
+        <v>3.85</v>
+      </c>
+      <c r="Q278">
+        <v>2.51</v>
+      </c>
+      <c r="R278">
+        <v>2.2</v>
+      </c>
+      <c r="S278">
+        <v>1.33</v>
+      </c>
+      <c r="T278">
+        <v>2.9</v>
+      </c>
+      <c r="U278">
+        <v>2.62</v>
+      </c>
+      <c r="V278">
+        <v>1.4</v>
+      </c>
+      <c r="W278">
+        <v>1.08</v>
+      </c>
+      <c r="X278">
+        <v>1.04</v>
+      </c>
+      <c r="Y278">
+        <v>1.25</v>
+      </c>
+      <c r="Z278">
+        <v>3.28</v>
+      </c>
+      <c r="AA278">
         <v>1.85</v>
       </c>
-      <c r="Q278">
-        <v>4.4</v>
-      </c>
-      <c r="R278">
-        <v>2.1</v>
-      </c>
-      <c r="S278">
-        <v>1.4</v>
-      </c>
-      <c r="T278">
-        <v>2.7</v>
-      </c>
-      <c r="U278">
-        <v>2.77</v>
-      </c>
-      <c r="V278">
-        <v>1.36</v>
-      </c>
-      <c r="W278">
-        <v>1.07</v>
-      </c>
-      <c r="X278">
-        <v>1.06</v>
-      </c>
-      <c r="Y278">
-        <v>1.34</v>
-      </c>
-      <c r="Z278">
-        <v>3.25</v>
-      </c>
-      <c r="AA278">
-        <v>2.1</v>
-      </c>
       <c r="AB278">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC278">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="AD278">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE278">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF278">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG278">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK278">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
+        <v>1.82</v>
+      </c>
+      <c r="O327">
+        <v>3.4</v>
+      </c>
+      <c r="P327">
+        <v>4.2</v>
+      </c>
+      <c r="Q327">
+        <v>2.46</v>
+      </c>
+      <c r="R327">
         <v>2.06</v>
       </c>
-      <c r="O327">
-        <v>3.1</v>
-      </c>
-      <c r="P327">
-        <v>3.6</v>
-      </c>
-      <c r="Q327">
-        <v>2.35</v>
-      </c>
-      <c r="R327">
-        <v>2</v>
-      </c>
       <c r="S327">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T327">
-        <v>2.51</v>
+        <v>2.68</v>
       </c>
       <c r="U327">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="V327">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W327">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X327">
         <v>1.01</v>
       </c>
       <c r="Y327">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z327">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="AA327">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB327">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC327">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AD327">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE327">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF327">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AG327">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>1.22</v>
       </c>
       <c r="AK327">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="O328">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P328">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q328">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="R328">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="S328">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T328">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="U328">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="V328">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W328">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X328">
+        <v>1.03</v>
+      </c>
+      <c r="Y328">
+        <v>1.4</v>
+      </c>
+      <c r="Z328">
+        <v>2.56</v>
+      </c>
+      <c r="AA328">
+        <v>2.33</v>
+      </c>
+      <c r="AB328">
+        <v>1.51</v>
+      </c>
+      <c r="AC328">
+        <v>4.55</v>
+      </c>
+      <c r="AD328">
+        <v>1.13</v>
+      </c>
+      <c r="AE328">
         <v>1.01</v>
       </c>
-      <c r="Y328">
-        <v>1.28</v>
-      </c>
-      <c r="Z328">
-        <v>3.08</v>
-      </c>
-      <c r="AA328">
-        <v>1.95</v>
-      </c>
-      <c r="AB328">
-        <v>1.73</v>
-      </c>
-      <c r="AC328">
-        <v>3.42</v>
-      </c>
-      <c r="AD328">
-        <v>1.23</v>
-      </c>
-      <c r="AE328">
-        <v>1.05</v>
-      </c>
       <c r="AF328">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AG328">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK328">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O329">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P329">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q329">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="R329">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S329">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T329">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="U329">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V329">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W329">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X329">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y329">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z329">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AA329">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB329">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC329">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AD329">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE329">
         <v>1.01</v>
       </c>
       <c r="AF329">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG329">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK329">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -57359,7 +57359,7 @@
         </is>
       </c>
       <c r="N350">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="O350">
         <v>3.8</v>
@@ -57368,7 +57368,7 @@
         <v>5.25</v>
       </c>
       <c r="Q350">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R350">
         <v>2.2</v>
@@ -57432,7 +57432,7 @@
         <v>1.15</v>
       </c>
       <c r="AK350">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL350">
         <v>0</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="O5">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
+        <v>2.11</v>
+      </c>
+      <c r="R5">
         <v>2.4</v>
       </c>
-      <c r="R5">
-        <v>2.1</v>
-      </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>3.38</v>
       </c>
       <c r="P6">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AK15">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="U16">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O18">
+        <v>3.2</v>
+      </c>
+      <c r="P18">
         <v>3.1</v>
       </c>
-      <c r="P18">
-        <v>3.14</v>
-      </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AD19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
         <v>1.11</v>
@@ -4393,25 +4393,25 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.05</v>
@@ -4420,28 +4420,28 @@
         <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA25">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE25">
         <v>1.07</v>
       </c>
       <c r="AF25">
+        <v>1.8</v>
+      </c>
+      <c r="AG25">
         <v>1.84</v>
-      </c>
-      <c r="AG25">
-        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>2.18</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
         <v>3.18</v>
@@ -4731,7 +4731,7 @@
         <v>2.7</v>
       </c>
       <c r="U27">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="V27">
         <v>1.35</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.7</v>
+        <v>4.38</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -5534,7 +5534,7 @@
         <v>3.12</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
         <v>2.25</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>1.45</v>
+      </c>
+      <c r="O35">
+        <v>3.95</v>
+      </c>
+      <c r="P35">
+        <v>5.5</v>
+      </c>
+      <c r="Q35">
+        <v>1.73</v>
+      </c>
+      <c r="R35">
+        <v>2.25</v>
+      </c>
+      <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>3.3</v>
+      </c>
+      <c r="U35">
+        <v>1.98</v>
+      </c>
+      <c r="V35">
+        <v>1.44</v>
+      </c>
+      <c r="W35">
+        <v>1.12</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.15</v>
+      </c>
+      <c r="Z35">
+        <v>4.2</v>
+      </c>
+      <c r="AA35">
         <v>1.47</v>
       </c>
-      <c r="O35">
-        <v>4.3</v>
-      </c>
-      <c r="P35">
-        <v>6.15</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="O50">
-        <v>6.52</v>
+        <v>6.4</v>
       </c>
       <c r="P50">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P69">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -11580,10 +11580,10 @@
         <v>2.38</v>
       </c>
       <c r="V69">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11595,10 +11595,10 @@
         <v>4.5</v>
       </c>
       <c r="AA69">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB69">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC69">
         <v>2.41</v>
@@ -11607,7 +11607,7 @@
         <v>1.48</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
         <v>1.55</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11746,7 +11746,7 @@
         <v>1.66</v>
       </c>
       <c r="W70">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.02</v>
@@ -11761,7 +11761,7 @@
         <v>1.37</v>
       </c>
       <c r="AB70">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
         <v>2.1</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>5.05</v>
       </c>
       <c r="P71">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q71">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="R71">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="V71">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>5.39</v>
+        <v>6.5</v>
       </c>
       <c r="AA71">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AC71">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD71">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF71">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O72">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q72">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="R72">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U72">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V72">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
-        <v>6.5</v>
+        <v>5.39</v>
       </c>
       <c r="AA72">
+        <v>1.43</v>
+      </c>
+      <c r="AB72">
+        <v>2.46</v>
+      </c>
+      <c r="AC72">
+        <v>2.2</v>
+      </c>
+      <c r="AD72">
+        <v>1.61</v>
+      </c>
+      <c r="AE72">
+        <v>1.26</v>
+      </c>
+      <c r="AF72">
         <v>1.4</v>
       </c>
-      <c r="AB72">
-        <v>3.1</v>
-      </c>
-      <c r="AC72">
-        <v>1.9</v>
-      </c>
-      <c r="AD72">
-        <v>1.79</v>
-      </c>
-      <c r="AE72">
-        <v>1.33</v>
-      </c>
-      <c r="AF72">
-        <v>1.44</v>
-      </c>
       <c r="AG72">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O73">
         <v>3.55</v>
@@ -12730,10 +12730,10 @@
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z76">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AA76">
         <v>2.21</v>
@@ -12742,7 +12742,7 @@
         <v>1.61</v>
       </c>
       <c r="AC76">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="AD76">
         <v>1.17</v>
@@ -13032,55 +13032,55 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O80">
         <v>3.2</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q81">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S81">
         <v>1.28</v>
@@ -13548,13 +13548,13 @@
         <v>1.18</v>
       </c>
       <c r="Z81">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB81">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AC81">
         <v>2.49</v>
@@ -13563,13 +13563,13 @@
         <v>1.42</v>
       </c>
       <c r="AE81">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>1.85</v>
       </c>
       <c r="AB82">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC82">
         <v>3.04</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O83">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P83">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="Q83">
         <v>2.81</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P84">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q84">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S84">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U84">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="V84">
         <v>1.44</v>
       </c>
       <c r="W84">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z84">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA84">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB84">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC84">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD84">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE84">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF84">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK84">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q85">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R85">
         <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T85">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U85">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="V85">
         <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
         <v>1.03</v>
@@ -14200,28 +14200,28 @@
         <v>1.3</v>
       </c>
       <c r="Z85">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA85">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AB85">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC85">
         <v>3.6</v>
       </c>
       <c r="AD85">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE85">
         <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>3.5</v>
       </c>
       <c r="Q89">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R89">
         <v>2.05</v>
@@ -14837,7 +14837,7 @@
         <v>2.45</v>
       </c>
       <c r="U89">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V89">
         <v>1.37</v>
@@ -14849,16 +14849,16 @@
         <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z89">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA89">
         <v>2.1</v>
       </c>
       <c r="AB89">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC89">
         <v>3.28</v>
@@ -15009,13 +15009,13 @@
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
         <v>1.19</v>
       </c>
       <c r="Z90">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="AA90">
         <v>1.85</v>
@@ -15024,7 +15024,7 @@
         <v>1.98</v>
       </c>
       <c r="AC90">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AD90">
         <v>1.38</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O91">
         <v>3.25</v>
@@ -15160,7 +15160,7 @@
         <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U91">
         <v>2.73</v>
@@ -15175,10 +15175,10 @@
         <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z91">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AA91">
         <v>1.91</v>
@@ -15326,7 +15326,7 @@
         <v>3.14</v>
       </c>
       <c r="U92">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
         <v>1.45</v>
@@ -15350,7 +15350,7 @@
         <v>2.05</v>
       </c>
       <c r="AC92">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD92">
         <v>1.38</v>
@@ -15362,7 +15362,7 @@
         <v>1.58</v>
       </c>
       <c r="AG92">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -18420,7 +18420,7 @@
         <v>1.42</v>
       </c>
       <c r="T111">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U111">
         <v>2.75</v>
@@ -18438,7 +18438,7 @@
         <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AA111">
         <v>2</v>
@@ -18453,13 +18453,13 @@
         <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG111">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB112">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -20684,16 +20684,16 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O125">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="Q125">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R125">
         <v>2.2</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
         <v>1.91</v>
@@ -20868,7 +20868,7 @@
         <v>3.8</v>
       </c>
       <c r="U126">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V126">
         <v>1.62</v>
@@ -20898,7 +20898,7 @@
         <v>1.58</v>
       </c>
       <c r="AE126">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF126">
         <v>1.46</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>2.87</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="P127">
-        <v>6.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q127">
-        <v>1.75</v>
+        <v>3.32</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S127">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U127">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V127">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W127">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z127">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA127">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB127">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AC127">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE127">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF127">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AK127">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O128">
         <v>4.66</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O129">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="P129">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="Q129">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="R129">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T129">
         <v>4</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA129">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB129">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AC129">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD129">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE129">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF129">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG129">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AK129">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21547,7 +21547,7 @@
         <v>1.39</v>
       </c>
       <c r="AD130">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AE130">
         <v>1.89</v>
@@ -21686,7 +21686,7 @@
         <v>2.34</v>
       </c>
       <c r="V131">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
         <v>1.11</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O139">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P139">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="Q139">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="R139">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S139">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T139">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U139">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="V139">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W139">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y139">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z139">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AA139">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AB139">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC139">
-        <v>2.06</v>
+        <v>2.61</v>
       </c>
       <c r="AD139">
+        <v>1.42</v>
+      </c>
+      <c r="AE139">
+        <v>1.13</v>
+      </c>
+      <c r="AF139">
         <v>1.4</v>
       </c>
-      <c r="AE139">
-        <v>1.15</v>
-      </c>
-      <c r="AF139">
-        <v>1.36</v>
-      </c>
       <c r="AG139">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,65 +23129,65 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="O140">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="Q140">
+        <v>2.77</v>
+      </c>
+      <c r="R140">
+        <v>2.24</v>
+      </c>
+      <c r="S140">
+        <v>1.26</v>
+      </c>
+      <c r="T140">
         <v>3.5</v>
       </c>
-      <c r="R140">
+      <c r="U140">
+        <v>1.98</v>
+      </c>
+      <c r="V140">
+        <v>1.44</v>
+      </c>
+      <c r="W140">
+        <v>1.12</v>
+      </c>
+      <c r="X140">
+        <v>1.01</v>
+      </c>
+      <c r="Y140">
+        <v>1.14</v>
+      </c>
+      <c r="Z140">
+        <v>3.2</v>
+      </c>
+      <c r="AA140">
+        <v>1.6</v>
+      </c>
+      <c r="AB140">
+        <v>2.2</v>
+      </c>
+      <c r="AC140">
+        <v>2.06</v>
+      </c>
+      <c r="AD140">
+        <v>1.4</v>
+      </c>
+      <c r="AE140">
+        <v>1.15</v>
+      </c>
+      <c r="AF140">
+        <v>1.36</v>
+      </c>
+      <c r="AG140">
         <v>2.1</v>
       </c>
-      <c r="S140">
-        <v>1.27</v>
-      </c>
-      <c r="T140">
-        <v>2.63</v>
-      </c>
-      <c r="U140">
-        <v>2.34</v>
-      </c>
-      <c r="V140">
-        <v>1.48</v>
-      </c>
-      <c r="W140">
-        <v>1.11</v>
-      </c>
-      <c r="X140">
-        <v>1.02</v>
-      </c>
-      <c r="Y140">
-        <v>1.13</v>
-      </c>
-      <c r="Z140">
-        <v>3.13</v>
-      </c>
-      <c r="AA140">
-        <v>1.49</v>
-      </c>
-      <c r="AB140">
-        <v>1.89</v>
-      </c>
-      <c r="AC140">
-        <v>2.61</v>
-      </c>
-      <c r="AD140">
-        <v>1.42</v>
-      </c>
-      <c r="AE140">
-        <v>1.13</v>
-      </c>
-      <c r="AF140">
-        <v>1.4</v>
-      </c>
-      <c r="AG140">
-        <v>2</v>
-      </c>
       <c r="AH140" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="O144">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P144">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q144">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="R144">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T144">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U144">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
+        <v>1.05</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+      <c r="Y144">
+        <v>1.21</v>
+      </c>
+      <c r="Z144">
+        <v>3.58</v>
+      </c>
+      <c r="AA144">
+        <v>1.84</v>
+      </c>
+      <c r="AB144">
+        <v>1.92</v>
+      </c>
+      <c r="AC144">
+        <v>2.92</v>
+      </c>
+      <c r="AD144">
+        <v>1.38</v>
+      </c>
+      <c r="AE144">
         <v>1.08</v>
       </c>
-      <c r="X144">
-        <v>1.01</v>
-      </c>
-      <c r="Y144">
-        <v>1.27</v>
-      </c>
-      <c r="Z144">
-        <v>3.28</v>
-      </c>
-      <c r="AA144">
-        <v>2.03</v>
-      </c>
-      <c r="AB144">
-        <v>1.8</v>
-      </c>
-      <c r="AC144">
-        <v>3.47</v>
-      </c>
-      <c r="AD144">
+      <c r="AF144">
+        <v>1.65</v>
+      </c>
+      <c r="AG144">
+        <v>2.15</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.24</v>
       </c>
-      <c r="AE144">
-        <v>1.04</v>
-      </c>
-      <c r="AF144">
-        <v>1.75</v>
-      </c>
-      <c r="AG144">
-        <v>1.92</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.26</v>
-      </c>
       <c r="AK144">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,65 +23944,65 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P145">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q145">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="R145">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="S145">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T145">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="U145">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V145">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W145">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z145">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA145">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AB145">
+        <v>1.8</v>
+      </c>
+      <c r="AC145">
+        <v>3.47</v>
+      </c>
+      <c r="AD145">
+        <v>1.24</v>
+      </c>
+      <c r="AE145">
+        <v>1.04</v>
+      </c>
+      <c r="AF145">
+        <v>1.75</v>
+      </c>
+      <c r="AG145">
         <v>1.92</v>
       </c>
-      <c r="AC145">
-        <v>2.92</v>
-      </c>
-      <c r="AD145">
-        <v>1.38</v>
-      </c>
-      <c r="AE145">
-        <v>1.08</v>
-      </c>
-      <c r="AF145">
-        <v>1.65</v>
-      </c>
-      <c r="AG145">
-        <v>2.15</v>
-      </c>
       <c r="AH145" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK145">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="O153">
+        <v>4.2</v>
+      </c>
+      <c r="P153">
+        <v>1.65</v>
+      </c>
+      <c r="Q153">
+        <v>3.9</v>
+      </c>
+      <c r="R153">
+        <v>2.28</v>
+      </c>
+      <c r="S153">
+        <v>1.23</v>
+      </c>
+      <c r="T153">
         <v>3.5</v>
       </c>
-      <c r="P153">
-        <v>2.5</v>
-      </c>
-      <c r="Q153">
-        <v>3.1</v>
-      </c>
-      <c r="R153">
-        <v>2.18</v>
-      </c>
-      <c r="S153">
-        <v>1.36</v>
-      </c>
-      <c r="T153">
-        <v>2.82</v>
-      </c>
       <c r="U153">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="V153">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X153">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z153">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="AA153">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AB153">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AC153">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="AD153">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE153">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF153">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG153">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK153">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="O154">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P154">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="Q154">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="R154">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S154">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="V154">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W154">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA154">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AB154">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AC154">
-        <v>2.31</v>
+        <v>2.73</v>
       </c>
       <c r="AD154">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE154">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG154">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="O155">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q155">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="R155">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="S155">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T155">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="U155">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="V155">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W155">
+        <v>1.06</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.26</v>
+      </c>
+      <c r="Z155">
+        <v>3.4</v>
+      </c>
+      <c r="AA155">
+        <v>1.9</v>
+      </c>
+      <c r="AB155">
+        <v>1.82</v>
+      </c>
+      <c r="AC155">
+        <v>3.14</v>
+      </c>
+      <c r="AD155">
+        <v>1.3</v>
+      </c>
+      <c r="AE155">
         <v>1.1</v>
       </c>
-      <c r="X155">
-        <v>1.02</v>
-      </c>
-      <c r="Y155">
-        <v>1.16</v>
-      </c>
-      <c r="Z155">
-        <v>4.15</v>
-      </c>
-      <c r="AA155">
-        <v>1.66</v>
-      </c>
-      <c r="AB155">
-        <v>2.12</v>
-      </c>
-      <c r="AC155">
-        <v>2.72</v>
-      </c>
-      <c r="AD155">
-        <v>1.42</v>
-      </c>
-      <c r="AE155">
-        <v>1.14</v>
-      </c>
       <c r="AF155">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG155">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AK155">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
+        <v>1.97</v>
+      </c>
+      <c r="O156">
+        <v>3.3</v>
+      </c>
+      <c r="P156">
+        <v>3.25</v>
+      </c>
+      <c r="Q156">
+        <v>2.55</v>
+      </c>
+      <c r="R156">
         <v>2.15</v>
       </c>
-      <c r="O156">
-        <v>3.6</v>
-      </c>
-      <c r="P156">
-        <v>3</v>
-      </c>
-      <c r="Q156">
+      <c r="S156">
+        <v>1.34</v>
+      </c>
+      <c r="T156">
         <v>2.7</v>
       </c>
-      <c r="R156">
-        <v>2.18</v>
-      </c>
-      <c r="S156">
-        <v>1.3</v>
-      </c>
-      <c r="T156">
-        <v>3.3</v>
-      </c>
       <c r="U156">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="V156">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z156">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA156">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AB156">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AC156">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="AD156">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE156">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG156">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.29</v>
       </c>
       <c r="AK156">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="O158">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q158">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="S158">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="U158">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="V158">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W158">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y158">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z158">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="AA158">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB158">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AC158">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="AD158">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE158">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF158">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.26</v>
       </c>
       <c r="AK158">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="O159">
+        <v>3.7</v>
+      </c>
+      <c r="P159">
+        <v>1.85</v>
+      </c>
+      <c r="Q159">
+        <v>4.2</v>
+      </c>
+      <c r="R159">
+        <v>2.27</v>
+      </c>
+      <c r="S159">
+        <v>1.29</v>
+      </c>
+      <c r="T159">
         <v>3.3</v>
       </c>
-      <c r="P159">
-        <v>3.25</v>
-      </c>
-      <c r="Q159">
-        <v>2.55</v>
-      </c>
-      <c r="R159">
-        <v>2.15</v>
-      </c>
-      <c r="S159">
-        <v>1.34</v>
-      </c>
-      <c r="T159">
-        <v>2.7</v>
-      </c>
       <c r="U159">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="V159">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA159">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB159">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC159">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="AD159">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF159">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG159">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="AK159">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26715,31 +26715,31 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="O162">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P162">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q162">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R162">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S162">
         <v>1.3</v>
       </c>
       <c r="T162">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U162">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="V162">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W162">
         <v>1.11</v>
@@ -26748,31 +26748,31 @@
         <v>1.03</v>
       </c>
       <c r="Y162">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z162">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="AA162">
         <v>1.75</v>
       </c>
       <c r="AB162">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC162">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD162">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE162">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF162">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG162">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK162">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,31 +26878,31 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O163">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P163">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q163">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="R163">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S163">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T163">
         <v>3.5</v>
       </c>
       <c r="U163">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="V163">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="W163">
         <v>1.15</v>
@@ -26917,25 +26917,25 @@
         <v>4.65</v>
       </c>
       <c r="AA163">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AB163">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AC163">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AD163">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE163">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF163">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG163">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="O165">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P165">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27376,55 +27376,55 @@
         <v>0</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="O168">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P168">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="Q168">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R168">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="S168">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="T168">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="U168">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="V168">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="W168">
+        <v>1.25</v>
+      </c>
+      <c r="X168">
+        <v>1.01</v>
+      </c>
+      <c r="Y168">
+        <v>1.03</v>
+      </c>
+      <c r="Z168">
+        <v>4.2</v>
+      </c>
+      <c r="AA168">
+        <v>1.2</v>
+      </c>
+      <c r="AB168">
+        <v>2.75</v>
+      </c>
+      <c r="AC168">
+        <v>1.57</v>
+      </c>
+      <c r="AD168">
+        <v>1.77</v>
+      </c>
+      <c r="AE168">
         <v>1.33</v>
       </c>
-      <c r="X168">
-        <v>0</v>
-      </c>
-      <c r="Y168">
-        <v>1.01</v>
-      </c>
-      <c r="Z168">
-        <v>11</v>
-      </c>
-      <c r="AA168">
-        <v>1.16</v>
-      </c>
-      <c r="AB168">
-        <v>4.15</v>
-      </c>
-      <c r="AC168">
-        <v>1.5</v>
-      </c>
-      <c r="AD168">
-        <v>2.55</v>
-      </c>
-      <c r="AE168">
-        <v>1.66</v>
-      </c>
       <c r="AF168">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG168">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK168">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.11</v>
+        <v>2.85</v>
       </c>
       <c r="O169">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P169">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="Q169">
-        <v>2.36</v>
+        <v>3.34</v>
       </c>
       <c r="R169">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="S169">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T169">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="U169">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="V169">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="W169">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X169">
         <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z169">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA169">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB169">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC169">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="AD169">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE169">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF169">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="AG169">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK169">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,65 +28019,65 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.85</v>
+        <v>1.79</v>
       </c>
       <c r="O170">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P170">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q170">
-        <v>3.34</v>
+        <v>2.22</v>
       </c>
       <c r="R170">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="S170">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="T170">
+        <v>6.2</v>
+      </c>
+      <c r="U170">
+        <v>1.62</v>
+      </c>
+      <c r="V170">
+        <v>2.05</v>
+      </c>
+      <c r="W170">
+        <v>1.33</v>
+      </c>
+      <c r="X170">
+        <v>0</v>
+      </c>
+      <c r="Y170">
+        <v>1.01</v>
+      </c>
+      <c r="Z170">
+        <v>11</v>
+      </c>
+      <c r="AA170">
+        <v>1.16</v>
+      </c>
+      <c r="AB170">
+        <v>4.15</v>
+      </c>
+      <c r="AC170">
+        <v>1.5</v>
+      </c>
+      <c r="AD170">
+        <v>2.55</v>
+      </c>
+      <c r="AE170">
+        <v>1.66</v>
+      </c>
+      <c r="AF170">
+        <v>1.25</v>
+      </c>
+      <c r="AG170">
         <v>3.75</v>
       </c>
-      <c r="U170">
-        <v>2.25</v>
-      </c>
-      <c r="V170">
-        <v>1.61</v>
-      </c>
-      <c r="W170">
-        <v>1.14</v>
-      </c>
-      <c r="X170">
-        <v>1.01</v>
-      </c>
-      <c r="Y170">
-        <v>1.14</v>
-      </c>
-      <c r="Z170">
-        <v>5.5</v>
-      </c>
-      <c r="AA170">
-        <v>1.57</v>
-      </c>
-      <c r="AB170">
-        <v>2.35</v>
-      </c>
-      <c r="AC170">
-        <v>2.26</v>
-      </c>
-      <c r="AD170">
-        <v>1.51</v>
-      </c>
-      <c r="AE170">
-        <v>1.22</v>
-      </c>
-      <c r="AF170">
-        <v>1.46</v>
-      </c>
-      <c r="AG170">
-        <v>2.63</v>
-      </c>
       <c r="AH170" t="inlineStr">
         <is>
           <t>[]</t>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK170">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O173">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="P173">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="Q173">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="R173">
         <v>2.08</v>
       </c>
       <c r="S173">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T173">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U173">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="V173">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X173">
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z173">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA173">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AB173">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC173">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD173">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE173">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF173">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG173">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O175">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="P175">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q175">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="R175">
         <v>2.08</v>
       </c>
       <c r="S175">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T175">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U175">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V175">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W175">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z175">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA175">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AB175">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC175">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD175">
+        <v>1.31</v>
+      </c>
+      <c r="AE175">
+        <v>1.14</v>
+      </c>
+      <c r="AF175">
+        <v>1.57</v>
+      </c>
+      <c r="AG175">
+        <v>2.08</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
         <v>1.3</v>
       </c>
-      <c r="AE175">
-        <v>1.1</v>
-      </c>
-      <c r="AF175">
-        <v>1.73</v>
-      </c>
-      <c r="AG175">
-        <v>2.1</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.28</v>
-      </c>
       <c r="AK175">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29501,10 +29501,10 @@
         <v>2.25</v>
       </c>
       <c r="S179">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T179">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U179">
         <v>2.64</v>
@@ -29516,34 +29516,34 @@
         <v>1.06</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y179">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z179">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB179">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC179">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD179">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE179">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF179">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG179">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>1.18</v>
       </c>
       <c r="AK179">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,80 +29975,80 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.17</v>
+        <v>2.67</v>
       </c>
       <c r="O182">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="P182">
-        <v>15</v>
+        <v>2.37</v>
       </c>
       <c r="Q182">
-        <v>1.47</v>
+        <v>3.22</v>
       </c>
       <c r="R182">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S182">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="T182">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="U182">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="V182">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="W182">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="X182">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z182">
-        <v>6.35</v>
+        <v>4.35</v>
       </c>
       <c r="AA182">
+        <v>1.62</v>
+      </c>
+      <c r="AB182">
+        <v>2.2</v>
+      </c>
+      <c r="AC182">
+        <v>2.6</v>
+      </c>
+      <c r="AD182">
+        <v>1.44</v>
+      </c>
+      <c r="AE182">
+        <v>1.14</v>
+      </c>
+      <c r="AF182">
+        <v>1.5</v>
+      </c>
+      <c r="AG182">
+        <v>2.42</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ182">
         <v>1.3</v>
       </c>
-      <c r="AB182">
-        <v>3.25</v>
-      </c>
-      <c r="AC182">
-        <v>1.82</v>
-      </c>
-      <c r="AD182">
-        <v>2</v>
-      </c>
-      <c r="AE182">
-        <v>1.34</v>
-      </c>
-      <c r="AF182">
-        <v>1.95</v>
-      </c>
-      <c r="AG182">
-        <v>1.78</v>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ182">
-        <v>1.03</v>
-      </c>
       <c r="AK182">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.67</v>
+        <v>1.17</v>
       </c>
       <c r="O183">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="P183">
-        <v>2.37</v>
+        <v>15</v>
       </c>
       <c r="Q183">
-        <v>3.22</v>
+        <v>1.47</v>
       </c>
       <c r="R183">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S183">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T183">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U183">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="V183">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="W183">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X183">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y183">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z183">
-        <v>4.35</v>
+        <v>6.35</v>
       </c>
       <c r="AA183">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AB183">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC183">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AD183">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AE183">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AF183">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG183">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AK183">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O185">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P185">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q185">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="R185">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="S185">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U185">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="V185">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W185">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X185">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z185">
-        <v>5.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA185">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AB185">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AC185">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="AD185">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE185">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF185">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG185">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK185">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="O186">
-        <v>5</v>
+        <v>3.54</v>
       </c>
       <c r="P186">
-        <v>6.06</v>
+        <v>3.3</v>
       </c>
       <c r="Q186">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="R186">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="S186">
+        <v>1.29</v>
+      </c>
+      <c r="T186">
+        <v>3.3</v>
+      </c>
+      <c r="U186">
+        <v>2.4</v>
+      </c>
+      <c r="V186">
+        <v>1.5</v>
+      </c>
+      <c r="W186">
+        <v>1.08</v>
+      </c>
+      <c r="X186">
+        <v>1.02</v>
+      </c>
+      <c r="Y186">
         <v>1.2</v>
       </c>
-      <c r="T186">
-        <v>4.2</v>
-      </c>
-      <c r="U186">
-        <v>2</v>
-      </c>
-      <c r="V186">
-        <v>1.71</v>
-      </c>
-      <c r="W186">
-        <v>1.18</v>
-      </c>
-      <c r="X186">
-        <v>1.01</v>
-      </c>
-      <c r="Y186">
-        <v>1.08</v>
-      </c>
       <c r="Z186">
-        <v>5.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA186">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AB186">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AC186">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="AD186">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE186">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG186">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,65 +30790,65 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P187">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="Q187">
+        <v>2.33</v>
+      </c>
+      <c r="R187">
+        <v>2.38</v>
+      </c>
+      <c r="S187">
+        <v>1.25</v>
+      </c>
+      <c r="T187">
         <v>3.4</v>
       </c>
-      <c r="R187">
-        <v>2.18</v>
-      </c>
-      <c r="S187">
-        <v>1.29</v>
-      </c>
-      <c r="T187">
-        <v>3.3</v>
-      </c>
       <c r="U187">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V187">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W187">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X187">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z187">
         <v>4.5</v>
       </c>
       <c r="AA187">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB187">
+        <v>2.3</v>
+      </c>
+      <c r="AC187">
+        <v>2.63</v>
+      </c>
+      <c r="AD187">
+        <v>1.47</v>
+      </c>
+      <c r="AE187">
+        <v>1.11</v>
+      </c>
+      <c r="AF187">
+        <v>1.62</v>
+      </c>
+      <c r="AG187">
         <v>2.2</v>
       </c>
-      <c r="AC187">
-        <v>2.5</v>
-      </c>
-      <c r="AD187">
-        <v>1.45</v>
-      </c>
-      <c r="AE187">
-        <v>1.19</v>
-      </c>
-      <c r="AF187">
-        <v>1.5</v>
-      </c>
-      <c r="AG187">
-        <v>2.38</v>
-      </c>
       <c r="AH187" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O188">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P188">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q188">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R188">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S188">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T188">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U188">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V188">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W188">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X188">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z188">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="AA188">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB188">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AC188">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="AD188">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE188">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG188">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK188">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="O189">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P189">
+        <v>4.33</v>
+      </c>
+      <c r="Q189">
+        <v>2.25</v>
+      </c>
+      <c r="R189">
+        <v>2.32</v>
+      </c>
+      <c r="S189">
+        <v>1.29</v>
+      </c>
+      <c r="T189">
         <v>3.5</v>
       </c>
-      <c r="Q189">
-        <v>2.62</v>
-      </c>
-      <c r="R189">
-        <v>2.1</v>
-      </c>
-      <c r="S189">
-        <v>1.4</v>
-      </c>
-      <c r="T189">
-        <v>2.7</v>
-      </c>
       <c r="U189">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="V189">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W189">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X189">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="Z189">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="AA189">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AB189">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="AC189">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="AD189">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE189">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF189">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AG189">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK189">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O190">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P190">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q190">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="R190">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S190">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T190">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U190">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="V190">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W190">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X190">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y190">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z190">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA190">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB190">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC190">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="AD190">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE190">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF190">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AG190">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,65 +31442,65 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="O191">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P191">
-        <v>4.33</v>
+        <v>6.06</v>
       </c>
       <c r="Q191">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="R191">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T191">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U191">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V191">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="W191">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X191">
         <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z191">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA191">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AB191">
+        <v>3</v>
+      </c>
+      <c r="AC191">
+        <v>2.03</v>
+      </c>
+      <c r="AD191">
+        <v>1.8</v>
+      </c>
+      <c r="AE191">
+        <v>1.3</v>
+      </c>
+      <c r="AF191">
+        <v>1.57</v>
+      </c>
+      <c r="AG191">
         <v>2.3</v>
       </c>
-      <c r="AC191">
-        <v>2.63</v>
-      </c>
-      <c r="AD191">
-        <v>1.47</v>
-      </c>
-      <c r="AE191">
-        <v>1.11</v>
-      </c>
-      <c r="AF191">
-        <v>1.62</v>
-      </c>
-      <c r="AG191">
-        <v>2.2</v>
-      </c>
       <c r="AH191" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK191">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="O192">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P192">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="Q192">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="R192">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S192">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="V192">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="W192">
+        <v>1.08</v>
+      </c>
+      <c r="X192">
+        <v>1.02</v>
+      </c>
+      <c r="Y192">
         <v>1.19</v>
       </c>
-      <c r="X192">
-        <v>1.01</v>
-      </c>
-      <c r="Y192">
-        <v>1.07</v>
-      </c>
       <c r="Z192">
-        <v>5.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA192">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AB192">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC192">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AD192">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AE192">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AF192">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG192">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK192">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="O193">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P193">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q193">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="R193">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="S193">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="T193">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="U193">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="V193">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X193">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z193">
-        <v>4.2</v>
+        <v>5.85</v>
       </c>
       <c r="AA193">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AB193">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="AC193">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="AD193">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE193">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AF193">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AG193">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK193">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32586,7 +32586,7 @@
         <v>3.2</v>
       </c>
       <c r="O198">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P198">
         <v>1.95</v>
@@ -32616,7 +32616,7 @@
         <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z198">
         <v>4.1</v>
@@ -33247,7 +33247,7 @@
         <v>3.6</v>
       </c>
       <c r="R202">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S202">
         <v>1.36</v>
@@ -34243,13 +34243,13 @@
         <v>1.05</v>
       </c>
       <c r="X208">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y208">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z208">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AA208">
         <v>2.2</v>
@@ -34261,7 +34261,7 @@
         <v>3.78</v>
       </c>
       <c r="AD208">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE208">
         <v>1.03</v>
@@ -34382,7 +34382,7 @@
         <v>4</v>
       </c>
       <c r="P209">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q209">
         <v>2.2</v>
@@ -34400,7 +34400,7 @@
         <v>1.95</v>
       </c>
       <c r="V209">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W209">
         <v>1.19</v>
@@ -34548,10 +34548,10 @@
         <v>9</v>
       </c>
       <c r="Q210">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R210">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S210">
         <v>1.4</v>
@@ -34572,31 +34572,31 @@
         <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z210">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA210">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AB210">
         <v>1.8</v>
       </c>
       <c r="AC210">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD210">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE210">
         <v>1.03</v>
       </c>
       <c r="AF210">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="AG210">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK210">
         <v>4</v>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O211">
         <v>3.5</v>
@@ -34759,7 +34759,7 @@
         <v>1.49</v>
       </c>
       <c r="AG211">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34898,22 +34898,22 @@
         <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z212">
         <v>4.05</v>
       </c>
       <c r="AA212">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB212">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC212">
         <v>2.56</v>
       </c>
       <c r="AD212">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE212">
         <v>1.19</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O219">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P219">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36537,7 +36537,7 @@
         <v>1.95</v>
       </c>
       <c r="AB222">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC222">
         <v>3.2</v>
@@ -36568,7 +36568,7 @@
         <v>1.19</v>
       </c>
       <c r="AK222">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O229">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P229">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q229">
-        <v>2.77</v>
+        <v>4.24</v>
       </c>
       <c r="R229">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S229">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T229">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="U229">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="V229">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W229">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X229">
+        <v>1.03</v>
+      </c>
+      <c r="Y229">
+        <v>1.35</v>
+      </c>
+      <c r="Z229">
+        <v>2.74</v>
+      </c>
+      <c r="AA229">
+        <v>2.18</v>
+      </c>
+      <c r="AB229">
+        <v>1.58</v>
+      </c>
+      <c r="AC229">
+        <v>4.05</v>
+      </c>
+      <c r="AD229">
+        <v>1.16</v>
+      </c>
+      <c r="AE229">
         <v>1.01</v>
       </c>
-      <c r="Y229">
-        <v>1.23</v>
-      </c>
-      <c r="Z229">
-        <v>3.42</v>
-      </c>
-      <c r="AA229">
-        <v>2.1</v>
-      </c>
-      <c r="AB229">
+      <c r="AF229">
         <v>1.88</v>
       </c>
-      <c r="AC229">
-        <v>3.05</v>
-      </c>
-      <c r="AD229">
-        <v>1.28</v>
-      </c>
-      <c r="AE229">
-        <v>1.06</v>
-      </c>
-      <c r="AF229">
-        <v>1.7</v>
-      </c>
       <c r="AG229">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AK229">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
+        <v>2.15</v>
+      </c>
+      <c r="O230">
         <v>3.2</v>
       </c>
-      <c r="O230">
-        <v>3</v>
-      </c>
       <c r="P230">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q230">
-        <v>4.24</v>
+        <v>2.77</v>
       </c>
       <c r="R230">
+        <v>2.2</v>
+      </c>
+      <c r="S230">
+        <v>1.37</v>
+      </c>
+      <c r="T230">
+        <v>2.88</v>
+      </c>
+      <c r="U230">
+        <v>2.88</v>
+      </c>
+      <c r="V230">
+        <v>1.36</v>
+      </c>
+      <c r="W230">
+        <v>1.06</v>
+      </c>
+      <c r="X230">
+        <v>1.01</v>
+      </c>
+      <c r="Y230">
+        <v>1.23</v>
+      </c>
+      <c r="Z230">
+        <v>3.42</v>
+      </c>
+      <c r="AA230">
         <v>1.9</v>
       </c>
-      <c r="S230">
-        <v>1.45</v>
-      </c>
-      <c r="T230">
-        <v>2.42</v>
-      </c>
-      <c r="U230">
-        <v>3.18</v>
-      </c>
-      <c r="V230">
-        <v>1.27</v>
-      </c>
-      <c r="W230">
-        <v>1.05</v>
-      </c>
-      <c r="X230">
-        <v>1.03</v>
-      </c>
-      <c r="Y230">
-        <v>1.35</v>
-      </c>
-      <c r="Z230">
-        <v>2.74</v>
-      </c>
-      <c r="AA230">
-        <v>2.18</v>
-      </c>
       <c r="AB230">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AC230">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD230">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE230">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF230">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG230">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37971,55 +37971,55 @@
         <v>2.73</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -38943,10 +38943,10 @@
         <v>2.8</v>
       </c>
       <c r="O237">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P237">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q237">
         <v>3.6</v>
@@ -38997,7 +38997,7 @@
         <v>1.74</v>
       </c>
       <c r="AG237">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>2.37</v>
       </c>
       <c r="O238">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P238">
         <v>2.75</v>
@@ -39118,10 +39118,10 @@
         <v>2.12</v>
       </c>
       <c r="S238">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T238">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="U238">
         <v>2.94</v>
@@ -39266,10 +39266,10 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O239">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P239">
         <v>3</v>
@@ -39305,10 +39305,10 @@
         <v>3.2</v>
       </c>
       <c r="AA239">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB239">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC239">
         <v>3.05</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,31 +40081,31 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="O244">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P244">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="Q244">
-        <v>2.02</v>
+        <v>2.69</v>
       </c>
       <c r="R244">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="S244">
         <v>1.14</v>
       </c>
       <c r="T244">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U244">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V244">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="W244">
         <v>1.2</v>
@@ -40114,31 +40114,31 @@
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z244">
-        <v>6.9</v>
+        <v>6.15</v>
       </c>
       <c r="AA244">
+        <v>1.36</v>
+      </c>
+      <c r="AB244">
+        <v>2.87</v>
+      </c>
+      <c r="AC244">
+        <v>1.92</v>
+      </c>
+      <c r="AD244">
+        <v>1.82</v>
+      </c>
+      <c r="AE244">
+        <v>1.31</v>
+      </c>
+      <c r="AF244">
         <v>1.33</v>
       </c>
-      <c r="AB244">
+      <c r="AG244">
         <v>3.1</v>
-      </c>
-      <c r="AC244">
-        <v>1.84</v>
-      </c>
-      <c r="AD244">
-        <v>1.84</v>
-      </c>
-      <c r="AE244">
-        <v>1.33</v>
-      </c>
-      <c r="AF244">
-        <v>1.38</v>
-      </c>
-      <c r="AG244">
-        <v>2.76</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.2</v>
       </c>
       <c r="AK244">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,31 +40244,31 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="O245">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P245">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="Q245">
-        <v>2.69</v>
+        <v>2.02</v>
       </c>
       <c r="R245">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="S245">
         <v>1.14</v>
       </c>
       <c r="T245">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U245">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V245">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W245">
         <v>1.2</v>
@@ -40277,31 +40277,31 @@
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z245">
-        <v>6.15</v>
+        <v>6.9</v>
       </c>
       <c r="AA245">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB245">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC245">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD245">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE245">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF245">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AG245">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>1.2</v>
       </c>
       <c r="AK245">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O247">
         <v>3</v>
       </c>
       <c r="P247">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q247">
         <v>3.2</v>
@@ -40585,7 +40585,7 @@
         <v>2.1</v>
       </c>
       <c r="S247">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T247">
         <v>2.79</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O248">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P248">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q248">
         <v>2.52</v>
@@ -41240,13 +41240,13 @@
         <v>1.4</v>
       </c>
       <c r="T251">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U251">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="V251">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W251">
         <v>1.07</v>
@@ -41258,7 +41258,7 @@
         <v>1.38</v>
       </c>
       <c r="Z251">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="AA251">
         <v>2.11</v>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK251">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O256">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P256">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q256">
         <v>2.62</v>
@@ -42203,34 +42203,34 @@
         <v>2.2</v>
       </c>
       <c r="O257">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P257">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q257">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R257">
         <v>2.1</v>
       </c>
       <c r="S257">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T257">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U257">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="V257">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W257">
         <v>1.06</v>
       </c>
       <c r="X257">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y257">
         <v>1.38</v>
@@ -42239,25 +42239,25 @@
         <v>2.87</v>
       </c>
       <c r="AA257">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AB257">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC257">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD257">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE257">
         <v>1.07</v>
       </c>
       <c r="AF257">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG257">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42366,62 +42366,62 @@
         <v>2.32</v>
       </c>
       <c r="O258">
+        <v>3.05</v>
+      </c>
+      <c r="P258">
+        <v>2.76</v>
+      </c>
+      <c r="Q258">
+        <v>2.9</v>
+      </c>
+      <c r="R258">
+        <v>1.98</v>
+      </c>
+      <c r="S258">
+        <v>1.37</v>
+      </c>
+      <c r="T258">
+        <v>2.72</v>
+      </c>
+      <c r="U258">
+        <v>2.75</v>
+      </c>
+      <c r="V258">
+        <v>1.38</v>
+      </c>
+      <c r="W258">
+        <v>1.08</v>
+      </c>
+      <c r="X258">
+        <v>1.02</v>
+      </c>
+      <c r="Y258">
+        <v>1.28</v>
+      </c>
+      <c r="Z258">
+        <v>3.18</v>
+      </c>
+      <c r="AA258">
+        <v>1.95</v>
+      </c>
+      <c r="AB258">
+        <v>1.85</v>
+      </c>
+      <c r="AC258">
         <v>3.2</v>
       </c>
-      <c r="P258">
-        <v>2.66</v>
-      </c>
-      <c r="Q258">
-        <v>2.94</v>
-      </c>
-      <c r="R258">
-        <v>2.08</v>
-      </c>
-      <c r="S258">
-        <v>1.31</v>
-      </c>
-      <c r="T258">
-        <v>3.08</v>
-      </c>
-      <c r="U258">
-        <v>2.45</v>
-      </c>
-      <c r="V258">
-        <v>1.47</v>
-      </c>
-      <c r="W258">
-        <v>1.11</v>
-      </c>
-      <c r="X258">
-        <v>1</v>
-      </c>
-      <c r="Y258">
-        <v>1.21</v>
-      </c>
-      <c r="Z258">
-        <v>3.58</v>
-      </c>
-      <c r="AA258">
-        <v>1.85</v>
-      </c>
-      <c r="AB258">
+      <c r="AD258">
+        <v>1.26</v>
+      </c>
+      <c r="AE258">
+        <v>1.06</v>
+      </c>
+      <c r="AF258">
+        <v>1.75</v>
+      </c>
+      <c r="AG258">
         <v>1.95</v>
       </c>
-      <c r="AC258">
-        <v>2.7</v>
-      </c>
-      <c r="AD258">
-        <v>1.36</v>
-      </c>
-      <c r="AE258">
-        <v>1.11</v>
-      </c>
-      <c r="AF258">
-        <v>1.62</v>
-      </c>
-      <c r="AG258">
-        <v>2.2</v>
-      </c>
       <c r="AH258" t="inlineStr">
         <is>
           <t>[]</t>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK258">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42698,10 +42698,10 @@
         <v>15</v>
       </c>
       <c r="Q260">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R260">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S260">
         <v>1.17</v>
@@ -42734,13 +42734,13 @@
         <v>2.91</v>
       </c>
       <c r="AC260">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD260">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE260">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF260">
         <v>2</v>
@@ -43220,7 +43220,7 @@
         <v>1.46</v>
       </c>
       <c r="AB263">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AC263">
         <v>2.27</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="O267">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="P267">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43869,10 +43869,10 @@
         <v>0</v>
       </c>
       <c r="AA267">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB267">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC267">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O275">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P275">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -45152,7 +45152,7 @@
         <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="U275">
         <v>2.85</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="O277">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P277">
+        <v>3.45</v>
+      </c>
+      <c r="Q277">
+        <v>2.51</v>
+      </c>
+      <c r="R277">
+        <v>2.07</v>
+      </c>
+      <c r="S277">
+        <v>1.33</v>
+      </c>
+      <c r="T277">
+        <v>2.9</v>
+      </c>
+      <c r="U277">
+        <v>2.59</v>
+      </c>
+      <c r="V277">
+        <v>1.4</v>
+      </c>
+      <c r="W277">
+        <v>1.08</v>
+      </c>
+      <c r="X277">
+        <v>1.03</v>
+      </c>
+      <c r="Y277">
+        <v>1.25</v>
+      </c>
+      <c r="Z277">
+        <v>3.28</v>
+      </c>
+      <c r="AA277">
         <v>1.85</v>
       </c>
-      <c r="Q277">
-        <v>4.4</v>
-      </c>
-      <c r="R277">
-        <v>2.1</v>
-      </c>
-      <c r="S277">
-        <v>1.4</v>
-      </c>
-      <c r="T277">
-        <v>2.7</v>
-      </c>
-      <c r="U277">
-        <v>2.77</v>
-      </c>
-      <c r="V277">
-        <v>1.36</v>
-      </c>
-      <c r="W277">
+      <c r="AB277">
+        <v>1.9</v>
+      </c>
+      <c r="AC277">
+        <v>3.04</v>
+      </c>
+      <c r="AD277">
+        <v>1.29</v>
+      </c>
+      <c r="AE277">
         <v>1.07</v>
       </c>
-      <c r="X277">
-        <v>1.06</v>
-      </c>
-      <c r="Y277">
-        <v>1.34</v>
-      </c>
-      <c r="Z277">
-        <v>3.25</v>
-      </c>
-      <c r="AA277">
-        <v>2.1</v>
-      </c>
-      <c r="AB277">
-        <v>1.72</v>
-      </c>
-      <c r="AC277">
-        <v>3.58</v>
-      </c>
-      <c r="AD277">
-        <v>1.25</v>
-      </c>
-      <c r="AE277">
-        <v>1.04</v>
-      </c>
       <c r="AF277">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG277">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,80 +45623,80 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.79</v>
+        <v>3.4</v>
       </c>
       <c r="O278">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P278">
-        <v>3.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q278">
-        <v>2.51</v>
+        <v>4.4</v>
       </c>
       <c r="R278">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S278">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T278">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U278">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V278">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W278">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X278">
+        <v>1.06</v>
+      </c>
+      <c r="Y278">
+        <v>1.35</v>
+      </c>
+      <c r="Z278">
+        <v>3.25</v>
+      </c>
+      <c r="AA278">
+        <v>2.1</v>
+      </c>
+      <c r="AB278">
+        <v>1.72</v>
+      </c>
+      <c r="AC278">
+        <v>3.9</v>
+      </c>
+      <c r="AD278">
+        <v>1.25</v>
+      </c>
+      <c r="AE278">
         <v>1.04</v>
       </c>
-      <c r="Y278">
+      <c r="AF278">
+        <v>1.85</v>
+      </c>
+      <c r="AG278">
+        <v>1.85</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
+        <v>1.22</v>
+      </c>
+      <c r="AK278">
         <v>1.25</v>
-      </c>
-      <c r="Z278">
-        <v>3.28</v>
-      </c>
-      <c r="AA278">
-        <v>1.85</v>
-      </c>
-      <c r="AB278">
-        <v>1.9</v>
-      </c>
-      <c r="AC278">
-        <v>3.04</v>
-      </c>
-      <c r="AD278">
-        <v>1.29</v>
-      </c>
-      <c r="AE278">
-        <v>1.08</v>
-      </c>
-      <c r="AF278">
-        <v>1.67</v>
-      </c>
-      <c r="AG278">
-        <v>2.05</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.24</v>
-      </c>
-      <c r="AK278">
-        <v>1.71</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45792,7 +45792,7 @@
         <v>4</v>
       </c>
       <c r="P279">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="Q279">
         <v>2.3</v>
@@ -45831,10 +45831,10 @@
         <v>2.87</v>
       </c>
       <c r="AC279">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD279">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE279">
         <v>1.28</v>
@@ -46770,7 +46770,7 @@
         <v>4.05</v>
       </c>
       <c r="P285">
-        <v>4.4</v>
+        <v>4.74</v>
       </c>
       <c r="Q285">
         <v>1.85</v>
@@ -46779,7 +46779,7 @@
         <v>2.52</v>
       </c>
       <c r="S285">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T285">
         <v>3.86</v>
@@ -47099,7 +47099,7 @@
         <v>2.46</v>
       </c>
       <c r="Q287">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="R287">
         <v>2.05</v>
@@ -47126,7 +47126,7 @@
         <v>1.33</v>
       </c>
       <c r="Z287">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AA287">
         <v>2.09</v>
@@ -47144,7 +47144,7 @@
         <v>1.05</v>
       </c>
       <c r="AF287">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG287">
         <v>1.85</v>
@@ -47914,10 +47914,10 @@
         <v>2.66</v>
       </c>
       <c r="Q292">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R292">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S292">
         <v>1.33</v>
@@ -47926,34 +47926,34 @@
         <v>3</v>
       </c>
       <c r="U292">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="V292">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W292">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X292">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y292">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z292">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA292">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB292">
         <v>1.72</v>
       </c>
       <c r="AC292">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AD292">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE292">
         <v>1.1</v>
@@ -47962,7 +47962,7 @@
         <v>1.73</v>
       </c>
       <c r="AG292">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>1.3</v>
       </c>
       <c r="AK292">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O297">
         <v>3</v>
       </c>
       <c r="P297">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Q297">
         <v>3.1</v>
@@ -48735,10 +48735,10 @@
         <v>1.97</v>
       </c>
       <c r="S297">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T297">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U297">
         <v>3.1</v>
@@ -48756,13 +48756,13 @@
         <v>1.4</v>
       </c>
       <c r="Z297">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA297">
         <v>2.2</v>
       </c>
       <c r="AB297">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC297">
         <v>3.78</v>
@@ -49544,25 +49544,25 @@
         <v>8.75</v>
       </c>
       <c r="Q302">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R302">
         <v>2.38</v>
       </c>
       <c r="S302">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T302">
         <v>2.94</v>
       </c>
       <c r="U302">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V302">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W302">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X302">
         <v>1.02</v>
@@ -49586,13 +49586,13 @@
         <v>1.42</v>
       </c>
       <c r="AE302">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF302">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG302">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AK302">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50187,34 +50187,34 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O306">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P306">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q306">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R306">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S306">
         <v>1.29</v>
       </c>
       <c r="T306">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U306">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V306">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W306">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X306">
         <v>1.02</v>
@@ -50226,25 +50226,25 @@
         <v>4.75</v>
       </c>
       <c r="AA306">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB306">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AC306">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD306">
         <v>1.52</v>
       </c>
       <c r="AE306">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF306">
         <v>1.75</v>
       </c>
       <c r="AG306">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>1.11</v>
       </c>
       <c r="AK306">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -51023,13 +51023,13 @@
         <v>3.9</v>
       </c>
       <c r="U311">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V311">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W311">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X311">
         <v>1.02</v>
@@ -51165,19 +51165,19 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="O312">
         <v>3.15</v>
       </c>
       <c r="P312">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="Q312">
         <v>3.45</v>
       </c>
       <c r="R312">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S312">
         <v>1.37</v>
@@ -51195,7 +51195,7 @@
         <v>1.03</v>
       </c>
       <c r="X312">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y312">
         <v>1.26</v>
@@ -51210,7 +51210,7 @@
         <v>1.85</v>
       </c>
       <c r="AC312">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD312">
         <v>1.31</v>
@@ -51331,7 +51331,7 @@
         <v>1.35</v>
       </c>
       <c r="O313">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="P313">
         <v>6</v>
@@ -51340,7 +51340,7 @@
         <v>1.83</v>
       </c>
       <c r="R313">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="S313">
         <v>1.25</v>
@@ -51506,10 +51506,10 @@
         <v>1.97</v>
       </c>
       <c r="S314">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T314">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="U314">
         <v>2.9</v>
@@ -52668,7 +52668,7 @@
         <v>1.05</v>
       </c>
       <c r="Z321">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA321">
         <v>1.26</v>

--- a/jogos_2026-10-10.xlsx
+++ b/jogos_2026-10-10.xlsx
@@ -665,13 +665,13 @@
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AA2">
         <v>1.74</v>
@@ -843,7 +843,7 @@
         <v>1.77</v>
       </c>
       <c r="AC3">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
         <v>1.26</v>
@@ -973,7 +973,7 @@
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -1009,10 +1009,10 @@
         <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.9</v>
@@ -1127,7 +1127,7 @@
         <v>1.66</v>
       </c>
       <c r="O5">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
         <v>4.5</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O6">
         <v>3.38</v>
@@ -1326,10 +1326,10 @@
         <v>3.25</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
         <v>3.6</v>
@@ -1360,7 +1360,7 @@
         <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="AA7">
         <v>1.86</v>
@@ -1495,10 +1495,10 @@
         <v>1.88</v>
       </c>
       <c r="AC7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
         <v>1.07</v>
@@ -1634,7 +1634,7 @@
         <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="V8">
         <v>1.44</v>
@@ -1646,7 +1646,7 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
         <v>3.5</v>
@@ -1957,7 +1957,7 @@
         <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
         <v>3.2</v>
@@ -1984,7 +1984,7 @@
         <v>1.6</v>
       </c>
       <c r="AC10">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD10">
         <v>1.16</v>
@@ -2111,10 +2111,10 @@
         <v>4.2</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
         <v>1.25</v>
@@ -2123,10 +2123,10 @@
         <v>3.46</v>
       </c>
       <c r="U11">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
         <v>1.11</v>
@@ -2283,16 +2283,16 @@
         <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U12">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2301,28 +2301,28 @@
         <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AA12">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG12">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="O13">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
         <v>3.05</v>
@@ -2449,7 +2449,7 @@
         <v>2.64</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V13">
         <v>1.35</v>
@@ -2467,13 +2467,13 @@
         <v>2.83</v